--- a/Business Analysis/checkupp_sprint_plan_2026.xlsx
+++ b/Business Analysis/checkupp_sprint_plan_2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Business Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37D23B83-79F3-4239-82A8-F931986BF081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{484FF25F-2CDB-4DC1-9D6D-6DB2053B8871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,8 +34,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
   <si>
     <t>Epic</t>
   </si>
@@ -84,12 +106,68 @@
   <si>
     <t>Story Points Done</t>
   </si>
+  <si>
+    <t>Setup</t>
+  </si>
+  <si>
+    <t>Clone the folllowing GitHub repositories:
+1. checkupp-mobile
+2. checkupp-api</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>XS</t>
+  </si>
+  <si>
+    <t>ToDo</t>
+  </si>
+  <si>
+    <t>Your Appointments Overview</t>
+  </si>
+  <si>
+    <t>Frontend</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Tap </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Your Appointments Overview</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button to view appointments</t>
+    </r>
+  </si>
+  <si>
+    <t>Alekhya</t>
+  </si>
+  <si>
+    <t>1. Change the Title of existing section to: "Your Appointments Overview"
+2. Make the section tappable by wrapping the element inside button/pressable</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -112,8 +190,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -129,6 +215,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -160,7 +252,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -180,9 +272,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -193,6 +282,15 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1571,25 +1669,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L73"/>
+  <dimension ref="A1:L109"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.88671875" style="9" customWidth="1"/>
-    <col min="2" max="2" width="4.77734375" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.21875" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.6640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5546875" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.33203125" style="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.88671875" style="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.33203125" style="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.77734375" style="9" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5546875" style="9" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.44140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.88671875" style="9"/>
+    <col min="1" max="1" width="6.88671875" style="12" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" style="12" customWidth="1"/>
+    <col min="3" max="3" width="13.21875" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.5546875" style="13" customWidth="1"/>
+    <col min="7" max="7" width="12.109375" style="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.88671875" style="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.33203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.77734375" style="12" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.5546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.44140625" style="12" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.88671875" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>11</v>
       </c>
@@ -1627,119 +1725,1871 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F30" s="8"/>
-    </row>
-    <row r="31" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F31" s="10"/>
-    </row>
-    <row r="32" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F32" s="10"/>
-    </row>
-    <row r="33" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F33" s="10"/>
-    </row>
-    <row r="34" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F34" s="10"/>
-    </row>
-    <row r="35" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F35" s="10"/>
-    </row>
-    <row r="36" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F36" s="10"/>
-    </row>
-    <row r="37" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F37" s="10"/>
-    </row>
-    <row r="38" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F38" s="10"/>
-    </row>
-    <row r="39" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F39" s="10"/>
-    </row>
-    <row r="40" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F40" s="10"/>
-    </row>
-    <row r="41" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F41" s="10"/>
-    </row>
-    <row r="42" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F42" s="10"/>
-    </row>
-    <row r="43" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F43" s="10"/>
-    </row>
-    <row r="44" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F44" s="10"/>
-    </row>
-    <row r="45" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F45" s="10"/>
-    </row>
-    <row r="46" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F46" s="10"/>
-    </row>
-    <row r="47" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F47" s="10"/>
-    </row>
-    <row r="54" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F54" s="10"/>
-    </row>
-    <row r="55" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F55" s="10"/>
-    </row>
-    <row r="56" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F56" s="10"/>
-    </row>
-    <row r="57" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F57" s="10"/>
-    </row>
-    <row r="58" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F58" s="10"/>
-    </row>
-    <row r="59" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F59" s="10"/>
-    </row>
-    <row r="60" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F60" s="10"/>
-    </row>
-    <row r="61" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F61" s="10"/>
-    </row>
-    <row r="62" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F62" s="10"/>
-    </row>
-    <row r="63" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F63" s="10"/>
-    </row>
-    <row r="64" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F64" s="10"/>
-    </row>
-    <row r="65" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F65" s="8"/>
-    </row>
-    <row r="66" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F66" s="10"/>
-    </row>
-    <row r="67" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F67" s="8"/>
-    </row>
-    <row r="68" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F68" s="8"/>
-    </row>
-    <row r="69" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F69" s="10"/>
-    </row>
-    <row r="70" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F70" s="10"/>
-    </row>
-    <row r="71" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F71" s="10"/>
-    </row>
-    <row r="72" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F72" s="10"/>
-    </row>
-    <row r="73" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F73" s="10"/>
+    <row r="2" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="8">
+        <v>1</v>
+      </c>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="8" cm="1">
+        <f t="array" ref="I2">_xlfn.SWITCH(H2,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="8"/>
+      <c r="L2" s="8"/>
+    </row>
+    <row r="3" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="8">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="8" cm="1">
+        <f t="array" ref="I3">_xlfn.SWITCH(H3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8" t="str" cm="1">
+        <f t="array" ref="I4">_xlfn.SWITCH(H4,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8" t="str" cm="1">
+        <f t="array" ref="I5">_xlfn.SWITCH(H5,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8" t="str" cm="1">
+        <f t="array" ref="I6">_xlfn.SWITCH(H6,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8" t="str" cm="1">
+        <f t="array" ref="I7">_xlfn.SWITCH(H7,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8" t="str" cm="1">
+        <f t="array" ref="I8">_xlfn.SWITCH(H8,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8" t="str" cm="1">
+        <f t="array" ref="I9">_xlfn.SWITCH(H9,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8" t="str" cm="1">
+        <f t="array" ref="I10">_xlfn.SWITCH(H10,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8" t="str" cm="1">
+        <f t="array" ref="I11">_xlfn.SWITCH(H11,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8" t="str" cm="1">
+        <f t="array" ref="I12">_xlfn.SWITCH(H12,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8" t="str" cm="1">
+        <f t="array" ref="I13">_xlfn.SWITCH(H13,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8" t="str" cm="1">
+        <f t="array" ref="I14">_xlfn.SWITCH(H14,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8" t="str" cm="1">
+        <f t="array" ref="I15">_xlfn.SWITCH(H15,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8" t="str" cm="1">
+        <f t="array" ref="I16">_xlfn.SWITCH(H16,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8" t="str" cm="1">
+        <f t="array" ref="I17">_xlfn.SWITCH(H17,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8" t="str" cm="1">
+        <f t="array" ref="I18">_xlfn.SWITCH(H18,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8" t="str" cm="1">
+        <f t="array" ref="I19">_xlfn.SWITCH(H19,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8" t="str" cm="1">
+        <f t="array" ref="I20">_xlfn.SWITCH(H20,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8" t="str" cm="1">
+        <f t="array" ref="I21">_xlfn.SWITCH(H21,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8" t="str" cm="1">
+        <f t="array" ref="I22">_xlfn.SWITCH(H22,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8" t="str" cm="1">
+        <f t="array" ref="I23">_xlfn.SWITCH(H23,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8" t="str" cm="1">
+        <f t="array" ref="I24">_xlfn.SWITCH(H24,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8" t="str" cm="1">
+        <f t="array" ref="I25">_xlfn.SWITCH(H25,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8" t="str" cm="1">
+        <f t="array" ref="I26">_xlfn.SWITCH(H26,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8" t="str" cm="1">
+        <f t="array" ref="I27">_xlfn.SWITCH(H27,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8" t="str" cm="1">
+        <f t="array" ref="I28">_xlfn.SWITCH(H28,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8" t="str" cm="1">
+        <f t="array" ref="I29">_xlfn.SWITCH(H29,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J29" s="8"/>
+      <c r="K29" s="8"/>
+      <c r="L29" s="8"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" s="8"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8" t="str" cm="1">
+        <f t="array" ref="I30">_xlfn.SWITCH(H30,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J30" s="8"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="8"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" s="8"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="8" t="str" cm="1">
+        <f t="array" ref="I31">_xlfn.SWITCH(H31,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J31" s="8"/>
+      <c r="K31" s="8"/>
+      <c r="L31" s="8"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A32" s="8"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="8" t="str" cm="1">
+        <f t="array" ref="I32">_xlfn.SWITCH(H32,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J32" s="8"/>
+      <c r="K32" s="8"/>
+      <c r="L32" s="8"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A33" s="8"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8" t="str" cm="1">
+        <f t="array" ref="I33">_xlfn.SWITCH(H33,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J33" s="8"/>
+      <c r="K33" s="8"/>
+      <c r="L33" s="8"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" s="8"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8" t="str" cm="1">
+        <f t="array" ref="I34">_xlfn.SWITCH(H34,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="8"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35" s="8"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="8" t="str" cm="1">
+        <f t="array" ref="I35">_xlfn.SWITCH(H35,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J35" s="8"/>
+      <c r="K35" s="8"/>
+      <c r="L35" s="8"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36" s="8"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="8" t="str" cm="1">
+        <f t="array" ref="I36">_xlfn.SWITCH(H36,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J36" s="8"/>
+      <c r="K36" s="8"/>
+      <c r="L36" s="8"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A37" s="8"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="8"/>
+      <c r="I37" s="8" t="str" cm="1">
+        <f t="array" ref="I37">_xlfn.SWITCH(H37,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J37" s="8"/>
+      <c r="K37" s="8"/>
+      <c r="L37" s="8"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A38" s="8"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="8"/>
+      <c r="I38" s="8" t="str" cm="1">
+        <f t="array" ref="I38">_xlfn.SWITCH(H38,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J38" s="8"/>
+      <c r="K38" s="8"/>
+      <c r="L38" s="8"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A39" s="8"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="8"/>
+      <c r="I39" s="8" t="str" cm="1">
+        <f t="array" ref="I39">_xlfn.SWITCH(H39,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J39" s="8"/>
+      <c r="K39" s="8"/>
+      <c r="L39" s="8"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A40" s="8"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
+      <c r="I40" s="8" t="str" cm="1">
+        <f t="array" ref="I40">_xlfn.SWITCH(H40,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J40" s="8"/>
+      <c r="K40" s="8"/>
+      <c r="L40" s="8"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A41" s="8"/>
+      <c r="B41" s="8"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="8"/>
+      <c r="I41" s="8" t="str" cm="1">
+        <f t="array" ref="I41">_xlfn.SWITCH(H41,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J41" s="8"/>
+      <c r="K41" s="8"/>
+      <c r="L41" s="8"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A42" s="8"/>
+      <c r="B42" s="8"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="8"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="8"/>
+      <c r="H42" s="8"/>
+      <c r="I42" s="8" t="str" cm="1">
+        <f t="array" ref="I42">_xlfn.SWITCH(H42,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J42" s="8"/>
+      <c r="K42" s="8"/>
+      <c r="L42" s="8"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A43" s="8"/>
+      <c r="B43" s="8"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="8"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="8"/>
+      <c r="I43" s="8" t="str" cm="1">
+        <f t="array" ref="I43">_xlfn.SWITCH(H43,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J43" s="8"/>
+      <c r="K43" s="8"/>
+      <c r="L43" s="8"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A44" s="8"/>
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="9"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="8"/>
+      <c r="I44" s="8" t="str" cm="1">
+        <f t="array" ref="I44">_xlfn.SWITCH(H44,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J44" s="8"/>
+      <c r="K44" s="8"/>
+      <c r="L44" s="8"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A45" s="8"/>
+      <c r="B45" s="8"/>
+      <c r="C45" s="8"/>
+      <c r="D45" s="8"/>
+      <c r="E45" s="8"/>
+      <c r="F45" s="9"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="8"/>
+      <c r="I45" s="8" t="str" cm="1">
+        <f t="array" ref="I45">_xlfn.SWITCH(H45,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J45" s="8"/>
+      <c r="K45" s="8"/>
+      <c r="L45" s="8"/>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A46" s="8"/>
+      <c r="B46" s="8"/>
+      <c r="C46" s="8"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="8"/>
+      <c r="F46" s="9"/>
+      <c r="G46" s="8"/>
+      <c r="H46" s="8"/>
+      <c r="I46" s="8" t="str" cm="1">
+        <f t="array" ref="I46">_xlfn.SWITCH(H46,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J46" s="8"/>
+      <c r="K46" s="8"/>
+      <c r="L46" s="8"/>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A47" s="8"/>
+      <c r="B47" s="8"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8"/>
+      <c r="F47" s="9"/>
+      <c r="G47" s="8"/>
+      <c r="H47" s="8"/>
+      <c r="I47" s="8" t="str" cm="1">
+        <f t="array" ref="I47">_xlfn.SWITCH(H47,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J47" s="8"/>
+      <c r="K47" s="8"/>
+      <c r="L47" s="8"/>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A48" s="8"/>
+      <c r="B48" s="8"/>
+      <c r="C48" s="8"/>
+      <c r="D48" s="8"/>
+      <c r="E48" s="8"/>
+      <c r="F48" s="10"/>
+      <c r="G48" s="8"/>
+      <c r="H48" s="8"/>
+      <c r="I48" s="8" t="str" cm="1">
+        <f t="array" ref="I48">_xlfn.SWITCH(H48,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J48" s="8"/>
+      <c r="K48" s="8"/>
+      <c r="L48" s="8"/>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A49" s="8"/>
+      <c r="B49" s="8"/>
+      <c r="C49" s="8"/>
+      <c r="D49" s="8"/>
+      <c r="E49" s="8"/>
+      <c r="F49" s="10"/>
+      <c r="G49" s="8"/>
+      <c r="H49" s="8"/>
+      <c r="I49" s="8" t="str" cm="1">
+        <f t="array" ref="I49">_xlfn.SWITCH(H49,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J49" s="8"/>
+      <c r="K49" s="8"/>
+      <c r="L49" s="8"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A50" s="8"/>
+      <c r="B50" s="8"/>
+      <c r="C50" s="8"/>
+      <c r="D50" s="8"/>
+      <c r="E50" s="8"/>
+      <c r="F50" s="10"/>
+      <c r="G50" s="8"/>
+      <c r="H50" s="8"/>
+      <c r="I50" s="8" t="str" cm="1">
+        <f t="array" ref="I50">_xlfn.SWITCH(H50,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J50" s="8"/>
+      <c r="K50" s="8"/>
+      <c r="L50" s="8"/>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A51" s="8"/>
+      <c r="B51" s="8"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="10"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="8" t="str" cm="1">
+        <f t="array" ref="I51">_xlfn.SWITCH(H51,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="8"/>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A52" s="8"/>
+      <c r="B52" s="8"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="10"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="8" t="str" cm="1">
+        <f t="array" ref="I52">_xlfn.SWITCH(H52,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J52" s="8"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="8"/>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A53" s="8"/>
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="10"/>
+      <c r="G53" s="8"/>
+      <c r="H53" s="8"/>
+      <c r="I53" s="8" t="str" cm="1">
+        <f t="array" ref="I53">_xlfn.SWITCH(H53,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J53" s="8"/>
+      <c r="K53" s="8"/>
+      <c r="L53" s="8"/>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A54" s="8"/>
+      <c r="B54" s="8"/>
+      <c r="C54" s="8"/>
+      <c r="D54" s="8"/>
+      <c r="E54" s="8"/>
+      <c r="F54" s="9"/>
+      <c r="G54" s="8"/>
+      <c r="H54" s="8"/>
+      <c r="I54" s="8" t="str" cm="1">
+        <f t="array" ref="I54">_xlfn.SWITCH(H54,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J54" s="8"/>
+      <c r="K54" s="8"/>
+      <c r="L54" s="8"/>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A55" s="8"/>
+      <c r="B55" s="8"/>
+      <c r="C55" s="8"/>
+      <c r="D55" s="8"/>
+      <c r="E55" s="8"/>
+      <c r="F55" s="9"/>
+      <c r="G55" s="8"/>
+      <c r="H55" s="8"/>
+      <c r="I55" s="8" t="str" cm="1">
+        <f t="array" ref="I55">_xlfn.SWITCH(H55,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J55" s="8"/>
+      <c r="K55" s="8"/>
+      <c r="L55" s="8"/>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A56" s="8"/>
+      <c r="B56" s="8"/>
+      <c r="C56" s="8"/>
+      <c r="D56" s="8"/>
+      <c r="E56" s="8"/>
+      <c r="F56" s="9"/>
+      <c r="G56" s="8"/>
+      <c r="H56" s="8"/>
+      <c r="I56" s="8" t="str" cm="1">
+        <f t="array" ref="I56">_xlfn.SWITCH(H56,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J56" s="8"/>
+      <c r="K56" s="8"/>
+      <c r="L56" s="8"/>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A57" s="8"/>
+      <c r="B57" s="8"/>
+      <c r="C57" s="8"/>
+      <c r="D57" s="8"/>
+      <c r="E57" s="8"/>
+      <c r="F57" s="9"/>
+      <c r="G57" s="8"/>
+      <c r="H57" s="8"/>
+      <c r="I57" s="8" t="str" cm="1">
+        <f t="array" ref="I57">_xlfn.SWITCH(H57,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J57" s="8"/>
+      <c r="K57" s="8"/>
+      <c r="L57" s="8"/>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A58" s="8"/>
+      <c r="B58" s="8"/>
+      <c r="C58" s="8"/>
+      <c r="D58" s="8"/>
+      <c r="E58" s="8"/>
+      <c r="F58" s="9"/>
+      <c r="G58" s="8"/>
+      <c r="H58" s="8"/>
+      <c r="I58" s="8" t="str" cm="1">
+        <f t="array" ref="I58">_xlfn.SWITCH(H58,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J58" s="8"/>
+      <c r="K58" s="8"/>
+      <c r="L58" s="8"/>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A59" s="8"/>
+      <c r="B59" s="8"/>
+      <c r="C59" s="8"/>
+      <c r="D59" s="8"/>
+      <c r="E59" s="8"/>
+      <c r="F59" s="9"/>
+      <c r="G59" s="8"/>
+      <c r="H59" s="8"/>
+      <c r="I59" s="8" t="str" cm="1">
+        <f t="array" ref="I59">_xlfn.SWITCH(H59,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J59" s="8"/>
+      <c r="K59" s="8"/>
+      <c r="L59" s="8"/>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A60" s="8"/>
+      <c r="B60" s="8"/>
+      <c r="C60" s="8"/>
+      <c r="D60" s="8"/>
+      <c r="E60" s="8"/>
+      <c r="F60" s="9"/>
+      <c r="G60" s="8"/>
+      <c r="H60" s="8"/>
+      <c r="I60" s="8" t="str" cm="1">
+        <f t="array" ref="I60">_xlfn.SWITCH(H60,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J60" s="8"/>
+      <c r="K60" s="8"/>
+      <c r="L60" s="8"/>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A61" s="8"/>
+      <c r="B61" s="8"/>
+      <c r="C61" s="8"/>
+      <c r="D61" s="8"/>
+      <c r="E61" s="8"/>
+      <c r="F61" s="9"/>
+      <c r="G61" s="8"/>
+      <c r="H61" s="8"/>
+      <c r="I61" s="8" t="str" cm="1">
+        <f t="array" ref="I61">_xlfn.SWITCH(H61,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J61" s="8"/>
+      <c r="K61" s="8"/>
+      <c r="L61" s="8"/>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A62" s="8"/>
+      <c r="B62" s="8"/>
+      <c r="C62" s="8"/>
+      <c r="D62" s="8"/>
+      <c r="E62" s="8"/>
+      <c r="F62" s="9"/>
+      <c r="G62" s="8"/>
+      <c r="H62" s="8"/>
+      <c r="I62" s="8" t="str" cm="1">
+        <f t="array" ref="I62">_xlfn.SWITCH(H62,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J62" s="8"/>
+      <c r="K62" s="8"/>
+      <c r="L62" s="8"/>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A63" s="8"/>
+      <c r="B63" s="8"/>
+      <c r="C63" s="8"/>
+      <c r="D63" s="8"/>
+      <c r="E63" s="8"/>
+      <c r="F63" s="9"/>
+      <c r="G63" s="8"/>
+      <c r="H63" s="8"/>
+      <c r="I63" s="8" t="str" cm="1">
+        <f t="array" ref="I63">_xlfn.SWITCH(H63,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J63" s="8"/>
+      <c r="K63" s="8"/>
+      <c r="L63" s="8"/>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A64" s="8"/>
+      <c r="B64" s="8"/>
+      <c r="C64" s="8"/>
+      <c r="D64" s="8"/>
+      <c r="E64" s="8"/>
+      <c r="F64" s="9"/>
+      <c r="G64" s="8"/>
+      <c r="H64" s="8"/>
+      <c r="I64" s="8" t="str" cm="1">
+        <f t="array" ref="I64">_xlfn.SWITCH(H64,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J64" s="8"/>
+      <c r="K64" s="8"/>
+      <c r="L64" s="8"/>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A65" s="8"/>
+      <c r="B65" s="8"/>
+      <c r="C65" s="8"/>
+      <c r="D65" s="8"/>
+      <c r="E65" s="8"/>
+      <c r="F65" s="7"/>
+      <c r="G65" s="8"/>
+      <c r="H65" s="8"/>
+      <c r="I65" s="8" t="str" cm="1">
+        <f t="array" ref="I65">_xlfn.SWITCH(H65,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J65" s="8"/>
+      <c r="K65" s="8"/>
+      <c r="L65" s="8"/>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A66" s="8"/>
+      <c r="B66" s="8"/>
+      <c r="C66" s="8"/>
+      <c r="D66" s="8"/>
+      <c r="E66" s="8"/>
+      <c r="F66" s="9"/>
+      <c r="G66" s="8"/>
+      <c r="H66" s="8"/>
+      <c r="I66" s="8" t="str" cm="1">
+        <f t="array" ref="I66">_xlfn.SWITCH(H66,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J66" s="8"/>
+      <c r="K66" s="8"/>
+      <c r="L66" s="8"/>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A67" s="8"/>
+      <c r="B67" s="8"/>
+      <c r="C67" s="8"/>
+      <c r="D67" s="8"/>
+      <c r="E67" s="8"/>
+      <c r="F67" s="7"/>
+      <c r="G67" s="8"/>
+      <c r="H67" s="8"/>
+      <c r="I67" s="8" t="str" cm="1">
+        <f t="array" ref="I67">_xlfn.SWITCH(H67,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J67" s="8"/>
+      <c r="K67" s="8"/>
+      <c r="L67" s="8"/>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A68" s="8"/>
+      <c r="B68" s="8"/>
+      <c r="C68" s="8"/>
+      <c r="D68" s="8"/>
+      <c r="E68" s="8"/>
+      <c r="F68" s="7"/>
+      <c r="G68" s="8"/>
+      <c r="H68" s="8"/>
+      <c r="I68" s="8" t="str" cm="1">
+        <f t="array" ref="I68">_xlfn.SWITCH(H68,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J68" s="8"/>
+      <c r="K68" s="8"/>
+      <c r="L68" s="8"/>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A69" s="8"/>
+      <c r="B69" s="8"/>
+      <c r="C69" s="8"/>
+      <c r="D69" s="8"/>
+      <c r="E69" s="8"/>
+      <c r="F69" s="9"/>
+      <c r="G69" s="8"/>
+      <c r="H69" s="8"/>
+      <c r="I69" s="8" t="str" cm="1">
+        <f t="array" ref="I69">_xlfn.SWITCH(H69,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J69" s="8"/>
+      <c r="K69" s="8"/>
+      <c r="L69" s="8"/>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A70" s="8"/>
+      <c r="B70" s="8"/>
+      <c r="C70" s="8"/>
+      <c r="D70" s="8"/>
+      <c r="E70" s="8"/>
+      <c r="F70" s="9"/>
+      <c r="G70" s="8"/>
+      <c r="H70" s="8"/>
+      <c r="I70" s="8" t="str" cm="1">
+        <f t="array" ref="I70">_xlfn.SWITCH(H70,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J70" s="8"/>
+      <c r="K70" s="8"/>
+      <c r="L70" s="8"/>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A71" s="8"/>
+      <c r="B71" s="8"/>
+      <c r="C71" s="8"/>
+      <c r="D71" s="8"/>
+      <c r="E71" s="8"/>
+      <c r="F71" s="9"/>
+      <c r="G71" s="8"/>
+      <c r="H71" s="8"/>
+      <c r="I71" s="8" t="str" cm="1">
+        <f t="array" ref="I71">_xlfn.SWITCH(H71,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J71" s="8"/>
+      <c r="K71" s="8"/>
+      <c r="L71" s="8"/>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A72" s="8"/>
+      <c r="B72" s="8"/>
+      <c r="C72" s="8"/>
+      <c r="D72" s="8"/>
+      <c r="E72" s="8"/>
+      <c r="F72" s="9"/>
+      <c r="G72" s="8"/>
+      <c r="H72" s="8"/>
+      <c r="I72" s="8" t="str" cm="1">
+        <f t="array" ref="I72">_xlfn.SWITCH(H72,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J72" s="8"/>
+      <c r="K72" s="8"/>
+      <c r="L72" s="8"/>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A73" s="8"/>
+      <c r="B73" s="8"/>
+      <c r="C73" s="8"/>
+      <c r="D73" s="8"/>
+      <c r="E73" s="8"/>
+      <c r="F73" s="9"/>
+      <c r="G73" s="8"/>
+      <c r="H73" s="8"/>
+      <c r="I73" s="8" t="str" cm="1">
+        <f t="array" ref="I73">_xlfn.SWITCH(H73,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J73" s="8"/>
+      <c r="K73" s="8"/>
+      <c r="L73" s="8"/>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A74" s="8"/>
+      <c r="B74" s="8"/>
+      <c r="C74" s="8"/>
+      <c r="D74" s="8"/>
+      <c r="E74" s="8"/>
+      <c r="F74" s="10"/>
+      <c r="G74" s="8"/>
+      <c r="H74" s="8"/>
+      <c r="I74" s="8" t="str" cm="1">
+        <f t="array" ref="I74">_xlfn.SWITCH(H74,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J74" s="8"/>
+      <c r="K74" s="8"/>
+      <c r="L74" s="8"/>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A75" s="8"/>
+      <c r="B75" s="8"/>
+      <c r="C75" s="8"/>
+      <c r="D75" s="8"/>
+      <c r="E75" s="8"/>
+      <c r="F75" s="10"/>
+      <c r="G75" s="8"/>
+      <c r="H75" s="8"/>
+      <c r="I75" s="8" t="str" cm="1">
+        <f t="array" ref="I75">_xlfn.SWITCH(H75,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J75" s="8"/>
+      <c r="K75" s="8"/>
+      <c r="L75" s="8"/>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A76" s="8"/>
+      <c r="B76" s="8"/>
+      <c r="C76" s="8"/>
+      <c r="D76" s="8"/>
+      <c r="E76" s="8"/>
+      <c r="F76" s="10"/>
+      <c r="G76" s="8"/>
+      <c r="H76" s="8"/>
+      <c r="I76" s="8" t="str" cm="1">
+        <f t="array" ref="I76">_xlfn.SWITCH(H76,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J76" s="8"/>
+      <c r="K76" s="8"/>
+      <c r="L76" s="8"/>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A77" s="8"/>
+      <c r="B77" s="8"/>
+      <c r="C77" s="8"/>
+      <c r="D77" s="8"/>
+      <c r="E77" s="8"/>
+      <c r="F77" s="10"/>
+      <c r="G77" s="8"/>
+      <c r="H77" s="8"/>
+      <c r="I77" s="8" t="str" cm="1">
+        <f t="array" ref="I77">_xlfn.SWITCH(H77,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J77" s="8"/>
+      <c r="K77" s="8"/>
+      <c r="L77" s="8"/>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A78" s="8"/>
+      <c r="B78" s="8"/>
+      <c r="C78" s="8"/>
+      <c r="D78" s="8"/>
+      <c r="E78" s="8"/>
+      <c r="F78" s="10"/>
+      <c r="G78" s="8"/>
+      <c r="H78" s="8"/>
+      <c r="I78" s="8" t="str" cm="1">
+        <f t="array" ref="I78">_xlfn.SWITCH(H78,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J78" s="8"/>
+      <c r="K78" s="8"/>
+      <c r="L78" s="8"/>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A79" s="8"/>
+      <c r="B79" s="8"/>
+      <c r="C79" s="8"/>
+      <c r="D79" s="8"/>
+      <c r="E79" s="8"/>
+      <c r="F79" s="10"/>
+      <c r="G79" s="8"/>
+      <c r="H79" s="8"/>
+      <c r="I79" s="8" t="str" cm="1">
+        <f t="array" ref="I79">_xlfn.SWITCH(H79,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J79" s="8"/>
+      <c r="K79" s="8"/>
+      <c r="L79" s="8"/>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A80" s="8"/>
+      <c r="B80" s="8"/>
+      <c r="C80" s="8"/>
+      <c r="D80" s="8"/>
+      <c r="E80" s="8"/>
+      <c r="F80" s="10"/>
+      <c r="G80" s="8"/>
+      <c r="H80" s="8"/>
+      <c r="I80" s="8" t="str" cm="1">
+        <f t="array" ref="I80">_xlfn.SWITCH(H80,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J80" s="8"/>
+      <c r="K80" s="8"/>
+      <c r="L80" s="8"/>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A81" s="8"/>
+      <c r="B81" s="8"/>
+      <c r="C81" s="8"/>
+      <c r="D81" s="8"/>
+      <c r="E81" s="8"/>
+      <c r="F81" s="10"/>
+      <c r="G81" s="8"/>
+      <c r="H81" s="8"/>
+      <c r="I81" s="8" t="str" cm="1">
+        <f t="array" ref="I81">_xlfn.SWITCH(H81,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J81" s="8"/>
+      <c r="K81" s="8"/>
+      <c r="L81" s="8"/>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A82" s="8"/>
+      <c r="B82" s="8"/>
+      <c r="C82" s="8"/>
+      <c r="D82" s="8"/>
+      <c r="E82" s="8"/>
+      <c r="F82" s="10"/>
+      <c r="G82" s="8"/>
+      <c r="H82" s="8"/>
+      <c r="I82" s="8" t="str" cm="1">
+        <f t="array" ref="I82">_xlfn.SWITCH(H82,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J82" s="8"/>
+      <c r="K82" s="8"/>
+      <c r="L82" s="8"/>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A83" s="8"/>
+      <c r="B83" s="8"/>
+      <c r="C83" s="8"/>
+      <c r="D83" s="8"/>
+      <c r="E83" s="8"/>
+      <c r="F83" s="10"/>
+      <c r="G83" s="8"/>
+      <c r="H83" s="8"/>
+      <c r="I83" s="8" t="str" cm="1">
+        <f t="array" ref="I83">_xlfn.SWITCH(H83,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J83" s="8"/>
+      <c r="K83" s="8"/>
+      <c r="L83" s="8"/>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A84" s="8"/>
+      <c r="B84" s="8"/>
+      <c r="C84" s="8"/>
+      <c r="D84" s="8"/>
+      <c r="E84" s="8"/>
+      <c r="F84" s="10"/>
+      <c r="G84" s="8"/>
+      <c r="H84" s="8"/>
+      <c r="I84" s="8" t="str" cm="1">
+        <f t="array" ref="I84">_xlfn.SWITCH(H84,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J84" s="8"/>
+      <c r="K84" s="8"/>
+      <c r="L84" s="8"/>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A85" s="8"/>
+      <c r="B85" s="8"/>
+      <c r="C85" s="8"/>
+      <c r="D85" s="8"/>
+      <c r="E85" s="8"/>
+      <c r="F85" s="10"/>
+      <c r="G85" s="8"/>
+      <c r="H85" s="8"/>
+      <c r="I85" s="8" t="str" cm="1">
+        <f t="array" ref="I85">_xlfn.SWITCH(H85,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J85" s="8"/>
+      <c r="K85" s="8"/>
+      <c r="L85" s="8"/>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A86" s="8"/>
+      <c r="B86" s="8"/>
+      <c r="C86" s="8"/>
+      <c r="D86" s="8"/>
+      <c r="E86" s="8"/>
+      <c r="F86" s="10"/>
+      <c r="G86" s="8"/>
+      <c r="H86" s="8"/>
+      <c r="I86" s="8" t="str" cm="1">
+        <f t="array" ref="I86">_xlfn.SWITCH(H86,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J86" s="8"/>
+      <c r="K86" s="8"/>
+      <c r="L86" s="8"/>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A87" s="8"/>
+      <c r="B87" s="8"/>
+      <c r="C87" s="8"/>
+      <c r="D87" s="8"/>
+      <c r="E87" s="8"/>
+      <c r="F87" s="10"/>
+      <c r="G87" s="8"/>
+      <c r="H87" s="8"/>
+      <c r="I87" s="8" t="str" cm="1">
+        <f t="array" ref="I87">_xlfn.SWITCH(H87,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J87" s="8"/>
+      <c r="K87" s="8"/>
+      <c r="L87" s="8"/>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A88" s="8"/>
+      <c r="B88" s="8"/>
+      <c r="C88" s="8"/>
+      <c r="D88" s="8"/>
+      <c r="E88" s="8"/>
+      <c r="F88" s="10"/>
+      <c r="G88" s="8"/>
+      <c r="H88" s="8"/>
+      <c r="I88" s="8" t="str" cm="1">
+        <f t="array" ref="I88">_xlfn.SWITCH(H88,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J88" s="8"/>
+      <c r="K88" s="8"/>
+      <c r="L88" s="8"/>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A89" s="8"/>
+      <c r="B89" s="8"/>
+      <c r="C89" s="8"/>
+      <c r="D89" s="8"/>
+      <c r="E89" s="8"/>
+      <c r="F89" s="10"/>
+      <c r="G89" s="8"/>
+      <c r="H89" s="8"/>
+      <c r="I89" s="8" t="str" cm="1">
+        <f t="array" ref="I89">_xlfn.SWITCH(H89,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J89" s="8"/>
+      <c r="K89" s="8"/>
+      <c r="L89" s="8"/>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A90" s="8"/>
+      <c r="B90" s="8"/>
+      <c r="C90" s="8"/>
+      <c r="D90" s="8"/>
+      <c r="E90" s="8"/>
+      <c r="F90" s="10"/>
+      <c r="G90" s="8"/>
+      <c r="H90" s="8"/>
+      <c r="I90" s="8" t="str" cm="1">
+        <f t="array" ref="I90">_xlfn.SWITCH(H90,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J90" s="8"/>
+      <c r="K90" s="8"/>
+      <c r="L90" s="8"/>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A91" s="8"/>
+      <c r="B91" s="8"/>
+      <c r="C91" s="8"/>
+      <c r="D91" s="8"/>
+      <c r="E91" s="8"/>
+      <c r="F91" s="10"/>
+      <c r="G91" s="8"/>
+      <c r="H91" s="8"/>
+      <c r="I91" s="8" t="str" cm="1">
+        <f t="array" ref="I91">_xlfn.SWITCH(H91,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J91" s="8"/>
+      <c r="K91" s="8"/>
+      <c r="L91" s="8"/>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A92" s="8"/>
+      <c r="B92" s="8"/>
+      <c r="C92" s="8"/>
+      <c r="D92" s="8"/>
+      <c r="E92" s="8"/>
+      <c r="F92" s="10"/>
+      <c r="G92" s="8"/>
+      <c r="H92" s="8"/>
+      <c r="I92" s="8" t="str" cm="1">
+        <f t="array" ref="I92">_xlfn.SWITCH(H92,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J92" s="8"/>
+      <c r="K92" s="8"/>
+      <c r="L92" s="8"/>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A93" s="8"/>
+      <c r="B93" s="8"/>
+      <c r="C93" s="8"/>
+      <c r="D93" s="8"/>
+      <c r="E93" s="8"/>
+      <c r="F93" s="10"/>
+      <c r="G93" s="8"/>
+      <c r="H93" s="8"/>
+      <c r="I93" s="8" t="str" cm="1">
+        <f t="array" ref="I93">_xlfn.SWITCH(H93,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J93" s="8"/>
+      <c r="K93" s="8"/>
+      <c r="L93" s="8"/>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A94" s="8"/>
+      <c r="B94" s="8"/>
+      <c r="C94" s="8"/>
+      <c r="D94" s="8"/>
+      <c r="E94" s="8"/>
+      <c r="F94" s="10"/>
+      <c r="G94" s="8"/>
+      <c r="H94" s="8"/>
+      <c r="I94" s="8" t="str" cm="1">
+        <f t="array" ref="I94">_xlfn.SWITCH(H94,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J94" s="8"/>
+      <c r="K94" s="8"/>
+      <c r="L94" s="8"/>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A95" s="8"/>
+      <c r="B95" s="8"/>
+      <c r="C95" s="8"/>
+      <c r="D95" s="8"/>
+      <c r="E95" s="8"/>
+      <c r="F95" s="10"/>
+      <c r="G95" s="8"/>
+      <c r="H95" s="8"/>
+      <c r="I95" s="8" t="str" cm="1">
+        <f t="array" ref="I95">_xlfn.SWITCH(H95,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J95" s="8"/>
+      <c r="K95" s="8"/>
+      <c r="L95" s="8"/>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A96" s="8"/>
+      <c r="B96" s="8"/>
+      <c r="C96" s="8"/>
+      <c r="D96" s="8"/>
+      <c r="E96" s="8"/>
+      <c r="F96" s="10"/>
+      <c r="G96" s="8"/>
+      <c r="H96" s="8"/>
+      <c r="I96" s="8" t="str" cm="1">
+        <f t="array" ref="I96">_xlfn.SWITCH(H96,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J96" s="8"/>
+      <c r="K96" s="8"/>
+      <c r="L96" s="8"/>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A97" s="8"/>
+      <c r="B97" s="8"/>
+      <c r="C97" s="8"/>
+      <c r="D97" s="8"/>
+      <c r="E97" s="8"/>
+      <c r="F97" s="10"/>
+      <c r="G97" s="8"/>
+      <c r="H97" s="8"/>
+      <c r="I97" s="8" t="str" cm="1">
+        <f t="array" ref="I97">_xlfn.SWITCH(H97,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J97" s="8"/>
+      <c r="K97" s="8"/>
+      <c r="L97" s="8"/>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A98" s="8"/>
+      <c r="B98" s="8"/>
+      <c r="C98" s="8"/>
+      <c r="D98" s="8"/>
+      <c r="E98" s="8"/>
+      <c r="F98" s="10"/>
+      <c r="G98" s="8"/>
+      <c r="H98" s="8"/>
+      <c r="I98" s="8" t="str" cm="1">
+        <f t="array" ref="I98">_xlfn.SWITCH(H98,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J98" s="8"/>
+      <c r="K98" s="8"/>
+      <c r="L98" s="8"/>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A99" s="8"/>
+      <c r="B99" s="8"/>
+      <c r="C99" s="8"/>
+      <c r="D99" s="8"/>
+      <c r="E99" s="8"/>
+      <c r="F99" s="10"/>
+      <c r="G99" s="8"/>
+      <c r="H99" s="8"/>
+      <c r="I99" s="8" t="str" cm="1">
+        <f t="array" ref="I99">_xlfn.SWITCH(H99,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J99" s="8"/>
+      <c r="K99" s="8"/>
+      <c r="L99" s="8"/>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A100" s="8"/>
+      <c r="B100" s="8"/>
+      <c r="C100" s="8"/>
+      <c r="D100" s="8"/>
+      <c r="E100" s="8"/>
+      <c r="F100" s="10"/>
+      <c r="G100" s="8"/>
+      <c r="H100" s="8"/>
+      <c r="I100" s="8" t="str" cm="1">
+        <f t="array" ref="I100">_xlfn.SWITCH(H100,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J100" s="8"/>
+      <c r="K100" s="8"/>
+      <c r="L100" s="8"/>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A101" s="8"/>
+      <c r="B101" s="8"/>
+      <c r="C101" s="8"/>
+      <c r="D101" s="8"/>
+      <c r="E101" s="8"/>
+      <c r="F101" s="10"/>
+      <c r="G101" s="8"/>
+      <c r="H101" s="8"/>
+      <c r="I101" s="8" t="str" cm="1">
+        <f t="array" ref="I101">_xlfn.SWITCH(H101,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J101" s="8"/>
+      <c r="K101" s="8"/>
+      <c r="L101" s="8"/>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A102" s="8"/>
+      <c r="B102" s="8"/>
+      <c r="C102" s="8"/>
+      <c r="D102" s="8"/>
+      <c r="E102" s="8"/>
+      <c r="F102" s="10"/>
+      <c r="G102" s="8"/>
+      <c r="H102" s="8"/>
+      <c r="I102" s="8" t="str" cm="1">
+        <f t="array" ref="I102">_xlfn.SWITCH(H102,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J102" s="8"/>
+      <c r="K102" s="8"/>
+      <c r="L102" s="8"/>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A103" s="8"/>
+      <c r="B103" s="8"/>
+      <c r="C103" s="8"/>
+      <c r="D103" s="8"/>
+      <c r="E103" s="8"/>
+      <c r="F103" s="10"/>
+      <c r="G103" s="8"/>
+      <c r="H103" s="8"/>
+      <c r="I103" s="8" t="str" cm="1">
+        <f t="array" ref="I103">_xlfn.SWITCH(H103,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J103" s="8"/>
+      <c r="K103" s="8"/>
+      <c r="L103" s="8"/>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A104" s="8"/>
+      <c r="B104" s="8"/>
+      <c r="C104" s="8"/>
+      <c r="D104" s="8"/>
+      <c r="E104" s="8"/>
+      <c r="F104" s="10"/>
+      <c r="G104" s="8"/>
+      <c r="H104" s="8"/>
+      <c r="I104" s="8" t="str" cm="1">
+        <f t="array" ref="I104">_xlfn.SWITCH(H104,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J104" s="8"/>
+      <c r="K104" s="8"/>
+      <c r="L104" s="8"/>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A105" s="8"/>
+      <c r="B105" s="8"/>
+      <c r="C105" s="8"/>
+      <c r="D105" s="8"/>
+      <c r="E105" s="8"/>
+      <c r="F105" s="10"/>
+      <c r="G105" s="8"/>
+      <c r="H105" s="8"/>
+      <c r="I105" s="8" t="str" cm="1">
+        <f t="array" ref="I105">_xlfn.SWITCH(H105,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J105" s="8"/>
+      <c r="K105" s="8"/>
+      <c r="L105" s="8"/>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A106" s="8"/>
+      <c r="B106" s="8"/>
+      <c r="C106" s="8"/>
+      <c r="D106" s="8"/>
+      <c r="E106" s="8"/>
+      <c r="F106" s="10"/>
+      <c r="G106" s="8"/>
+      <c r="H106" s="8"/>
+      <c r="I106" s="8" t="str" cm="1">
+        <f t="array" ref="I106">_xlfn.SWITCH(H106,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J106" s="8"/>
+      <c r="K106" s="8"/>
+      <c r="L106" s="8"/>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A107" s="8"/>
+      <c r="B107" s="8"/>
+      <c r="C107" s="8"/>
+      <c r="D107" s="8"/>
+      <c r="E107" s="8"/>
+      <c r="F107" s="10"/>
+      <c r="G107" s="8"/>
+      <c r="H107" s="8"/>
+      <c r="I107" s="8" t="str" cm="1">
+        <f t="array" ref="I107">_xlfn.SWITCH(H107,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J107" s="8"/>
+      <c r="K107" s="8"/>
+      <c r="L107" s="8"/>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A108" s="8"/>
+      <c r="B108" s="8"/>
+      <c r="C108" s="8"/>
+      <c r="D108" s="8"/>
+      <c r="E108" s="8"/>
+      <c r="F108" s="10"/>
+      <c r="G108" s="8"/>
+      <c r="H108" s="8"/>
+      <c r="I108" s="8" t="str" cm="1">
+        <f t="array" ref="I108">_xlfn.SWITCH(H108,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J108" s="8"/>
+      <c r="K108" s="8"/>
+      <c r="L108" s="8"/>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A109" s="8"/>
+      <c r="B109" s="8"/>
+      <c r="C109" s="8"/>
+      <c r="D109" s="8"/>
+      <c r="E109" s="8"/>
+      <c r="F109" s="10"/>
+      <c r="G109" s="8"/>
+      <c r="H109" s="8"/>
+      <c r="I109" s="8" t="str" cm="1">
+        <f t="array" ref="I109">_xlfn.SWITCH(H109,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J109" s="8"/>
+      <c r="K109" s="8"/>
+      <c r="L109" s="8"/>
     </row>
   </sheetData>
   <autoFilter ref="E1:E120" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Business Analysis/checkupp_sprint_plan_2026.xlsx
+++ b/Business Analysis/checkupp_sprint_plan_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Business Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{484FF25F-2CDB-4DC1-9D6D-6DB2053B8871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{811B6EF7-E8D3-4FD3-B284-9C9FA341B9A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="53">
   <si>
     <t>Epic</t>
   </si>
@@ -124,43 +124,1580 @@
     <t>ToDo</t>
   </si>
   <si>
-    <t>Your Appointments Overview</t>
-  </si>
-  <si>
     <t>Frontend</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Tap </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Your Appointments Overview</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button to view appointments</t>
-    </r>
   </si>
   <si>
     <t>Alekhya</t>
   </si>
   <si>
-    <t>1. Change the Title of existing section to: "Your Appointments Overview"
-2. Make the section tappable by wrapping the element inside button/pressable</t>
+    <t>Backend</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>Sayan</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Update Prisma Schema for Appointments
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Description</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: Open </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-api/prisma/schema.prisma</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Ensure the Appointment model has the following fields: status (Enum: UPCOMING, DUE, COMPLETED, CANCELLED, DISMISSED), scheduledDate (DateTime), updatedDate (DateTime), completedDate (DateTime), healthcareProvider (String?), facilityName (String?), facilityAddress (String?), and a foreign key relation to the User model. Run npx prisma format and create a migration script using npx prisma migrate dev.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Acceptance Criteria</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Prisma schema is updated, and the migration is successfully applied to the local PostgreSQL database.</t>
+    </r>
+  </si>
+  <si>
+    <t>Your Health Overview</t>
+  </si>
+  <si>
+    <t>Database Schema Verification</t>
+  </si>
+  <si>
+    <t>Setup Dev environment</t>
+  </si>
+  <si>
+    <t>Dashboard Navigation &amp; Top Tabs</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Appointment Summary</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Endpoint
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Description:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> In </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-api/src/modules/appointments/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, create a new </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>GET /me/appointments/summary</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> endpoint. The controller should call a service that uses Prisma to run a grouped count query (prisma.appointment.groupBy) filtered by the authenticated user's ID (req.user.id). It should return a JSON payload with counts for upcoming, due, and completed.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Extract </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>HealthOverviewSection</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Component
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Description:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 
+1. Create a new file: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/components/HealthOverviewSection.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+2. Cut the entire "Your Health Overview" UI block (the Animated.View wrapping the title, stats, and charts) starting around line 309 in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/app/(tabs)/home.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+3. Paste it into the new HealthOverviewSection component. Ensure all necessary imports (React, NativeWind classes, typography/font sizing utilities) are moved over.
+4. Wrap it in an Expo Router &lt;Link&gt; or Pressable with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>router.push('/appointments')</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Apply active opacity styling using NativeWind.
+5. In </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/app/(tabs)/home.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, import and render </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>&lt;HealthOverviewSection /&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in the exact place the old code was removed.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Acceptance Criteria:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- The HealthOverviewSection exists as a standalone, exported functional component.
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/app/(tabs)/home.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> is successfully- refactored and no longer contains the hardcoded </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"Your Health Overview</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>" markup.
+- The UI renders identically on the Home Screen with no visual regressions.
+- Tapping the new modularized component successfully routes the user to the /appointments screen.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Create Appointments Screen </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Layout</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Tabs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Description:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Create a new file </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/app/appointments/index.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Implement the base layout using a safe area view. Reuse the existing top-tab UI pattern (similar to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/components/screening/ScreeningTabs.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>). Integrate useApiQuery from checkupp-mobile/lib/query/useApiQuery.ts to fetch the data from /me/appointments/summary. Bind the fetched counts to the tab headers.</t>
+    </r>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>View Upcoming Appointments</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Create Fetch Appointments List Endpoint</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Description:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> In checkupp-api, create a parameterized </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>GET /me/appointments</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> endpoint. It must accept a query param ?status=upcoming|due|completed. Use Prisma to fetch appointments for the logged-in user matching the status, sorted by scheduledDate ASC. Validate the query param using Joi in the routing layer.</t>
+    </r>
+  </si>
+  <si>
+    <t>Atish</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Build Modular </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AppointmentCard</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Component
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Description:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/components/appointments/AppointmentCard.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. It must accept props for Name, Date, and Time. Use NativeWind for styling. Ensure it is wrapped in a TouchableOpacity to handle future click events.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Implement </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Upcoming List</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Empty State</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Description:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> In </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/app/appointments/index.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (under the Upcoming tab condition), use TanStack Query to call /me/appointments?status=upcoming. Render the data using a FlatList of AppointmentCard components. If the data array is empty, render </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/components/EmptyState.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> passing the exact prop: message="You don't have any upcoming appointments".</t>
+    </r>
+  </si>
+  <si>
+    <t>View Due Appointments</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Implement </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Due List</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> View
+Description: Extend the logic in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/app/appointments/index.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. When the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Due</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tab is active, trigger the query for /me/appointments?status=due. Map the payload to the AppointmentCard (mapping updatedDate and updatedTime to the card props). Use the EmptyState component for 0 results.</t>
+    </r>
+  </si>
+  <si>
+    <t>View Completed Appointments</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Implement </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Completed List</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> View
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Description:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Extend the tab logic in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/app/appointments/index.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Trigger query /me/appointments?status=completed. Map completedDate to the AppointmentCard. Render empty state appropriately.</t>
+    </r>
+  </si>
+  <si>
+    <t>Appointment Details Bottom Sheet &amp; Actions</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Create Cancel &amp; Dismiss Endpoints</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Description:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PATCH /me/appointments/:id/cancel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>PATCH /me/appointments/:id/dismiss endpoints</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Validate that the appointment belongs to req.user.id. Update the status column in Prisma to CANCELLED and DISMISSED respectively.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AppointmentDetails</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Bottom Sheet UI
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Description:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/components/appointments/AppointmentDetailsSheet.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Use </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@gorhom/bottom-sheet</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (standard in RN, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>install and import</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>). The sheet must accept an appointment object. Render Name, Date, Time, Provider, Location. Implement a fallback rendering logic: if a value is null/undefined, output "N/A" using a helper function. Add placeholder slots for the CTA buttons at the bottom.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Wire Up </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Reschedule</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> CTA button
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Description:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> In </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AppointmentDetailsSheet.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, conditionally render a primary </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CustomButton.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> labeled "Reschedule" if the status is </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Upcoming</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> or </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Due</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. On press, it must trigger the existing booking modal flow.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Implement Native </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Calendar Deletion Logic</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Description:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Create a helper function in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/lib/notifications/calendar.ts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to handle calendar deletion. It must safely request native calendar read/write permissions (handling denied states). Query the device's calendar for the specific eventId (stored with the appointment payload) and execute the deletion.</t>
+    </r>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Wire Up </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cancel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Dismiss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> CTAs (Mutations)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Description:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Add a secondary CustomButton.tsx labeled "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cancel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>" (for Upcoming) and "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Dismiss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">" (for Due). Use useApiMutation from </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/lib/query/useApiMutation.ts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to call the respective BE endpoints.
+For </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cancel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: Call BE -&gt; Call Calendar Deletion -&gt; Close Sheet -&gt; Invalidate TanStack Query cache for /me/appointments to optimistically update the UI.
+For </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Dismiss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Call BE -&gt; Close Sheet -&gt; Invalidate cache.</t>
+    </r>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Write </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Integration Tests</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for Bottom Sheet Actions
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Description:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>In checkupp-mobile/tests/appointments/viewAppointmentDetails.test.js</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, mock the TanStack query mutations and calendar library. Test that tapping the cards opens the sheet, and tapping CTAs fires the correct mocked functions.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1677,7 +3214,7 @@
     <col min="3" max="3" width="13.21875" style="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.6640625" style="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.5546875" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.5546875" style="13" customWidth="1"/>
+    <col min="6" max="6" width="52.6640625" style="13" customWidth="1"/>
     <col min="7" max="7" width="12.109375" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.88671875" style="12" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.33203125" style="12" bestFit="1" customWidth="1"/>
@@ -1725,12 +3262,16 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="8">
         <v>1</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
+      <c r="B2" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.1</v>
+      </c>
       <c r="D2" s="8"/>
       <c r="E2" s="8" t="s">
         <v>16</v>
@@ -1754,34 +3295,34 @@
       <c r="K2" s="8"/>
       <c r="L2" s="8"/>
     </row>
-    <row r="3" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A3" s="8">
         <v>2</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C3" s="8">
-        <v>1.1000000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="D3" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="8" t="s">
-        <v>22</v>
-      </c>
       <c r="F3" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="H3" s="8" t="s">
         <v>24</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>19</v>
       </c>
       <c r="I3" s="8" cm="1">
         <f t="array" ref="I3">_xlfn.SWITCH(H3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" s="8" t="s">
         <v>20</v>
@@ -1789,239 +3330,479 @@
       <c r="K3" s="8"/>
       <c r="L3" s="8"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8" t="str" cm="1">
+    <row r="4" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="8">
+        <v>3</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" s="8" cm="1">
         <f t="array" ref="I4">_xlfn.SWITCH(H4,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J4" s="8"/>
+        <v>2</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>20</v>
+      </c>
       <c r="K4" s="8"/>
       <c r="L4" s="8"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8" t="str" cm="1">
+    <row r="5" spans="1:12" ht="369" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="8">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5" s="8" cm="1">
         <f t="array" ref="I5">_xlfn.SWITCH(H5,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J5" s="8"/>
+        <v>1</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>20</v>
+      </c>
       <c r="K5" s="8"/>
       <c r="L5" s="8"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8" t="str" cm="1">
+    <row r="6" spans="1:12" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="8">
+        <v>5</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" s="8" cm="1">
         <f t="array" ref="I6">_xlfn.SWITCH(H6,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J6" s="8"/>
+        <v>3</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>20</v>
+      </c>
       <c r="K6" s="8"/>
       <c r="L6" s="8"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8" t="str" cm="1">
+    <row r="7" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="8">
+        <v>6</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7" s="8" cm="1">
         <f t="array" ref="I7">_xlfn.SWITCH(H7,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J7" s="8"/>
+        <v>2</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>20</v>
+      </c>
       <c r="K7" s="8"/>
       <c r="L7" s="8"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8" t="str" cm="1">
+    <row r="8" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8" s="8" cm="1">
         <f t="array" ref="I8">_xlfn.SWITCH(H8,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J8" s="8"/>
+        <v>2</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>20</v>
+      </c>
       <c r="K8" s="8"/>
       <c r="L8" s="8"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8" t="str" cm="1">
+    <row r="9" spans="1:12" ht="144" x14ac:dyDescent="0.3">
+      <c r="A9" s="8">
+        <v>8</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="8">
+        <v>1.2</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I9" s="8" cm="1">
         <f t="array" ref="I9">_xlfn.SWITCH(H9,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J9" s="8"/>
+        <v>3</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>20</v>
+      </c>
       <c r="K9" s="8"/>
       <c r="L9" s="8"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8" t="str" cm="1">
+    <row r="10" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="8">
+        <v>9</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="8">
+        <v>1.3</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I10" s="8" cm="1">
         <f t="array" ref="I10">_xlfn.SWITCH(H10,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J10" s="8"/>
+        <v>2</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>20</v>
+      </c>
       <c r="K10" s="8"/>
       <c r="L10" s="8"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8" t="str" cm="1">
+    <row r="11" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A11" s="8">
+        <v>10</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="8">
+        <v>1.4</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I11" s="8" cm="1">
         <f t="array" ref="I11">_xlfn.SWITCH(H11,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J11" s="8"/>
+        <v>2</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>20</v>
+      </c>
       <c r="K11" s="8"/>
       <c r="L11" s="8"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8" t="str" cm="1">
+    <row r="12" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="8">
+        <v>11</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I12" s="8" cm="1">
         <f t="array" ref="I12">_xlfn.SWITCH(H12,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="J12" s="8"/>
       <c r="K12" s="8"/>
       <c r="L12" s="8"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8" t="str" cm="1">
+    <row r="13" spans="1:12" ht="144" x14ac:dyDescent="0.3">
+      <c r="A13" s="8">
+        <v>12</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I13" s="8" cm="1">
         <f t="array" ref="I13">_xlfn.SWITCH(H13,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="J13" s="8"/>
       <c r="K13" s="8"/>
       <c r="L13" s="8"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8" t="str" cm="1">
+    <row r="14" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="8">
+        <v>13</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I14" s="8" cm="1">
         <f t="array" ref="I14">_xlfn.SWITCH(H14,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="J14" s="8"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8" t="str" cm="1">
+    <row r="15" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A15" s="8">
+        <v>14</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="I15" s="8" cm="1">
         <f t="array" ref="I15">_xlfn.SWITCH(H15,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="J15" s="8"/>
       <c r="K15" s="8"/>
       <c r="L15" s="8"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8" t="str" cm="1">
+    <row r="16" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="8">
+        <v>15</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I16" s="8" cm="1">
         <f t="array" ref="I16">_xlfn.SWITCH(H16,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="J16" s="8"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8" t="str" cm="1">
+    <row r="17" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="8">
+        <v>16</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I17" s="8" cm="1">
         <f t="array" ref="I17">_xlfn.SWITCH(H17,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>

--- a/Business Analysis/checkupp_sprint_plan_2026.xlsx
+++ b/Business Analysis/checkupp_sprint_plan_2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Business Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{811B6EF7-E8D3-4FD3-B284-9C9FA341B9A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F8F3891-7D42-429D-A89B-5FE05E183957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="52">
   <si>
     <t>Epic</t>
   </si>
@@ -139,513 +139,10 @@
     <t>Sayan</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Update Prisma Schema for Appointments
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Description</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: Open </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-api/prisma/schema.prisma</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. Ensure the Appointment model has the following fields: status (Enum: UPCOMING, DUE, COMPLETED, CANCELLED, DISMISSED), scheduledDate (DateTime), updatedDate (DateTime), completedDate (DateTime), healthcareProvider (String?), facilityName (String?), facilityAddress (String?), and a foreign key relation to the User model. Run npx prisma format and create a migration script using npx prisma migrate dev.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Acceptance Criteria</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: Prisma schema is updated, and the migration is successfully applied to the local PostgreSQL database.</t>
-    </r>
-  </si>
-  <si>
     <t>Your Health Overview</t>
   </si>
   <si>
-    <t>Database Schema Verification</t>
-  </si>
-  <si>
     <t>Setup Dev environment</t>
-  </si>
-  <si>
-    <t>Dashboard Navigation &amp; Top Tabs</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Create </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Appointment Summary</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Endpoint
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Description:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> In </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-api/src/modules/appointments/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, create a new </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>GET /me/appointments/summary</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> endpoint. The controller should call a service that uses Prisma to run a grouped count query (prisma.appointment.groupBy) filtered by the authenticated user's ID (req.user.id). It should return a JSON payload with counts for upcoming, due, and completed.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Extract </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>HealthOverviewSection</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Component
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Description:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 
-1. Create a new file: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-mobile/components/HealthOverviewSection.tsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.
-2. Cut the entire "Your Health Overview" UI block (the Animated.View wrapping the title, stats, and charts) starting around line 309 in </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-mobile/app/(tabs)/home.tsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.
-3. Paste it into the new HealthOverviewSection component. Ensure all necessary imports (React, NativeWind classes, typography/font sizing utilities) are moved over.
-4. Wrap it in an Expo Router &lt;Link&gt; or Pressable with </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>router.push('/appointments')</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. Apply active opacity styling using NativeWind.
-5. In </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-mobile/app/(tabs)/home.tsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, import and render </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>&lt;HealthOverviewSection /&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> in the exact place the old code was removed.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Acceptance Criteria:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-- The HealthOverviewSection exists as a standalone, exported functional component.
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-mobile/app/(tabs)/home.tsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> is successfully- refactored and no longer contains the hardcoded </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"Your Health Overview</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>" markup.
-- The UI renders identically on the Home Screen with no visual regressions.
-- Tapping the new modularized component successfully routes the user to the /appointments screen.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Create Appointments Screen </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Layout</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> &amp; </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Tabs</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Description:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Create a new file </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-mobile/app/appointments/index.tsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. Implement the base layout using a safe area view. Reuse the existing top-tab UI pattern (similar to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-mobile/components/screening/ScreeningTabs.tsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>). Integrate useApiQuery from checkupp-mobile/lib/query/useApiQuery.ts to fetch the data from /me/appointments/summary. Bind the fetched counts to the tab headers.</t>
-    </r>
   </si>
   <si>
     <t>M</t>
@@ -654,1021 +151,1171 @@
     <t>View Upcoming Appointments</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Create Fetch Appointments List Endpoint</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Description:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> In checkupp-api, create a parameterized </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>GET /me/appointments</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> endpoint. It must accept a query param ?status=upcoming|due|completed. Use Prisma to fetch appointments for the logged-in user matching the status, sorted by scheduledDate ASC. Validate the query param using Joi in the routing layer.</t>
-    </r>
-  </si>
-  <si>
     <t>Atish</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Build Modular </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>AppointmentCard</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Component
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Description:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Create </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-mobile/components/appointments/AppointmentCard.tsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>. It must accept props for Name, Date, and Time. Use NativeWind for styling. Ensure it is wrapped in a TouchableOpacity to handle future click events.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Implement </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Upcoming List</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> &amp; </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Empty State</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Description:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> In </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-mobile/app/appointments/index.tsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (under the Upcoming tab condition), use TanStack Query to call /me/appointments?status=upcoming. Render the data using a FlatList of AppointmentCard components. If the data array is empty, render </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-mobile/components/EmptyState.tsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> passing the exact prop: message="You don't have any upcoming appointments".</t>
-    </r>
-  </si>
-  <si>
-    <t>View Due Appointments</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Implement </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Due List</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> View
-Description: Extend the logic in </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-mobile/app/appointments/index.tsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. When the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Due</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> tab is active, trigger the query for /me/appointments?status=due. Map the payload to the AppointmentCard (mapping updatedDate and updatedTime to the card props). Use the EmptyState component for 0 results.</t>
-    </r>
-  </si>
-  <si>
-    <t>View Completed Appointments</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Implement </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Completed List</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> View
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Description:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Extend the tab logic in </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-mobile/app/appointments/index.tsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>. Trigger query /me/appointments?status=completed. Map completedDate to the AppointmentCard. Render empty state appropriately.</t>
-    </r>
-  </si>
-  <si>
-    <t>Appointment Details Bottom Sheet &amp; Actions</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Create Cancel &amp; Dismiss Endpoints</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Description:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Create </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PATCH /me/appointments/:id/cancel</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>PATCH /me/appointments/:id/dismiss endpoints</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>. Validate that the appointment belongs to req.user.id. Update the status column in Prisma to CANCELLED and DISMISSED respectively.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Create </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>AppointmentDetails</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Bottom Sheet UI
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Description:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Create </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-mobile/components/appointments/AppointmentDetailsSheet.tsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. Use </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>@gorhom/bottom-sheet</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (standard in RN, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>install and import</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>). The sheet must accept an appointment object. Render Name, Date, Time, Provider, Location. Implement a fallback rendering logic: if a value is null/undefined, output "N/A" using a helper function. Add placeholder slots for the CTA buttons at the bottom.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Wire Up </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Reschedule</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> CTA button
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Description:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> In </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>AppointmentDetailsSheet.tsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, conditionally render a primary </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>CustomButton.tsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> labeled "Reschedule" if the status is </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Upcoming</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> or </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Due</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>. On press, it must trigger the existing booking modal flow.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Implement Native </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Calendar Deletion Logic</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Description:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Create a helper function in </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-mobile/lib/notifications/calendar.ts</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> to handle calendar deletion. It must safely request native calendar read/write permissions (handling denied states). Query the device's calendar for the specific eventId (stored with the appointment payload) and execute the deletion.</t>
-    </r>
   </si>
   <si>
     <t>L</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Wire Up </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Cancel</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> &amp; </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Dismiss</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> CTAs (Mutations)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Description:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Add a secondary CustomButton.tsx labeled "</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Cancel</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>" (for Upcoming) and "</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Dismiss</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">" (for Due). Use useApiMutation from </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-mobile/lib/query/useApiMutation.ts</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> to call the respective BE endpoints.
-For </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Cancel</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: Call BE -&gt; Call Calendar Deletion -&gt; Close Sheet -&gt; Invalidate TanStack Query cache for /me/appointments to optimistically update the UI.
-For </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Dismiss</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: Call BE -&gt; Close Sheet -&gt; Invalidate cache.</t>
-    </r>
-  </si>
-  <si>
     <t>Test</t>
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Write </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Integration Tests</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> for Bottom Sheet Actions
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Description:</t>
-    </r>
-    <r>
-      <rPr>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Extract Hardcoded "Your Health Overview" Section into a Standalone Component &amp; Import in Home Screen</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/components/home/HealthOverviewSection.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- Modify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/app/(tabs)/home.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- Extract Component: Remove the entire JSX block under {/* Stats Overview */} from </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/app/(tabs)/home.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (the card displaying the "Your Health Overview" title, overviewStatus subtitle, completion percentage, and upcoming count).
+- Create a new modular, functional React Native component at </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/components/home/HealthOverviewSection.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+- Define TypeScript interface HealthOverviewSectionProps:
+TypeScript
+export interface HealthOverviewSectionProps {
+  overview: ScreeningOverviewData;  loading: boolean; refreshing: boolean; onPress: () =&gt; void; }
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Make Interactive</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: Wrap the outermost white card container (bg-white rounded-xl border border-gray-100) in a TouchableOpacity with activeOpacity={0.7} and assign onPress={onPress}.
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Add a visual affordance (e.g., a subtle chevron-forward icon from @expo/vector-icons/Ionicons next to the count badge) so users understand the card is tappable.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- Refactor Home Screen: In </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/app/(tabs)/home.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>import HealthOverviewSection from @/components/home/HealthOverviewSection</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.
+- Replace the extracted hardcoded block with:
+TypeScript
+&lt;HealthOverviewSection
+  overview={overview} loading={loading} refreshing={refreshing} onPress={() =&gt; router.push("/health-overview")} /&gt;
+- Ensure all responsive scaling utilities (scale, verticalScale, getFontSize, getSpacing) and NativeWind/Tailwind classes are imported cleanly in HealthOverviewSection.tsx with zero visual regression.</t>
+    </r>
+  </si>
+  <si>
+    <t>Make Your Health Overview interactive and modular</t>
+  </si>
+  <si>
+    <t>1.1, 1.2, 1.3, 1.4</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Define Time-Bucketed Screening Overview TypeScript Interfaces &amp; Validation Schemas</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- Modify: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-api/src/modules/screenings/screening.validation.ts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- Modify: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-api/src/modules/screenings/screening.constants.ts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- In </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-api/src/modules/screenings/screening.constants.ts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, define and export canonical type definitions for time-bucketed overview responses:
+TypeScript
+export interface ScreeningOverviewItem {
+  id: string; 
+  name: string;
+  date: string; // ISO-8601 date string
+  screeningType: 'cancer' | 'health' | 'immunization';
+  status: 'PENDING' | 'COMPLETED' | 'OVERDUE' | 'RESCHEDULED';
+  isOverdue: boolean;
+}
+export interface ScreeningOverviewResponse {
+  counts: {
+    upcoming: number;
+    due: number;
+    completed: number;
+  };
+  upcoming: ScreeningOverviewItem[];
+  due: ScreeningOverviewItem[];
+  completed: ScreeningOverviewItem[];
+}
+- In </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-api/src/modules/screenings/screening.validation.ts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, ensure request schema validation for the overview route requires zero query parameters and relies strictly on authenticated JWT user context.</t>
+    </r>
+  </si>
+  <si>
+    <t>Dev environment setup</t>
+  </si>
+  <si>
+    <t>Implement business logic for Your Health Overview</t>
+  </si>
+  <si>
+    <t>backend</t>
+  </si>
+  <si>
+    <t>Implement backend API for Your Health Overview</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Implement </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>GET /me/screenings/overview</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Time-Bucketed Aggregation Endpoint
+1. Modify: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-api/src/modules/screenings/screening.service.ts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">,  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-api/src/modules/screenings/screening.controller.ts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">checkupp-api/src/modules/screenings/screening.routes.ts
+2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Database Querying: 
+- In </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-api/src/modules/screenings/screening.service.ts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, implement </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>getScreeningOverview(userId: string): Promise&lt;ScreeningOverviewResponse&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. 
+- Query PostgreSQL using Prisma (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>prisma.screeningRecord</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> or </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>prisma.screeningDueItem</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">) filtered strictly by </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>userId</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to guarantee tenant isolation (US 1.1–1.4 AC: Only screenings associated with the logged-in user's account must be displayed).
+3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Date Comparison &amp; Time-Bucketing Rules</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">:
+- Calculate </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>daysUntilDue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> relative to the server’s UTC midnight today boundary (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>now = new Date().setUTCHours(0,0,0,0)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">).
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Upcoming Bucket (US 1.2)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: Filter records </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>where status !== 'COMPLETED'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AND </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0 &lt;= daysUntilDue &lt;= 90</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Sort by </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>date</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ascending.
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Due Bucket (US 1.3)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: Filter records </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>where status !== 'COMPLETED'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AND either:
+a. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>daysUntilDue &lt; 0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Screening date missed -&gt; set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>isOverdue: true</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">).
+b. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>90 &lt; daysUntilDue &lt;= 365</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Due within a year -&gt;  set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>isOverdue: false</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).
+c. Sort overdue items (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>isOverdue: true</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">) first, followed by regular due items by </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>date</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ascending.
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Completed Bucket (US 1.4)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: Filter records </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>where status === 'COMPLETED'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Sort by completed screening date descending.
+4. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Count Calculation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: Populate the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>counts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> object with the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.length</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> of each evaluated bucket: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>{ upcoming: upcoming.length, due: due.length, completed: completed.length }</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+5. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Controller &amp; Route Wiring</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">:
+- In </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>screening.controller.ts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>getOverviewHandler</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> wrapped in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>asyncHandler</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+- In </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>screening.routes.ts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, register </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>router.get('/overview', authMiddleware, getOverviewHandler)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Automated Unit &amp; Integration Test Suite for Overview Date Boundaries &amp; Overdue Flags</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
@@ -1679,32 +1326,2619 @@
     </r>
     <r>
       <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>In checkupp-mobile/tests/appointments/viewAppointmentDetails.test.js</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, mock the TanStack query mutations and calendar library. Test that tapping the cards opens the sheet, and tapping CTAs fires the correct mocked functions.</t>
-    </r>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-api/tests/modules/screenings/overview.test.ts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2. Use </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Jest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>supertest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> against the Express server instance.
+3. Seed test database with a mock user (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>user-test-uuid</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) and 5 screening records:
+- Record A: Due in +15 days (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>status: PENDING</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> -&gt; should appear in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Upcoming</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>isOverdue: false</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).
+- Record B: Due in +90 days (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>status: PENDING</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> -&gt; should appear in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Upcoming</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, boundary test).
+- Record C: Due in +180 days (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>status: PENDING</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> -&gt; should appear in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Due</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>isOverdue: false</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).
+- Record D: Due in -10 days (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>status: PENDING</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> -&gt; should appear in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Due</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>isOverdue: true</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).
+- Record E: Completed 5 days ago (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>status: COMPLETED</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> -&gt; should appear in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Completed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">).
+4. Assert that:
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>res.status === 200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>res.body.counts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> equals { </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>upcoming: 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>due: 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>completed: 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> }.
+- Record D has </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>isOverdue: true</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>due</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> array.
+- Another user’s JWT token receives an empty overview response (isolation check).</t>
+    </r>
+  </si>
+  <si>
+    <t>Unit &amp; Integration tests for Your Health Overview</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Extend TanStack Query Hook &amp; API Client for /me/screenings/overview</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1. Modify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/lib/features/screenings/overview.ts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>and checkupp-mobile/lib/query/keys.ts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2. In </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/lib/query/keys.ts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, ensure </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>screeningKeys.overview(userId)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> is defined for cache invalidation.
+3. In </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/lib/features/screenings/overview.ts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">:
+- Define the frontend interface matching the backend </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ScreeningOverviewResponse</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+- Implement a custom hook </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>useScreeningOverviewData(userId: string)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> using TanStack Query’s </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>useQuery</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:
+TypeScript
+export const useScreeningOverviewData = (userId?: string) =&gt; {
+  return useQuery&lt;ScreeningOverviewResponse&gt;({
+    queryKey: ['screenings', 'overview', userId],
+    queryFn: async () =&gt; {
+      const response = await apiClient.get('/me/screenings/overview');
+      return response.data;
+    },
+    enabled: !!userId,
+    staleTime: 1000 * 60 * 5, // 5 minutes cache
+  });
+};</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Build Reusable ScreeningOverviewCard.tsx Component with Overdue Red Styling</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1. Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/components/screening/ScreeningOverviewCard.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Props Interface</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">:
+TypeScript
+export interface ScreeningOverviewCardProps {
+  item: ScreeningOverviewItem;
+  type: 'upcoming' | 'due' | 'completed';
+  onPress: (item: ScreeningOverviewItem) =&gt; void;
+}
+3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Card Content</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:
+- Render the screening name (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>item.name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">) in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Poppins-Medium</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>font-pmedium</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">).
+- Format </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>item.date</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> using </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>date-fns</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>format(new Date(item.date), "dd MMM yyyy")</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> accompanied by a calendar icon </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(@expo/vector-icons/Ionicons calendar-outline</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">).
+- Implement an accessible touch target (&gt;= 44px height) wrapped in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>TouchableOpacity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+4. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Overdue Highlight Styling (US 1.3 AC 2)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">:
+- When </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>type === 'due'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AND </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>item.isOverdue === true</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">:
+a. Apply distinctive red card styling: border color </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>#EF4444</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>border-red-500</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">), background tint </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>#FEF2F2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>bg-red-50</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">), and date text color </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>#DC2626</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>text-red-600</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">).
+b. Render a distinct text badge in the top right: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"OVERDUE"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in bold uppercase font with red background </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>#FEE2E2 (bg-red-100 px-2 py-0.5 rounded text-red-700 font-pbold</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">).
+- For normal items, use standard neutral </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>styling (bg-white border-gray-100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Build Your Health Overview Screen &amp; Segmented Top Tabs Layout</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1. Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/app/health-overview/index.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/components/screening/OverviewTopTabs.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2. Top Segmented Control (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OverviewTopTabs.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">):
+- Build a pill-shaped segmented control with three horizontal tabs: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Upcoming</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Due</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Completed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+- Accept props: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>activeTab: 'upcoming' | 'due' | 'completed'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>counts: { upcoming: number; due: number; completed: number }</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>onTabChange: (tab) =&gt; void</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+- Render each tab label dynamically appending the count in parentheses:
+a. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Upcoming (${counts.upcoming})</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+b. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Due (${counts.due})</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+c. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Completed (${counts.completed})</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- Active tab state renders with primary cyan accent </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(bg-[#00CED1] text-white font-psemibold</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>), while inactive tabs render in neutral gray (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>bg-gray-100 text-gray-600</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).
+3. Screen Scaffold (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/app/health-overview/index.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">):
+- Use </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>SafeAreaView</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> from </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>react-native-safe-area-context</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.
+- Implement a navigation header with a Back button (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>router.back()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) and Title "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Your Health Overview</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">".
+- Initialize state </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[activeTab, setActiveTab] = useState&lt;'upcoming' | 'due' | 'completed'&gt;('upcoming')</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> so that the "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Upcoming</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>" tab is active by default upon landing (US 1.1 AC).</t>
+    </r>
+  </si>
+  <si>
+    <t>1.2, 1.3, 1.4</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Implement Tab FlatList Views, Pull-to-Refresh, Empty States &amp; Press Handlers</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1. Modify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/app/health-overview/index.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Data Rendering (FlatList)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">:
+- Consume </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>useScreeningOverviewData(userId)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+- Select active array based on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>activeTab: data[activeTab] || []</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+- Render a performant React Native </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FlatList</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> using </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ScreeningOverviewCard</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> as </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>renderItem</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, using </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>item.id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> as </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>keyExtractor</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Pull-to-Refresh</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: Integrate </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RefreshControl</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> into </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FlatList</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> wired to TanStack Query’s </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>refetch()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> method with spinner tint </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>#00CED1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+4. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Strict Empty States (US 1.2–1.4 AC)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">:
+- When </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>data[activeTab].length === 0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, render an </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>EmptyState</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> component displaying the exact strings mandated by acceptance criteria:
+a. When </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>activeTab === 'upcoming'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"You don't have any upcoming screenings."</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+b. When </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>activeTab === 'due'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"You don't have any due screenings."</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+c. When </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>activeTab === 'completed'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"You don't have any completed screenings."</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+5. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Press Handler</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: On card press (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>onPress</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">), trigger Expo Router navigation to pass the screening item context: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>router.push({ pathname: '/health-screening', params: { id: item.id, type: item.screeningType } })</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>1.1, 1.2, 1.3, 1.5</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Automated Jest Test Suite for "Your Health Overview" Navigation, Tabs &amp; Empty States
+1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/tests/screenings/viewScreeningsOverview.test.js</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2. Setup Jest test suite </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>using @testing-library/react-native</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+3. Mock </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>useScreeningOverviewData</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hook to return controlled payloads:
+- Test Case 1: Asserts top tab labels render exact counts (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Upcoming (2)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Due (1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Completed (0)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">).
+- Test Case 2: Asserts default active tab is </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Upcoming</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and renders upcoming items.
+- Test Case 3: Simulates user tap on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Due</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tab -&gt; verifies overdue item renders the "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OVERDUE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">" badge and red styling class.
+- Test Case 4: Simulates empty list payloads -&gt; verifies exact strings </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>("You don't have any upcoming screenings."</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"You don't have any due screenings."</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"You don't have any completed screenings."</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) appear without console warnings.</t>
+    </r>
+  </si>
+  <si>
+    <t>View Upcoming, Due, Completed screenings</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1731,6 +3965,19 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1789,7 +4036,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1828,6 +4075,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3262,17 +5512,19 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="49.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="8">
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C2" s="8">
         <v>0.1</v>
       </c>
-      <c r="D2" s="8"/>
+      <c r="D2" s="8" t="s">
+        <v>37</v>
+      </c>
       <c r="E2" s="8" t="s">
         <v>16</v>
       </c>
@@ -3295,27 +5547,27 @@
       <c r="K2" s="8"/>
       <c r="L2" s="8"/>
     </row>
-    <row r="3" spans="1:12" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A3" s="8">
         <v>2</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C3" s="8">
-        <v>0.2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>24</v>
@@ -3330,34 +5582,34 @@
       <c r="K3" s="8"/>
       <c r="L3" s="8"/>
     </row>
-    <row r="4" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A4" s="8">
         <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="8">
-        <v>1.1000000000000001</v>
+        <v>26</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>35</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>23</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>25</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I4" s="8" cm="1">
         <f t="array" ref="I4">_xlfn.SWITCH(H4,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J4" s="8" t="s">
         <v>20</v>
@@ -3365,34 +5617,34 @@
       <c r="K4" s="8"/>
       <c r="L4" s="8"/>
     </row>
-    <row r="5" spans="1:12" ht="369" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="381.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8">
         <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="8">
-        <v>1.1000000000000001</v>
+        <v>26</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>35</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="I5" s="8" cm="1">
         <f t="array" ref="I5">_xlfn.SWITCH(H5,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J5" s="8" t="s">
         <v>20</v>
@@ -3400,30 +5652,30 @@
       <c r="K5" s="8"/>
       <c r="L5" s="8"/>
     </row>
-    <row r="6" spans="1:12" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>5</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="8">
-        <v>1.1000000000000001</v>
+        <v>26</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>35</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="G6" s="8" t="s">
         <v>22</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="I6" s="8" cm="1">
         <f t="array" ref="I6">_xlfn.SWITCH(H6,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -3435,27 +5687,27 @@
       <c r="K6" s="8"/>
       <c r="L6" s="8"/>
     </row>
-    <row r="7" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="403.2" x14ac:dyDescent="0.3">
       <c r="A7" s="8">
         <v>6</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="8">
-        <v>1.2</v>
+        <v>26</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>35</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>36</v>
+        <v>21</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>44</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="H7" s="8" t="s">
         <v>24</v>
@@ -3470,27 +5722,27 @@
       <c r="K7" s="8"/>
       <c r="L7" s="8"/>
     </row>
-    <row r="8" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
         <v>7</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C8" s="8">
         <v>1.2</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>21</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>24</v>
@@ -3505,30 +5757,30 @@
       <c r="K8" s="8"/>
       <c r="L8" s="8"/>
     </row>
-    <row r="9" spans="1:12" ht="144" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" ht="403.2" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
         <v>8</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C9" s="8">
-        <v>1.2</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>21</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="I9" s="8" cm="1">
         <f t="array" ref="I9">_xlfn.SWITCH(H9,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
@@ -3540,34 +5792,34 @@
       <c r="K9" s="8"/>
       <c r="L9" s="8"/>
     </row>
-    <row r="10" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="388.8" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
         <v>9</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="8">
-        <v>1.3</v>
+        <v>26</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>47</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>21</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I10" s="8" cm="1">
         <f t="array" ref="I10">_xlfn.SWITCH(H10,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J10" s="8" t="s">
         <v>20</v>
@@ -3575,34 +5827,30 @@
       <c r="K10" s="8"/>
       <c r="L10" s="8"/>
     </row>
-    <row r="11" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="8">
-        <v>10</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="8">
-        <v>1.4</v>
+    <row r="11" spans="1:12" ht="259.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8" t="s">
+        <v>49</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I11" s="8" cm="1">
         <f t="array" ref="I11">_xlfn.SWITCH(H11,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J11" s="8" t="s">
         <v>20</v>
@@ -3610,199 +5858,103 @@
       <c r="K11" s="8"/>
       <c r="L11" s="8"/>
     </row>
-    <row r="12" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="8">
-        <v>11</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="I12" s="8" cm="1">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8" t="str" cm="1">
         <f t="array" ref="I12">_xlfn.SWITCH(H12,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v/>
       </c>
       <c r="J12" s="8"/>
       <c r="K12" s="8"/>
       <c r="L12" s="8"/>
     </row>
-    <row r="13" spans="1:12" ht="144" x14ac:dyDescent="0.3">
-      <c r="A13" s="8">
-        <v>12</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="I13" s="8" cm="1">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8" t="str" cm="1">
         <f t="array" ref="I13">_xlfn.SWITCH(H13,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v/>
       </c>
       <c r="J13" s="8"/>
       <c r="K13" s="8"/>
       <c r="L13" s="8"/>
     </row>
-    <row r="14" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="8">
-        <v>13</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="I14" s="8" cm="1">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8" t="str" cm="1">
         <f t="array" ref="I14">_xlfn.SWITCH(H14,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
+        <v/>
       </c>
       <c r="J14" s="8"/>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
     </row>
-    <row r="15" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="8">
-        <v>14</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="I15" s="8" cm="1">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8" t="str" cm="1">
         <f t="array" ref="I15">_xlfn.SWITCH(H15,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>5</v>
+        <v/>
       </c>
       <c r="J15" s="8"/>
       <c r="K15" s="8"/>
       <c r="L15" s="8"/>
     </row>
-    <row r="16" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="8">
-        <v>15</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C16" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="I16" s="8" cm="1">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8" t="str" cm="1">
         <f t="array" ref="I16">_xlfn.SWITCH(H16,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v/>
       </c>
       <c r="J16" s="8"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
     </row>
-    <row r="17" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="8">
-        <v>16</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="I17" s="8" cm="1">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8" t="str" cm="1">
         <f t="array" ref="I17">_xlfn.SWITCH(H17,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
+        <v/>
       </c>
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
@@ -5374,6 +7526,7 @@
     </row>
   </sheetData>
   <autoFilter ref="E1:E120" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Business Analysis/checkupp_sprint_plan_2026.xlsx
+++ b/Business Analysis/checkupp_sprint_plan_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Business Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F8F3891-7D42-429D-A89B-5FE05E183957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8192B95-03C2-4075-A726-592A9CCDD3B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -160,212 +160,6 @@
     <t>Test</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Extract Hardcoded "Your Health Overview" Section into a Standalone Component &amp; Import in Home Screen</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-- Create </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-mobile/components/home/HealthOverviewSection.tsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-- Modify </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-mobile/app/(tabs)/home.tsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-- Extract Component: Remove the entire JSX block under {/* Stats Overview */} from </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-mobile/app/(tabs)/home.tsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (the card displaying the "Your Health Overview" title, overviewStatus subtitle, completion percentage, and upcoming count).
-- Create a new modular, functional React Native component at </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-mobile/components/home/HealthOverviewSection.tsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.
-- Define TypeScript interface HealthOverviewSectionProps:
-TypeScript
-export interface HealthOverviewSectionProps {
-  overview: ScreeningOverviewData;  loading: boolean; refreshing: boolean; onPress: () =&gt; void; }
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Make Interactive</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: Wrap the outermost white card container (bg-white rounded-xl border border-gray-100) in a TouchableOpacity with activeOpacity={0.7} and assign onPress={onPress}.
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Add a visual affordance (e.g., a subtle chevron-forward icon from @expo/vector-icons/Ionicons next to the count badge) so users understand the card is tappable.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-- Refactor Home Screen: In </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-mobile/app/(tabs)/home.tsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>import HealthOverviewSection from @/components/home/HealthOverviewSection</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.
-- Replace the extracted hardcoded block with:
-TypeScript
-&lt;HealthOverviewSection
-  overview={overview} loading={loading} refreshing={refreshing} onPress={() =&gt; router.push("/health-overview")} /&gt;
-- Ensure all responsive scaling utilities (scale, verticalScale, getFontSize, getSpacing) and NativeWind/Tailwind classes are imported cleanly in HealthOverviewSection.tsx with zero visual regression.</t>
-    </r>
-  </si>
-  <si>
     <t>Make Your Health Overview interactive and modular</t>
   </si>
   <si>
@@ -3933,12 +3727,239 @@
   <si>
     <t>View Upcoming, Due, Completed screenings</t>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Extract Hardcoded "Your Health Overview" Section into a Standalone Component &amp; Import in Home Screen</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/components/home/HealthOverviewSection.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- Modify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/app/(tabs)/home.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- Extract Component: Remove the entire JSX block under {/* Stats Overview */} from </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/app/(tabs)/home.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (the card displaying the "Your Health Overview" title, overviewStatus subtitle, completion percentage, and upcoming count).
+- Create a new modular, functional React Native component at </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/components/home/HealthOverviewSection.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+- Define TypeScript interface HealthOverviewSectionProps:
+TypeScript
+export interface HealthOverviewSectionProps {
+  overview: ScreeningOverviewData;  loading: boolean; refreshing: boolean; onPress: () =&gt; void; }
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Make Interactive</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: Wrap the outermost white card container (bg-white rounded-xl border border-gray-100) in a TouchableOpacity with activeOpacity={0.7} and assign onPress={onPress}.
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1" tint="4.9989318521683403E-2"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Add a visual affordance: Text - "See more" + subtle chevron-forward (&gt;) icon from </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1" tint="4.9989318521683403E-2"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@expo/vector-icons/Ionicons</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1" tint="4.9989318521683403E-2"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, so users understand the card is tappable. Render this at the bottom of the card, aligned center.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- Refactor Home Screen: In </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/app/(tabs)/home.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>import HealthOverviewSection from @/components/home/HealthOverviewSection</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.
+- Replace the extracted hardcoded block with:
+TypeScript
+&lt;HealthOverviewSection
+  overview={overview} loading={loading} refreshing={refreshing} onPress={() =&gt; router.push("/health-overview")} /&gt;
+- Ensure all responsive scaling utilities (scale, verticalScale, getFontSize, getSpacing) and NativeWind/Tailwind classes are imported cleanly in HealthOverviewSection.tsx with zero visual regression.</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3970,14 +3991,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
+      <sz val="11"/>
+      <color theme="1" tint="4.9989318521683403E-2"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1" tint="4.9989318521683403E-2"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -4036,7 +4065,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4075,9 +4104,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5523,7 +5549,7 @@
         <v>0.1</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E2" s="8" t="s">
         <v>16</v>
@@ -5558,13 +5584,13 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>21</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>22</v>
@@ -5590,16 +5616,16 @@
         <v>26</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>23</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>25</v>
@@ -5625,16 +5651,16 @@
         <v>26</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D5" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="10" t="s">
         <v>40</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>41</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>25</v>
@@ -5660,16 +5686,16 @@
         <v>26</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>32</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G6" s="8" t="s">
         <v>22</v>
@@ -5695,7 +5721,7 @@
         <v>26</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>29</v>
@@ -5703,8 +5729,8 @@
       <c r="E7" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="14" t="s">
-        <v>44</v>
+      <c r="F7" s="10" t="s">
+        <v>43</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>22</v>
@@ -5739,7 +5765,7 @@
         <v>21</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>30</v>
@@ -5774,7 +5800,7 @@
         <v>21</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>30</v>
@@ -5800,16 +5826,16 @@
         <v>26</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>21</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>30</v>
@@ -5831,16 +5857,16 @@
       <c r="A11" s="8"/>
       <c r="B11" s="8"/>
       <c r="C11" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>32</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>30</v>
@@ -7526,7 +7552,7 @@
     </row>
   </sheetData>
   <autoFilter ref="E1:E120" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Business Analysis/checkupp_sprint_plan_2026.xlsx
+++ b/Business Analysis/checkupp_sprint_plan_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Business Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8192B95-03C2-4075-A726-592A9CCDD3B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{980E1814-A99E-4A7D-BC2B-A55986CEA89F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Sprint 01 Burndown" sheetId="4" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sprint 01'!$E$1:$E$120</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sprint 01'!$E$1:$E$123</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="74">
   <si>
     <t>Epic</t>
   </si>
@@ -163,19 +163,375 @@
     <t>Make Your Health Overview interactive and modular</t>
   </si>
   <si>
-    <t>1.1, 1.2, 1.3, 1.4</t>
+    <t>Dev environment setup</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Define Time-Bucketed Screening Overview TypeScript Interfaces &amp; Validation Schemas</t>
+    <t>Implement business logic for Your Health Overview</t>
+  </si>
+  <si>
+    <t>Implement backend API for Your Health Overview</t>
+  </si>
+  <si>
+    <t>Unit &amp; Integration tests for Your Health Overview</t>
+  </si>
+  <si>
+    <t>View Upcoming, Due, Completed screenings</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Extract Hardcoded "Your Health Overview" Section into a Standalone Component &amp; Import in Home Screen</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/components/home/HealthOverviewSection.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- Modify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/app/(tabs)/home.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- Extract Component: Remove the entire JSX block under {/* Stats Overview */} from </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/app/(tabs)/home.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (the card displaying the "Your Health Overview" title, overviewStatus subtitle, completion percentage, and upcoming count).
+- Create a new modular, functional React Native component at </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/components/home/HealthOverviewSection.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+- Define TypeScript interface HealthOverviewSectionProps:
+TypeScript
+export interface HealthOverviewSectionProps {
+  overview: ScreeningOverviewData;  loading: boolean; refreshing: boolean; onPress: () =&gt; void; }
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Make Interactive</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: Wrap the outermost white card container (bg-white rounded-xl border border-gray-100) in a TouchableOpacity with activeOpacity={0.7} and assign onPress={onPress}.
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1" tint="4.9989318521683403E-2"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Add a visual affordance: Text - "See more" + subtle chevron-forward (&gt;) icon from </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1" tint="4.9989318521683403E-2"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@expo/vector-icons/Ionicons</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1" tint="4.9989318521683403E-2"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, so users understand the card is tappable. Render this at the bottom of the card, aligned center.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- Refactor Home Screen: In </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/app/(tabs)/home.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>import HealthOverviewSection from @/components/home/HealthOverviewSection</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.
+- Replace the extracted hardcoded block with:
+TypeScript
+&lt;HealthOverviewSection
+  overview={overview} loading={loading} refreshing={refreshing} onPress={() =&gt; router.push("/health-overview")} /&gt;
+- Ensure all responsive scaling utilities (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>scale</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>verticalScale</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>getFontSize</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>getSpacing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">) and NativeWind/Tailwind classes are imported cleanly in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>HealthOverviewSection.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> with zero visual regression.</t>
+    </r>
+  </si>
+  <si>
+    <t>1.1, 1.6</t>
+  </si>
+  <si>
+    <t>1.2, 1.3, 1.4, 1.5</t>
+  </si>
+  <si>
+    <t>1.1, 1.2, 1.3, 1.4, 1.8</t>
+  </si>
+  <si>
+    <t>1.1, 1.2, 1.3, 1.4, 1.6, 1.7</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Define Time-Bucketed Screening Overview TypeScript Interfaces, Validation &amp; Sorting Constants</t>
     </r>
     <r>
       <rPr>
@@ -296,653 +652,1591 @@
     </r>
   </si>
   <si>
-    <t>Dev environment setup</t>
+    <t>1.1, 1.2, 1.3, 1.4, 1.7</t>
   </si>
   <si>
-    <t>Implement business logic for Your Health Overview</t>
+    <r>
+      <t xml:space="preserve">Implement </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>GET /me/screenings/overview</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Time-Bucketed Aggregation &amp; Chronological Sorting Endpoint
+1. Modify: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-api/src/modules/screenings/screening.service.ts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">,  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-api/src/modules/screenings/screening.controller.ts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-api/src/modules/screenings/screening.routes.ts
+2. Database Querying</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: 
+- In </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-api/src/modules/screenings/screening.service.ts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, implement </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>getScreeningOverview(userId: string): Promise&lt;ScreeningOverviewResponse&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. 
+- Query Prisma (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>prisma.screeningDueItem.findMany</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>prisma.screeningRecord.findMany</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">) filtered </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>strictly by userId: userId</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for multi-tenant isolation. (US 1.1–1.4 AC: Only screenings associated with the logged-in user's account must be displayed).
+3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Date Bucketing Rules</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (US 1.2–1.4):
+- Calculate </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>daysUntilDue = Math.floor((dueDate.getTime() - Date.now()) / (1000 * 60 * 60 * 24))</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Upcoming</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (0 &lt;= daysUntilDue &lt;= 90): Items with non-completed status due within 0 to 90 days.
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Due</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (91 &lt;= daysUntilDue &lt;= 365 OR daysUntilDue &lt; 0): Items with non-completed status. If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>daysUntilDue &lt; 0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, flag </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>isOverdue = true</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and set</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> status = 'OVERDUE'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Completed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: Items where status === 'COMPLETED'. Use the completion record date as </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>date</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+4. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Chronological Sorting Engine</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (US 1.7 AC):
+- Sort </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>upcoming</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> array chronologically ascending by </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>date</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (earliest upcoming screening at top).
+- Sort </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>due</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> array with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Overdue pinned to top</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (sorted by most overdue first: smallest/most negative </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>daysUntilDue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ascending), followed by standard due screenings sorted chronologically ascending by </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>date</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+- Sort </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>completed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> array chronologically </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>descending</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> by completion date (most recently completed at top).
+5. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Counts Calculation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: Return </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>{ counts: { upcoming: upcoming.length, due: due.length, completed: completed.length }, upcoming, due, completed }</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+6. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Route Binding</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: Register </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>router.get('/overview', authMiddleware, getOverviewHandler) in checkupp-api/src/modules/screenings/screening.routes.ts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
   </si>
   <si>
-    <t>backend</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Implement Background Cycle Recalculation Service &amp; Schedule Auto-Transition Logic</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1. Modify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-api/src/modules/screenings/screening.service.ts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-api/src/modules/screenings/screening.controller.ts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Auto-Transition Hook</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: In </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-api/src/modules/screenings/screening.service.ts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, inside </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>saveScreeningRecord(userId, screeningId, recordPayload)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, after persisting the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>COMPLETED</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> record, immediately mark the active </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ScreeningDueItem</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> as </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>status: 'COMPLETED'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Next Cycle Calculation Engine</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (US 1.6 AC 3):
+- Fetch the canonical clinical guideline interval from </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ScreeningDefinition</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (e.g., intervalMonths: 12, 24, or 3).
+- Calculate </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nextDueDate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>= addMonths(recordPayload.completedDate, intervalMonths)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+- Create a new </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ScreeningDueItem</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>userId</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>with date: nextDueDate.toISOString()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>status: 'PENDING'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Immediate Schedule Reflection</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: Ensure any subsequent call to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>GET /me/screenings/overview</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> immediately reflects the newly completed item under </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Completed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and appropriately places the newly generated next cycle item under </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Upcoming</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> or </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Due</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nextDueDate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
   </si>
   <si>
-    <t>Implement backend API for Your Health Overview</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Automated Unit &amp; Integration Test Suite for Overview Date Boundaries &amp; Overdue Flags</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-api/tests/modules/screenings/overview-sorting-and-cycles.test.ts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2. Use </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Jest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>supertest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> against the Express server instance.
+3. Seed test database with a mock user (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>user-test-uuid</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">)
+4. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Test Case 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Chronological Sorting - US 1.7): Seed 3 Upcoming items (due in +80, +10, +45 days). Assert </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>res.body.upcoming</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> is ordered: +10, +45, +80.
+5. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Test Case 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Overdue Pinning - US 1.7 AC 2):Seed 2 Due items (+120, +200 days) and 2 Overdue items (-5 days, -30 days). Assert </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>res.body.due order</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: -30 days (most overdue first), -5 days, +120 days, +200 days.
+6. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Test Case 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Next Cycle Auto-Transition - US 1.6):Execute </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>POST /me/screenings/records</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to complete an overdue test with a 12-month interval. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Execute GET /me/screenings/overview</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> -&gt; verify old item is in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>completed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and a new item due in 365 days exists in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>due</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Implement </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>GET /me/screenings/overview</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Time-Bucketed Aggregation Endpoint
-1. Modify: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-api/src/modules/screenings/screening.service.ts</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">,  </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-api/src/modules/screenings/screening.controller.ts</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">checkupp-api/src/modules/screenings/screening.routes.ts
-2. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Database Querying: 
-- In </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-api/src/modules/screenings/screening.service.ts</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, implement </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>getScreeningOverview(userId: string): Promise&lt;ScreeningOverviewResponse&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>. 
-- Query PostgreSQL using Prisma (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>prisma.screeningRecord</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> or </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>prisma.screeningDueItem</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">) filtered strictly by </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>userId</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> to guarantee tenant isolation (US 1.1–1.4 AC: Only screenings associated with the logged-in user's account must be displayed).
-3. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Date Comparison &amp; Time-Bucketing Rules</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">:
-- Calculate </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>daysUntilDue</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> relative to the server’s UTC midnight today boundary (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>now = new Date().setUTCHours(0,0,0,0)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">).
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Upcoming Bucket (US 1.2)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: Filter records </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>where status !== 'COMPLETED'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> AND </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>0 &lt;= daysUntilDue &lt;= 90</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. Sort by </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>date</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> ascending.
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Due Bucket (US 1.3)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: Filter records </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>where status !== 'COMPLETED'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> AND either:
-a. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>daysUntilDue &lt; 0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (Screening date missed -&gt; set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>isOverdue: true</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">).
-b. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>90 &lt; daysUntilDue &lt;= 365</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (Due within a year -&gt;  set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>isOverdue: false</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>).
-c. Sort overdue items (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>isOverdue: true</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">) first, followed by regular due items by </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>date</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> ascending.
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Completed Bucket (US 1.4)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: Filter records </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>where status === 'COMPLETED'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. Sort by completed screening date descending.
-4. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Count Calculation</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: Populate the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>counts</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> object with the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.length</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> of each evaluated bucket: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>{ upcoming: upcoming.length, due: due.length, completed: completed.length }</t>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Extend TanStack Query Client, Hook &amp; Offline Cache Persistence for /me/screenings/overview</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1. Modify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">checkupp-mobile/lib/features/screenings/overview.ts </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/lib/query/keys.ts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2. Define query key </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>screeningKeys.overview(userId)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/lib/query/keys.ts</t>
     </r>
     <r>
       <rPr>
@@ -953,135 +2247,64 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">.
-5. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Controller &amp; Route Wiring</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">:
-- In </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>screening.controller.ts</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, create </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>getOverviewHandler</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> wrapped in </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>asyncHandler</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.
-- In </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>screening.routes.ts</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, register </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>router.get('/overview', authMiddleware, getOverviewHandler)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
+3. In </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/lib/features/screenings/overview.ts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, implement custom query hook </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>useScreeningOverview(userId?: string)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:
+TypeScript
+export const useScreeningOverview = (userId?: string) =&gt; {
+  return useQuery&lt;ScreeningOverviewResponse, Error&gt;({
+    queryKey: ['screenings', 'overview', userId],
+    queryFn: async () =&gt; {
+      const { data } = await apiClient.get('/me/screenings/overview');
+      return data;
+    },
+    enabled: !!userId,
+    staleTime: 1000 * 60 * 5,
+    gcTime: 1000 * 60 * 60 * 24, // 24h cache persistence for offline mode
+    retry: 1,
+  });
+};
+4. Ensure TanStack Query is configured with AsyncStorage/MMKV persistence so that cached schedule data remains accessible during offline starts (US 1.8).</t>
     </r>
   </si>
   <si>
@@ -1094,778 +2317,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Automated Unit &amp; Integration Test Suite for Overview Date Boundaries &amp; Overdue Flags</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-1.</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Create </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-api/tests/modules/screenings/overview.test.ts</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-2. Use </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Jest</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>supertest</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> against the Express server instance.
-3. Seed test database with a mock user (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>user-test-uuid</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>) and 5 screening records:
-- Record A: Due in +15 days (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>status: PENDING</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> -&gt; should appear in </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Upcoming</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>isOverdue: false</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>).
-- Record B: Due in +90 days (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>status: PENDING</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> -&gt; should appear in </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Upcoming</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, boundary test).
-- Record C: Due in +180 days (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>status: PENDING</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> -&gt; should appear in </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Due</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>isOverdue: false</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>).
-- Record D: Due in -10 days (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>status: PENDING</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> -&gt; should appear in </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Due</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>isOverdue: true</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>).
-- Record E: Completed 5 days ago (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>status: COMPLETED</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> -&gt; should appear in </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Completed</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">).
-4. Assert that:
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>res.status === 200</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>res.body.counts</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> equals { </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>upcoming: 2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>due: 2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>completed: 1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> }.
-- Record D has </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>isOverdue: true</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> in the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>due</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> array.
-- Another user’s JWT token receives an empty overview response (isolation check).</t>
-    </r>
-  </si>
-  <si>
-    <t>Unit &amp; Integration tests for Your Health Overview</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Extend TanStack Query Hook &amp; API Client for /me/screenings/overview</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-1. Modify </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-mobile/lib/features/screenings/overview.ts</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>and checkupp-mobile/lib/query/keys.ts</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-2. In </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-mobile/lib/query/keys.ts</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, ensure </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>screeningKeys.overview(userId)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> is defined for cache invalidation.
-3. In </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-mobile/lib/features/screenings/overview.ts</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">:
-- Define the frontend interface matching the backend </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ScreeningOverviewResponse</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.
-- Implement a custom hook </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>useScreeningOverviewData(userId: string)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> using TanStack Query’s </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>useQuery</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>:
-TypeScript
-export const useScreeningOverviewData = (userId?: string) =&gt; {
-  return useQuery&lt;ScreeningOverviewResponse&gt;({
-    queryKey: ['screenings', 'overview', userId],
-    queryFn: async () =&gt; {
-      const response = await apiClient.get('/me/screenings/overview');
-      return response.data;
-    },
-    enabled: !!userId,
-    staleTime: 1000 * 60 * 5, // 5 minutes cache
-  });
-};</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Build Reusable ScreeningOverviewCard.tsx Component with Overdue Red Styling</t>
+      <t>Build Reusable ScreeningOverviewCard.tsx Component with Overdue Red Styling &amp; Tap Handlers</t>
     </r>
     <r>
       <rPr>
@@ -2375,7 +2827,50 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>).</t>
+      <t xml:space="preserve">).
+5. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Tap Handler</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: Trigger </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>onPress(item)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> when pressed (to open decision modal in FE-1.6).</t>
     </r>
   </si>
   <si>
@@ -2388,7 +2883,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Build Your Health Overview Screen &amp; Segmented Top Tabs Layout</t>
+      <t>Build Your Health Overview Screen &amp; Segmented Top Tabs Layout &amp; Dynamic Count Badges</t>
     </r>
     <r>
       <rPr>
@@ -2852,11 +3347,11 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>" tab is active by default upon landing (US 1.1 AC).</t>
+      <t>" tab is active by default upon landing.</t>
     </r>
   </si>
   <si>
-    <t>1.2, 1.3, 1.4</t>
+    <t>1.2, 1.3, 1.4, 1.8</t>
   </si>
   <si>
     <r>
@@ -2868,7 +3363,2053 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Implement Tab FlatList Views, Pull-to-Refresh, Empty States &amp; Press Handlers</t>
+      <t>Implement Tab FlatList Views, Pull-to-Refresh, Skeleton Loaders &amp; Strict Empty States</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1. Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/components/screening/OverviewSkeletonLoader.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and Modify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/app/health-overview/index.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Skeleton Loaders</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (US 1.8 AC 2): Build </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OverviewSkeletonLoader.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> displaying 3 animated gray placeholder cards (bg-gray-200 animate-pulse h-20 rounded-xl mb-3) when </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>isLoading === true</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+3. Pull-to-Refresh &amp; Offline Cache Behavior (US 1.8 AC 1, 3): 
+- Attach </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>RefreshControl</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>FlatList</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">:
+TypeScript&lt;RefreshControl
+  refreshing={isRefetching}
+  onRefresh={handleRefresh}
+  tintColor="#00CED1"
+/&gt;
+- In </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>handleRefresh</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:
+- Trigger refetch().
+- If offline (!netInfo.isConnected), ensure spinner dismisses within 3 seconds (setTimeout(() =&gt; setIsRefetching(false), 3000)) and trigger snackbar/toast: Exact string required: "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>No internet connection. Showing your last saved schedule.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">"
+- Keep previously cached cards visible on screen without disruption.
+4. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Strict Empty States</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (US 1.2–1.4 AC):
+- When </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>data[activeTab].length === 0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and not loading, render </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>EmptyState</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">:
+a. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>activeTab === 'upcoming'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> -&gt; "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>You don't have any upcoming screenings.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">"
+b. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>activeTab === 'due</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>' -&gt; "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>You don't have any due screenings.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">"
+c. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>activeTab === 'completed'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> -&gt; "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>You don't have any completed screenings.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"</t>
+    </r>
+  </si>
+  <si>
+    <t>1.5, 1.6</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Integrate "Have you had this screening?" Decision Modal &amp; Routing to Existing Forms/Booking Modal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1. Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/components/screening/ScreeningDecisionModal.tsx and checkupp-mobile/app/health-overview/index.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Build Decision Modal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (ScreeningDecisionModal.tsx):
+- Extend </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BaseModal.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/components/screening/shared/modals/BaseModal.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">).
+- Props: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>visible: boolean</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>item: ScreeningOverviewItem | null</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>onClose: () =&gt; void</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>onSelectYes: () =&gt; void</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>onSelectNo: () =&gt; void.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- Display the screening name (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>item?.name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) as header subtitle.
+- Render prompt string exactly: "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Have you had this screening?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>" (US 1.5 AC 2).
+- Render two accessible CTA buttons: "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Yes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>" (Primary #00CED1) and "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>No</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">" (Secondary outline).
+3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Connect Routing &amp; Actions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">:
+- In </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/app/health-overview/index.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, when a card is pressed, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>selectedItem</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and open </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ScreeningDecisionModal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.
+- On "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Yes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">" tap (US 1.5 AC 4):
+a. Dismiss modal and route to the existing data entry form: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>router.push({ pathname: '/(tabs)/health-screening', params: { openFormFor: selectedItem.id, type: selectedItem.screeningType } })</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.
+b. Upon successful form submission, TanStack Query invalidation (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>queryClient.invalidateQueries({ queryKey: ['screenings', 'overview'] })</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">) ensures the card immediately transitions to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Completed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and tab count badges update (US 1.6).
+- On "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>No</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>" tap (US 1.5 AC 5):
+Dismiss modal and open the existing appointment booking modal (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>bookingFlow.ts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> / appointment booking modal component).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Implement Offline Cold-Start Empty State Card &amp; Retryable Error Banner Handlers</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1. Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/components/screening/OverviewOfflineState.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/components/screening/OverviewErrorBanner.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and Modify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/app/health-overview/index.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Offline Cold Start Component</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (OverviewOfflineState.tsx):
+- When </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>isError &amp;&amp; !data</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and network is offline, render an offline empty-state card.
+- Display exact string: "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>You're offline. Connect to the internet to load your screenings.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>" (US 1.8 AC 4).
+- Render an interactive [</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Retry</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">] button that calls </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>refetch()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Server Error Banner</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (OverviewErrorBanner.tsx):
+- When server returns </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>500 Internal Server Error</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>isError === true</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">) AND cached </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>data</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> exists:
+a. Do not crash or hide cached items (US 1.8 AC 5).
+b. Render a top yellow/red retryable error banner: "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Unable to sync latest schedule. Showing offline copy.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>" with a [</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Retry</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>] link.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Automated Jest Frontend Test Suite for Overview Workflows, Pull-to-Refresh, Offline States &amp; Modal Actions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1.  Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/tests/screenings/healthOverviewEpicWorkflows.test.js</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1. Configure Jest + </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@testing-library/react-native</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> with mocked Expo Router, NetInfo, and TanStack Query.
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Test Case 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Tab Counts &amp; Chronological Order - US 1.1, 1.7):
+a. Verify tab titles render Upcoming (2), Due (2), Completed (1).
+b. Verify Due tab renders Overdue card at index 0 with red #EF4444 styling and "OVERDUE" badge.
+-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Test Case 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Decision Modal &amp; Routing - US 1.5):
+a. Simulate tap on upcoming card. Assert modal appears with exact text "Have you had this screening?".
+b. Simulate press on "Yes". Assert router.push is called with form parameters.
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Test Case 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Offline Cache &amp; Refresh - US 1.8):
+- Simulate offline network state + pull-to-refresh. Assert spinner dismisses within 3000ms and toast "No internet connection. Showing your last saved schedule." is rendered.
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Test Case 4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Offline Cold Start - US 1.8):
+a. Simulate offline network + data: undefined. Assert exact text "You're offline. Connect to the internet to load your screenings." is rendered.
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Test Case 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Empty State Exact Strings - US 1.2–1.4):
+a. Pass empty arrays for all 3 tabs. Assert exact strings:
+"</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>You don't have any upcoming screenings.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"
+"</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>You don't have any due screenings.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"
+"</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>You don't have any completed screenings.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"</t>
+    </r>
+  </si>
+  <si>
+    <t>1.1, 1.2, 1.3, 1.4, 1.5, 1.6, 1.7, 1.8</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Define Prisma Schema Models, TypeScript Interfaces &amp; Joi Validation Schemas for Custom Conditions
+1. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Modify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-api/prisma/schema.prisma</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-api/src/modules/screenings/screening.constants.ts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-api/src/modules/screenings/screening.validation.ts
+2. Prisma Schema</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (schema.prisma):
+- Add </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CustomCondition</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CustomConditionRecord</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> models with strict tenant isolation (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>userId</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> indexed FK):
+model CustomCondition {
+  id              String                  @id @default(uuid())
+  userId          String
+  conditionName   String
+  monitoringType  String                  // e.g. "Blood test", "Imaging/ Radiology", "Other: [custom]"
+  frequencyType   String                  // "Monthly" | "Every 3 Months" | "Every 6 Months" | "Annually" | "Custom"
+  customInterval  Int?                    // Numeric stepper value when frequencyType == "Custom"
+  customUnit      String?                 // "Days" | "Months" | "Years"
+  careProvider    String
+  createdAt       DateTime                @default(now())
+  updatedAt       DateTime                @updatedAt
+  records         CustomConditionRecord[]
+  @@index([userId])
+}
+model CustomConditionRecord {
+  id                 String          @id @default(uuid())
+  customConditionId  String
+  userId             String
+  checkDate          DateTime
+  outcomeNotes       String?
+  createdAt          DateTime        @default(now())
+  customCondition    CustomCondition @relation(fields: [customConditionId], references: [id], onDelete: Cascade)
+  @@index([customConditionId])
+  @@index([userId])
+}
+2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Canonical TypeScript Interfaces</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (screening.constants.ts): Export matching DTO types </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CustomConditionItem</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CustomConditionRecordPayload</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Joi Validation Schemas</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (screening.validation.ts):
+- Define </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>createCustomConditionSchema</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">:
+a. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>conditionName</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: required non-empty string (&lt;= 100 chars).
+b. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>monitoringType</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: required string.
+c. f</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>requencyType</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: required enum (['Monthly', 'Every 3 Months', 'Every 6 Months', 'Annually', 'Custom']).
+d. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>customInterval</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: required positive integer when </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>frequencyType === 'Custom'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, optional otherwise.
+e. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>customUnit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: required enum (['Days', 'Months', 'Years']) when </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>frequencyType === 'Custom'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+f. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>careProvider</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: required non-empty string &lt; 100 chars).
+- Define </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>logCustomConditionRecordSchema</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">:
+a. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkDate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: required ISO-8601 UTC date string &lt;= current system date).
+b. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>outcomeNotes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: optional string &lt;= 2000$ chars).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Implement POST /me/screenings/custom-conditions &amp; GET /me/screenings/custom-conditions CRUD Endpoints</t>
     </r>
     <r>
       <rPr>
@@ -2890,7 +5431,1804 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>checkupp-mobile/app/health-overview/index.tsx</t>
+      <t>checkupp-api/src/modules/screenings/screening.service.ts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-api/src/modules/screenings/screening.controller.ts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-api/src/modules/screenings/screening.routes.ts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Service Implementation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (screening.service.ts):
+- Implement </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>createCustomCondition(userId: string, payload: CreateCustomConditionDTO): Promise&lt;CustomConditionItem&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> storing the entity in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>prisma.customCondition</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+- Implement </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>getUserCustomConditions(userId: string): Promise&lt;CustomConditionItem[]&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> fetching all conditions for </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>userId</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, including the most recent associated record (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>records: { orderBy: { checkDate: 'desc' }, take: 1 }</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) to supply the "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Last: [Date]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">" timestamp to the UI.
+2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Controller &amp; Router Wiring</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">:
+- In </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>screening.controller.ts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, add </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>createCustomConditionHandler</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>getCustomConditionsHandler</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> wrapped in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>asyncHandler</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+- In </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>screening.routes.ts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, register:
+a. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>router.post('/custom-conditions', authMiddleware, validate(createCustomConditionSchema), createCustomConditionHandler)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+b. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>router.get('/custom-conditions', authMiddleware, getCustomConditionsHandler)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Audit Logging</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">:
+- Trigger immutable audit event </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CREATE_CUSTOM_CONDITION</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> via </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>audit.service.ts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> upon successful creation.</t>
+    </r>
+  </si>
+  <si>
+    <t>18.2, 18.3, 18.4</t>
+  </si>
+  <si>
+    <t>18.1, 18.2, 18.3, 18.4, 18.5</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Implement POST /me/screenings/custom-conditions/:id/records Outcome Logging &amp; Due-Date Advancement Engine</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1. Modify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-api/src/modules/screenings/screening.service.ts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-api/src/modules/screenings/screening.controller.ts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">checkupp-api/src/modules/screenings/screening.routes.ts
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Outcome Logging Service</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (screening.service.ts):
+- Implement </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>logCustomConditionRecord(userId: string, customConditionId: string, payload: CustomRecordPayload)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">:
+a. Verify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>prisma.customCondition.findFirst({ where: { id: customConditionId, userId } })</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> exists </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(return 404 NotFoundError</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> if unauthorized/missing).
+b. Insert row into prisma.customConditionRecord.
+3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Scheduling Engine Integration</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">:
+a. Calculate </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>nextDueDate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> relative to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>payload.checkDate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> based on frequency:
+- Monthly: addMonths(checkDate, 1)
+- Every 3 Months: addMonths(checkDate, 3)
+- Every 6 Months: addMonths(checkDate, 6)
+- Annually: addYears(checkDate, 1)
+- Custom: add </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>customInterval</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> according to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>customUnit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Days, Months, or Years).
+b. Ensure the custom condition item reflects this updated schedule when queried.
+4. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Router Binding</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: Register </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>router.post('/custom-conditions/:id/records', authMiddleware, validate(logCustomConditionRecordSchema), logCustomConditionRecordHandler)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Automated Jest Unit &amp; Integration Test Suite for Custom Condition Creation, Frequency Math &amp; Outcome Logging</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1. Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">checkupp-api/tests/modules/screenings/customConditions.test.ts
+2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Setup Jest + supertest against the Express server seeded with mock user user-test-uuid.
+3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Test Case 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Creation - US 18.2, 18.3): Send valid payload with "Custom" frequency (customInterval: 45, customUnit: 'Days'). Assert HTTP 201 Created and database persistence.
+4. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Test Case 2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(Validation Rejection - US 18.2 AC 10): Omit careProvider or send empty conditionName. Assert HTTP 400 Bad Request.
+5. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Test Case 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Outcome Logging &amp; Latest Date - US 18.5):
+- POST an outcome record with checkDate: "2026-08-02T00:00:00.000Z".
+- Execute GET /me/screenings/custom-conditions and verify the payload returns the latest record check date to support green badge UI rendering.
+6. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Test Case 4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Tenant Isolation): Verify another user's JWT token receives 404 when attempting to log an outcome against user-test-uuid's custom condition ID.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Build SpecificConditionsTriggerCard.tsx Action Component &amp; Import into Health Checks Screening Tab
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">1. Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/components/screening/SpecificConditionsTriggerCard.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">checkupp-mobile/app/(tabs)/health-screening.tsx
+2. Build Trigger Card </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(SpecificConditionsTriggerCard.tsx): 
+- Create a modular functional React Native component styled with a clean white card border (bg-white rounded-xl border border-gray-100 p-4 mb-4).
+- Render button/tab title: "Specific Conditions" in Poppins-SemiBold (font-psemibold).
+- Render exact subtext (US 18.1 AC 2): "Uncommon, rare and specific conditions to me" in neutral gray (text-gray-500 font-pregular text-xs).
+- Render an add icon (+) indicator on the right side using @expo/vector-icons/Ionicons (add-circle-outline or add icon with primary cyan #00CED1 tint) (US 18.1 AC 3).
+- Accept prop: onPress: () =&gt; void. Wrap card in TouchableOpacity with accessible touch target (&gt;= 44px height).
+2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Integrate into Screen</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (health-screening.tsx):
+- Import SpecificConditionsTriggerCard.
+- Render it at the top of the "Available Health Checks" list when the "Health Checks" top tab is active.
+- Attach onPress={() =&gt; setIsAddModalVisible(true)} to open the bottom sheet created.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Build AddSpecificConditionModal.tsx Bottom Sheet Form with Dynamic Conditional Fields &amp; Validation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1. Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/components/screening/AddSpecificConditionModal.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2. Modal Scaffold:
+- Extend </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BaseModal.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (checkupp-mobile/components/screening/shared/modals/BaseModal.tsx) configured as a bottom sheet.
+- Title: "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Add Specific Condition</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">".
+3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Form State &amp; Essential Inputs</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (US 18.2 AC 1–4):
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Condition or Diagnosis</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: Free-text input (InputField.tsx).
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Monitoring Type</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: Dropdown selector (Picker.tsx) with options: "Blood test", "Imaging/ Radiology", "Doctor Review", "Endoscopy", "Other...".
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>How Often?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: Multi-choice selectable chips ("Monthly", "Every 3 Months", "Every 6 Months", "Annually", "Custom...").
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Doctor or Care Provider</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: Free-text input (InputField.tsx).
+4. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Conditional Dynamic UI Rendering</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (US 18.2 AC 7, 8):
+- When monitoringType === 'Other...': Render an additional free-text field labeled "Specify Monitoring Type".
+- When frequencyType === 'Custom...': Render:
+a. An engraved numeric stepper control (InputField.tsx with up/down chevrons chevron-up and chevron-down incrementing/decrementing customInterval by 1, minimum 1).
+b. A secondary dropdown (Picker.tsx) with options: "Days", "Months", "Years".
+5. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Strict Mandatory Field Validation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (US 18.2 AC 10):
+- Compute isFormValid: true only when condition name, monitoring type (plus custom specification if "Other..."), frequency (plus numeric interval/unit if "Custom..."), and doctor provider are all non-empty.
+- Keep the primary "Save" button visually disabled (opacity-50) and untappable (disabled={!isFormValid}) until validation passes.
+- When clicked, trigger callback onSave(formData) to open the confirmation modal.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Automated Jest Test Suite for Specific Conditions Trigger, Conditional Form Inputs, Modals &amp; Outcome Badges
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">1. Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">checkupp-mobile/tests/screenings/specificConditionsLifecycle.test.js
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">2. Configure Jest + </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>@testing-library/react-native</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> with mocked Expo Router and TanStack Query.
+3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Test Case 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Trigger Card &amp; Subtext - US 18.1):Assert "Specific Conditions" card renders exact subtext "Uncommon, rare and specific conditions to me" and + icon.
+3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Test Case 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Conditional Form Inputs &amp; Validation - US 18.2):Open bottom sheet. Select "Other..." monitoring -&gt; verify free-text specification field appears.Select "Custom..." frequency -&gt; verify numeric stepper chevrons and unit dropdown appear.Assert "Save" button is disabled until all required fields contain text.
+4. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Test Case 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Summary Confirmation &amp; Back to Editing - US 18.3):Fill valid form and click Save. Verify summary modal displays matching data.Click "Back to Editing" -&gt; assert summary modal closes and bottom sheet form inputs retain typed text.
+5. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Test Case 4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Card Styling &amp; Green Outcome Pill Badge - US 18.4, 18.5):Render CustomConditionCard with mock latestRecordDate: "2026-08-02T00:00:00.000Z".Assert green pill badge is rendered with exact text "Last: 02 Aug 2026" and #15803D green text class.
+6. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Test Case 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Decision Modal &amp; Booking Navigation - US 18.4):Simulate tap on custom condition card -&gt; assert "Have you had this screening?" decision modal opens.Click "No" -&gt;assert appointment booking flow is invoked. Click "Yes" -&gt; assert LogSpecificConditionModal is invoked.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Build LogSpecificConditionModal.tsx Full-Screen Outcome Form &amp; Wire Save Mutation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1. Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/components/screening/LogSpecificConditionModal.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">checkupp-mobile/lib/features/screenings/mutations.ts
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Full-Screen Modal Scaffold</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (US 18.5 AC 1):
+- Build full-screen modal view with header displaying read-only metadata: condition name, monitoring type, frequency, and care provider.
+3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Form Input Components</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (US 18.5 AC 2, 3, 4):
+- Date of Check: Use DatePickerInput.tsx defaulting to current system date (new Date()). Allow user selection up to current date.
+- Outcome or Clinical Notes: Spacious multi-line free-text area (InputField.tsx with multiline={true} and numberOfLines={4}).
+4. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CTA Buttons &amp; Workflow</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (US 18.5 AC 4, 5, 6):
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Sticky footer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> with two buttons:
+a. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Secondary</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: Cancel: Tapping closes modal and returns user to Available Health Checks - Health Checks top tab - Screenings bottom tab with zero data persistence.
+b. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Primary</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Save: Tapping executes useLogCustomConditionRecordMutation({ customConditionId, checkDate, outcomeNotes }).
+- Upon success, invalidate query ['screenings', 'custom-conditions'], close full-screen modal, return user to Health Checks list, and confirm the card now displays the green "Last: [Today's Logging Date]" pill badge.</t>
+    </r>
+  </si>
+  <si>
+    <t>18.4, 18.5</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Integrate Custom Condition List Rendering &amp; Wire Existing Decision Modal ("Have you had this screening?")</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1. Modify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/app/(tabs)/health-screening.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/lib/features/screenings/queries.ts
+2. Data Query &amp; List Rendering</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">:
+- Implement useCustomConditionsQuery(userId) in queries.ts fetching GET /me/screenings/custom-conditions.
+- In health-screening.tsx, merge/render CustomConditionCard components inside the "Available Health Checks" FlatList directly below the trigger card.
+3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Wire Decision Modal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (US 18.4 AC 4–7):
+- When CustomConditionCard is tapped (onPress), open the app's existing ScreeningDecisionModal ("Have you had this screening?").
+- Pass the custom condition name as subtitle.
+- On "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Yes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>" tap (AC 6): Close decision modal and open LogSpecificConditionModal (FE-18.6) passing customConditionId and metadata.
+- On "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>No</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>" tap (AC 7): Close decision modal and open the app's existing appointment booking modal (bookingFlow.ts).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Build Reusable CustomConditionCard.tsx Component with Distinctive Styling &amp; Green "Last: [Date]" Pill Badge
+1. Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/components/screening/CustomConditionCard.tsx</t>
     </r>
     <r>
       <rPr>
@@ -2912,7 +7250,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Data Rendering (FlatList)</t>
+      <t>Props Interface</t>
     </r>
     <r>
       <rPr>
@@ -2923,156 +7261,11 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">:
-- Consume </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>useScreeningOverviewData(userId)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.
-- Select active array based on </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>activeTab: data[activeTab] || []</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.
-- Render a performant React Native </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>FlatList</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> using </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ScreeningOverviewCard</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> as </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>renderItem</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, using </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>item.id</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> as </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>keyExtractor</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.
+TypeScript
+export interface CustomConditionCardProps {
+  item: CustomConditionItem;
+  onPress: (item: CustomConditionItem) =&gt; void;
+}
 3. </t>
     </r>
     <r>
@@ -3084,875 +7277,207 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Pull-to-Refresh</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: Integrate </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>RefreshControl</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> into </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>FlatList</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> wired to TanStack Query’s </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>refetch()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> method with spinner tint </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>#00CED1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.
-4. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Strict Empty States (US 1.2–1.4 AC)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">:
-- When </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>data[activeTab].length === 0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, render an </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>EmptyState</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> component displaying the exact strings mandated by acceptance criteria:
-a. When </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>activeTab === 'upcoming'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"You don't have any upcoming screenings."</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-b. When </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>activeTab === 'due'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"You don't have any due screenings."</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-c. When </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>activeTab === 'completed'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"You don't have any completed screenings."</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-5. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Press Handler</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: On card press (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>onPress</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">), trigger Expo Router navigation to pass the screening item context: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>router.push({ pathname: '/health-screening', params: { id: item.id, type: item.screeningType } })</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
+      <t>Distinctive Custom Styling</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (US 18.4 AC 1, 2, 3):
+- Apply visual distinction from default system screenings while keeping structural layout identical: use a subtle teal/cyan border accent (border-l-4 border-l-[#00CED1] bg-white rounded-xl border border-gray-100 p-4 mb-3).
+- Display condition Name (item.conditionName) in Poppins-Medium and frequency (item.frequencyType, formatting custom interval if applicable, e.g., "Every 45 Days") as subtitle.
+- Display chevron-forward icon from @expo/vector-icons/Ionicons on the far right.
+4.  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Green Outcome Pill Badge Support</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (US 18.5 AC 6):
+- If item.latestRecordDate exists, render a soft green pill badge in the top-right corner of the card:
+a. Background #DCFCE7 (bg-green-100), text #15803D (text-green-800 text-xs font-psemibold px-2.5 py-1 rounded-full).
+b. Format string exactly as mandated: "Last: [Today's Logging Date]" (e.g., format(new Date(item.latestRecordDate), "'Last:' dd MMM yyyy")).</t>
     </r>
   </si>
   <si>
-    <t>1.1, 1.2, 1.3, 1.5</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Build ConfirmSpecificConditionModal.tsx Summary Dialog &amp; Connect TanStack Query Submission Mutation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1. Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/components/screening/ConfirmSpecificConditionModal.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, Modify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">checkupp-mobile/lib/features/screenings/mutations.ts
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>TanStack Query Mutation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (mutations.ts):
+- Implement useCreateCustomConditionMutation() calling apiClient.post('/me/screenings/custom-conditions', payload).
+- On success, invalidate query key ['screenings', 'custom-conditions'] and ['screenings', 'overview'].
+3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Build Confirmation Modal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (ConfirmSpecificConditionModal.tsx):
+- Render a centered popup modal displaying a clear summary of all entered fields: Condition Name, Monitoring Type, Frequency, and Care Provider.
+- Render two accessible CTA buttons (US 18.3 AC 3–5):
+a. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Primary</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Button: "Submit" (solid #00CED1 background). Clicking triggers mutate(formData). On success, close both the summary modal and bottom sheet, adding the new card to the list.
+b. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Secondary</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Button: "Back to Editing" (outlined button). Clicking closes ConfirmSpecificConditionModal while keeping AddSpecificConditionModal open with all form state preserved intact.</t>
+    </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Automated Jest Test Suite for "Your Health Overview" Navigation, Tabs &amp; Empty States
-1. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Create </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-mobile/tests/screenings/viewScreeningsOverview.test.js</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-2. Setup Jest test suite </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>using @testing-library/react-native</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.
-3. Mock </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>useScreeningOverviewData</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> hook to return controlled payloads:
-- Test Case 1: Asserts top tab labels render exact counts (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Upcoming (2)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Due (1)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Completed (0)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">).
-- Test Case 2: Asserts default active tab is </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Upcoming</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> and renders upcoming items.
-- Test Case 3: Simulates user tap on </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Due</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> tab -&gt; verifies overdue item renders the "</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>OVERDUE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">" badge and red styling class.
-- Test Case 4: Simulates empty list payloads -&gt; verifies exact strings </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>("You don't have any upcoming screenings."</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"You don't have any due screenings."</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"You don't have any completed screenings."</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>) appear without console warnings.</t>
-    </r>
-  </si>
-  <si>
-    <t>View Upcoming, Due, Completed screenings</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Extract Hardcoded "Your Health Overview" Section into a Standalone Component &amp; Import in Home Screen</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-- Create </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-mobile/components/home/HealthOverviewSection.tsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-- Modify </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-mobile/app/(tabs)/home.tsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-- Extract Component: Remove the entire JSX block under {/* Stats Overview */} from </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-mobile/app/(tabs)/home.tsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (the card displaying the "Your Health Overview" title, overviewStatus subtitle, completion percentage, and upcoming count).
-- Create a new modular, functional React Native component at </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-mobile/components/home/HealthOverviewSection.tsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.
-- Define TypeScript interface HealthOverviewSectionProps:
-TypeScript
-export interface HealthOverviewSectionProps {
-  overview: ScreeningOverviewData;  loading: boolean; refreshing: boolean; onPress: () =&gt; void; }
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Make Interactive</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: Wrap the outermost white card container (bg-white rounded-xl border border-gray-100) in a TouchableOpacity with activeOpacity={0.7} and assign onPress={onPress}.
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1" tint="4.9989318521683403E-2"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Add a visual affordance: Text - "See more" + subtle chevron-forward (&gt;) icon from </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1" tint="4.9989318521683403E-2"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>@expo/vector-icons/Ionicons</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1" tint="4.9989318521683403E-2"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, so users understand the card is tappable. Render this at the bottom of the card, aligned center.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-- Refactor Home Screen: In </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-mobile/app/(tabs)/home.tsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>import HealthOverviewSection from @/components/home/HealthOverviewSection</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.
-- Replace the extracted hardcoded block with:
-TypeScript
-&lt;HealthOverviewSection
-  overview={overview} loading={loading} refreshing={refreshing} onPress={() =&gt; router.push("/health-overview")} /&gt;
-- Ensure all responsive scaling utilities (scale, verticalScale, getFontSize, getSpacing) and NativeWind/Tailwind classes are imported cleanly in HealthOverviewSection.tsx with zero visual regression.</t>
-    </r>
+    <t>Needs Review</t>
   </si>
 </sst>
 </file>
@@ -5482,7 +9007,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L109"/>
+  <dimension ref="A1:L112"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.88671875" style="12" customWidth="1"/>
@@ -5549,7 +9074,7 @@
         <v>0.1</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E2" s="8" t="s">
         <v>16</v>
@@ -5573,7 +9098,7 @@
       <c r="K2" s="8"/>
       <c r="L2" s="8"/>
     </row>
-    <row r="3" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="408.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8">
         <v>2</v>
       </c>
@@ -5590,7 +9115,7 @@
         <v>21</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>22</v>
@@ -5608,7 +9133,7 @@
       <c r="K3" s="8"/>
       <c r="L3" s="8"/>
     </row>
-    <row r="4" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="408.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8">
         <v>3</v>
       </c>
@@ -5616,16 +9141,16 @@
         <v>26</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>23</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>25</v>
@@ -5643,7 +9168,7 @@
       <c r="K4" s="8"/>
       <c r="L4" s="8"/>
     </row>
-    <row r="5" spans="1:12" ht="381.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="408.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8">
         <v>4</v>
       </c>
@@ -5651,16 +9176,16 @@
         <v>26</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>25</v>
@@ -5679,68 +9204,60 @@
       <c r="L5" s="8"/>
     </row>
     <row r="6" spans="1:12" ht="331.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="8">
-        <v>5</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>42</v>
-      </c>
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8">
+        <v>1.6</v>
+      </c>
+      <c r="D6" s="8"/>
       <c r="E6" s="8" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I6" s="8" cm="1">
         <f t="array" ref="I6">_xlfn.SWITCH(H6,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>20</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="J6" s="8"/>
       <c r="K6" s="8"/>
       <c r="L6" s="8"/>
     </row>
-    <row r="7" spans="1:12" ht="403.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="272.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>26</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>22</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I7" s="8" cm="1">
         <f t="array" ref="I7">_xlfn.SWITCH(H7,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J7" s="8" t="s">
         <v>20</v>
@@ -5750,13 +9267,13 @@
     </row>
     <row r="8" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="8">
-        <v>1.2</v>
+      <c r="C8" s="8" t="s">
+        <v>42</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>29</v>
@@ -5765,17 +9282,17 @@
         <v>21</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I8" s="8" cm="1">
         <f t="array" ref="I8">_xlfn.SWITCH(H8,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J8" s="8" t="s">
         <v>20</v>
@@ -5783,15 +9300,15 @@
       <c r="K8" s="8"/>
       <c r="L8" s="8"/>
     </row>
-    <row r="9" spans="1:12" ht="403.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="8">
-        <v>1.1000000000000001</v>
+      <c r="C9" s="8" t="s">
+        <v>41</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>29</v>
@@ -5800,17 +9317,17 @@
         <v>21</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>30</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I9" s="8" cm="1">
         <f t="array" ref="I9">_xlfn.SWITCH(H9,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J9" s="8" t="s">
         <v>20</v>
@@ -5818,24 +9335,24 @@
       <c r="K9" s="8"/>
       <c r="L9" s="8"/>
     </row>
-    <row r="10" spans="1:12" ht="388.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="396" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>26</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>21</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>30</v>
@@ -5853,30 +9370,34 @@
       <c r="K10" s="8"/>
       <c r="L10" s="8"/>
     </row>
-    <row r="11" spans="1:12" ht="259.2" x14ac:dyDescent="0.3">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
+    <row r="11" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="8">
+        <v>9</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>26</v>
+      </c>
       <c r="C11" s="8" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>30</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I11" s="8" cm="1">
         <f t="array" ref="I11">_xlfn.SWITCH(H11,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J11" s="8" t="s">
         <v>20</v>
@@ -5884,239 +9405,387 @@
       <c r="K11" s="8"/>
       <c r="L11" s="8"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="408.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
+      <c r="C12" s="8" t="s">
+        <v>54</v>
+      </c>
       <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8" t="str" cm="1">
+      <c r="E12" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I12" s="8" cm="1">
         <f t="array" ref="I12">_xlfn.SWITCH(H12,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="J12" s="8"/>
       <c r="K12" s="8"/>
       <c r="L12" s="8"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
+      <c r="C13" s="8">
+        <v>1.8</v>
+      </c>
       <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8" t="str" cm="1">
+      <c r="E13" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I13" s="8" cm="1">
         <f t="array" ref="I13">_xlfn.SWITCH(H13,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="J13" s="8"/>
       <c r="K13" s="8"/>
       <c r="L13" s="8"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A14" s="8"/>
       <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8" t="str" cm="1">
+      <c r="C14" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="I14" s="8" cm="1">
         <f t="array" ref="I14">_xlfn.SWITCH(H14,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J14" s="8"/>
+        <v>5</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>20</v>
+      </c>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8" t="str" cm="1">
+      <c r="D15" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I15" s="8" cm="1">
         <f t="array" ref="I15">_xlfn.SWITCH(H15,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
+      <c r="K15" s="8" t="s">
+        <v>73</v>
+      </c>
       <c r="L15" s="8"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8" t="str" cm="1">
+      <c r="D16" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="I16" s="8" cm="1">
         <f t="array" ref="I16">_xlfn.SWITCH(H16,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
+      <c r="K16" s="8" t="s">
+        <v>73</v>
+      </c>
       <c r="L16" s="8"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
+      <c r="C17" s="8">
+        <v>18.5</v>
+      </c>
       <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8" t="str" cm="1">
+      <c r="E17" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="I17" s="8" cm="1">
         <f t="array" ref="I17">_xlfn.SWITCH(H17,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
+      <c r="K17" s="8" t="s">
+        <v>73</v>
+      </c>
       <c r="L17" s="8"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" ht="315.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="8"/>
       <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
+      <c r="C18" s="8" t="s">
+        <v>62</v>
+      </c>
       <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8" t="str" cm="1">
+      <c r="E18" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I18" s="8" cm="1">
         <f t="array" ref="I18">_xlfn.SWITCH(H18,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="J18" s="8"/>
       <c r="K18" s="8"/>
       <c r="L18" s="8"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" ht="383.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
+      <c r="C19" s="8">
+        <v>18.100000000000001</v>
+      </c>
       <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8" t="str" cm="1">
+      <c r="E19" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I19" s="8" cm="1">
         <f t="array" ref="I19">_xlfn.SWITCH(H19,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="J19" s="8"/>
       <c r="K19" s="8"/>
       <c r="L19" s="8"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
+      <c r="C20" s="8">
+        <v>18.2</v>
+      </c>
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8" t="str" cm="1">
+      <c r="F20" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="I20" s="8" cm="1">
         <f t="array" ref="I20">_xlfn.SWITCH(H20,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="J20" s="8"/>
       <c r="K20" s="8"/>
       <c r="L20" s="8"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" ht="360" x14ac:dyDescent="0.3">
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
+      <c r="C21" s="8">
+        <v>18.3</v>
+      </c>
       <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8" t="str" cm="1">
+      <c r="E21" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I21" s="8" cm="1">
         <f t="array" ref="I21">_xlfn.SWITCH(H21,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="J21" s="8"/>
       <c r="K21" s="8"/>
       <c r="L21" s="8"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" ht="409.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="8"/>
       <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
+      <c r="C22" s="8" t="s">
+        <v>69</v>
+      </c>
       <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8" t="str" cm="1">
+      <c r="E22" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I22" s="8" cm="1">
         <f t="array" ref="I22">_xlfn.SWITCH(H22,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="J22" s="8"/>
       <c r="K22" s="8"/>
       <c r="L22" s="8"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
+      <c r="C23" s="8">
+        <v>18.399999999999999</v>
+      </c>
       <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8" t="str" cm="1">
+      <c r="E23" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="I23" s="8" cm="1">
         <f t="array" ref="I23">_xlfn.SWITCH(H23,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="J23" s="8"/>
       <c r="K23" s="8"/>
       <c r="L23" s="8"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" ht="388.8" x14ac:dyDescent="0.3">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
+      <c r="C24" s="8">
+        <v>18.5</v>
+      </c>
       <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8" t="str" cm="1">
+      <c r="E24" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="I24" s="8" cm="1">
         <f t="array" ref="I24">_xlfn.SWITCH(H24,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="J24" s="8"/>
       <c r="K24" s="8"/>
       <c r="L24" s="8"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A25" s="8"/>
       <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
+      <c r="C25" s="8" t="s">
+        <v>62</v>
+      </c>
       <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8" t="str" cm="1">
+      <c r="E25" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="I25" s="8" cm="1">
         <f t="array" ref="I25">_xlfn.SWITCH(H25,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="J25" s="8"/>
       <c r="K25" s="8"/>
@@ -6196,7 +9865,7 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="7"/>
+      <c r="F30" s="10"/>
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
       <c r="I30" s="8" t="str" cm="1">
@@ -6213,7 +9882,7 @@
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
       <c r="E31" s="8"/>
-      <c r="F31" s="9"/>
+      <c r="F31" s="10"/>
       <c r="G31" s="8"/>
       <c r="H31" s="8"/>
       <c r="I31" s="8" t="str" cm="1">
@@ -6230,7 +9899,7 @@
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
       <c r="E32" s="8"/>
-      <c r="F32" s="9"/>
+      <c r="F32" s="10"/>
       <c r="G32" s="8"/>
       <c r="H32" s="8"/>
       <c r="I32" s="8" t="str" cm="1">
@@ -6247,7 +9916,7 @@
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
       <c r="E33" s="8"/>
-      <c r="F33" s="9"/>
+      <c r="F33" s="7"/>
       <c r="G33" s="8"/>
       <c r="H33" s="8"/>
       <c r="I33" s="8" t="str" cm="1">
@@ -6502,7 +10171,7 @@
       <c r="C48" s="8"/>
       <c r="D48" s="8"/>
       <c r="E48" s="8"/>
-      <c r="F48" s="10"/>
+      <c r="F48" s="9"/>
       <c r="G48" s="8"/>
       <c r="H48" s="8"/>
       <c r="I48" s="8" t="str" cm="1">
@@ -6519,7 +10188,7 @@
       <c r="C49" s="8"/>
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
-      <c r="F49" s="10"/>
+      <c r="F49" s="9"/>
       <c r="G49" s="8"/>
       <c r="H49" s="8"/>
       <c r="I49" s="8" t="str" cm="1">
@@ -6536,7 +10205,7 @@
       <c r="C50" s="8"/>
       <c r="D50" s="8"/>
       <c r="E50" s="8"/>
-      <c r="F50" s="10"/>
+      <c r="F50" s="9"/>
       <c r="G50" s="8"/>
       <c r="H50" s="8"/>
       <c r="I50" s="8" t="str" cm="1">
@@ -6604,7 +10273,7 @@
       <c r="C54" s="8"/>
       <c r="D54" s="8"/>
       <c r="E54" s="8"/>
-      <c r="F54" s="9"/>
+      <c r="F54" s="10"/>
       <c r="G54" s="8"/>
       <c r="H54" s="8"/>
       <c r="I54" s="8" t="str" cm="1">
@@ -6621,7 +10290,7 @@
       <c r="C55" s="8"/>
       <c r="D55" s="8"/>
       <c r="E55" s="8"/>
-      <c r="F55" s="9"/>
+      <c r="F55" s="10"/>
       <c r="G55" s="8"/>
       <c r="H55" s="8"/>
       <c r="I55" s="8" t="str" cm="1">
@@ -6638,7 +10307,7 @@
       <c r="C56" s="8"/>
       <c r="D56" s="8"/>
       <c r="E56" s="8"/>
-      <c r="F56" s="9"/>
+      <c r="F56" s="10"/>
       <c r="G56" s="8"/>
       <c r="H56" s="8"/>
       <c r="I56" s="8" t="str" cm="1">
@@ -6791,7 +10460,7 @@
       <c r="C65" s="8"/>
       <c r="D65" s="8"/>
       <c r="E65" s="8"/>
-      <c r="F65" s="7"/>
+      <c r="F65" s="9"/>
       <c r="G65" s="8"/>
       <c r="H65" s="8"/>
       <c r="I65" s="8" t="str" cm="1">
@@ -6825,7 +10494,7 @@
       <c r="C67" s="8"/>
       <c r="D67" s="8"/>
       <c r="E67" s="8"/>
-      <c r="F67" s="7"/>
+      <c r="F67" s="9"/>
       <c r="G67" s="8"/>
       <c r="H67" s="8"/>
       <c r="I67" s="8" t="str" cm="1">
@@ -6876,7 +10545,7 @@
       <c r="C70" s="8"/>
       <c r="D70" s="8"/>
       <c r="E70" s="8"/>
-      <c r="F70" s="9"/>
+      <c r="F70" s="7"/>
       <c r="G70" s="8"/>
       <c r="H70" s="8"/>
       <c r="I70" s="8" t="str" cm="1">
@@ -6893,7 +10562,7 @@
       <c r="C71" s="8"/>
       <c r="D71" s="8"/>
       <c r="E71" s="8"/>
-      <c r="F71" s="9"/>
+      <c r="F71" s="7"/>
       <c r="G71" s="8"/>
       <c r="H71" s="8"/>
       <c r="I71" s="8" t="str" cm="1">
@@ -6944,7 +10613,7 @@
       <c r="C74" s="8"/>
       <c r="D74" s="8"/>
       <c r="E74" s="8"/>
-      <c r="F74" s="10"/>
+      <c r="F74" s="9"/>
       <c r="G74" s="8"/>
       <c r="H74" s="8"/>
       <c r="I74" s="8" t="str" cm="1">
@@ -6961,7 +10630,7 @@
       <c r="C75" s="8"/>
       <c r="D75" s="8"/>
       <c r="E75" s="8"/>
-      <c r="F75" s="10"/>
+      <c r="F75" s="9"/>
       <c r="G75" s="8"/>
       <c r="H75" s="8"/>
       <c r="I75" s="8" t="str" cm="1">
@@ -6978,7 +10647,7 @@
       <c r="C76" s="8"/>
       <c r="D76" s="8"/>
       <c r="E76" s="8"/>
-      <c r="F76" s="10"/>
+      <c r="F76" s="9"/>
       <c r="G76" s="8"/>
       <c r="H76" s="8"/>
       <c r="I76" s="8" t="str" cm="1">
@@ -7550,8 +11219,59 @@
       <c r="K109" s="8"/>
       <c r="L109" s="8"/>
     </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A110" s="8"/>
+      <c r="B110" s="8"/>
+      <c r="C110" s="8"/>
+      <c r="D110" s="8"/>
+      <c r="E110" s="8"/>
+      <c r="F110" s="10"/>
+      <c r="G110" s="8"/>
+      <c r="H110" s="8"/>
+      <c r="I110" s="8" t="str" cm="1">
+        <f t="array" ref="I110">_xlfn.SWITCH(H110,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J110" s="8"/>
+      <c r="K110" s="8"/>
+      <c r="L110" s="8"/>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A111" s="8"/>
+      <c r="B111" s="8"/>
+      <c r="C111" s="8"/>
+      <c r="D111" s="8"/>
+      <c r="E111" s="8"/>
+      <c r="F111" s="10"/>
+      <c r="G111" s="8"/>
+      <c r="H111" s="8"/>
+      <c r="I111" s="8" t="str" cm="1">
+        <f t="array" ref="I111">_xlfn.SWITCH(H111,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J111" s="8"/>
+      <c r="K111" s="8"/>
+      <c r="L111" s="8"/>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A112" s="8"/>
+      <c r="B112" s="8"/>
+      <c r="C112" s="8"/>
+      <c r="D112" s="8"/>
+      <c r="E112" s="8"/>
+      <c r="F112" s="10"/>
+      <c r="G112" s="8"/>
+      <c r="H112" s="8"/>
+      <c r="I112" s="8" t="str" cm="1">
+        <f t="array" ref="I112">_xlfn.SWITCH(H112,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J112" s="8"/>
+      <c r="K112" s="8"/>
+      <c r="L112" s="8"/>
+    </row>
   </sheetData>
-  <autoFilter ref="E1:E120" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="E1:E123" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Business Analysis/checkupp_sprint_plan_2026.xlsx
+++ b/Business Analysis/checkupp_sprint_plan_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Business Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{980E1814-A99E-4A7D-BC2B-A55986CEA89F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93CF3DE5-ED11-4C57-B392-47B92705B402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9007,7 +9007,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L112"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:L123"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.88671875" style="12" customWidth="1"/>
@@ -9063,7 +9064,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="49.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="49.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="8">
         <v>1</v>
       </c>
@@ -9098,7 +9099,7 @@
       <c r="K2" s="8"/>
       <c r="L2" s="8"/>
     </row>
-    <row r="3" spans="1:12" ht="408.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="408.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8">
         <v>2</v>
       </c>
@@ -9133,7 +9134,7 @@
       <c r="K3" s="8"/>
       <c r="L3" s="8"/>
     </row>
-    <row r="4" spans="1:12" ht="408.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="408.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8">
         <v>3</v>
       </c>
@@ -9168,7 +9169,7 @@
       <c r="K4" s="8"/>
       <c r="L4" s="8"/>
     </row>
-    <row r="5" spans="1:12" ht="408.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="408.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8">
         <v>4</v>
       </c>
@@ -9203,7 +9204,7 @@
       <c r="K5" s="8"/>
       <c r="L5" s="8"/>
     </row>
-    <row r="6" spans="1:12" ht="331.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="331.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8">
@@ -9250,7 +9251,7 @@
         <v>48</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="H7" s="8" t="s">
         <v>28</v>
@@ -9265,7 +9266,7 @@
       <c r="K7" s="8"/>
       <c r="L7" s="8"/>
     </row>
-    <row r="8" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
         <v>6</v>
       </c>
@@ -9300,7 +9301,7 @@
       <c r="K8" s="8"/>
       <c r="L8" s="8"/>
     </row>
-    <row r="9" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
         <v>7</v>
       </c>
@@ -9335,7 +9336,7 @@
       <c r="K9" s="8"/>
       <c r="L9" s="8"/>
     </row>
-    <row r="10" spans="1:12" ht="396" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="396" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
         <v>8</v>
       </c>
@@ -9370,7 +9371,7 @@
       <c r="K10" s="8"/>
       <c r="L10" s="8"/>
     </row>
-    <row r="11" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8">
         <v>9</v>
       </c>
@@ -9405,7 +9406,7 @@
       <c r="K11" s="8"/>
       <c r="L11" s="8"/>
     </row>
-    <row r="12" spans="1:12" ht="408.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="408.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="8" t="s">
@@ -9432,7 +9433,7 @@
       <c r="K12" s="8"/>
       <c r="L12" s="8"/>
     </row>
-    <row r="13" spans="1:12" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="302.39999999999998" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="8">
@@ -9490,7 +9491,7 @@
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
     </row>
-    <row r="15" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -9519,7 +9520,7 @@
       </c>
       <c r="L15" s="8"/>
     </row>
-    <row r="16" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
@@ -9548,7 +9549,7 @@
       </c>
       <c r="L16" s="8"/>
     </row>
-    <row r="17" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
       <c r="C17" s="8">
@@ -9604,7 +9605,7 @@
       <c r="K18" s="8"/>
       <c r="L18" s="8"/>
     </row>
-    <row r="19" spans="1:12" ht="383.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" ht="383.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="8">
@@ -9631,7 +9632,7 @@
       <c r="K19" s="8"/>
       <c r="L19" s="8"/>
     </row>
-    <row r="20" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="8">
@@ -9656,7 +9657,7 @@
       <c r="K20" s="8"/>
       <c r="L20" s="8"/>
     </row>
-    <row r="21" spans="1:12" ht="360" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" ht="360" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
       <c r="C21" s="8">
@@ -9683,7 +9684,7 @@
       <c r="K21" s="8"/>
       <c r="L21" s="8"/>
     </row>
-    <row r="22" spans="1:12" ht="409.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" ht="409.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="8"/>
       <c r="B22" s="8"/>
       <c r="C22" s="8" t="s">
@@ -9710,7 +9711,7 @@
       <c r="K22" s="8"/>
       <c r="L22" s="8"/>
     </row>
-    <row r="23" spans="1:12" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" ht="302.39999999999998" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8">
@@ -9737,7 +9738,7 @@
       <c r="K23" s="8"/>
       <c r="L23" s="8"/>
     </row>
-    <row r="24" spans="1:12" ht="388.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" ht="388.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8">
@@ -9791,7 +9792,7 @@
       <c r="K25" s="8"/>
       <c r="L25" s="8"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -9808,7 +9809,7 @@
       <c r="K26" s="8"/>
       <c r="L26" s="8"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
@@ -9825,7 +9826,7 @@
       <c r="K27" s="8"/>
       <c r="L27" s="8"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
@@ -9842,7 +9843,7 @@
       <c r="K28" s="8"/>
       <c r="L28" s="8"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
@@ -9859,7 +9860,7 @@
       <c r="K29" s="8"/>
       <c r="L29" s="8"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="8"/>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
@@ -9876,7 +9877,7 @@
       <c r="K30" s="8"/>
       <c r="L30" s="8"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="8"/>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
@@ -9893,7 +9894,7 @@
       <c r="K31" s="8"/>
       <c r="L31" s="8"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="8"/>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
@@ -9910,7 +9911,7 @@
       <c r="K32" s="8"/>
       <c r="L32" s="8"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="8"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
@@ -9927,7 +9928,7 @@
       <c r="K33" s="8"/>
       <c r="L33" s="8"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="8"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -9944,7 +9945,7 @@
       <c r="K34" s="8"/>
       <c r="L34" s="8"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="8"/>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
@@ -9961,7 +9962,7 @@
       <c r="K35" s="8"/>
       <c r="L35" s="8"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="8"/>
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
@@ -9978,7 +9979,7 @@
       <c r="K36" s="8"/>
       <c r="L36" s="8"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
@@ -9995,7 +9996,7 @@
       <c r="K37" s="8"/>
       <c r="L37" s="8"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="8"/>
       <c r="B38" s="8"/>
       <c r="C38" s="8"/>
@@ -10012,7 +10013,7 @@
       <c r="K38" s="8"/>
       <c r="L38" s="8"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="8"/>
       <c r="B39" s="8"/>
       <c r="C39" s="8"/>
@@ -10029,7 +10030,7 @@
       <c r="K39" s="8"/>
       <c r="L39" s="8"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="8"/>
       <c r="B40" s="8"/>
       <c r="C40" s="8"/>
@@ -10046,7 +10047,7 @@
       <c r="K40" s="8"/>
       <c r="L40" s="8"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="8"/>
       <c r="B41" s="8"/>
       <c r="C41" s="8"/>
@@ -10063,7 +10064,7 @@
       <c r="K41" s="8"/>
       <c r="L41" s="8"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="8"/>
       <c r="B42" s="8"/>
       <c r="C42" s="8"/>
@@ -10080,7 +10081,7 @@
       <c r="K42" s="8"/>
       <c r="L42" s="8"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="8"/>
       <c r="B43" s="8"/>
       <c r="C43" s="8"/>
@@ -10097,7 +10098,7 @@
       <c r="K43" s="8"/>
       <c r="L43" s="8"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="8"/>
       <c r="B44" s="8"/>
       <c r="C44" s="8"/>
@@ -10114,7 +10115,7 @@
       <c r="K44" s="8"/>
       <c r="L44" s="8"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="8"/>
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
@@ -10131,7 +10132,7 @@
       <c r="K45" s="8"/>
       <c r="L45" s="8"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="8"/>
       <c r="B46" s="8"/>
       <c r="C46" s="8"/>
@@ -10148,7 +10149,7 @@
       <c r="K46" s="8"/>
       <c r="L46" s="8"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="8"/>
       <c r="B47" s="8"/>
       <c r="C47" s="8"/>
@@ -10165,7 +10166,7 @@
       <c r="K47" s="8"/>
       <c r="L47" s="8"/>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="8"/>
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
@@ -10182,7 +10183,7 @@
       <c r="K48" s="8"/>
       <c r="L48" s="8"/>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="8"/>
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
@@ -10199,7 +10200,7 @@
       <c r="K49" s="8"/>
       <c r="L49" s="8"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="8"/>
       <c r="B50" s="8"/>
       <c r="C50" s="8"/>
@@ -10216,7 +10217,7 @@
       <c r="K50" s="8"/>
       <c r="L50" s="8"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="8"/>
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
@@ -10233,7 +10234,7 @@
       <c r="K51" s="8"/>
       <c r="L51" s="8"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="8"/>
       <c r="B52" s="8"/>
       <c r="C52" s="8"/>
@@ -10250,7 +10251,7 @@
       <c r="K52" s="8"/>
       <c r="L52" s="8"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="8"/>
       <c r="B53" s="8"/>
       <c r="C53" s="8"/>
@@ -10267,7 +10268,7 @@
       <c r="K53" s="8"/>
       <c r="L53" s="8"/>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="8"/>
       <c r="B54" s="8"/>
       <c r="C54" s="8"/>
@@ -10284,7 +10285,7 @@
       <c r="K54" s="8"/>
       <c r="L54" s="8"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="8"/>
       <c r="B55" s="8"/>
       <c r="C55" s="8"/>
@@ -10301,7 +10302,7 @@
       <c r="K55" s="8"/>
       <c r="L55" s="8"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="8"/>
       <c r="B56" s="8"/>
       <c r="C56" s="8"/>
@@ -10318,7 +10319,7 @@
       <c r="K56" s="8"/>
       <c r="L56" s="8"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="8"/>
       <c r="B57" s="8"/>
       <c r="C57" s="8"/>
@@ -10335,7 +10336,7 @@
       <c r="K57" s="8"/>
       <c r="L57" s="8"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="8"/>
       <c r="B58" s="8"/>
       <c r="C58" s="8"/>
@@ -10352,7 +10353,7 @@
       <c r="K58" s="8"/>
       <c r="L58" s="8"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="8"/>
       <c r="B59" s="8"/>
       <c r="C59" s="8"/>
@@ -10369,7 +10370,7 @@
       <c r="K59" s="8"/>
       <c r="L59" s="8"/>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="8"/>
       <c r="B60" s="8"/>
       <c r="C60" s="8"/>
@@ -10386,7 +10387,7 @@
       <c r="K60" s="8"/>
       <c r="L60" s="8"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="8"/>
       <c r="B61" s="8"/>
       <c r="C61" s="8"/>
@@ -10403,7 +10404,7 @@
       <c r="K61" s="8"/>
       <c r="L61" s="8"/>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="8"/>
       <c r="B62" s="8"/>
       <c r="C62" s="8"/>
@@ -10420,7 +10421,7 @@
       <c r="K62" s="8"/>
       <c r="L62" s="8"/>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="8"/>
       <c r="B63" s="8"/>
       <c r="C63" s="8"/>
@@ -10437,7 +10438,7 @@
       <c r="K63" s="8"/>
       <c r="L63" s="8"/>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="8"/>
       <c r="B64" s="8"/>
       <c r="C64" s="8"/>
@@ -10454,7 +10455,7 @@
       <c r="K64" s="8"/>
       <c r="L64" s="8"/>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="8"/>
       <c r="B65" s="8"/>
       <c r="C65" s="8"/>
@@ -10471,7 +10472,7 @@
       <c r="K65" s="8"/>
       <c r="L65" s="8"/>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="8"/>
       <c r="B66" s="8"/>
       <c r="C66" s="8"/>
@@ -10488,7 +10489,7 @@
       <c r="K66" s="8"/>
       <c r="L66" s="8"/>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="8"/>
       <c r="B67" s="8"/>
       <c r="C67" s="8"/>
@@ -10505,7 +10506,7 @@
       <c r="K67" s="8"/>
       <c r="L67" s="8"/>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="8"/>
       <c r="B68" s="8"/>
       <c r="C68" s="8"/>
@@ -10522,7 +10523,7 @@
       <c r="K68" s="8"/>
       <c r="L68" s="8"/>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="8"/>
       <c r="B69" s="8"/>
       <c r="C69" s="8"/>
@@ -10539,7 +10540,7 @@
       <c r="K69" s="8"/>
       <c r="L69" s="8"/>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="8"/>
       <c r="B70" s="8"/>
       <c r="C70" s="8"/>
@@ -10556,7 +10557,7 @@
       <c r="K70" s="8"/>
       <c r="L70" s="8"/>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="8"/>
       <c r="B71" s="8"/>
       <c r="C71" s="8"/>
@@ -10573,7 +10574,7 @@
       <c r="K71" s="8"/>
       <c r="L71" s="8"/>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="8"/>
       <c r="B72" s="8"/>
       <c r="C72" s="8"/>
@@ -10590,7 +10591,7 @@
       <c r="K72" s="8"/>
       <c r="L72" s="8"/>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="8"/>
       <c r="B73" s="8"/>
       <c r="C73" s="8"/>
@@ -10607,7 +10608,7 @@
       <c r="K73" s="8"/>
       <c r="L73" s="8"/>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="8"/>
       <c r="B74" s="8"/>
       <c r="C74" s="8"/>
@@ -10624,7 +10625,7 @@
       <c r="K74" s="8"/>
       <c r="L74" s="8"/>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="8"/>
       <c r="B75" s="8"/>
       <c r="C75" s="8"/>
@@ -10641,7 +10642,7 @@
       <c r="K75" s="8"/>
       <c r="L75" s="8"/>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="8"/>
       <c r="B76" s="8"/>
       <c r="C76" s="8"/>
@@ -10658,7 +10659,7 @@
       <c r="K76" s="8"/>
       <c r="L76" s="8"/>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="8"/>
       <c r="B77" s="8"/>
       <c r="C77" s="8"/>
@@ -10675,7 +10676,7 @@
       <c r="K77" s="8"/>
       <c r="L77" s="8"/>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="8"/>
       <c r="B78" s="8"/>
       <c r="C78" s="8"/>
@@ -10692,7 +10693,7 @@
       <c r="K78" s="8"/>
       <c r="L78" s="8"/>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="8"/>
       <c r="B79" s="8"/>
       <c r="C79" s="8"/>
@@ -10709,7 +10710,7 @@
       <c r="K79" s="8"/>
       <c r="L79" s="8"/>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="8"/>
       <c r="B80" s="8"/>
       <c r="C80" s="8"/>
@@ -10726,7 +10727,7 @@
       <c r="K80" s="8"/>
       <c r="L80" s="8"/>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="8"/>
       <c r="B81" s="8"/>
       <c r="C81" s="8"/>
@@ -10743,7 +10744,7 @@
       <c r="K81" s="8"/>
       <c r="L81" s="8"/>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="8"/>
       <c r="B82" s="8"/>
       <c r="C82" s="8"/>
@@ -10760,7 +10761,7 @@
       <c r="K82" s="8"/>
       <c r="L82" s="8"/>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="8"/>
       <c r="B83" s="8"/>
       <c r="C83" s="8"/>
@@ -10777,7 +10778,7 @@
       <c r="K83" s="8"/>
       <c r="L83" s="8"/>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="8"/>
       <c r="B84" s="8"/>
       <c r="C84" s="8"/>
@@ -10794,7 +10795,7 @@
       <c r="K84" s="8"/>
       <c r="L84" s="8"/>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="8"/>
       <c r="B85" s="8"/>
       <c r="C85" s="8"/>
@@ -10811,7 +10812,7 @@
       <c r="K85" s="8"/>
       <c r="L85" s="8"/>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="8"/>
       <c r="B86" s="8"/>
       <c r="C86" s="8"/>
@@ -10828,7 +10829,7 @@
       <c r="K86" s="8"/>
       <c r="L86" s="8"/>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="8"/>
       <c r="B87" s="8"/>
       <c r="C87" s="8"/>
@@ -10845,7 +10846,7 @@
       <c r="K87" s="8"/>
       <c r="L87" s="8"/>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="8"/>
       <c r="B88" s="8"/>
       <c r="C88" s="8"/>
@@ -10862,7 +10863,7 @@
       <c r="K88" s="8"/>
       <c r="L88" s="8"/>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="8"/>
       <c r="B89" s="8"/>
       <c r="C89" s="8"/>
@@ -10879,7 +10880,7 @@
       <c r="K89" s="8"/>
       <c r="L89" s="8"/>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="8"/>
       <c r="B90" s="8"/>
       <c r="C90" s="8"/>
@@ -10896,7 +10897,7 @@
       <c r="K90" s="8"/>
       <c r="L90" s="8"/>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="8"/>
       <c r="B91" s="8"/>
       <c r="C91" s="8"/>
@@ -10913,7 +10914,7 @@
       <c r="K91" s="8"/>
       <c r="L91" s="8"/>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="8"/>
       <c r="B92" s="8"/>
       <c r="C92" s="8"/>
@@ -10930,7 +10931,7 @@
       <c r="K92" s="8"/>
       <c r="L92" s="8"/>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="8"/>
       <c r="B93" s="8"/>
       <c r="C93" s="8"/>
@@ -10947,7 +10948,7 @@
       <c r="K93" s="8"/>
       <c r="L93" s="8"/>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="8"/>
       <c r="B94" s="8"/>
       <c r="C94" s="8"/>
@@ -10964,7 +10965,7 @@
       <c r="K94" s="8"/>
       <c r="L94" s="8"/>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="8"/>
       <c r="B95" s="8"/>
       <c r="C95" s="8"/>
@@ -10981,7 +10982,7 @@
       <c r="K95" s="8"/>
       <c r="L95" s="8"/>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="8"/>
       <c r="B96" s="8"/>
       <c r="C96" s="8"/>
@@ -10998,7 +10999,7 @@
       <c r="K96" s="8"/>
       <c r="L96" s="8"/>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="8"/>
       <c r="B97" s="8"/>
       <c r="C97" s="8"/>
@@ -11015,7 +11016,7 @@
       <c r="K97" s="8"/>
       <c r="L97" s="8"/>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="8"/>
       <c r="B98" s="8"/>
       <c r="C98" s="8"/>
@@ -11032,7 +11033,7 @@
       <c r="K98" s="8"/>
       <c r="L98" s="8"/>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="8"/>
       <c r="B99" s="8"/>
       <c r="C99" s="8"/>
@@ -11049,7 +11050,7 @@
       <c r="K99" s="8"/>
       <c r="L99" s="8"/>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="8"/>
       <c r="B100" s="8"/>
       <c r="C100" s="8"/>
@@ -11066,7 +11067,7 @@
       <c r="K100" s="8"/>
       <c r="L100" s="8"/>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="8"/>
       <c r="B101" s="8"/>
       <c r="C101" s="8"/>
@@ -11083,7 +11084,7 @@
       <c r="K101" s="8"/>
       <c r="L101" s="8"/>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="8"/>
       <c r="B102" s="8"/>
       <c r="C102" s="8"/>
@@ -11100,7 +11101,7 @@
       <c r="K102" s="8"/>
       <c r="L102" s="8"/>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="8"/>
       <c r="B103" s="8"/>
       <c r="C103" s="8"/>
@@ -11117,7 +11118,7 @@
       <c r="K103" s="8"/>
       <c r="L103" s="8"/>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="8"/>
       <c r="B104" s="8"/>
       <c r="C104" s="8"/>
@@ -11134,7 +11135,7 @@
       <c r="K104" s="8"/>
       <c r="L104" s="8"/>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="8"/>
       <c r="B105" s="8"/>
       <c r="C105" s="8"/>
@@ -11151,7 +11152,7 @@
       <c r="K105" s="8"/>
       <c r="L105" s="8"/>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="8"/>
       <c r="B106" s="8"/>
       <c r="C106" s="8"/>
@@ -11168,7 +11169,7 @@
       <c r="K106" s="8"/>
       <c r="L106" s="8"/>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="8"/>
       <c r="B107" s="8"/>
       <c r="C107" s="8"/>
@@ -11185,7 +11186,7 @@
       <c r="K107" s="8"/>
       <c r="L107" s="8"/>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="8"/>
       <c r="B108" s="8"/>
       <c r="C108" s="8"/>
@@ -11202,7 +11203,7 @@
       <c r="K108" s="8"/>
       <c r="L108" s="8"/>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="8"/>
       <c r="B109" s="8"/>
       <c r="C109" s="8"/>
@@ -11219,7 +11220,7 @@
       <c r="K109" s="8"/>
       <c r="L109" s="8"/>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="8"/>
       <c r="B110" s="8"/>
       <c r="C110" s="8"/>
@@ -11236,7 +11237,7 @@
       <c r="K110" s="8"/>
       <c r="L110" s="8"/>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="8"/>
       <c r="B111" s="8"/>
       <c r="C111" s="8"/>
@@ -11253,7 +11254,7 @@
       <c r="K111" s="8"/>
       <c r="L111" s="8"/>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="8"/>
       <c r="B112" s="8"/>
       <c r="C112" s="8"/>
@@ -11270,8 +11271,25 @@
       <c r="K112" s="8"/>
       <c r="L112" s="8"/>
     </row>
+    <row r="113" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="114" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="115" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="116" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="117" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="118" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="119" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="120" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="121" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="122" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="123" hidden="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <autoFilter ref="E1:E123" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="E1:E123" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Test"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Business Analysis/checkupp_sprint_plan_2026.xlsx
+++ b/Business Analysis/checkupp_sprint_plan_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Business Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93CF3DE5-ED11-4C57-B392-47B92705B402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A5E8C5E-172E-4994-8F25-E5413AB277D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9007,8 +9007,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:L123"/>
+  <dimension ref="A1:L112"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.88671875" style="12" customWidth="1"/>
@@ -9064,7 +9063,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="49.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="49.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="8">
         <v>1</v>
       </c>
@@ -9099,7 +9098,7 @@
       <c r="K2" s="8"/>
       <c r="L2" s="8"/>
     </row>
-    <row r="3" spans="1:12" ht="408.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="408.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8">
         <v>2</v>
       </c>
@@ -9134,7 +9133,7 @@
       <c r="K3" s="8"/>
       <c r="L3" s="8"/>
     </row>
-    <row r="4" spans="1:12" ht="408.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="408.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8">
         <v>3</v>
       </c>
@@ -9169,7 +9168,7 @@
       <c r="K4" s="8"/>
       <c r="L4" s="8"/>
     </row>
-    <row r="5" spans="1:12" ht="408.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="408.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8">
         <v>4</v>
       </c>
@@ -9204,7 +9203,7 @@
       <c r="K5" s="8"/>
       <c r="L5" s="8"/>
     </row>
-    <row r="6" spans="1:12" ht="331.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A6" s="8"/>
       <c r="B6" s="8"/>
       <c r="C6" s="8">
@@ -9266,7 +9265,7 @@
       <c r="K7" s="8"/>
       <c r="L7" s="8"/>
     </row>
-    <row r="8" spans="1:12" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
         <v>6</v>
       </c>
@@ -9301,7 +9300,7 @@
       <c r="K8" s="8"/>
       <c r="L8" s="8"/>
     </row>
-    <row r="9" spans="1:12" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
         <v>7</v>
       </c>
@@ -9336,7 +9335,7 @@
       <c r="K9" s="8"/>
       <c r="L9" s="8"/>
     </row>
-    <row r="10" spans="1:12" ht="396" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="396" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
         <v>8</v>
       </c>
@@ -9371,7 +9370,7 @@
       <c r="K10" s="8"/>
       <c r="L10" s="8"/>
     </row>
-    <row r="11" spans="1:12" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A11" s="8">
         <v>9</v>
       </c>
@@ -9406,7 +9405,7 @@
       <c r="K11" s="8"/>
       <c r="L11" s="8"/>
     </row>
-    <row r="12" spans="1:12" ht="408.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="408.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8"/>
       <c r="B12" s="8"/>
       <c r="C12" s="8" t="s">
@@ -9433,7 +9432,7 @@
       <c r="K12" s="8"/>
       <c r="L12" s="8"/>
     </row>
-    <row r="13" spans="1:12" ht="302.39999999999998" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A13" s="8"/>
       <c r="B13" s="8"/>
       <c r="C13" s="8">
@@ -9491,7 +9490,7 @@
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
     </row>
-    <row r="15" spans="1:12" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A15" s="8"/>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
@@ -9520,7 +9519,7 @@
       </c>
       <c r="L15" s="8"/>
     </row>
-    <row r="16" spans="1:12" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
@@ -9549,7 +9548,7 @@
       </c>
       <c r="L16" s="8"/>
     </row>
-    <row r="17" spans="1:12" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A17" s="8"/>
       <c r="B17" s="8"/>
       <c r="C17" s="8">
@@ -9605,7 +9604,7 @@
       <c r="K18" s="8"/>
       <c r="L18" s="8"/>
     </row>
-    <row r="19" spans="1:12" ht="383.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" ht="383.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8"/>
       <c r="B19" s="8"/>
       <c r="C19" s="8">
@@ -9632,7 +9631,7 @@
       <c r="K19" s="8"/>
       <c r="L19" s="8"/>
     </row>
-    <row r="20" spans="1:12" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A20" s="8"/>
       <c r="B20" s="8"/>
       <c r="C20" s="8">
@@ -9657,7 +9656,7 @@
       <c r="K20" s="8"/>
       <c r="L20" s="8"/>
     </row>
-    <row r="21" spans="1:12" ht="360" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" ht="360" x14ac:dyDescent="0.3">
       <c r="A21" s="8"/>
       <c r="B21" s="8"/>
       <c r="C21" s="8">
@@ -9684,7 +9683,7 @@
       <c r="K21" s="8"/>
       <c r="L21" s="8"/>
     </row>
-    <row r="22" spans="1:12" ht="409.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" ht="409.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="8"/>
       <c r="B22" s="8"/>
       <c r="C22" s="8" t="s">
@@ -9711,7 +9710,7 @@
       <c r="K22" s="8"/>
       <c r="L22" s="8"/>
     </row>
-    <row r="23" spans="1:12" ht="302.39999999999998" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A23" s="8"/>
       <c r="B23" s="8"/>
       <c r="C23" s="8">
@@ -9738,7 +9737,7 @@
       <c r="K23" s="8"/>
       <c r="L23" s="8"/>
     </row>
-    <row r="24" spans="1:12" ht="388.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" ht="388.8" x14ac:dyDescent="0.3">
       <c r="A24" s="8"/>
       <c r="B24" s="8"/>
       <c r="C24" s="8">
@@ -9792,7 +9791,7 @@
       <c r="K25" s="8"/>
       <c r="L25" s="8"/>
     </row>
-    <row r="26" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -9809,7 +9808,7 @@
       <c r="K26" s="8"/>
       <c r="L26" s="8"/>
     </row>
-    <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
@@ -9826,7 +9825,7 @@
       <c r="K27" s="8"/>
       <c r="L27" s="8"/>
     </row>
-    <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
@@ -9843,7 +9842,7 @@
       <c r="K28" s="8"/>
       <c r="L28" s="8"/>
     </row>
-    <row r="29" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
@@ -9860,7 +9859,7 @@
       <c r="K29" s="8"/>
       <c r="L29" s="8"/>
     </row>
-    <row r="30" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="8"/>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
@@ -9877,7 +9876,7 @@
       <c r="K30" s="8"/>
       <c r="L30" s="8"/>
     </row>
-    <row r="31" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="8"/>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
@@ -9894,7 +9893,7 @@
       <c r="K31" s="8"/>
       <c r="L31" s="8"/>
     </row>
-    <row r="32" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="8"/>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
@@ -9911,7 +9910,7 @@
       <c r="K32" s="8"/>
       <c r="L32" s="8"/>
     </row>
-    <row r="33" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="8"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
@@ -9928,7 +9927,7 @@
       <c r="K33" s="8"/>
       <c r="L33" s="8"/>
     </row>
-    <row r="34" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="8"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -9945,7 +9944,7 @@
       <c r="K34" s="8"/>
       <c r="L34" s="8"/>
     </row>
-    <row r="35" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="8"/>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
@@ -9962,7 +9961,7 @@
       <c r="K35" s="8"/>
       <c r="L35" s="8"/>
     </row>
-    <row r="36" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="8"/>
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
@@ -9979,7 +9978,7 @@
       <c r="K36" s="8"/>
       <c r="L36" s="8"/>
     </row>
-    <row r="37" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
@@ -9996,7 +9995,7 @@
       <c r="K37" s="8"/>
       <c r="L37" s="8"/>
     </row>
-    <row r="38" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="8"/>
       <c r="B38" s="8"/>
       <c r="C38" s="8"/>
@@ -10013,7 +10012,7 @@
       <c r="K38" s="8"/>
       <c r="L38" s="8"/>
     </row>
-    <row r="39" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="8"/>
       <c r="B39" s="8"/>
       <c r="C39" s="8"/>
@@ -10030,7 +10029,7 @@
       <c r="K39" s="8"/>
       <c r="L39" s="8"/>
     </row>
-    <row r="40" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="8"/>
       <c r="B40" s="8"/>
       <c r="C40" s="8"/>
@@ -10047,7 +10046,7 @@
       <c r="K40" s="8"/>
       <c r="L40" s="8"/>
     </row>
-    <row r="41" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="8"/>
       <c r="B41" s="8"/>
       <c r="C41" s="8"/>
@@ -10064,7 +10063,7 @@
       <c r="K41" s="8"/>
       <c r="L41" s="8"/>
     </row>
-    <row r="42" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="8"/>
       <c r="B42" s="8"/>
       <c r="C42" s="8"/>
@@ -10081,7 +10080,7 @@
       <c r="K42" s="8"/>
       <c r="L42" s="8"/>
     </row>
-    <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="8"/>
       <c r="B43" s="8"/>
       <c r="C43" s="8"/>
@@ -10098,7 +10097,7 @@
       <c r="K43" s="8"/>
       <c r="L43" s="8"/>
     </row>
-    <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="8"/>
       <c r="B44" s="8"/>
       <c r="C44" s="8"/>
@@ -10115,7 +10114,7 @@
       <c r="K44" s="8"/>
       <c r="L44" s="8"/>
     </row>
-    <row r="45" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="8"/>
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
@@ -10132,7 +10131,7 @@
       <c r="K45" s="8"/>
       <c r="L45" s="8"/>
     </row>
-    <row r="46" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="8"/>
       <c r="B46" s="8"/>
       <c r="C46" s="8"/>
@@ -10149,7 +10148,7 @@
       <c r="K46" s="8"/>
       <c r="L46" s="8"/>
     </row>
-    <row r="47" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="8"/>
       <c r="B47" s="8"/>
       <c r="C47" s="8"/>
@@ -10166,7 +10165,7 @@
       <c r="K47" s="8"/>
       <c r="L47" s="8"/>
     </row>
-    <row r="48" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="8"/>
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
@@ -10183,7 +10182,7 @@
       <c r="K48" s="8"/>
       <c r="L48" s="8"/>
     </row>
-    <row r="49" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="8"/>
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
@@ -10200,7 +10199,7 @@
       <c r="K49" s="8"/>
       <c r="L49" s="8"/>
     </row>
-    <row r="50" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="8"/>
       <c r="B50" s="8"/>
       <c r="C50" s="8"/>
@@ -10217,7 +10216,7 @@
       <c r="K50" s="8"/>
       <c r="L50" s="8"/>
     </row>
-    <row r="51" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="8"/>
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
@@ -10234,7 +10233,7 @@
       <c r="K51" s="8"/>
       <c r="L51" s="8"/>
     </row>
-    <row r="52" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="8"/>
       <c r="B52" s="8"/>
       <c r="C52" s="8"/>
@@ -10251,7 +10250,7 @@
       <c r="K52" s="8"/>
       <c r="L52" s="8"/>
     </row>
-    <row r="53" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="8"/>
       <c r="B53" s="8"/>
       <c r="C53" s="8"/>
@@ -10268,7 +10267,7 @@
       <c r="K53" s="8"/>
       <c r="L53" s="8"/>
     </row>
-    <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="8"/>
       <c r="B54" s="8"/>
       <c r="C54" s="8"/>
@@ -10285,7 +10284,7 @@
       <c r="K54" s="8"/>
       <c r="L54" s="8"/>
     </row>
-    <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="8"/>
       <c r="B55" s="8"/>
       <c r="C55" s="8"/>
@@ -10302,7 +10301,7 @@
       <c r="K55" s="8"/>
       <c r="L55" s="8"/>
     </row>
-    <row r="56" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="8"/>
       <c r="B56" s="8"/>
       <c r="C56" s="8"/>
@@ -10319,7 +10318,7 @@
       <c r="K56" s="8"/>
       <c r="L56" s="8"/>
     </row>
-    <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="8"/>
       <c r="B57" s="8"/>
       <c r="C57" s="8"/>
@@ -10336,7 +10335,7 @@
       <c r="K57" s="8"/>
       <c r="L57" s="8"/>
     </row>
-    <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="8"/>
       <c r="B58" s="8"/>
       <c r="C58" s="8"/>
@@ -10353,7 +10352,7 @@
       <c r="K58" s="8"/>
       <c r="L58" s="8"/>
     </row>
-    <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="8"/>
       <c r="B59" s="8"/>
       <c r="C59" s="8"/>
@@ -10370,7 +10369,7 @@
       <c r="K59" s="8"/>
       <c r="L59" s="8"/>
     </row>
-    <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="8"/>
       <c r="B60" s="8"/>
       <c r="C60" s="8"/>
@@ -10387,7 +10386,7 @@
       <c r="K60" s="8"/>
       <c r="L60" s="8"/>
     </row>
-    <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="8"/>
       <c r="B61" s="8"/>
       <c r="C61" s="8"/>
@@ -10404,7 +10403,7 @@
       <c r="K61" s="8"/>
       <c r="L61" s="8"/>
     </row>
-    <row r="62" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="8"/>
       <c r="B62" s="8"/>
       <c r="C62" s="8"/>
@@ -10421,7 +10420,7 @@
       <c r="K62" s="8"/>
       <c r="L62" s="8"/>
     </row>
-    <row r="63" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="8"/>
       <c r="B63" s="8"/>
       <c r="C63" s="8"/>
@@ -10438,7 +10437,7 @@
       <c r="K63" s="8"/>
       <c r="L63" s="8"/>
     </row>
-    <row r="64" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="8"/>
       <c r="B64" s="8"/>
       <c r="C64" s="8"/>
@@ -10455,7 +10454,7 @@
       <c r="K64" s="8"/>
       <c r="L64" s="8"/>
     </row>
-    <row r="65" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" s="8"/>
       <c r="B65" s="8"/>
       <c r="C65" s="8"/>
@@ -10472,7 +10471,7 @@
       <c r="K65" s="8"/>
       <c r="L65" s="8"/>
     </row>
-    <row r="66" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" s="8"/>
       <c r="B66" s="8"/>
       <c r="C66" s="8"/>
@@ -10489,7 +10488,7 @@
       <c r="K66" s="8"/>
       <c r="L66" s="8"/>
     </row>
-    <row r="67" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" s="8"/>
       <c r="B67" s="8"/>
       <c r="C67" s="8"/>
@@ -10506,7 +10505,7 @@
       <c r="K67" s="8"/>
       <c r="L67" s="8"/>
     </row>
-    <row r="68" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="8"/>
       <c r="B68" s="8"/>
       <c r="C68" s="8"/>
@@ -10523,7 +10522,7 @@
       <c r="K68" s="8"/>
       <c r="L68" s="8"/>
     </row>
-    <row r="69" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" s="8"/>
       <c r="B69" s="8"/>
       <c r="C69" s="8"/>
@@ -10540,7 +10539,7 @@
       <c r="K69" s="8"/>
       <c r="L69" s="8"/>
     </row>
-    <row r="70" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" s="8"/>
       <c r="B70" s="8"/>
       <c r="C70" s="8"/>
@@ -10557,7 +10556,7 @@
       <c r="K70" s="8"/>
       <c r="L70" s="8"/>
     </row>
-    <row r="71" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" s="8"/>
       <c r="B71" s="8"/>
       <c r="C71" s="8"/>
@@ -10574,7 +10573,7 @@
       <c r="K71" s="8"/>
       <c r="L71" s="8"/>
     </row>
-    <row r="72" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" s="8"/>
       <c r="B72" s="8"/>
       <c r="C72" s="8"/>
@@ -10591,7 +10590,7 @@
       <c r="K72" s="8"/>
       <c r="L72" s="8"/>
     </row>
-    <row r="73" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="8"/>
       <c r="B73" s="8"/>
       <c r="C73" s="8"/>
@@ -10608,7 +10607,7 @@
       <c r="K73" s="8"/>
       <c r="L73" s="8"/>
     </row>
-    <row r="74" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" s="8"/>
       <c r="B74" s="8"/>
       <c r="C74" s="8"/>
@@ -10625,7 +10624,7 @@
       <c r="K74" s="8"/>
       <c r="L74" s="8"/>
     </row>
-    <row r="75" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="8"/>
       <c r="B75" s="8"/>
       <c r="C75" s="8"/>
@@ -10642,7 +10641,7 @@
       <c r="K75" s="8"/>
       <c r="L75" s="8"/>
     </row>
-    <row r="76" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="8"/>
       <c r="B76" s="8"/>
       <c r="C76" s="8"/>
@@ -10659,7 +10658,7 @@
       <c r="K76" s="8"/>
       <c r="L76" s="8"/>
     </row>
-    <row r="77" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" s="8"/>
       <c r="B77" s="8"/>
       <c r="C77" s="8"/>
@@ -10676,7 +10675,7 @@
       <c r="K77" s="8"/>
       <c r="L77" s="8"/>
     </row>
-    <row r="78" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" s="8"/>
       <c r="B78" s="8"/>
       <c r="C78" s="8"/>
@@ -10693,7 +10692,7 @@
       <c r="K78" s="8"/>
       <c r="L78" s="8"/>
     </row>
-    <row r="79" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" s="8"/>
       <c r="B79" s="8"/>
       <c r="C79" s="8"/>
@@ -10710,7 +10709,7 @@
       <c r="K79" s="8"/>
       <c r="L79" s="8"/>
     </row>
-    <row r="80" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" s="8"/>
       <c r="B80" s="8"/>
       <c r="C80" s="8"/>
@@ -10727,7 +10726,7 @@
       <c r="K80" s="8"/>
       <c r="L80" s="8"/>
     </row>
-    <row r="81" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" s="8"/>
       <c r="B81" s="8"/>
       <c r="C81" s="8"/>
@@ -10744,7 +10743,7 @@
       <c r="K81" s="8"/>
       <c r="L81" s="8"/>
     </row>
-    <row r="82" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" s="8"/>
       <c r="B82" s="8"/>
       <c r="C82" s="8"/>
@@ -10761,7 +10760,7 @@
       <c r="K82" s="8"/>
       <c r="L82" s="8"/>
     </row>
-    <row r="83" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" s="8"/>
       <c r="B83" s="8"/>
       <c r="C83" s="8"/>
@@ -10778,7 +10777,7 @@
       <c r="K83" s="8"/>
       <c r="L83" s="8"/>
     </row>
-    <row r="84" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" s="8"/>
       <c r="B84" s="8"/>
       <c r="C84" s="8"/>
@@ -10795,7 +10794,7 @@
       <c r="K84" s="8"/>
       <c r="L84" s="8"/>
     </row>
-    <row r="85" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" s="8"/>
       <c r="B85" s="8"/>
       <c r="C85" s="8"/>
@@ -10812,7 +10811,7 @@
       <c r="K85" s="8"/>
       <c r="L85" s="8"/>
     </row>
-    <row r="86" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" s="8"/>
       <c r="B86" s="8"/>
       <c r="C86" s="8"/>
@@ -10829,7 +10828,7 @@
       <c r="K86" s="8"/>
       <c r="L86" s="8"/>
     </row>
-    <row r="87" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" s="8"/>
       <c r="B87" s="8"/>
       <c r="C87" s="8"/>
@@ -10846,7 +10845,7 @@
       <c r="K87" s="8"/>
       <c r="L87" s="8"/>
     </row>
-    <row r="88" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" s="8"/>
       <c r="B88" s="8"/>
       <c r="C88" s="8"/>
@@ -10863,7 +10862,7 @@
       <c r="K88" s="8"/>
       <c r="L88" s="8"/>
     </row>
-    <row r="89" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" s="8"/>
       <c r="B89" s="8"/>
       <c r="C89" s="8"/>
@@ -10880,7 +10879,7 @@
       <c r="K89" s="8"/>
       <c r="L89" s="8"/>
     </row>
-    <row r="90" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" s="8"/>
       <c r="B90" s="8"/>
       <c r="C90" s="8"/>
@@ -10897,7 +10896,7 @@
       <c r="K90" s="8"/>
       <c r="L90" s="8"/>
     </row>
-    <row r="91" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" s="8"/>
       <c r="B91" s="8"/>
       <c r="C91" s="8"/>
@@ -10914,7 +10913,7 @@
       <c r="K91" s="8"/>
       <c r="L91" s="8"/>
     </row>
-    <row r="92" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" s="8"/>
       <c r="B92" s="8"/>
       <c r="C92" s="8"/>
@@ -10931,7 +10930,7 @@
       <c r="K92" s="8"/>
       <c r="L92" s="8"/>
     </row>
-    <row r="93" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" s="8"/>
       <c r="B93" s="8"/>
       <c r="C93" s="8"/>
@@ -10948,7 +10947,7 @@
       <c r="K93" s="8"/>
       <c r="L93" s="8"/>
     </row>
-    <row r="94" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" s="8"/>
       <c r="B94" s="8"/>
       <c r="C94" s="8"/>
@@ -10965,7 +10964,7 @@
       <c r="K94" s="8"/>
       <c r="L94" s="8"/>
     </row>
-    <row r="95" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" s="8"/>
       <c r="B95" s="8"/>
       <c r="C95" s="8"/>
@@ -10982,7 +10981,7 @@
       <c r="K95" s="8"/>
       <c r="L95" s="8"/>
     </row>
-    <row r="96" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" s="8"/>
       <c r="B96" s="8"/>
       <c r="C96" s="8"/>
@@ -10999,7 +10998,7 @@
       <c r="K96" s="8"/>
       <c r="L96" s="8"/>
     </row>
-    <row r="97" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" s="8"/>
       <c r="B97" s="8"/>
       <c r="C97" s="8"/>
@@ -11016,7 +11015,7 @@
       <c r="K97" s="8"/>
       <c r="L97" s="8"/>
     </row>
-    <row r="98" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" s="8"/>
       <c r="B98" s="8"/>
       <c r="C98" s="8"/>
@@ -11033,7 +11032,7 @@
       <c r="K98" s="8"/>
       <c r="L98" s="8"/>
     </row>
-    <row r="99" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99" s="8"/>
       <c r="B99" s="8"/>
       <c r="C99" s="8"/>
@@ -11050,7 +11049,7 @@
       <c r="K99" s="8"/>
       <c r="L99" s="8"/>
     </row>
-    <row r="100" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" s="8"/>
       <c r="B100" s="8"/>
       <c r="C100" s="8"/>
@@ -11067,7 +11066,7 @@
       <c r="K100" s="8"/>
       <c r="L100" s="8"/>
     </row>
-    <row r="101" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" s="8"/>
       <c r="B101" s="8"/>
       <c r="C101" s="8"/>
@@ -11084,7 +11083,7 @@
       <c r="K101" s="8"/>
       <c r="L101" s="8"/>
     </row>
-    <row r="102" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" s="8"/>
       <c r="B102" s="8"/>
       <c r="C102" s="8"/>
@@ -11101,7 +11100,7 @@
       <c r="K102" s="8"/>
       <c r="L102" s="8"/>
     </row>
-    <row r="103" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" s="8"/>
       <c r="B103" s="8"/>
       <c r="C103" s="8"/>
@@ -11118,7 +11117,7 @@
       <c r="K103" s="8"/>
       <c r="L103" s="8"/>
     </row>
-    <row r="104" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104" s="8"/>
       <c r="B104" s="8"/>
       <c r="C104" s="8"/>
@@ -11135,7 +11134,7 @@
       <c r="K104" s="8"/>
       <c r="L104" s="8"/>
     </row>
-    <row r="105" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" s="8"/>
       <c r="B105" s="8"/>
       <c r="C105" s="8"/>
@@ -11152,7 +11151,7 @@
       <c r="K105" s="8"/>
       <c r="L105" s="8"/>
     </row>
-    <row r="106" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" s="8"/>
       <c r="B106" s="8"/>
       <c r="C106" s="8"/>
@@ -11169,7 +11168,7 @@
       <c r="K106" s="8"/>
       <c r="L106" s="8"/>
     </row>
-    <row r="107" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" s="8"/>
       <c r="B107" s="8"/>
       <c r="C107" s="8"/>
@@ -11186,7 +11185,7 @@
       <c r="K107" s="8"/>
       <c r="L107" s="8"/>
     </row>
-    <row r="108" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" s="8"/>
       <c r="B108" s="8"/>
       <c r="C108" s="8"/>
@@ -11203,7 +11202,7 @@
       <c r="K108" s="8"/>
       <c r="L108" s="8"/>
     </row>
-    <row r="109" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109" s="8"/>
       <c r="B109" s="8"/>
       <c r="C109" s="8"/>
@@ -11220,7 +11219,7 @@
       <c r="K109" s="8"/>
       <c r="L109" s="8"/>
     </row>
-    <row r="110" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" s="8"/>
       <c r="B110" s="8"/>
       <c r="C110" s="8"/>
@@ -11237,7 +11236,7 @@
       <c r="K110" s="8"/>
       <c r="L110" s="8"/>
     </row>
-    <row r="111" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A111" s="8"/>
       <c r="B111" s="8"/>
       <c r="C111" s="8"/>
@@ -11254,7 +11253,7 @@
       <c r="K111" s="8"/>
       <c r="L111" s="8"/>
     </row>
-    <row r="112" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112" s="8"/>
       <c r="B112" s="8"/>
       <c r="C112" s="8"/>
@@ -11271,25 +11270,8 @@
       <c r="K112" s="8"/>
       <c r="L112" s="8"/>
     </row>
-    <row r="113" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="114" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="115" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="116" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="117" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="118" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="119" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="120" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="121" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="122" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="123" hidden="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <autoFilter ref="E1:E123" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Test"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="E1:E123" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Business Analysis/checkupp_sprint_plan_2026.xlsx
+++ b/Business Analysis/checkupp_sprint_plan_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Business Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A5E8C5E-172E-4994-8F25-E5413AB277D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA739F07-699D-4C92-A550-EA26520D2503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="76">
   <si>
     <t>Epic</t>
   </si>
@@ -7479,6 +7479,12 @@
   <si>
     <t>Needs Review</t>
   </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>View Upcoming Screenings</t>
+  </si>
 </sst>
 </file>
 
@@ -7590,7 +7596,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -7630,6 +7636,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7733,7 +7742,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Sprint 01 Burndown'!$B$1</c:f>
+              <c:f>'Sprint 01 Burndown'!$C$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7756,63 +7765,36 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>'Sprint 01 Burndown'!$B$2:$B$19</c:f>
+              <c:f>'Sprint 01 Burndown'!$C$2:$C$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>160</c:v>
+                  <c:v>82</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>160</c:v>
+                  <c:v>74</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>160</c:v>
+                  <c:v>66</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>160</c:v>
+                  <c:v>66</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>160</c:v>
+                  <c:v>66</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>160</c:v>
+                  <c:v>66</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>160</c:v>
+                  <c:v>66</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>160</c:v>
+                  <c:v>66</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>160</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>160</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>130</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>115</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>75</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>55</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>0</c:v>
+                  <c:v>66</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7829,7 +7811,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Sprint 01 Burndown'!$C$1</c:f>
+              <c:f>'Sprint 01 Burndown'!$D$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -7852,62 +7834,35 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>'Sprint 01 Burndown'!$C$2:$C$19</c:f>
+              <c:f>'Sprint 01 Burndown'!$D$2:$D$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>160</c:v>
+                  <c:v>82</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>150</c:v>
+                  <c:v>71.75</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>140</c:v>
+                  <c:v>61.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>130</c:v>
+                  <c:v>51.25</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>120</c:v>
+                  <c:v>41</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>110</c:v>
+                  <c:v>30.75</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>100</c:v>
+                  <c:v>20.5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>90</c:v>
+                  <c:v>10.25</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>80</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>70</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>60</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>50</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>40</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="17">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -7932,7 +7887,7 @@
         <c:axId val="228576623"/>
         <c:axId val="228581423"/>
       </c:lineChart>
-      <c:catAx>
+      <c:dateAx>
         <c:axId val="228576623"/>
         <c:scaling>
           <c:orientation val="minMax"/>
@@ -7977,11 +7932,10 @@
         </c:txPr>
         <c:crossAx val="228581423"/>
         <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
+        <c:auto val="0"/>
         <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
+        <c:baseTimeUnit val="days"/>
+      </c:dateAx>
       <c:valAx>
         <c:axId val="228581423"/>
         <c:scaling>
@@ -8681,16 +8635,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>167640</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>182880</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
+      <xdr:col>19</xdr:col>
       <xdr:colOff>30480</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>91440</xdr:rowOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>7398</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -9204,7 +9158,9 @@
       <c r="L5" s="8"/>
     </row>
     <row r="6" spans="1:12" ht="331.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="8"/>
+      <c r="A6" s="8">
+        <v>5</v>
+      </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8">
         <v>1.6</v>
@@ -9232,7 +9188,7 @@
     </row>
     <row r="7" spans="1:12" ht="272.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>26</v>
@@ -9267,7 +9223,7 @@
     </row>
     <row r="8" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>26</v>
@@ -9276,7 +9232,7 @@
         <v>42</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>21</v>
@@ -9285,7 +9241,7 @@
         <v>49</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>28</v>
@@ -9302,7 +9258,7 @@
     </row>
     <row r="9" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>26</v>
@@ -9337,7 +9293,7 @@
     </row>
     <row r="10" spans="1:12" ht="396" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>26</v>
@@ -9372,7 +9328,7 @@
     </row>
     <row r="11" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A11" s="8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>26</v>
@@ -9406,7 +9362,9 @@
       <c r="L11" s="8"/>
     </row>
     <row r="12" spans="1:12" ht="408.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="8"/>
+      <c r="A12" s="8">
+        <v>11</v>
+      </c>
       <c r="B12" s="8"/>
       <c r="C12" s="8" t="s">
         <v>54</v>
@@ -9433,7 +9391,9 @@
       <c r="L12" s="8"/>
     </row>
     <row r="13" spans="1:12" ht="302.39999999999998" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
+      <c r="A13" s="8">
+        <v>12</v>
+      </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8">
         <v>1.8</v>
@@ -9460,7 +9420,9 @@
       <c r="L13" s="8"/>
     </row>
     <row r="14" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="8"/>
+      <c r="A14" s="8">
+        <v>13</v>
+      </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8" t="s">
         <v>58</v>
@@ -9491,7 +9453,9 @@
       <c r="L14" s="8"/>
     </row>
     <row r="15" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="8"/>
+      <c r="A15" s="8">
+        <v>14</v>
+      </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
       <c r="D15" s="8" t="s">
@@ -9520,7 +9484,9 @@
       <c r="L15" s="8"/>
     </row>
     <row r="16" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="8"/>
+      <c r="A16" s="8">
+        <v>15</v>
+      </c>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
       <c r="D16" s="8" t="s">
@@ -9549,7 +9515,9 @@
       <c r="L16" s="8"/>
     </row>
     <row r="17" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="8"/>
+      <c r="A17" s="8">
+        <v>16</v>
+      </c>
       <c r="B17" s="8"/>
       <c r="C17" s="8">
         <v>18.5</v>
@@ -9578,7 +9546,9 @@
       <c r="L17" s="8"/>
     </row>
     <row r="18" spans="1:12" ht="315.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="8"/>
+      <c r="A18" s="8">
+        <v>17</v>
+      </c>
       <c r="B18" s="8"/>
       <c r="C18" s="8" t="s">
         <v>62</v>
@@ -9605,7 +9575,9 @@
       <c r="L18" s="8"/>
     </row>
     <row r="19" spans="1:12" ht="383.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="8"/>
+      <c r="A19" s="8">
+        <v>18</v>
+      </c>
       <c r="B19" s="8"/>
       <c r="C19" s="8">
         <v>18.100000000000001</v>
@@ -9632,7 +9604,9 @@
       <c r="L19" s="8"/>
     </row>
     <row r="20" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="8"/>
+      <c r="A20" s="8">
+        <v>19</v>
+      </c>
       <c r="B20" s="8"/>
       <c r="C20" s="8">
         <v>18.2</v>
@@ -9657,7 +9631,9 @@
       <c r="L20" s="8"/>
     </row>
     <row r="21" spans="1:12" ht="360" x14ac:dyDescent="0.3">
-      <c r="A21" s="8"/>
+      <c r="A21" s="8">
+        <v>20</v>
+      </c>
       <c r="B21" s="8"/>
       <c r="C21" s="8">
         <v>18.3</v>
@@ -9684,7 +9660,9 @@
       <c r="L21" s="8"/>
     </row>
     <row r="22" spans="1:12" ht="409.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="8"/>
+      <c r="A22" s="8">
+        <v>21</v>
+      </c>
       <c r="B22" s="8"/>
       <c r="C22" s="8" t="s">
         <v>69</v>
@@ -9711,7 +9689,9 @@
       <c r="L22" s="8"/>
     </row>
     <row r="23" spans="1:12" ht="302.39999999999998" x14ac:dyDescent="0.3">
-      <c r="A23" s="8"/>
+      <c r="A23" s="8">
+        <v>22</v>
+      </c>
       <c r="B23" s="8"/>
       <c r="C23" s="8">
         <v>18.399999999999999</v>
@@ -9738,7 +9718,9 @@
       <c r="L23" s="8"/>
     </row>
     <row r="24" spans="1:12" ht="388.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="8"/>
+      <c r="A24" s="8">
+        <v>23</v>
+      </c>
       <c r="B24" s="8"/>
       <c r="C24" s="8">
         <v>18.5</v>
@@ -9765,7 +9747,9 @@
       <c r="L24" s="8"/>
     </row>
     <row r="25" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="8"/>
+      <c r="A25" s="8">
+        <v>24</v>
+      </c>
       <c r="B25" s="8"/>
       <c r="C25" s="8" t="s">
         <v>62</v>
@@ -11280,279 +11264,202 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D389B43-8ACA-4B5D-A185-0146C384427F}">
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.77734375" style="5" customWidth="1"/>
-    <col min="3" max="3" width="10.77734375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="8.88671875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="10.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.77734375" style="5" customWidth="1"/>
+    <col min="4" max="4" width="10.77734375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>0</v>
       </c>
-      <c r="B2" s="4">
-        <v>160</v>
-      </c>
-      <c r="C2" s="1">
-        <v>160</v>
+      <c r="B2" s="14">
+        <v>46237</v>
+      </c>
+      <c r="C2" s="4">
+        <f>82-SUM(E$2:E2)</f>
+        <v>82</v>
       </c>
       <c r="D2" s="1">
+        <f xml:space="preserve"> 82*(1-1/8*A2)</f>
+        <v>82</v>
+      </c>
+      <c r="E2" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3" s="4">
-        <v>160</v>
-      </c>
-      <c r="C3" s="2">
-        <v>150</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B3" s="14">
+        <v>46238</v>
+      </c>
+      <c r="C3" s="4">
+        <f>82-SUM(E$2:E3)</f>
+        <v>74</v>
+      </c>
+      <c r="D3" s="1">
+        <f t="shared" ref="D3:D10" si="0" xml:space="preserve"> 82*(1-1/8*A3)</f>
+        <v>71.75</v>
+      </c>
+      <c r="E3" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>2</v>
       </c>
-      <c r="B4" s="4">
-        <v>160</v>
-      </c>
-      <c r="C4" s="1">
-        <v>140</v>
-      </c>
-      <c r="D4" s="2">
-        <v>0</v>
-      </c>
-      <c r="K4" s="3"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B4" s="14">
+        <v>46239</v>
+      </c>
+      <c r="C4" s="4">
+        <f>82-SUM(E$2:E4)</f>
+        <v>66</v>
+      </c>
+      <c r="D4" s="1">
+        <f t="shared" si="0"/>
+        <v>61.5</v>
+      </c>
+      <c r="E4" s="2">
+        <v>8</v>
+      </c>
+      <c r="L4" s="3"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>3</v>
       </c>
-      <c r="B5" s="4">
-        <v>160</v>
-      </c>
-      <c r="C5" s="2">
-        <v>130</v>
-      </c>
-      <c r="D5" s="2">
+      <c r="B5" s="14">
+        <v>46240</v>
+      </c>
+      <c r="C5" s="4">
+        <f>82-SUM(E$2:E5)</f>
+        <v>66</v>
+      </c>
+      <c r="D5" s="1">
+        <f t="shared" si="0"/>
+        <v>51.25</v>
+      </c>
+      <c r="E5" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>4</v>
       </c>
-      <c r="B6" s="4">
-        <v>160</v>
-      </c>
-      <c r="C6" s="1">
-        <v>120</v>
-      </c>
-      <c r="D6" s="2">
+      <c r="B6" s="14">
+        <v>46241</v>
+      </c>
+      <c r="C6" s="4">
+        <f>82-SUM(E$2:E6)</f>
+        <v>66</v>
+      </c>
+      <c r="D6" s="1">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="E6" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>5</v>
       </c>
-      <c r="B7" s="4">
-        <v>160</v>
-      </c>
-      <c r="C7" s="2">
-        <v>110</v>
-      </c>
-      <c r="D7" s="2">
+      <c r="B7" s="14">
+        <v>46244</v>
+      </c>
+      <c r="C7" s="4">
+        <f>82-SUM(E$2:E7)</f>
+        <v>66</v>
+      </c>
+      <c r="D7" s="1">
+        <f t="shared" si="0"/>
+        <v>30.75</v>
+      </c>
+      <c r="E7" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>6</v>
       </c>
-      <c r="B8" s="4">
-        <v>160</v>
-      </c>
-      <c r="C8" s="1">
-        <v>100</v>
-      </c>
-      <c r="D8" s="2">
+      <c r="B8" s="14">
+        <v>46245</v>
+      </c>
+      <c r="C8" s="4">
+        <f>82-SUM(E$2:E8)</f>
+        <v>66</v>
+      </c>
+      <c r="D8" s="1">
+        <f t="shared" si="0"/>
+        <v>20.5</v>
+      </c>
+      <c r="E8" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>7</v>
       </c>
-      <c r="B9" s="4">
-        <v>160</v>
-      </c>
-      <c r="C9" s="2">
-        <v>90</v>
-      </c>
-      <c r="D9" s="2">
+      <c r="B9" s="14">
+        <v>46246</v>
+      </c>
+      <c r="C9" s="4">
+        <f>82-SUM(E$2:E9)</f>
+        <v>66</v>
+      </c>
+      <c r="D9" s="1">
+        <f t="shared" si="0"/>
+        <v>10.25</v>
+      </c>
+      <c r="E9" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>8</v>
       </c>
-      <c r="B10" s="4">
-        <v>160</v>
-      </c>
-      <c r="C10" s="1">
-        <v>80</v>
-      </c>
-      <c r="D10" s="2">
+      <c r="B10" s="14">
+        <v>46247</v>
+      </c>
+      <c r="C10" s="4">
+        <f>82-SUM(E$2:E10)</f>
+        <v>66</v>
+      </c>
+      <c r="D10" s="1">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
-        <v>9</v>
-      </c>
-      <c r="B11" s="4">
-        <v>160</v>
-      </c>
-      <c r="C11" s="2">
-        <v>70</v>
-      </c>
-      <c r="D11" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
-        <v>10</v>
-      </c>
-      <c r="B12" s="5">
-        <v>130</v>
-      </c>
-      <c r="C12" s="1">
-        <v>60</v>
-      </c>
-      <c r="D12" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
-        <v>11</v>
-      </c>
-      <c r="B13" s="5">
-        <v>115</v>
-      </c>
-      <c r="C13" s="2">
-        <v>50</v>
-      </c>
-      <c r="D13" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
-        <v>12</v>
-      </c>
-      <c r="B14" s="5">
-        <v>75</v>
-      </c>
-      <c r="C14" s="1">
-        <v>40</v>
-      </c>
-      <c r="D14" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
-        <v>13</v>
-      </c>
-      <c r="B15" s="5">
-        <v>55</v>
-      </c>
-      <c r="C15" s="2">
-        <v>30</v>
-      </c>
-      <c r="D15" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="2">
-        <v>14</v>
-      </c>
-      <c r="B16" s="5">
-        <v>5</v>
-      </c>
-      <c r="C16" s="1">
-        <v>20</v>
-      </c>
-      <c r="D16" s="2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="2">
-        <v>15</v>
-      </c>
-      <c r="B17" s="5">
-        <v>0</v>
-      </c>
-      <c r="C17" s="2">
-        <v>10</v>
-      </c>
-      <c r="D17" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="2">
-        <v>16</v>
-      </c>
-      <c r="B18" s="5">
-        <v>0</v>
-      </c>
-      <c r="C18" s="1">
-        <v>0</v>
-      </c>
-      <c r="D18" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="2">
-        <v>17</v>
-      </c>
-      <c r="B19" s="5">
-        <v>0</v>
-      </c>
-      <c r="C19" s="2">
-        <v>0</v>
-      </c>
-      <c r="D19" s="2">
+      <c r="E10" s="2">
         <v>0</v>
       </c>
     </row>

--- a/Business Analysis/checkupp_sprint_plan_2026.xlsx
+++ b/Business Analysis/checkupp_sprint_plan_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Business Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA739F07-699D-4C92-A550-EA26520D2503}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B724599E-6C01-443E-8D63-0E1228C1D30A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint 01" sheetId="1" r:id="rId1"/>
@@ -7763,6 +7763,42 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Sprint 01 Burndown'!$B$2:$B$10</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yyyy</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>46237</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46238</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46239</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46240</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46241</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46244</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46245</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46246</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46247</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
           <c:val>
             <c:numRef>
               <c:f>'Sprint 01 Burndown'!$C$2:$C$10</c:f>
@@ -7832,6 +7868,42 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Sprint 01 Burndown'!$B$2:$B$10</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yyyy</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>46237</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46238</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46239</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46240</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46241</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46244</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46245</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46246</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46247</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
           <c:val>
             <c:numRef>
               <c:f>'Sprint 01 Burndown'!$D$2:$D$10</c:f>
@@ -7894,6 +7966,7 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:numFmt formatCode="m/d/yyyy" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -8641,8 +8714,8 @@
       <xdr:rowOff>182880</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>36990</xdr:colOff>
       <xdr:row>20</xdr:row>
       <xdr:rowOff>7398</xdr:rowOff>
     </xdr:to>

--- a/Business Analysis/checkupp_sprint_plan_2026.xlsx
+++ b/Business Analysis/checkupp_sprint_plan_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Business Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B724599E-6C01-443E-8D63-0E1228C1D30A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDAEA8B3-48D1-4D1D-8668-E648835DEF43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint 01" sheetId="1" r:id="rId1"/>
@@ -7216,110 +7216,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Build Reusable CustomConditionCard.tsx Component with Distinctive Styling &amp; Green "Last: [Date]" Pill Badge
-1. Create </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-mobile/components/screening/CustomConditionCard.tsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-2. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Props Interface</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">:
-TypeScript
-export interface CustomConditionCardProps {
-  item: CustomConditionItem;
-  onPress: (item: CustomConditionItem) =&gt; void;
-}
-3. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Distinctive Custom Styling</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (US 18.4 AC 1, 2, 3):
-- Apply visual distinction from default system screenings while keeping structural layout identical: use a subtle teal/cyan border accent (border-l-4 border-l-[#00CED1] bg-white rounded-xl border border-gray-100 p-4 mb-3).
-- Display condition Name (item.conditionName) in Poppins-Medium and frequency (item.frequencyType, formatting custom interval if applicable, e.g., "Every 45 Days") as subtitle.
-- Display chevron-forward icon from @expo/vector-icons/Ionicons on the far right.
-4.  </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Green Outcome Pill Badge Support</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (US 18.5 AC 6):
-- If item.latestRecordDate exists, render a soft green pill badge in the top-right corner of the card:
-a. Background #DCFCE7 (bg-green-100), text #15803D (text-green-800 text-xs font-psemibold px-2.5 py-1 rounded-full).
-b. Format string exactly as mandated: "Last: [Today's Logging Date]" (e.g., format(new Date(item.latestRecordDate), "'Last:' dd MMM yyyy")).</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <rPr>
         <b/>
         <sz val="11"/>
@@ -7484,6 +7380,128 @@
   </si>
   <si>
     <t>View Upcoming Screenings</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Build Reusable CustomConditionCard.tsx Component with Distinctive Styling &amp; Green "Last: [Date]" Pill Badge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1. Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/components/screening/CustomConditionCard.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Props Interface</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">:
+TypeScript
+export interface CustomConditionCardProps {
+  item: CustomConditionItem;
+  onPress: (item: CustomConditionItem) =&gt; void;
+}
+3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Distinctive Custom Styling</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (US 18.4 AC 1, 2, 3):
+- Apply visual distinction from default system screenings while keeping structural layout identical: use a subtle teal/cyan border accent (border-l-4 border-l-[#00CED1] bg-white rounded-xl border border-gray-100 p-4 mb-3).
+- Display condition Name (item.conditionName) in Poppins-Medium and frequency (item.frequencyType, formatting custom interval if applicable, e.g., "Every 45 Days") as subtitle.
+- Display chevron-forward icon from @expo/vector-icons/Ionicons on the far right.
+4.  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Green Outcome Pill Badge Support</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (US 18.5 AC 6):
+- If item.latestRecordDate exists, render a soft green pill badge in the top-right corner of the card:
+a. Background #DCFCE7 (bg-green-100), text #15803D (text-green-800 text-xs font-psemibold px-2.5 py-1 rounded-full).
+b. Format string exactly as mandated: "Last: [Today's Logging Date]" (e.g., format(new Date(item.latestRecordDate), "'Last:' dd MMM yyyy")).</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -9305,7 +9323,7 @@
         <v>42</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>21</v>
@@ -9552,7 +9570,7 @@
       </c>
       <c r="J15" s="8"/>
       <c r="K15" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L15" s="8"/>
     </row>
@@ -9583,7 +9601,7 @@
       </c>
       <c r="J16" s="8"/>
       <c r="K16" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L16" s="8"/>
     </row>
@@ -9614,7 +9632,7 @@
       </c>
       <c r="J17" s="8"/>
       <c r="K17" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L17" s="8"/>
     </row>
@@ -9716,10 +9734,10 @@
         <v>21</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="H21" s="8" t="s">
         <v>28</v>
@@ -9745,7 +9763,7 @@
         <v>21</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G22" s="8" t="s">
         <v>22</v>
@@ -11352,7 +11370,7 @@
         <v>12</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>13</v>

--- a/Business Analysis/checkupp_sprint_plan_2026.xlsx
+++ b/Business Analysis/checkupp_sprint_plan_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Business Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDAEA8B3-48D1-4D1D-8668-E648835DEF43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17D3AF12-7261-4541-9680-4FF1AF270EA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2317,572 +2317,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Build Reusable ScreeningOverviewCard.tsx Component with Overdue Red Styling &amp; Tap Handlers</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-1. Create </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-mobile/components/screening/ScreeningOverviewCard.tsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-2. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Props Interface</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">:
-TypeScript
-export interface ScreeningOverviewCardProps {
-  item: ScreeningOverviewItem;
-  type: 'upcoming' | 'due' | 'completed';
-  onPress: (item: ScreeningOverviewItem) =&gt; void;
-}
-3. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Card Content</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>:
-- Render the screening name (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>item.name</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">) in </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Poppins-Medium</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>font-pmedium</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">).
-- Format </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>item.date</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> using </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>date-fns</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>format(new Date(item.date), "dd MMM yyyy")</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> accompanied by a calendar icon </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(@expo/vector-icons/Ionicons calendar-outline</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">).
-- Implement an accessible touch target (&gt;= 44px height) wrapped in </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>TouchableOpacity</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.
-4. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Overdue Highlight Styling (US 1.3 AC 2)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">:
-- When </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>type === 'due'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> AND </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>item.isOverdue === true</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">:
-a. Apply distinctive red card styling: border color </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>#EF4444</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>border-red-500</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">), background tint </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>#FEF2F2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>bg-red-50</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">), and date text color </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>#DC2626</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>text-red-600</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">).
-b. Render a distinct text badge in the top right: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"OVERDUE"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> in bold uppercase font with red background </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>#FEE2E2 (bg-red-100 px-2 py-0.5 rounded text-red-700 font-pbold</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">).
-- For normal items, use standard neutral </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>styling (bg-white border-gray-100</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">).
-5. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Tap Handler</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: Trigger </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>onPress(item)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> when pressed (to open decision modal in FE-1.6).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>Build Your Health Overview Screen &amp; Segmented Top Tabs Layout &amp; Dynamic Count Badges</t>
     </r>
     <r>
@@ -3774,526 +3208,6 @@
   </si>
   <si>
     <t>1.5, 1.6</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Integrate "Have you had this screening?" Decision Modal &amp; Routing to Existing Forms/Booking Modal</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-1. Create </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-mobile/components/screening/ScreeningDecisionModal.tsx and checkupp-mobile/app/health-overview/index.tsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-2. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Build Decision Modal</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (ScreeningDecisionModal.tsx):
-- Extend </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>BaseModal.tsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-mobile/components/screening/shared/modals/BaseModal.tsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">).
-- Props: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>visible: boolean</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>item: ScreeningOverviewItem | null</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>onClose: () =&gt; void</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>onSelectYes: () =&gt; void</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>onSelectNo: () =&gt; void.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-- Display the screening name (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>item?.name</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>) as header subtitle.
-- Render prompt string exactly: "</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Have you had this screening?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>" (US 1.5 AC 2).
-- Render two accessible CTA buttons: "</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Yes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>" (Primary #00CED1) and "</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>No</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">" (Secondary outline).
-3. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Connect Routing &amp; Actions</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">:
-- In </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-mobile/app/health-overview/index.tsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, when a card is pressed, set </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>selectedItem</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> and open </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ScreeningDecisionModal</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.
-- On "</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Yes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">" tap (US 1.5 AC 4):
-a. Dismiss modal and route to the existing data entry form: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>router.push({ pathname: '/(tabs)/health-screening', params: { openFormFor: selectedItem.id, type: selectedItem.screeningType } })</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.
-b. Upon successful form submission, TanStack Query invalidation (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>queryClient.invalidateQueries({ queryKey: ['screenings', 'overview'] })</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">) ensures the card immediately transitions to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Completed</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> and tab count badges update (US 1.6).
-- On "</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>No</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>" tap (US 1.5 AC 5):
-Dismiss modal and open the existing appointment booking modal (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>bookingFlow.ts</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> / appointment booking modal component).</t>
-    </r>
   </si>
   <si>
     <r>
@@ -6873,346 +5787,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Build LogSpecificConditionModal.tsx Full-Screen Outcome Form &amp; Wire Save Mutation</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-1. Create </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-mobile/components/screening/LogSpecificConditionModal.tsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">checkupp-mobile/lib/features/screenings/mutations.ts
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">2. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Full-Screen Modal Scaffold</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (US 18.5 AC 1):
-- Build full-screen modal view with header displaying read-only metadata: condition name, monitoring type, frequency, and care provider.
-3. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Form Input Components</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (US 18.5 AC 2, 3, 4):
-- Date of Check: Use DatePickerInput.tsx defaulting to current system date (new Date()). Allow user selection up to current date.
-- Outcome or Clinical Notes: Spacious multi-line free-text area (InputField.tsx with multiline={true} and numberOfLines={4}).
-4. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>CTA Buttons &amp; Workflow</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (US 18.5 AC 4, 5, 6):
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Sticky footer</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> with two buttons:
-a. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Secondary</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: Cancel: Tapping closes modal and returns user to Available Health Checks - Health Checks top tab - Screenings bottom tab with zero data persistence.
-b. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Primary</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: Save: Tapping executes useLogCustomConditionRecordMutation({ customConditionId, checkDate, outcomeNotes }).
-- Upon success, invalidate query ['screenings', 'custom-conditions'], close full-screen modal, return user to Health Checks list, and confirm the card now displays the green "Last: [Today's Logging Date]" pill badge.</t>
-    </r>
-  </si>
-  <si>
     <t>18.4, 18.5</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Integrate Custom Condition List Rendering &amp; Wire Existing Decision Modal ("Have you had this screening?")</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-1. Modify </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-mobile/app/(tabs)/health-screening.tsx</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-mobile/lib/features/screenings/queries.ts
-2. Data Query &amp; List Rendering</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">:
-- Implement useCustomConditionsQuery(userId) in queries.ts fetching GET /me/screenings/custom-conditions.
-- In health-screening.tsx, merge/render CustomConditionCard components inside the "Available Health Checks" FlatList directly below the trigger card.
-3. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Wire Decision Modal</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (US 18.4 AC 4–7):
-- When CustomConditionCard is tapped (onPress), open the app's existing ScreeningDecisionModal ("Have you had this screening?").
-- Pass the custom condition name as subtitle.
-- On "</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Yes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>" tap (AC 6): Close decision modal and open LogSpecificConditionModal (FE-18.6) passing customConditionId and metadata.
-- On "</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>No</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>" tap (AC 7): Close decision modal and open the app's existing appointment booking modal (bookingFlow.ts).</t>
-    </r>
   </si>
   <si>
     <r>
@@ -7391,7 +5966,527 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Build Reusable CustomConditionCard.tsx Component with Distinctive Styling &amp; Green "Last: [Date]" Pill Badge</t>
+      <t>Integrate "Have you had this screening?" Decision Modal &amp; Routing to Existing Forms/Booking Modal (DO THIS LIKE IT IS DONE IN OTHER EXISTING SCREENINGS)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1. Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/components/screening/ScreeningDecisionModal.tsx and checkupp-mobile/app/health-overview/index.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Build Decision Modal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (ScreeningDecisionModal.tsx):
+- Extend </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BaseModal.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/components/screening/shared/modals/BaseModal.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">).
+- Props: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>visible: boolean</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>item: ScreeningOverviewItem | null</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>onClose: () =&gt; void</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>onSelectYes: () =&gt; void</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>onSelectNo: () =&gt; void.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- Display the screening name (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>item?.name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) as header subtitle.
+- Render prompt string exactly: "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Have you had this screening?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>" (US 1.5 AC 2).
+- Render two accessible CTA buttons: "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Yes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>" (Primary #00CED1) and "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>No</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">" (Secondary outline).
+3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Connect Routing &amp; Actions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">:
+- In </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/app/health-overview/index.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, when a card is pressed, set </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>selectedItem</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and open </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ScreeningDecisionModal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.
+- On "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Yes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">" tap (US 1.5 AC 4):
+a. Dismiss modal and route to the existing data entry form: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>router.push({ pathname: '/(tabs)/health-screening', params: { openFormFor: selectedItem.id, type: selectedItem.screeningType } })</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.
+b. Upon successful form submission, TanStack Query invalidation (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>queryClient.invalidateQueries({ queryKey: ['screenings', 'overview'] })</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">) ensures the card immediately transitions to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Completed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and tab count badges update (US 1.6).
+- On "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>No</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>" tap (US 1.5 AC 5):
+Dismiss modal and open the existing appointment booking modal (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>bookingFlow.ts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> / appointment booking modal component).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Build Reusable CustomConditionCard.tsx Component with Distinctive Styling &amp; Green "Last: [Date]" Pill Badge (DO THIS LIKE IT IS DONE IN OTHER EXISTING SCREENINGS)</t>
     </r>
     <r>
       <rPr>
@@ -7503,12 +6598,1041 @@
 b. Format string exactly as mandated: "Last: [Today's Logging Date]" (e.g., format(new Date(item.latestRecordDate), "'Last:' dd MMM yyyy")).</t>
     </r>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Integrate Custom Condition List Rendering &amp; Wire Existing Decision Modal ("Have you had this screening?") (DO THIS LIKE IT IS DONE IN OTHER EXISTING SCREENINGS)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1. Modify </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/app/(tabs)/health-screening.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/lib/features/screenings/queries.ts
+2. Data Query &amp; List Rendering</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">:
+- Implement useCustomConditionsQuery(userId) in queries.ts fetching GET /me/screenings/custom-conditions.
+- In health-screening.tsx, merge/render CustomConditionCard components inside the "Available Health Checks" FlatList directly below the trigger card.
+3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Wire Decision Modal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (US 18.4 AC 4–7):
+- When CustomConditionCard is tapped (onPress), open the app's existing ScreeningDecisionModal ("Have you had this screening?").
+- Pass the custom condition name as subtitle.
+- On "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Yes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>" tap (AC 6): Close decision modal and open LogSpecificConditionModal (FE-18.6) passing customConditionId and metadata.
+- On "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>No</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>" tap (AC 7): Close decision modal and open the app's existing appointment booking modal (bookingFlow.ts).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Build LogSpecificConditionModal.tsx Full-Screen Outcome Form &amp; Wire Save Mutation (DO THIS LIKE IT IS DONE IN OTHER EXISTING SCREENINGS FORMS)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1. Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/components/screening/LogSpecificConditionModal.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">checkupp-mobile/lib/features/screenings/mutations.ts
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Full-Screen Modal Scaffold</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (US 18.5 AC 1):
+- Build full-screen modal view with header displaying read-only metadata: condition name, monitoring type, frequency, and care provider.
+3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Form Input Components</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (US 18.5 AC 2, 3, 4):
+- Date of Check: Use DatePickerInput.tsx defaulting to current system date (new Date()). Allow user selection up to current date.
+- Outcome or Clinical Notes: Spacious multi-line free-text area (InputField.tsx with multiline={true} and numberOfLines={4}).
+4. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CTA Buttons &amp; Workflow</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (US 18.5 AC 4, 5, 6):
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Sticky footer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> with two buttons:
+a. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Secondary</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: Cancel: Tapping closes modal and returns user to Available Health Checks - Health Checks top tab - Screenings bottom tab with zero data persistence.
+b. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Primary</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Save: Tapping executes useLogCustomConditionRecordMutation({ customConditionId, checkDate, outcomeNotes }).
+- Upon success, invalidate query ['screenings', 'custom-conditions'], close full-screen modal, return user to Health Checks list, and confirm the card now displays the green "Last: [Today's Logging Date]" pill badge.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Build Reusable ScreeningOverviewCard.tsx Component with Overdue Red Styling &amp; Tap Handlers</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1. Create </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>checkupp-mobile/components/screening/ScreeningOverviewCard.tsx</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Props Interface</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">:
+TypeScript
+export interface ScreeningOverviewCardProps {
+  item: ScreeningOverviewItem;
+  type: 'upcoming' | 'due' | 'completed';
+  onPress: (item: ScreeningOverviewItem) =&gt; void;
+}
+3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Card Content</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:
+- Render the screening name (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>item.name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">) in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Poppins-Medium</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>font-pmedium</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">).
+- Format </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>item.date</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> using </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>date-fns</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>format(new Date(item.date), "dd MMM yyyy")</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> accompanied by a calendar icon </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(@expo/vector-icons/Ionicons calendar-outline</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">).
+- Implement an accessible touch target (&gt;= 44px height) wrapped in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>TouchableOpacity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+4. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Overdue Highlight Styling (US 1.3 AC 2)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">:
+- When </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>type === 'due'</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> AND </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>item.isOverdue === true</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">:
+a. Apply distinctive red card styling: border color </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>#EF4444</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>border-red-500</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">), background tint </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>#FEF2F2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>bg-red-50</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">), and date text color </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>#DC2626</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>text-red-600</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">).
+b. Render a distinct text pill badge following wireframe: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">"no. of days/months/year/years ago" </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(e.g. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2 months ago</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1 year ago</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5 days ago</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">) in normal weight snake case font with red border color </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>#FEE2E2 (px-2 py-0.5 rounded text-red-700</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">).
+- For normal items, use standard neutral </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>styling (bg-white border-gray-100</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">).
+c. For </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Upcoming </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Due</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> cards: Render a text pill badge following wireframe: "in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>No. of days/months</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">". Text and pill border in brand primary color, no fill.
+5. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Tap Handler</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: Trigger </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>onPress(item)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> when pressed (to open decision modal in FE-1.6).</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7556,6 +7680,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1" tint="4.9989318521683403E-2"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -9052,7 +9183,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L112"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:L123"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.88671875" style="12" customWidth="1"/>
@@ -9108,7 +9240,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="49.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="49.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="8">
         <v>1</v>
       </c>
@@ -9178,7 +9310,7 @@
       <c r="K3" s="8"/>
       <c r="L3" s="8"/>
     </row>
-    <row r="4" spans="1:12" ht="408.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="408.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8">
         <v>3</v>
       </c>
@@ -9213,7 +9345,7 @@
       <c r="K4" s="8"/>
       <c r="L4" s="8"/>
     </row>
-    <row r="5" spans="1:12" ht="408.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="408.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8">
         <v>4</v>
       </c>
@@ -9248,7 +9380,7 @@
       <c r="K5" s="8"/>
       <c r="L5" s="8"/>
     </row>
-    <row r="6" spans="1:12" ht="331.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="331.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>5</v>
       </c>
@@ -9277,7 +9409,7 @@
       <c r="K6" s="8"/>
       <c r="L6" s="8"/>
     </row>
-    <row r="7" spans="1:12" ht="272.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="272.39999999999998" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8">
         <v>6</v>
       </c>
@@ -9323,7 +9455,7 @@
         <v>42</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>21</v>
@@ -9364,7 +9496,7 @@
         <v>21</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>30</v>
@@ -9399,7 +9531,7 @@
         <v>21</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>30</v>
@@ -9425,7 +9557,7 @@
         <v>26</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>38</v>
@@ -9434,7 +9566,7 @@
         <v>21</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>30</v>
@@ -9458,14 +9590,14 @@
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D12" s="8"/>
       <c r="E12" s="8" t="s">
         <v>21</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="G12" s="8" t="s">
         <v>22</v>
@@ -9494,7 +9626,7 @@
         <v>21</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>30</v>
@@ -9510,13 +9642,13 @@
       <c r="K13" s="8"/>
       <c r="L13" s="8"/>
     </row>
-    <row r="14" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
         <v>13</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>37</v>
@@ -9525,7 +9657,7 @@
         <v>32</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G14" s="8" t="s">
         <v>30</v>
@@ -9543,20 +9675,20 @@
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
     </row>
-    <row r="15" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
         <v>14</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
       <c r="D15" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>23</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>25</v>
@@ -9570,24 +9702,24 @@
       </c>
       <c r="J15" s="8"/>
       <c r="K15" s="8" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="L15" s="8"/>
     </row>
-    <row r="16" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
         <v>15</v>
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
       <c r="D16" s="8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>23</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G16" s="8" t="s">
         <v>25</v>
@@ -9601,11 +9733,11 @@
       </c>
       <c r="J16" s="8"/>
       <c r="K16" s="8" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="L16" s="8"/>
     </row>
-    <row r="17" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
         <v>16</v>
       </c>
@@ -9618,7 +9750,7 @@
         <v>23</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G17" s="8" t="s">
         <v>25</v>
@@ -9632,24 +9764,24 @@
       </c>
       <c r="J17" s="8"/>
       <c r="K17" s="8" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="L17" s="8"/>
     </row>
-    <row r="18" spans="1:12" ht="315.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" ht="315.60000000000002" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
         <v>17</v>
       </c>
       <c r="B18" s="8"/>
       <c r="C18" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D18" s="8"/>
       <c r="E18" s="8" t="s">
         <v>32</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G18" s="8" t="s">
         <v>30</v>
@@ -9678,7 +9810,7 @@
         <v>21</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G19" s="8" t="s">
         <v>22</v>
@@ -9694,7 +9826,7 @@
       <c r="K19" s="8"/>
       <c r="L19" s="8"/>
     </row>
-    <row r="20" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
         <v>19</v>
       </c>
@@ -9705,7 +9837,7 @@
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G20" s="8" t="s">
         <v>22</v>
@@ -9734,7 +9866,7 @@
         <v>21</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G21" s="8" t="s">
         <v>22</v>
@@ -9756,14 +9888,14 @@
       </c>
       <c r="B22" s="8"/>
       <c r="C22" s="8" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D22" s="8"/>
       <c r="E22" s="8" t="s">
         <v>21</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G22" s="8" t="s">
         <v>22</v>
@@ -9779,7 +9911,7 @@
       <c r="K22" s="8"/>
       <c r="L22" s="8"/>
     </row>
-    <row r="23" spans="1:12" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A23" s="8">
         <v>22</v>
       </c>
@@ -9792,7 +9924,7 @@
         <v>21</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G23" s="8" t="s">
         <v>22</v>
@@ -9808,7 +9940,7 @@
       <c r="K23" s="8"/>
       <c r="L23" s="8"/>
     </row>
-    <row r="24" spans="1:12" ht="388.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" ht="403.2" x14ac:dyDescent="0.3">
       <c r="A24" s="8">
         <v>23</v>
       </c>
@@ -9821,7 +9953,7 @@
         <v>21</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G24" s="8" t="s">
         <v>22</v>
@@ -9837,20 +9969,20 @@
       <c r="K24" s="8"/>
       <c r="L24" s="8"/>
     </row>
-    <row r="25" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="8">
         <v>24</v>
       </c>
       <c r="B25" s="8"/>
       <c r="C25" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D25" s="8"/>
       <c r="E25" s="8" t="s">
         <v>32</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G25" s="8" t="s">
         <v>30</v>
@@ -9866,7 +9998,7 @@
       <c r="K25" s="8"/>
       <c r="L25" s="8"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -9883,7 +10015,7 @@
       <c r="K26" s="8"/>
       <c r="L26" s="8"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
@@ -9900,7 +10032,7 @@
       <c r="K27" s="8"/>
       <c r="L27" s="8"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
@@ -9917,7 +10049,7 @@
       <c r="K28" s="8"/>
       <c r="L28" s="8"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
@@ -9934,7 +10066,7 @@
       <c r="K29" s="8"/>
       <c r="L29" s="8"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="8"/>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
@@ -9951,7 +10083,7 @@
       <c r="K30" s="8"/>
       <c r="L30" s="8"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="8"/>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
@@ -9968,7 +10100,7 @@
       <c r="K31" s="8"/>
       <c r="L31" s="8"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="8"/>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
@@ -9985,7 +10117,7 @@
       <c r="K32" s="8"/>
       <c r="L32" s="8"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="8"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
@@ -10002,7 +10134,7 @@
       <c r="K33" s="8"/>
       <c r="L33" s="8"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="8"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -10019,7 +10151,7 @@
       <c r="K34" s="8"/>
       <c r="L34" s="8"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="8"/>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
@@ -10036,7 +10168,7 @@
       <c r="K35" s="8"/>
       <c r="L35" s="8"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="8"/>
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
@@ -10053,7 +10185,7 @@
       <c r="K36" s="8"/>
       <c r="L36" s="8"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
@@ -10070,7 +10202,7 @@
       <c r="K37" s="8"/>
       <c r="L37" s="8"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="8"/>
       <c r="B38" s="8"/>
       <c r="C38" s="8"/>
@@ -10087,7 +10219,7 @@
       <c r="K38" s="8"/>
       <c r="L38" s="8"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="8"/>
       <c r="B39" s="8"/>
       <c r="C39" s="8"/>
@@ -10104,7 +10236,7 @@
       <c r="K39" s="8"/>
       <c r="L39" s="8"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="8"/>
       <c r="B40" s="8"/>
       <c r="C40" s="8"/>
@@ -10121,7 +10253,7 @@
       <c r="K40" s="8"/>
       <c r="L40" s="8"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="8"/>
       <c r="B41" s="8"/>
       <c r="C41" s="8"/>
@@ -10138,7 +10270,7 @@
       <c r="K41" s="8"/>
       <c r="L41" s="8"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="8"/>
       <c r="B42" s="8"/>
       <c r="C42" s="8"/>
@@ -10155,7 +10287,7 @@
       <c r="K42" s="8"/>
       <c r="L42" s="8"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="8"/>
       <c r="B43" s="8"/>
       <c r="C43" s="8"/>
@@ -10172,7 +10304,7 @@
       <c r="K43" s="8"/>
       <c r="L43" s="8"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="8"/>
       <c r="B44" s="8"/>
       <c r="C44" s="8"/>
@@ -10189,7 +10321,7 @@
       <c r="K44" s="8"/>
       <c r="L44" s="8"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="8"/>
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
@@ -10206,7 +10338,7 @@
       <c r="K45" s="8"/>
       <c r="L45" s="8"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="8"/>
       <c r="B46" s="8"/>
       <c r="C46" s="8"/>
@@ -10223,7 +10355,7 @@
       <c r="K46" s="8"/>
       <c r="L46" s="8"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="8"/>
       <c r="B47" s="8"/>
       <c r="C47" s="8"/>
@@ -10240,7 +10372,7 @@
       <c r="K47" s="8"/>
       <c r="L47" s="8"/>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="8"/>
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
@@ -10257,7 +10389,7 @@
       <c r="K48" s="8"/>
       <c r="L48" s="8"/>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="8"/>
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
@@ -10274,7 +10406,7 @@
       <c r="K49" s="8"/>
       <c r="L49" s="8"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="8"/>
       <c r="B50" s="8"/>
       <c r="C50" s="8"/>
@@ -10291,7 +10423,7 @@
       <c r="K50" s="8"/>
       <c r="L50" s="8"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="8"/>
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
@@ -10308,7 +10440,7 @@
       <c r="K51" s="8"/>
       <c r="L51" s="8"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="8"/>
       <c r="B52" s="8"/>
       <c r="C52" s="8"/>
@@ -10325,7 +10457,7 @@
       <c r="K52" s="8"/>
       <c r="L52" s="8"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="8"/>
       <c r="B53" s="8"/>
       <c r="C53" s="8"/>
@@ -10342,7 +10474,7 @@
       <c r="K53" s="8"/>
       <c r="L53" s="8"/>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="8"/>
       <c r="B54" s="8"/>
       <c r="C54" s="8"/>
@@ -10359,7 +10491,7 @@
       <c r="K54" s="8"/>
       <c r="L54" s="8"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="8"/>
       <c r="B55" s="8"/>
       <c r="C55" s="8"/>
@@ -10376,7 +10508,7 @@
       <c r="K55" s="8"/>
       <c r="L55" s="8"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="8"/>
       <c r="B56" s="8"/>
       <c r="C56" s="8"/>
@@ -10393,7 +10525,7 @@
       <c r="K56" s="8"/>
       <c r="L56" s="8"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="8"/>
       <c r="B57" s="8"/>
       <c r="C57" s="8"/>
@@ -10410,7 +10542,7 @@
       <c r="K57" s="8"/>
       <c r="L57" s="8"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="8"/>
       <c r="B58" s="8"/>
       <c r="C58" s="8"/>
@@ -10427,7 +10559,7 @@
       <c r="K58" s="8"/>
       <c r="L58" s="8"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="8"/>
       <c r="B59" s="8"/>
       <c r="C59" s="8"/>
@@ -10444,7 +10576,7 @@
       <c r="K59" s="8"/>
       <c r="L59" s="8"/>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="8"/>
       <c r="B60" s="8"/>
       <c r="C60" s="8"/>
@@ -10461,7 +10593,7 @@
       <c r="K60" s="8"/>
       <c r="L60" s="8"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="8"/>
       <c r="B61" s="8"/>
       <c r="C61" s="8"/>
@@ -10478,7 +10610,7 @@
       <c r="K61" s="8"/>
       <c r="L61" s="8"/>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="8"/>
       <c r="B62" s="8"/>
       <c r="C62" s="8"/>
@@ -10495,7 +10627,7 @@
       <c r="K62" s="8"/>
       <c r="L62" s="8"/>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="8"/>
       <c r="B63" s="8"/>
       <c r="C63" s="8"/>
@@ -10512,7 +10644,7 @@
       <c r="K63" s="8"/>
       <c r="L63" s="8"/>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="8"/>
       <c r="B64" s="8"/>
       <c r="C64" s="8"/>
@@ -10529,7 +10661,7 @@
       <c r="K64" s="8"/>
       <c r="L64" s="8"/>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="8"/>
       <c r="B65" s="8"/>
       <c r="C65" s="8"/>
@@ -10546,7 +10678,7 @@
       <c r="K65" s="8"/>
       <c r="L65" s="8"/>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="8"/>
       <c r="B66" s="8"/>
       <c r="C66" s="8"/>
@@ -10563,7 +10695,7 @@
       <c r="K66" s="8"/>
       <c r="L66" s="8"/>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="8"/>
       <c r="B67" s="8"/>
       <c r="C67" s="8"/>
@@ -10580,7 +10712,7 @@
       <c r="K67" s="8"/>
       <c r="L67" s="8"/>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="8"/>
       <c r="B68" s="8"/>
       <c r="C68" s="8"/>
@@ -10597,7 +10729,7 @@
       <c r="K68" s="8"/>
       <c r="L68" s="8"/>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="8"/>
       <c r="B69" s="8"/>
       <c r="C69" s="8"/>
@@ -10614,7 +10746,7 @@
       <c r="K69" s="8"/>
       <c r="L69" s="8"/>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="8"/>
       <c r="B70" s="8"/>
       <c r="C70" s="8"/>
@@ -10631,7 +10763,7 @@
       <c r="K70" s="8"/>
       <c r="L70" s="8"/>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="8"/>
       <c r="B71" s="8"/>
       <c r="C71" s="8"/>
@@ -10648,7 +10780,7 @@
       <c r="K71" s="8"/>
       <c r="L71" s="8"/>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="8"/>
       <c r="B72" s="8"/>
       <c r="C72" s="8"/>
@@ -10665,7 +10797,7 @@
       <c r="K72" s="8"/>
       <c r="L72" s="8"/>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="8"/>
       <c r="B73" s="8"/>
       <c r="C73" s="8"/>
@@ -10682,7 +10814,7 @@
       <c r="K73" s="8"/>
       <c r="L73" s="8"/>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="8"/>
       <c r="B74" s="8"/>
       <c r="C74" s="8"/>
@@ -10699,7 +10831,7 @@
       <c r="K74" s="8"/>
       <c r="L74" s="8"/>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="8"/>
       <c r="B75" s="8"/>
       <c r="C75" s="8"/>
@@ -10716,7 +10848,7 @@
       <c r="K75" s="8"/>
       <c r="L75" s="8"/>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="8"/>
       <c r="B76" s="8"/>
       <c r="C76" s="8"/>
@@ -10733,7 +10865,7 @@
       <c r="K76" s="8"/>
       <c r="L76" s="8"/>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="8"/>
       <c r="B77" s="8"/>
       <c r="C77" s="8"/>
@@ -10750,7 +10882,7 @@
       <c r="K77" s="8"/>
       <c r="L77" s="8"/>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="8"/>
       <c r="B78" s="8"/>
       <c r="C78" s="8"/>
@@ -10767,7 +10899,7 @@
       <c r="K78" s="8"/>
       <c r="L78" s="8"/>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="8"/>
       <c r="B79" s="8"/>
       <c r="C79" s="8"/>
@@ -10784,7 +10916,7 @@
       <c r="K79" s="8"/>
       <c r="L79" s="8"/>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="8"/>
       <c r="B80" s="8"/>
       <c r="C80" s="8"/>
@@ -10801,7 +10933,7 @@
       <c r="K80" s="8"/>
       <c r="L80" s="8"/>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="8"/>
       <c r="B81" s="8"/>
       <c r="C81" s="8"/>
@@ -10818,7 +10950,7 @@
       <c r="K81" s="8"/>
       <c r="L81" s="8"/>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="8"/>
       <c r="B82" s="8"/>
       <c r="C82" s="8"/>
@@ -10835,7 +10967,7 @@
       <c r="K82" s="8"/>
       <c r="L82" s="8"/>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="8"/>
       <c r="B83" s="8"/>
       <c r="C83" s="8"/>
@@ -10852,7 +10984,7 @@
       <c r="K83" s="8"/>
       <c r="L83" s="8"/>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="8"/>
       <c r="B84" s="8"/>
       <c r="C84" s="8"/>
@@ -10869,7 +11001,7 @@
       <c r="K84" s="8"/>
       <c r="L84" s="8"/>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="8"/>
       <c r="B85" s="8"/>
       <c r="C85" s="8"/>
@@ -10886,7 +11018,7 @@
       <c r="K85" s="8"/>
       <c r="L85" s="8"/>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="8"/>
       <c r="B86" s="8"/>
       <c r="C86" s="8"/>
@@ -10903,7 +11035,7 @@
       <c r="K86" s="8"/>
       <c r="L86" s="8"/>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="8"/>
       <c r="B87" s="8"/>
       <c r="C87" s="8"/>
@@ -10920,7 +11052,7 @@
       <c r="K87" s="8"/>
       <c r="L87" s="8"/>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="8"/>
       <c r="B88" s="8"/>
       <c r="C88" s="8"/>
@@ -10937,7 +11069,7 @@
       <c r="K88" s="8"/>
       <c r="L88" s="8"/>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="8"/>
       <c r="B89" s="8"/>
       <c r="C89" s="8"/>
@@ -10954,7 +11086,7 @@
       <c r="K89" s="8"/>
       <c r="L89" s="8"/>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="8"/>
       <c r="B90" s="8"/>
       <c r="C90" s="8"/>
@@ -10971,7 +11103,7 @@
       <c r="K90" s="8"/>
       <c r="L90" s="8"/>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="8"/>
       <c r="B91" s="8"/>
       <c r="C91" s="8"/>
@@ -10988,7 +11120,7 @@
       <c r="K91" s="8"/>
       <c r="L91" s="8"/>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="8"/>
       <c r="B92" s="8"/>
       <c r="C92" s="8"/>
@@ -11005,7 +11137,7 @@
       <c r="K92" s="8"/>
       <c r="L92" s="8"/>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="8"/>
       <c r="B93" s="8"/>
       <c r="C93" s="8"/>
@@ -11022,7 +11154,7 @@
       <c r="K93" s="8"/>
       <c r="L93" s="8"/>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="8"/>
       <c r="B94" s="8"/>
       <c r="C94" s="8"/>
@@ -11039,7 +11171,7 @@
       <c r="K94" s="8"/>
       <c r="L94" s="8"/>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="8"/>
       <c r="B95" s="8"/>
       <c r="C95" s="8"/>
@@ -11056,7 +11188,7 @@
       <c r="K95" s="8"/>
       <c r="L95" s="8"/>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="8"/>
       <c r="B96" s="8"/>
       <c r="C96" s="8"/>
@@ -11073,7 +11205,7 @@
       <c r="K96" s="8"/>
       <c r="L96" s="8"/>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="8"/>
       <c r="B97" s="8"/>
       <c r="C97" s="8"/>
@@ -11090,7 +11222,7 @@
       <c r="K97" s="8"/>
       <c r="L97" s="8"/>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="8"/>
       <c r="B98" s="8"/>
       <c r="C98" s="8"/>
@@ -11107,7 +11239,7 @@
       <c r="K98" s="8"/>
       <c r="L98" s="8"/>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="8"/>
       <c r="B99" s="8"/>
       <c r="C99" s="8"/>
@@ -11124,7 +11256,7 @@
       <c r="K99" s="8"/>
       <c r="L99" s="8"/>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="8"/>
       <c r="B100" s="8"/>
       <c r="C100" s="8"/>
@@ -11141,7 +11273,7 @@
       <c r="K100" s="8"/>
       <c r="L100" s="8"/>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="8"/>
       <c r="B101" s="8"/>
       <c r="C101" s="8"/>
@@ -11158,7 +11290,7 @@
       <c r="K101" s="8"/>
       <c r="L101" s="8"/>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="8"/>
       <c r="B102" s="8"/>
       <c r="C102" s="8"/>
@@ -11175,7 +11307,7 @@
       <c r="K102" s="8"/>
       <c r="L102" s="8"/>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="8"/>
       <c r="B103" s="8"/>
       <c r="C103" s="8"/>
@@ -11192,7 +11324,7 @@
       <c r="K103" s="8"/>
       <c r="L103" s="8"/>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="8"/>
       <c r="B104" s="8"/>
       <c r="C104" s="8"/>
@@ -11209,7 +11341,7 @@
       <c r="K104" s="8"/>
       <c r="L104" s="8"/>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="8"/>
       <c r="B105" s="8"/>
       <c r="C105" s="8"/>
@@ -11226,7 +11358,7 @@
       <c r="K105" s="8"/>
       <c r="L105" s="8"/>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="8"/>
       <c r="B106" s="8"/>
       <c r="C106" s="8"/>
@@ -11243,7 +11375,7 @@
       <c r="K106" s="8"/>
       <c r="L106" s="8"/>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="8"/>
       <c r="B107" s="8"/>
       <c r="C107" s="8"/>
@@ -11260,7 +11392,7 @@
       <c r="K107" s="8"/>
       <c r="L107" s="8"/>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="8"/>
       <c r="B108" s="8"/>
       <c r="C108" s="8"/>
@@ -11277,7 +11409,7 @@
       <c r="K108" s="8"/>
       <c r="L108" s="8"/>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="8"/>
       <c r="B109" s="8"/>
       <c r="C109" s="8"/>
@@ -11294,7 +11426,7 @@
       <c r="K109" s="8"/>
       <c r="L109" s="8"/>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="8"/>
       <c r="B110" s="8"/>
       <c r="C110" s="8"/>
@@ -11311,7 +11443,7 @@
       <c r="K110" s="8"/>
       <c r="L110" s="8"/>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="8"/>
       <c r="B111" s="8"/>
       <c r="C111" s="8"/>
@@ -11328,7 +11460,7 @@
       <c r="K111" s="8"/>
       <c r="L111" s="8"/>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="8"/>
       <c r="B112" s="8"/>
       <c r="C112" s="8"/>
@@ -11345,8 +11477,25 @@
       <c r="K112" s="8"/>
       <c r="L112" s="8"/>
     </row>
+    <row r="113" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="114" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="115" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="116" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="117" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="118" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="119" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="120" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="121" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="122" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="123" hidden="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <autoFilter ref="E1:E123" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="E1:E123" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Frontend"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -11370,7 +11519,7 @@
         <v>12</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>13</v>

--- a/Business Analysis/checkupp_sprint_plan_2026.xlsx
+++ b/Business Analysis/checkupp_sprint_plan_2026.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Business Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17D3AF12-7261-4541-9680-4FF1AF270EA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7B91493-6BDB-4450-BEF5-367657885E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint 01" sheetId="1" r:id="rId1"/>
     <sheet name="Sprint 01 Burndown" sheetId="4" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sprint 01'!$E$1:$E$123</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sprint 01'!$J$1:$J$112</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="77">
   <si>
     <t>Epic</t>
   </si>
@@ -522,1300 +522,7 @@
     <t>1.1, 1.2, 1.3, 1.4, 1.6, 1.7</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Define Time-Bucketed Screening Overview TypeScript Interfaces, Validation &amp; Sorting Constants</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-- Modify: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-api/src/modules/screenings/screening.validation.ts</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-- Modify: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-api/src/modules/screenings/screening.constants.ts</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-- In </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-api/src/modules/screenings/screening.constants.ts</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, define and export canonical type definitions for time-bucketed overview responses:
-TypeScript
-export interface ScreeningOverviewItem {
-  id: string; 
-  name: string;
-  date: string; // ISO-8601 date string
-  screeningType: 'cancer' | 'health' | 'immunization';
-  status: 'PENDING' | 'COMPLETED' | 'OVERDUE' | 'RESCHEDULED';
-  isOverdue: boolean;
-}
-export interface ScreeningOverviewResponse {
-  counts: {
-    upcoming: number;
-    due: number;
-    completed: number;
-  };
-  upcoming: ScreeningOverviewItem[];
-  due: ScreeningOverviewItem[];
-  completed: ScreeningOverviewItem[];
-}
-- In </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-api/src/modules/screenings/screening.validation.ts</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, ensure request schema validation for the overview route requires zero query parameters and relies strictly on authenticated JWT user context.</t>
-    </r>
-  </si>
-  <si>
     <t>1.1, 1.2, 1.3, 1.4, 1.7</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Implement </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>GET /me/screenings/overview</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Time-Bucketed Aggregation &amp; Chronological Sorting Endpoint
-1. Modify: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-api/src/modules/screenings/screening.service.ts</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">,  </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-api/src/modules/screenings/screening.controller.ts</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-api/src/modules/screenings/screening.routes.ts
-2. Database Querying</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: 
-- In </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-api/src/modules/screenings/screening.service.ts</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, implement </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>getScreeningOverview(userId: string): Promise&lt;ScreeningOverviewResponse&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>. 
-- Query Prisma (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>prisma.screeningDueItem.findMany</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>prisma.screeningRecord.findMany</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">) filtered </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>strictly by userId: userId</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> for multi-tenant isolation. (US 1.1–1.4 AC: Only screenings associated with the logged-in user's account must be displayed).
-3. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Date Bucketing Rules</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (US 1.2–1.4):
-- Calculate </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>daysUntilDue = Math.floor((dueDate.getTime() - Date.now()) / (1000 * 60 * 60 * 24))</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Upcoming</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (0 &lt;= daysUntilDue &lt;= 90): Items with non-completed status due within 0 to 90 days.
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Due</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (91 &lt;= daysUntilDue &lt;= 365 OR daysUntilDue &lt; 0): Items with non-completed status. If </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>daysUntilDue &lt; 0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, flag </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>isOverdue = true</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> and set</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> status = 'OVERDUE'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Completed</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: Items where status === 'COMPLETED'. Use the completion record date as </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>date</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.
-4. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Chronological Sorting Engine</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (US 1.7 AC):
-- Sort </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>upcoming</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> array chronologically ascending by </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>date</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (earliest upcoming screening at top).
-- Sort </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>due</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> array with </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Overdue pinned to top</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (sorted by most overdue first: smallest/most negative </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>daysUntilDue</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> ascending), followed by standard due screenings sorted chronologically ascending by </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>date</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.
-- Sort </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>completed</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> array chronologically </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>descending</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> by completion date (most recently completed at top).
-5. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Counts Calculation</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: Return </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>{ counts: { upcoming: upcoming.length, due: due.length, completed: completed.length }, upcoming, due, completed }</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.
-6. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Route Binding</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: Register </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>router.get('/overview', authMiddleware, getOverviewHandler) in checkupp-api/src/modules/screenings/screening.routes.ts</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Implement Background Cycle Recalculation Service &amp; Schedule Auto-Transition Logic</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-1. Modify </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-api/src/modules/screenings/screening.service.ts</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-api/src/modules/screenings/screening.controller.ts</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-2. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Auto-Transition Hook</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: In </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-api/src/modules/screenings/screening.service.ts</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, inside </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>saveScreeningRecord(userId, screeningId, recordPayload)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, after persisting the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>COMPLETED</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> record, immediately mark the active </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ScreeningDueItem</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> as </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>status: 'COMPLETED'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.
-2. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Next Cycle Calculation Engine</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (US 1.6 AC 3):
-- Fetch the canonical clinical guideline interval from </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ScreeningDefinition</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (e.g., intervalMonths: 12, 24, or 3).
-- Calculate </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>nextDueDate</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>= addMonths(recordPayload.completedDate, intervalMonths)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.
-- Create a new </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ScreeningDueItem</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> for </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>userId</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>with date: nextDueDate.toISOString()</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>status: 'PENDING'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.
-3. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Immediate Schedule Reflection</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: Ensure any subsequent call to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>GET /me/screenings/overview</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> immediately reflects the newly completed item under </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Completed</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> and appropriately places the newly generated next cycle item under </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Upcoming</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> or </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Due</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based on </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>nextDueDate</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
   </si>
   <si>
     <r>
@@ -3789,1341 +2496,10 @@
     <t>1.1, 1.2, 1.3, 1.4, 1.5, 1.6, 1.7, 1.8</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Define Prisma Schema Models, TypeScript Interfaces &amp; Joi Validation Schemas for Custom Conditions
-1. </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Modify </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-api/prisma/schema.prisma</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-api/src/modules/screenings/screening.constants.ts</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-api/src/modules/screenings/screening.validation.ts
-2. Prisma Schema</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (schema.prisma):
-- Add </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>CustomCondition</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>CustomConditionRecord</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> models with strict tenant isolation (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>userId</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> indexed FK):
-model CustomCondition {
-  id              String                  @id @default(uuid())
-  userId          String
-  conditionName   String
-  monitoringType  String                  // e.g. "Blood test", "Imaging/ Radiology", "Other: [custom]"
-  frequencyType   String                  // "Monthly" | "Every 3 Months" | "Every 6 Months" | "Annually" | "Custom"
-  customInterval  Int?                    // Numeric stepper value when frequencyType == "Custom"
-  customUnit      String?                 // "Days" | "Months" | "Years"
-  careProvider    String
-  createdAt       DateTime                @default(now())
-  updatedAt       DateTime                @updatedAt
-  records         CustomConditionRecord[]
-  @@index([userId])
-}
-model CustomConditionRecord {
-  id                 String          @id @default(uuid())
-  customConditionId  String
-  userId             String
-  checkDate          DateTime
-  outcomeNotes       String?
-  createdAt          DateTime        @default(now())
-  customCondition    CustomCondition @relation(fields: [customConditionId], references: [id], onDelete: Cascade)
-  @@index([customConditionId])
-  @@index([userId])
-}
-2. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Canonical TypeScript Interfaces</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (screening.constants.ts): Export matching DTO types </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>CustomConditionItem</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>CustomConditionRecordPayload</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.
-3. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Joi Validation Schemas</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (screening.validation.ts):
-- Define </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>createCustomConditionSchema</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">:
-a. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>conditionName</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: required non-empty string (&lt;= 100 chars).
-b. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>monitoringType</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: required string.
-c. f</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>requencyType</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: required enum (['Monthly', 'Every 3 Months', 'Every 6 Months', 'Annually', 'Custom']).
-d. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>customInterval</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: required positive integer when </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>frequencyType === 'Custom'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, optional otherwise.
-e. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>customUnit</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: required enum (['Days', 'Months', 'Years']) when </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>frequencyType === 'Custom'</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.
-f. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>careProvider</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: required non-empty string &lt; 100 chars).
-- Define </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>logCustomConditionRecordSchema</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">:
-a. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkDate</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: required ISO-8601 UTC date string &lt;= current system date).
-b. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>outcomeNotes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: optional string &lt;= 2000$ chars).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Implement POST /me/screenings/custom-conditions &amp; GET /me/screenings/custom-conditions CRUD Endpoints</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-1. Modify </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-api/src/modules/screenings/screening.service.ts</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-api/src/modules/screenings/screening.controller.ts</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-api/src/modules/screenings/screening.routes.ts</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-1. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Service Implementation</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (screening.service.ts):
-- Implement </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>createCustomCondition(userId: string, payload: CreateCustomConditionDTO): Promise&lt;CustomConditionItem&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> storing the entity in </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>prisma.customCondition</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.
-- Implement </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>getUserCustomConditions(userId: string): Promise&lt;CustomConditionItem[]&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> fetching all conditions for </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>userId</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>, including the most recent associated record (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>records: { orderBy: { checkDate: 'desc' }, take: 1 }</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>) to supply the "</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Last: [Date]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">" timestamp to the UI.
-2. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Controller &amp; Router Wiring</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">:
-- In </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>screening.controller.ts</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, add </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>createCustomConditionHandler</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>getCustomConditionsHandler</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> wrapped in </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>asyncHandler</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.
-- In </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>screening.routes.ts</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, register:
-a. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>router.post('/custom-conditions', authMiddleware, validate(createCustomConditionSchema), createCustomConditionHandler)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-b. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>router.get('/custom-conditions', authMiddleware, getCustomConditionsHandler)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-3. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Audit Logging</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">:
-- Trigger immutable audit event </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>CREATE_CUSTOM_CONDITION</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> via </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>audit.service.ts</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> upon successful creation.</t>
-    </r>
-  </si>
-  <si>
     <t>18.2, 18.3, 18.4</t>
   </si>
   <si>
     <t>18.1, 18.2, 18.3, 18.4, 18.5</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Implement POST /me/screenings/custom-conditions/:id/records Outcome Logging &amp; Due-Date Advancement Engine</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-1. Modify </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-api/src/modules/screenings/screening.service.ts</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>checkupp-api/src/modules/screenings/screening.controller.ts</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">checkupp-api/src/modules/screenings/screening.routes.ts
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">2. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Outcome Logging Service</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (screening.service.ts):
-- Implement </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>logCustomConditionRecord(userId: string, customConditionId: string, payload: CustomRecordPayload)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">:
-a. Verify </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>prisma.customCondition.findFirst({ where: { id: customConditionId, userId } })</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> exists </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(return 404 NotFoundError</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> if unauthorized/missing).
-b. Insert row into prisma.customConditionRecord.
-3. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Scheduling Engine Integration</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">:
-a. Calculate </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>nextDueDate</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> relative to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>payload.checkDate</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> based on frequency:
-- Monthly: addMonths(checkDate, 1)
-- Every 3 Months: addMonths(checkDate, 3)
-- Every 6 Months: addMonths(checkDate, 6)
-- Annually: addYears(checkDate, 1)
-- Custom: add </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>customInterval</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> according to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>customUnit</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (Days, Months, or Years).
-b. Ensure the custom condition item reflects this updated schedule when queried.
-4. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Router Binding</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: Register </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>router.post('/custom-conditions/:id/records', authMiddleware, validate(logCustomConditionRecordSchema), logCustomConditionRecordHandler)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
   </si>
   <si>
     <r>
@@ -7626,6 +5002,352 @@
       </rPr>
       <t xml:space="preserve"> when pressed (to open decision modal in FE-1.6).</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Define Time-Bucketed Screening Overview TypeScript Interfaces, Validation &amp; Sorting Constants</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Description:
+Establish the core API contract and data types required to serve the "Your Health Overview" dashboard (Epic 1) while ensuring compatibility with the new Specific Conditions architecture (Epic 18).
+Acceptance Criteria:
+TypeScript Interfaces: Modify checkupp-api/src/modules/screenings/screening.constants.ts to define and export the canonical type definitions for time-bucketed overview responses.
+Add the isSpecific flag to help the frontend render the custom condition UI badge.
+TypeScript
+export interface ScreeningOverviewItem {
+  id: string; // The ID of the ScreeningDueItem
+  name: string; // Mapped from either definition.name or specificCondition.conditionName
+  date: string; // ISO-8601 date string (dueDate or lastCompletedDate)
+  screeningType: 'cancer' | 'health' | 'immunization' | 'specific';
+  status: 'PENDING' | 'COMPLETED' | 'OVERDUE'; 
+  isOverdue: boolean;
+  isSpecific: boolean; // TRUE if this relies on specificConditionId
+}
+export interface ScreeningOverviewResponse {
+  counts: {
+    upcoming: number;
+    due: number;
+    completed: number;
+  };
+  upcoming: ScreeningOverviewItem[];
+  due: ScreeningOverviewItem[];
+  completed: ScreeningOverviewItem[];
+}
+Joi Validation: In checkupp-api/src/modules/screenings/screening.validation.ts, define the request schema validation for the overview route. It must explicitly require zero query parameters and rely strictly on the authenticated JWT user context (req.user.id) to fetch data.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Implement </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>GET /me/screenings/overview</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Time-Bucketed Aggregation &amp; Chronological Sorting Endpoint
+Description:
+Build the core data-fetching and sorting engine that powers the three top tabs (Upcoming, Due, Completed) on the "Your Health Overview" screen.
+Acceptance Criteria:
+Files to Modify: screening.service.ts, screening.controller.ts, screening.routes.ts.
+Database Querying:
+In screening.service.ts, implement getScreeningOverview(userId: string): Promise&lt;ScreeningOverviewResponse&gt;.
+Query prisma.screeningDueItem.findMany filtered strictly by userId.
+Crucial: Include polymorphic relations so the mapper can extract the correct name: include: { definition: true, specificCondition: true }.
+Date Bucketing Rules:
+Calculate exact calendar days: daysUntilDue = Math.floor((dueDate.getTime() - Date.now()) / (1000 * 60 * 60 * 24)).
+Upcoming: Items with non-completed status where 0 &lt;= daysUntilDue &lt;= 90.
+Due: Items with non-completed status where daysUntilDue &gt; 90 OR daysUntilDue &lt; 0. If daysUntilDue &lt; 0, flag isOverdue = true and override status to 'OVERDUE'.
+Completed: Items where status === 'COMPLETED'. Map the date property to lastCompletedDate.
+Chronological Sorting Engine:
+Sort upcoming array chronologically ascending by date (earliest upcoming screening at top).
+Sort due array with Overdue items pinned to the top (sorted by most overdue first: smallest/most negative daysUntilDue ascending), followed by standard due items sorted chronologically ascending by date.
+Sort completed array chronologically descending by completion date (most recently completed at top).
+Response Payload: Return { counts: { upcoming: upcoming.length, due: due.length, completed: completed.length }, upcoming, due, completed }.
+Route Binding: Register router.get('/overview', authMiddleware, getOverviewHandler) in screening.routes.ts.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Implement Background Cycle Recalculation Service &amp; Schedule Auto-Transition Logic</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Description:
+Ensure that when a user logs a result, the current due item is marked complete, and the next future due item is dynamically calculated and scheduled based on the clinical (or user-defined) frequency.
+Acceptance Criteria:
+Files to Modify: screening.service.ts, screening.controller.ts.
+Auto-Transition Hook: Inside the existing saveScreeningRecord(userId, screeningId, recordPayload) logic, immediately update the active ScreeningDueItem to status: 'COMPLETED' and set its lastCompletedDate to recordPayload.checkDate.
+Next Cycle Calculation Engine:
+Build logic to calculate the nextDueDate depending on the item type.
+If Standard Screening: Fetch canonical interval from ScreeningDefinition (or ScreeningPlan override). Use date-fns addMonths(recordPayload.checkDate, intervalMonths).
+If Specific Condition: Fetch specificInterval and specificUnit from SpecificCondition. Use dynamic date-fns addition based on the unit (e.g., if Unit is 'Days', use addDays; if 'Years', use addYears).
+Create a new ScreeningDueItem in the database for the userId with the calculated nextDueDate and status: 'PENDING'.
+Immediate Schedule Reflection: Ensure any subsequent call to GET /me/screenings/overview flawlessly places the newly completed item under the "Completed" tab and the newly generated next-cycle item under "Upcoming" or "Due".</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Define Prisma Schema, Interfaces &amp; Joi Validation for </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Specific Conditions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Description:
+Set up the foundational database schema, TypeScript DTOs, and request validation for the "Specific Conditions" feature, ensuring strict tenant isolation and integration with the existing "Your Health Overview" dashboard engine.
+Schema:
+model UserSpecificCondition {
+  id                    String                        @id @default(uuid())
+  userId                String
+  user                  User                          @relation(fields: [userId], references: [id], onDelete: Cascade)
+  // Directly maps to the 4 frontend inputs
+  conditionName         String
+  monitoringType        String                        // "Blood test", "Imaging/ Radiology", "Doctor Review", "Endoscopy", "Other: [custom]"
+  frequencyType         String                        // "Monthly", "Every 3 Months", "Every 6 Months", "Annually", "Custom"
+  customMonitoringType  Int?                          // Numeric stepper value (only populated if frequencyType == "Custom")
+  customFrequencyType   String?                       // "Days", "Months", "Years" (only populated if frequencyType == "Custom")
+  careProvider          String
+  createdAt             DateTime                      @default(now())
+  updatedAt             DateTime                      @updatedAt
+  records               UserSpecificConditionRecord[]
+  dueItems              ScreeningDueItem[]            // Powers the "Your Health Overview" dashboard
+  @@index([userId])
+}
+model UserSpecificConditionRecord {
+  id                        String                @id @default(uuid())
+  userSpecificConditionId   String
+  userSpecificCondition     UserSpecificCondition @relation(fields: [userSpecificConditionId], references: [id], onDelete: Cascade)
+  userId                    String
+  user                      User                  @relation(fields: [userId], references: [id], onDelete: Cascade)
+  // Directly maps to Screen 5 inputs
+  checkDate                 DateTime
+  outcomeNotes              String?
+  createdAt                 DateTime              @default(now())
+  updatedAt                 DateTime              @updatedAt
+  @@index([userSpecificConditionId])
+  @@index([userId])
+}
+// Ensure this is added to the existing ScreeningDueItem model:
+model ScreeningDueItem {
+  // ... existing fields ...
+  userSpecificConditionId   String?
+  userSpecificCondition     UserSpecificCondition? @relation(fields: [userSpecificConditionId], references: [id], onDelete: Cascade)
+}
+Technical Tasks:
+Modify prisma/schema.prisma:
+Create UserSpecificCondition model with fields: id, userId, conditionName, monitoringType, frequencyType, customMonitoringType (Int?), customFrequencyType (String?), careProvider, createdAt, updatedAt.
+Create UserSpecificConditionRecord model with fields: id, userSpecificConditionId, userId, checkDate, outcomeNotes, createdAt, updatedAt. (No attachments for V1).
+Crucial: Add userSpecificConditionId (String?) and the relation to the existing ScreeningDueItem model so custom conditions appear on the main dashboard.
+Update screening.constants.ts:
+Export the matching TypeScript interfaces (CreateSpecificConditionInput, etc.) so the frontend has a strict type contract.
+Update screening.validation.ts:
+Define createUserSpecificConditionSchema (Joi validation):
+conditionName, monitoringType, careProvider: required strings.
+frequencyType: required enum (Monthly, Every 3 Months, Every 6 Months, Annually, Custom).
+customMonitoringType: positive integer (required if frequencyType is 'Custom').
+customFrequencyType: enum (Days, Months, Years) (required if frequencyType is 'Custom').
+nextDueDate: required ISO-8601 date string.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Implement </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>POST</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &amp; </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>GET</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Endpoints for </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Specific Conditions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Description:
+Create the dedicated CRUD endpoints that allow a user to add a new specific condition to their profile and fetch their existing list.
+Technical Tasks:
+Service Implementation (screening.service.ts):
+Implement createUserSpecificCondition: Must wrap the creation in a prisma.$transaction. After creating the UserSpecificCondition, it must instantly create a ScreeningDueItem using the provided nextDueDate and calculated intervalMonths so it immediately appears on the user's Health Overview.
+Implement listUserSpecificConditions: Fetch all conditions for the authenticated userId. Use Prisma include to fetch the most recent associated record (records: { orderBy: { checkDate: 'desc' }, take: 1 }) to supply the "Last Checked" state to the UI.
+Controller &amp; Router (screening.controller.ts &amp; screening.routes.ts):
+Expose POST /me/screenings/specific-conditions (wrapped in Auth &amp; Joi validation).
+Expose GET /me/screenings/specific-conditions (wrapped in Auth).
+Audit Logging:
+Trigger an immutable audit event (screenings.specific_condition.create) via audit.service.ts upon successful creation.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Integrate Specific Conditions into the Central Record Logging Engine
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Description:
+Instead of creating a redundant, separate endpoint for logging custom outcomes, upgrade the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>existing POST /me/screenings/records</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> endpoint to intelligently handle Specific Conditions, keeping the mobile API calls unified.
+Technical Tasks:
+Modify createScreeningRecord inside screening.service.ts:
+Update the lookup logic to check if the incoming screeningDueItemId belongs to a UserSpecificCondition.
+If it does, route the data to create a UserSpecificConditionRecord (saving the checkDate and outcomeNotes).
+Complete the current ScreeningDueItem.
+Build the Specific Condition Auto-Advancement Engine:
+Calculate the nextDueDate based on the condition's frequency settings.
+If frequencyType is a standard dropdown (Monthly, Annually, etc.), add the exact months.
+If frequencyType is "Custom", run a switch statement on customFrequencyType to add accurate Days, Months, or Years based on the customMonitoringType stepper value.
+Generate the next ScreeningDueItem with the newly calculated date to ensure the recurrent loop continues on the dashboard.</t>
+    </r>
+  </si>
+  <si>
+    <t>Done</t>
   </si>
 </sst>
 </file>
@@ -7970,16 +5692,16 @@
                   <c:v>66</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>66</c:v>
+                  <c:v>62</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>66</c:v>
+                  <c:v>52</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>66</c:v>
+                  <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>66</c:v>
+                  <c:v>37</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9184,7 +6906,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:L123"/>
+  <dimension ref="A1:L112"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.88671875" style="12" customWidth="1"/>
@@ -9270,12 +6992,12 @@
         <v>1</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="K2" s="8"/>
       <c r="L2" s="8"/>
     </row>
-    <row r="3" spans="1:12" ht="408.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="408.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8">
         <v>2</v>
       </c>
@@ -9305,7 +7027,7 @@
         <v>2</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="K3" s="8"/>
       <c r="L3" s="8"/>
@@ -9318,7 +7040,7 @@
         <v>26</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>35</v>
@@ -9327,7 +7049,7 @@
         <v>23</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>25</v>
@@ -9340,7 +7062,7 @@
         <v>1</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="K4" s="8"/>
       <c r="L4" s="8"/>
@@ -9353,7 +7075,7 @@
         <v>26</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>36</v>
@@ -9362,7 +7084,7 @@
         <v>23</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>25</v>
@@ -9375,12 +7097,12 @@
         <v>5</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="K5" s="8"/>
       <c r="L5" s="8"/>
     </row>
-    <row r="6" spans="1:12" ht="331.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>5</v>
       </c>
@@ -9393,7 +7115,7 @@
         <v>23</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="G6" s="8" t="s">
         <v>25</v>
@@ -9405,7 +7127,9 @@
         <f t="array" ref="I6">_xlfn.SWITCH(H6,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J6" s="8"/>
+      <c r="J6" s="8" t="s">
+        <v>76</v>
+      </c>
       <c r="K6" s="8"/>
       <c r="L6" s="8"/>
     </row>
@@ -9426,7 +7150,7 @@
         <v>32</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>30</v>
@@ -9439,7 +7163,7 @@
         <v>3</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>20</v>
+        <v>76</v>
       </c>
       <c r="K7" s="8"/>
       <c r="L7" s="8"/>
@@ -9455,13 +7179,13 @@
         <v>42</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E8" s="8" t="s">
         <v>21</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>25</v>
@@ -9496,7 +7220,7 @@
         <v>21</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>30</v>
@@ -9531,7 +7255,7 @@
         <v>21</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>30</v>
@@ -9557,7 +7281,7 @@
         <v>26</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>38</v>
@@ -9566,7 +7290,7 @@
         <v>21</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>30</v>
@@ -9590,14 +7314,14 @@
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D12" s="8"/>
       <c r="E12" s="8" t="s">
         <v>21</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="G12" s="8" t="s">
         <v>22</v>
@@ -9609,7 +7333,9 @@
         <f t="array" ref="I12">_xlfn.SWITCH(H12,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J12" s="8"/>
+      <c r="J12" s="8" t="s">
+        <v>20</v>
+      </c>
       <c r="K12" s="8"/>
       <c r="L12" s="8"/>
     </row>
@@ -9626,7 +7352,7 @@
         <v>21</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>30</v>
@@ -9638,17 +7364,19 @@
         <f t="array" ref="I13">_xlfn.SWITCH(H13,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J13" s="8"/>
+      <c r="J13" s="8" t="s">
+        <v>20</v>
+      </c>
       <c r="K13" s="8"/>
       <c r="L13" s="8"/>
     </row>
-    <row r="14" spans="1:12" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
         <v>13</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>37</v>
@@ -9657,7 +7385,7 @@
         <v>32</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G14" s="8" t="s">
         <v>30</v>
@@ -9682,13 +7410,13 @@
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
       <c r="D15" s="8" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>23</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>25</v>
@@ -9700,9 +7428,11 @@
         <f t="array" ref="I15">_xlfn.SWITCH(H15,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J15" s="8"/>
+      <c r="J15" s="8" t="s">
+        <v>76</v>
+      </c>
       <c r="K15" s="8" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="L15" s="8"/>
     </row>
@@ -9713,13 +7443,13 @@
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
       <c r="D16" s="8" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>23</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="G16" s="8" t="s">
         <v>25</v>
@@ -9731,9 +7461,11 @@
         <f t="array" ref="I16">_xlfn.SWITCH(H16,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J16" s="8"/>
+      <c r="J16" s="8" t="s">
+        <v>76</v>
+      </c>
       <c r="K16" s="8" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="L16" s="8"/>
     </row>
@@ -9750,7 +7482,7 @@
         <v>23</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="G17" s="8" t="s">
         <v>25</v>
@@ -9762,9 +7494,11 @@
         <f t="array" ref="I17">_xlfn.SWITCH(H17,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J17" s="8"/>
+      <c r="J17" s="8" t="s">
+        <v>76</v>
+      </c>
       <c r="K17" s="8" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="L17" s="8"/>
     </row>
@@ -9774,14 +7508,14 @@
       </c>
       <c r="B18" s="8"/>
       <c r="C18" s="8" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D18" s="8"/>
       <c r="E18" s="8" t="s">
         <v>32</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G18" s="8" t="s">
         <v>30</v>
@@ -9793,11 +7527,13 @@
         <f t="array" ref="I18">_xlfn.SWITCH(H18,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J18" s="8"/>
+      <c r="J18" s="8" t="s">
+        <v>76</v>
+      </c>
       <c r="K18" s="8"/>
       <c r="L18" s="8"/>
     </row>
-    <row r="19" spans="1:12" ht="383.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" ht="383.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8">
         <v>18</v>
       </c>
@@ -9810,7 +7546,7 @@
         <v>21</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="G19" s="8" t="s">
         <v>22</v>
@@ -9822,7 +7558,9 @@
         <f t="array" ref="I19">_xlfn.SWITCH(H19,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J19" s="8"/>
+      <c r="J19" s="8" t="s">
+        <v>76</v>
+      </c>
       <c r="K19" s="8"/>
       <c r="L19" s="8"/>
     </row>
@@ -9837,7 +7575,7 @@
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="10" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="G20" s="8" t="s">
         <v>22</v>
@@ -9849,7 +7587,9 @@
         <f t="array" ref="I20">_xlfn.SWITCH(H20,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J20" s="8"/>
+      <c r="J20" s="8" t="s">
+        <v>76</v>
+      </c>
       <c r="K20" s="8"/>
       <c r="L20" s="8"/>
     </row>
@@ -9866,7 +7606,7 @@
         <v>21</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G21" s="8" t="s">
         <v>22</v>
@@ -9878,7 +7618,9 @@
         <f t="array" ref="I21">_xlfn.SWITCH(H21,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J21" s="8"/>
+      <c r="J21" s="8" t="s">
+        <v>20</v>
+      </c>
       <c r="K21" s="8"/>
       <c r="L21" s="8"/>
     </row>
@@ -9888,14 +7630,14 @@
       </c>
       <c r="B22" s="8"/>
       <c r="C22" s="8" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D22" s="8"/>
       <c r="E22" s="8" t="s">
         <v>21</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="G22" s="8" t="s">
         <v>22</v>
@@ -9907,7 +7649,9 @@
         <f t="array" ref="I22">_xlfn.SWITCH(H22,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J22" s="8"/>
+      <c r="J22" s="8" t="s">
+        <v>20</v>
+      </c>
       <c r="K22" s="8"/>
       <c r="L22" s="8"/>
     </row>
@@ -9924,7 +7668,7 @@
         <v>21</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G23" s="8" t="s">
         <v>22</v>
@@ -9936,7 +7680,9 @@
         <f t="array" ref="I23">_xlfn.SWITCH(H23,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J23" s="8"/>
+      <c r="J23" s="8" t="s">
+        <v>20</v>
+      </c>
       <c r="K23" s="8"/>
       <c r="L23" s="8"/>
     </row>
@@ -9953,7 +7699,7 @@
         <v>21</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G24" s="8" t="s">
         <v>22</v>
@@ -9965,7 +7711,9 @@
         <f t="array" ref="I24">_xlfn.SWITCH(H24,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J24" s="8"/>
+      <c r="J24" s="8" t="s">
+        <v>20</v>
+      </c>
       <c r="K24" s="8"/>
       <c r="L24" s="8"/>
     </row>
@@ -9975,14 +7723,14 @@
       </c>
       <c r="B25" s="8"/>
       <c r="C25" s="8" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D25" s="8"/>
       <c r="E25" s="8" t="s">
         <v>32</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="G25" s="8" t="s">
         <v>30</v>
@@ -9994,7 +7742,9 @@
         <f t="array" ref="I25">_xlfn.SWITCH(H25,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J25" s="8"/>
+      <c r="J25" s="8" t="s">
+        <v>76</v>
+      </c>
       <c r="K25" s="8"/>
       <c r="L25" s="8"/>
     </row>
@@ -11477,22 +9227,11 @@
       <c r="K112" s="8"/>
       <c r="L112" s="8"/>
     </row>
-    <row r="113" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="114" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="115" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="116" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="117" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="118" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="119" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="120" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="121" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="122" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="123" hidden="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <autoFilter ref="E1:E123" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="J1:J112" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="Frontend"/>
+        <filter val="ToDo"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -11519,7 +9258,7 @@
         <v>12</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>13</v>
@@ -11636,14 +9375,14 @@
       </c>
       <c r="C7" s="4">
         <f>82-SUM(E$2:E7)</f>
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D7" s="1">
         <f t="shared" si="0"/>
         <v>30.75</v>
       </c>
       <c r="E7" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
@@ -11655,14 +9394,14 @@
       </c>
       <c r="C8" s="4">
         <f>82-SUM(E$2:E8)</f>
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="D8" s="1">
         <f t="shared" si="0"/>
         <v>20.5</v>
       </c>
       <c r="E8" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
@@ -11674,14 +9413,14 @@
       </c>
       <c r="C9" s="4">
         <f>82-SUM(E$2:E9)</f>
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="D9" s="1">
         <f t="shared" si="0"/>
         <v>10.25</v>
       </c>
       <c r="E9" s="2">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
@@ -11693,7 +9432,7 @@
       </c>
       <c r="C10" s="4">
         <f>82-SUM(E$2:E10)</f>
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="D10" s="1">
         <f t="shared" si="0"/>

--- a/Business Analysis/checkupp_sprint_plan_2026.xlsx
+++ b/Business Analysis/checkupp_sprint_plan_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Business Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7B91493-6BDB-4450-BEF5-367657885E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB9CE57E-1583-4BD1-804B-D63B90208C71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Sprint 01 Burndown" sheetId="4" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sprint 01'!$J$1:$J$112</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sprint 01'!$E$1:$E$112</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="76">
   <si>
     <t>Epic</t>
   </si>
@@ -119,9 +119,6 @@
   </si>
   <si>
     <t>XS</t>
-  </si>
-  <si>
-    <t>ToDo</t>
   </si>
   <si>
     <t>Frontend</t>
@@ -5701,7 +5698,7 @@
                   <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>37</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6905,7 +6902,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:L112"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -6962,18 +6958,18 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="49.2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="49.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="8">
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C2" s="8">
         <v>0.1</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E2" s="8" t="s">
         <v>16</v>
@@ -6992,67 +6988,67 @@
         <v>1</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K2" s="8"/>
       <c r="L2" s="8"/>
     </row>
-    <row r="3" spans="1:12" ht="408.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="408.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8">
         <v>2</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C3" s="8">
         <v>1.1000000000000001</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E3" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="G3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>22</v>
-      </c>
       <c r="H3" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I3" s="8" cm="1">
         <f t="array" ref="I3">_xlfn.SWITCH(H3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K3" s="8"/>
       <c r="L3" s="8"/>
     </row>
-    <row r="4" spans="1:12" ht="408.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="408.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8">
         <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H4" s="8" t="s">
         <v>19</v>
@@ -7062,47 +7058,47 @@
         <v>1</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K4" s="8"/>
       <c r="L4" s="8"/>
     </row>
-    <row r="5" spans="1:12" ht="408.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="408.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8">
         <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I5" s="8" cm="1">
         <f t="array" ref="I5">_xlfn.SWITCH(H5,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K5" s="8"/>
       <c r="L5" s="8"/>
     </row>
-    <row r="6" spans="1:12" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
         <v>5</v>
       </c>
@@ -7112,58 +7108,58 @@
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I6" s="8" cm="1">
         <f t="array" ref="I6">_xlfn.SWITCH(H6,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K6" s="8"/>
       <c r="L6" s="8"/>
     </row>
-    <row r="7" spans="1:12" ht="272.39999999999998" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="272.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8">
         <v>6</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I7" s="8" cm="1">
         <f t="array" ref="I7">_xlfn.SWITCH(H7,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K7" s="8"/>
       <c r="L7" s="8"/>
@@ -7173,32 +7169,32 @@
         <v>7</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I8" s="8" cm="1">
         <f t="array" ref="I8">_xlfn.SWITCH(H8,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="K8" s="8"/>
       <c r="L8" s="8"/>
@@ -7208,32 +7204,32 @@
         <v>8</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D9" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="G9" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>30</v>
-      </c>
       <c r="H9" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I9" s="8" cm="1">
         <f t="array" ref="I9">_xlfn.SWITCH(H9,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="K9" s="8"/>
       <c r="L9" s="8"/>
@@ -7243,32 +7239,32 @@
         <v>9</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D10" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="G10" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E10" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>30</v>
-      </c>
       <c r="H10" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I10" s="8" cm="1">
         <f t="array" ref="I10">_xlfn.SWITCH(H10,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="K10" s="8"/>
       <c r="L10" s="8"/>
@@ -7278,32 +7274,32 @@
         <v>10</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>49</v>
-      </c>
       <c r="G11" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" s="8" t="s">
         <v>30</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>31</v>
       </c>
       <c r="I11" s="8" cm="1">
         <f t="array" ref="I11">_xlfn.SWITCH(H11,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="K11" s="8"/>
       <c r="L11" s="8"/>
@@ -7314,27 +7310,27 @@
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D12" s="8"/>
       <c r="E12" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="G12" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F12" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>22</v>
-      </c>
       <c r="H12" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I12" s="8" cm="1">
         <f t="array" ref="I12">_xlfn.SWITCH(H12,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="K12" s="8"/>
       <c r="L12" s="8"/>
@@ -7349,23 +7345,23 @@
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I13" s="8" cm="1">
         <f t="array" ref="I13">_xlfn.SWITCH(H13,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="K13" s="8"/>
       <c r="L13" s="8"/>
@@ -7376,100 +7372,100 @@
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G14" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H14" s="8" t="s">
         <v>30</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>31</v>
       </c>
       <c r="I14" s="8" cm="1">
         <f t="array" ref="I14">_xlfn.SWITCH(H14,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="K14" s="8"/>
       <c r="L14" s="8"/>
     </row>
-    <row r="15" spans="1:12" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
         <v>14</v>
       </c>
       <c r="B15" s="8"/>
       <c r="C15" s="8"/>
       <c r="D15" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I15" s="8" cm="1">
         <f t="array" ref="I15">_xlfn.SWITCH(H15,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L15" s="8"/>
     </row>
-    <row r="16" spans="1:12" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
         <v>15</v>
       </c>
       <c r="B16" s="8"/>
       <c r="C16" s="8"/>
       <c r="D16" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I16" s="8" cm="1">
         <f t="array" ref="I16">_xlfn.SWITCH(H16,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L16" s="8"/>
     </row>
-    <row r="17" spans="1:12" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
         <v>16</v>
       </c>
@@ -7479,61 +7475,61 @@
       </c>
       <c r="D17" s="8"/>
       <c r="E17" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I17" s="8" cm="1">
         <f t="array" ref="I17">_xlfn.SWITCH(H17,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L17" s="8"/>
     </row>
-    <row r="18" spans="1:12" ht="315.60000000000002" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" ht="315.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
         <v>17</v>
       </c>
       <c r="B18" s="8"/>
       <c r="C18" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D18" s="8"/>
       <c r="E18" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I18" s="8" cm="1">
         <f t="array" ref="I18">_xlfn.SWITCH(H18,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K18" s="8"/>
       <c r="L18" s="8"/>
     </row>
-    <row r="19" spans="1:12" ht="383.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" ht="383.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8">
         <v>18</v>
       </c>
@@ -7543,28 +7539,28 @@
       </c>
       <c r="D19" s="8"/>
       <c r="E19" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G19" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F19" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>22</v>
-      </c>
       <c r="H19" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I19" s="8" cm="1">
         <f t="array" ref="I19">_xlfn.SWITCH(H19,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K19" s="8"/>
       <c r="L19" s="8"/>
     </row>
-    <row r="20" spans="1:12" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
         <v>19</v>
       </c>
@@ -7573,22 +7569,24 @@
         <v>18.2</v>
       </c>
       <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
+      <c r="E20" s="8" t="s">
+        <v>20</v>
+      </c>
       <c r="F20" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I20" s="8" cm="1">
         <f t="array" ref="I20">_xlfn.SWITCH(H20,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K20" s="8"/>
       <c r="L20" s="8"/>
@@ -7603,23 +7601,23 @@
       </c>
       <c r="D21" s="8"/>
       <c r="E21" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G21" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F21" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>22</v>
-      </c>
       <c r="H21" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I21" s="8" cm="1">
         <f t="array" ref="I21">_xlfn.SWITCH(H21,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="K21" s="8"/>
       <c r="L21" s="8"/>
@@ -7630,27 +7628,27 @@
       </c>
       <c r="B22" s="8"/>
       <c r="C22" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D22" s="8"/>
       <c r="E22" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="G22" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>22</v>
-      </c>
       <c r="H22" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I22" s="8" cm="1">
         <f t="array" ref="I22">_xlfn.SWITCH(H22,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="K22" s="8"/>
       <c r="L22" s="8"/>
@@ -7665,23 +7663,23 @@
       </c>
       <c r="D23" s="8"/>
       <c r="E23" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="G23" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F23" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="G23" s="8" t="s">
-        <v>22</v>
-      </c>
       <c r="H23" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I23" s="8" cm="1">
         <f t="array" ref="I23">_xlfn.SWITCH(H23,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="K23" s="8"/>
       <c r="L23" s="8"/>
@@ -7696,59 +7694,59 @@
       </c>
       <c r="D24" s="8"/>
       <c r="E24" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="G24" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F24" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>22</v>
-      </c>
       <c r="H24" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I24" s="8" cm="1">
         <f t="array" ref="I24">_xlfn.SWITCH(H24,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="K24" s="8"/>
       <c r="L24" s="8"/>
     </row>
-    <row r="25" spans="1:12" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A25" s="8">
         <v>24</v>
       </c>
       <c r="B25" s="8"/>
       <c r="C25" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D25" s="8"/>
       <c r="E25" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G25" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H25" s="8" t="s">
         <v>30</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>31</v>
       </c>
       <c r="I25" s="8" cm="1">
         <f t="array" ref="I25">_xlfn.SWITCH(H25,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K25" s="8"/>
       <c r="L25" s="8"/>
     </row>
-    <row r="26" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="8"/>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -7765,7 +7763,7 @@
       <c r="K26" s="8"/>
       <c r="L26" s="8"/>
     </row>
-    <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="8"/>
       <c r="B27" s="8"/>
       <c r="C27" s="8"/>
@@ -7782,7 +7780,7 @@
       <c r="K27" s="8"/>
       <c r="L27" s="8"/>
     </row>
-    <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="8"/>
       <c r="B28" s="8"/>
       <c r="C28" s="8"/>
@@ -7799,7 +7797,7 @@
       <c r="K28" s="8"/>
       <c r="L28" s="8"/>
     </row>
-    <row r="29" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="8"/>
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
@@ -7816,7 +7814,7 @@
       <c r="K29" s="8"/>
       <c r="L29" s="8"/>
     </row>
-    <row r="30" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="8"/>
       <c r="B30" s="8"/>
       <c r="C30" s="8"/>
@@ -7833,7 +7831,7 @@
       <c r="K30" s="8"/>
       <c r="L30" s="8"/>
     </row>
-    <row r="31" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="8"/>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
@@ -7850,7 +7848,7 @@
       <c r="K31" s="8"/>
       <c r="L31" s="8"/>
     </row>
-    <row r="32" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="8"/>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
@@ -7867,7 +7865,7 @@
       <c r="K32" s="8"/>
       <c r="L32" s="8"/>
     </row>
-    <row r="33" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="8"/>
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
@@ -7884,7 +7882,7 @@
       <c r="K33" s="8"/>
       <c r="L33" s="8"/>
     </row>
-    <row r="34" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="8"/>
       <c r="B34" s="8"/>
       <c r="C34" s="8"/>
@@ -7901,7 +7899,7 @@
       <c r="K34" s="8"/>
       <c r="L34" s="8"/>
     </row>
-    <row r="35" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="8"/>
       <c r="B35" s="8"/>
       <c r="C35" s="8"/>
@@ -7918,7 +7916,7 @@
       <c r="K35" s="8"/>
       <c r="L35" s="8"/>
     </row>
-    <row r="36" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="8"/>
       <c r="B36" s="8"/>
       <c r="C36" s="8"/>
@@ -7935,7 +7933,7 @@
       <c r="K36" s="8"/>
       <c r="L36" s="8"/>
     </row>
-    <row r="37" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
@@ -7952,7 +7950,7 @@
       <c r="K37" s="8"/>
       <c r="L37" s="8"/>
     </row>
-    <row r="38" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="8"/>
       <c r="B38" s="8"/>
       <c r="C38" s="8"/>
@@ -7969,7 +7967,7 @@
       <c r="K38" s="8"/>
       <c r="L38" s="8"/>
     </row>
-    <row r="39" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="8"/>
       <c r="B39" s="8"/>
       <c r="C39" s="8"/>
@@ -7986,7 +7984,7 @@
       <c r="K39" s="8"/>
       <c r="L39" s="8"/>
     </row>
-    <row r="40" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="8"/>
       <c r="B40" s="8"/>
       <c r="C40" s="8"/>
@@ -8003,7 +8001,7 @@
       <c r="K40" s="8"/>
       <c r="L40" s="8"/>
     </row>
-    <row r="41" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="8"/>
       <c r="B41" s="8"/>
       <c r="C41" s="8"/>
@@ -8020,7 +8018,7 @@
       <c r="K41" s="8"/>
       <c r="L41" s="8"/>
     </row>
-    <row r="42" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="8"/>
       <c r="B42" s="8"/>
       <c r="C42" s="8"/>
@@ -8037,7 +8035,7 @@
       <c r="K42" s="8"/>
       <c r="L42" s="8"/>
     </row>
-    <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="8"/>
       <c r="B43" s="8"/>
       <c r="C43" s="8"/>
@@ -8054,7 +8052,7 @@
       <c r="K43" s="8"/>
       <c r="L43" s="8"/>
     </row>
-    <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="8"/>
       <c r="B44" s="8"/>
       <c r="C44" s="8"/>
@@ -8071,7 +8069,7 @@
       <c r="K44" s="8"/>
       <c r="L44" s="8"/>
     </row>
-    <row r="45" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="8"/>
       <c r="B45" s="8"/>
       <c r="C45" s="8"/>
@@ -8088,7 +8086,7 @@
       <c r="K45" s="8"/>
       <c r="L45" s="8"/>
     </row>
-    <row r="46" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="8"/>
       <c r="B46" s="8"/>
       <c r="C46" s="8"/>
@@ -8105,7 +8103,7 @@
       <c r="K46" s="8"/>
       <c r="L46" s="8"/>
     </row>
-    <row r="47" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="8"/>
       <c r="B47" s="8"/>
       <c r="C47" s="8"/>
@@ -8122,7 +8120,7 @@
       <c r="K47" s="8"/>
       <c r="L47" s="8"/>
     </row>
-    <row r="48" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="8"/>
       <c r="B48" s="8"/>
       <c r="C48" s="8"/>
@@ -8139,7 +8137,7 @@
       <c r="K48" s="8"/>
       <c r="L48" s="8"/>
     </row>
-    <row r="49" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="8"/>
       <c r="B49" s="8"/>
       <c r="C49" s="8"/>
@@ -8156,7 +8154,7 @@
       <c r="K49" s="8"/>
       <c r="L49" s="8"/>
     </row>
-    <row r="50" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="8"/>
       <c r="B50" s="8"/>
       <c r="C50" s="8"/>
@@ -8173,7 +8171,7 @@
       <c r="K50" s="8"/>
       <c r="L50" s="8"/>
     </row>
-    <row r="51" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="8"/>
       <c r="B51" s="8"/>
       <c r="C51" s="8"/>
@@ -8190,7 +8188,7 @@
       <c r="K51" s="8"/>
       <c r="L51" s="8"/>
     </row>
-    <row r="52" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="8"/>
       <c r="B52" s="8"/>
       <c r="C52" s="8"/>
@@ -8207,7 +8205,7 @@
       <c r="K52" s="8"/>
       <c r="L52" s="8"/>
     </row>
-    <row r="53" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="8"/>
       <c r="B53" s="8"/>
       <c r="C53" s="8"/>
@@ -8224,7 +8222,7 @@
       <c r="K53" s="8"/>
       <c r="L53" s="8"/>
     </row>
-    <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="8"/>
       <c r="B54" s="8"/>
       <c r="C54" s="8"/>
@@ -8241,7 +8239,7 @@
       <c r="K54" s="8"/>
       <c r="L54" s="8"/>
     </row>
-    <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="8"/>
       <c r="B55" s="8"/>
       <c r="C55" s="8"/>
@@ -8258,7 +8256,7 @@
       <c r="K55" s="8"/>
       <c r="L55" s="8"/>
     </row>
-    <row r="56" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="8"/>
       <c r="B56" s="8"/>
       <c r="C56" s="8"/>
@@ -8275,7 +8273,7 @@
       <c r="K56" s="8"/>
       <c r="L56" s="8"/>
     </row>
-    <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="8"/>
       <c r="B57" s="8"/>
       <c r="C57" s="8"/>
@@ -8292,7 +8290,7 @@
       <c r="K57" s="8"/>
       <c r="L57" s="8"/>
     </row>
-    <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="8"/>
       <c r="B58" s="8"/>
       <c r="C58" s="8"/>
@@ -8309,7 +8307,7 @@
       <c r="K58" s="8"/>
       <c r="L58" s="8"/>
     </row>
-    <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="8"/>
       <c r="B59" s="8"/>
       <c r="C59" s="8"/>
@@ -8326,7 +8324,7 @@
       <c r="K59" s="8"/>
       <c r="L59" s="8"/>
     </row>
-    <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="8"/>
       <c r="B60" s="8"/>
       <c r="C60" s="8"/>
@@ -8343,7 +8341,7 @@
       <c r="K60" s="8"/>
       <c r="L60" s="8"/>
     </row>
-    <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="8"/>
       <c r="B61" s="8"/>
       <c r="C61" s="8"/>
@@ -8360,7 +8358,7 @@
       <c r="K61" s="8"/>
       <c r="L61" s="8"/>
     </row>
-    <row r="62" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="8"/>
       <c r="B62" s="8"/>
       <c r="C62" s="8"/>
@@ -8377,7 +8375,7 @@
       <c r="K62" s="8"/>
       <c r="L62" s="8"/>
     </row>
-    <row r="63" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="8"/>
       <c r="B63" s="8"/>
       <c r="C63" s="8"/>
@@ -8394,7 +8392,7 @@
       <c r="K63" s="8"/>
       <c r="L63" s="8"/>
     </row>
-    <row r="64" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="8"/>
       <c r="B64" s="8"/>
       <c r="C64" s="8"/>
@@ -8411,7 +8409,7 @@
       <c r="K64" s="8"/>
       <c r="L64" s="8"/>
     </row>
-    <row r="65" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" s="8"/>
       <c r="B65" s="8"/>
       <c r="C65" s="8"/>
@@ -8428,7 +8426,7 @@
       <c r="K65" s="8"/>
       <c r="L65" s="8"/>
     </row>
-    <row r="66" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" s="8"/>
       <c r="B66" s="8"/>
       <c r="C66" s="8"/>
@@ -8445,7 +8443,7 @@
       <c r="K66" s="8"/>
       <c r="L66" s="8"/>
     </row>
-    <row r="67" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" s="8"/>
       <c r="B67" s="8"/>
       <c r="C67" s="8"/>
@@ -8462,7 +8460,7 @@
       <c r="K67" s="8"/>
       <c r="L67" s="8"/>
     </row>
-    <row r="68" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="8"/>
       <c r="B68" s="8"/>
       <c r="C68" s="8"/>
@@ -8479,7 +8477,7 @@
       <c r="K68" s="8"/>
       <c r="L68" s="8"/>
     </row>
-    <row r="69" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" s="8"/>
       <c r="B69" s="8"/>
       <c r="C69" s="8"/>
@@ -8496,7 +8494,7 @@
       <c r="K69" s="8"/>
       <c r="L69" s="8"/>
     </row>
-    <row r="70" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" s="8"/>
       <c r="B70" s="8"/>
       <c r="C70" s="8"/>
@@ -8513,7 +8511,7 @@
       <c r="K70" s="8"/>
       <c r="L70" s="8"/>
     </row>
-    <row r="71" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" s="8"/>
       <c r="B71" s="8"/>
       <c r="C71" s="8"/>
@@ -8530,7 +8528,7 @@
       <c r="K71" s="8"/>
       <c r="L71" s="8"/>
     </row>
-    <row r="72" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" s="8"/>
       <c r="B72" s="8"/>
       <c r="C72" s="8"/>
@@ -8547,7 +8545,7 @@
       <c r="K72" s="8"/>
       <c r="L72" s="8"/>
     </row>
-    <row r="73" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="8"/>
       <c r="B73" s="8"/>
       <c r="C73" s="8"/>
@@ -8564,7 +8562,7 @@
       <c r="K73" s="8"/>
       <c r="L73" s="8"/>
     </row>
-    <row r="74" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" s="8"/>
       <c r="B74" s="8"/>
       <c r="C74" s="8"/>
@@ -8581,7 +8579,7 @@
       <c r="K74" s="8"/>
       <c r="L74" s="8"/>
     </row>
-    <row r="75" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="8"/>
       <c r="B75" s="8"/>
       <c r="C75" s="8"/>
@@ -8598,7 +8596,7 @@
       <c r="K75" s="8"/>
       <c r="L75" s="8"/>
     </row>
-    <row r="76" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="8"/>
       <c r="B76" s="8"/>
       <c r="C76" s="8"/>
@@ -8615,7 +8613,7 @@
       <c r="K76" s="8"/>
       <c r="L76" s="8"/>
     </row>
-    <row r="77" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" s="8"/>
       <c r="B77" s="8"/>
       <c r="C77" s="8"/>
@@ -8632,7 +8630,7 @@
       <c r="K77" s="8"/>
       <c r="L77" s="8"/>
     </row>
-    <row r="78" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" s="8"/>
       <c r="B78" s="8"/>
       <c r="C78" s="8"/>
@@ -8649,7 +8647,7 @@
       <c r="K78" s="8"/>
       <c r="L78" s="8"/>
     </row>
-    <row r="79" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" s="8"/>
       <c r="B79" s="8"/>
       <c r="C79" s="8"/>
@@ -8666,7 +8664,7 @@
       <c r="K79" s="8"/>
       <c r="L79" s="8"/>
     </row>
-    <row r="80" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" s="8"/>
       <c r="B80" s="8"/>
       <c r="C80" s="8"/>
@@ -8683,7 +8681,7 @@
       <c r="K80" s="8"/>
       <c r="L80" s="8"/>
     </row>
-    <row r="81" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" s="8"/>
       <c r="B81" s="8"/>
       <c r="C81" s="8"/>
@@ -8700,7 +8698,7 @@
       <c r="K81" s="8"/>
       <c r="L81" s="8"/>
     </row>
-    <row r="82" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" s="8"/>
       <c r="B82" s="8"/>
       <c r="C82" s="8"/>
@@ -8717,7 +8715,7 @@
       <c r="K82" s="8"/>
       <c r="L82" s="8"/>
     </row>
-    <row r="83" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" s="8"/>
       <c r="B83" s="8"/>
       <c r="C83" s="8"/>
@@ -8734,7 +8732,7 @@
       <c r="K83" s="8"/>
       <c r="L83" s="8"/>
     </row>
-    <row r="84" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" s="8"/>
       <c r="B84" s="8"/>
       <c r="C84" s="8"/>
@@ -8751,7 +8749,7 @@
       <c r="K84" s="8"/>
       <c r="L84" s="8"/>
     </row>
-    <row r="85" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" s="8"/>
       <c r="B85" s="8"/>
       <c r="C85" s="8"/>
@@ -8768,7 +8766,7 @@
       <c r="K85" s="8"/>
       <c r="L85" s="8"/>
     </row>
-    <row r="86" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" s="8"/>
       <c r="B86" s="8"/>
       <c r="C86" s="8"/>
@@ -8785,7 +8783,7 @@
       <c r="K86" s="8"/>
       <c r="L86" s="8"/>
     </row>
-    <row r="87" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" s="8"/>
       <c r="B87" s="8"/>
       <c r="C87" s="8"/>
@@ -8802,7 +8800,7 @@
       <c r="K87" s="8"/>
       <c r="L87" s="8"/>
     </row>
-    <row r="88" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" s="8"/>
       <c r="B88" s="8"/>
       <c r="C88" s="8"/>
@@ -8819,7 +8817,7 @@
       <c r="K88" s="8"/>
       <c r="L88" s="8"/>
     </row>
-    <row r="89" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" s="8"/>
       <c r="B89" s="8"/>
       <c r="C89" s="8"/>
@@ -8836,7 +8834,7 @@
       <c r="K89" s="8"/>
       <c r="L89" s="8"/>
     </row>
-    <row r="90" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" s="8"/>
       <c r="B90" s="8"/>
       <c r="C90" s="8"/>
@@ -8853,7 +8851,7 @@
       <c r="K90" s="8"/>
       <c r="L90" s="8"/>
     </row>
-    <row r="91" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" s="8"/>
       <c r="B91" s="8"/>
       <c r="C91" s="8"/>
@@ -8870,7 +8868,7 @@
       <c r="K91" s="8"/>
       <c r="L91" s="8"/>
     </row>
-    <row r="92" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" s="8"/>
       <c r="B92" s="8"/>
       <c r="C92" s="8"/>
@@ -8887,7 +8885,7 @@
       <c r="K92" s="8"/>
       <c r="L92" s="8"/>
     </row>
-    <row r="93" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" s="8"/>
       <c r="B93" s="8"/>
       <c r="C93" s="8"/>
@@ -8904,7 +8902,7 @@
       <c r="K93" s="8"/>
       <c r="L93" s="8"/>
     </row>
-    <row r="94" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" s="8"/>
       <c r="B94" s="8"/>
       <c r="C94" s="8"/>
@@ -8921,7 +8919,7 @@
       <c r="K94" s="8"/>
       <c r="L94" s="8"/>
     </row>
-    <row r="95" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" s="8"/>
       <c r="B95" s="8"/>
       <c r="C95" s="8"/>
@@ -8938,7 +8936,7 @@
       <c r="K95" s="8"/>
       <c r="L95" s="8"/>
     </row>
-    <row r="96" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" s="8"/>
       <c r="B96" s="8"/>
       <c r="C96" s="8"/>
@@ -8955,7 +8953,7 @@
       <c r="K96" s="8"/>
       <c r="L96" s="8"/>
     </row>
-    <row r="97" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" s="8"/>
       <c r="B97" s="8"/>
       <c r="C97" s="8"/>
@@ -8972,7 +8970,7 @@
       <c r="K97" s="8"/>
       <c r="L97" s="8"/>
     </row>
-    <row r="98" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" s="8"/>
       <c r="B98" s="8"/>
       <c r="C98" s="8"/>
@@ -8989,7 +8987,7 @@
       <c r="K98" s="8"/>
       <c r="L98" s="8"/>
     </row>
-    <row r="99" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99" s="8"/>
       <c r="B99" s="8"/>
       <c r="C99" s="8"/>
@@ -9006,7 +9004,7 @@
       <c r="K99" s="8"/>
       <c r="L99" s="8"/>
     </row>
-    <row r="100" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" s="8"/>
       <c r="B100" s="8"/>
       <c r="C100" s="8"/>
@@ -9023,7 +9021,7 @@
       <c r="K100" s="8"/>
       <c r="L100" s="8"/>
     </row>
-    <row r="101" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" s="8"/>
       <c r="B101" s="8"/>
       <c r="C101" s="8"/>
@@ -9040,7 +9038,7 @@
       <c r="K101" s="8"/>
       <c r="L101" s="8"/>
     </row>
-    <row r="102" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" s="8"/>
       <c r="B102" s="8"/>
       <c r="C102" s="8"/>
@@ -9057,7 +9055,7 @@
       <c r="K102" s="8"/>
       <c r="L102" s="8"/>
     </row>
-    <row r="103" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" s="8"/>
       <c r="B103" s="8"/>
       <c r="C103" s="8"/>
@@ -9074,7 +9072,7 @@
       <c r="K103" s="8"/>
       <c r="L103" s="8"/>
     </row>
-    <row r="104" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104" s="8"/>
       <c r="B104" s="8"/>
       <c r="C104" s="8"/>
@@ -9091,7 +9089,7 @@
       <c r="K104" s="8"/>
       <c r="L104" s="8"/>
     </row>
-    <row r="105" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" s="8"/>
       <c r="B105" s="8"/>
       <c r="C105" s="8"/>
@@ -9108,7 +9106,7 @@
       <c r="K105" s="8"/>
       <c r="L105" s="8"/>
     </row>
-    <row r="106" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" s="8"/>
       <c r="B106" s="8"/>
       <c r="C106" s="8"/>
@@ -9125,7 +9123,7 @@
       <c r="K106" s="8"/>
       <c r="L106" s="8"/>
     </row>
-    <row r="107" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" s="8"/>
       <c r="B107" s="8"/>
       <c r="C107" s="8"/>
@@ -9142,7 +9140,7 @@
       <c r="K107" s="8"/>
       <c r="L107" s="8"/>
     </row>
-    <row r="108" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" s="8"/>
       <c r="B108" s="8"/>
       <c r="C108" s="8"/>
@@ -9159,7 +9157,7 @@
       <c r="K108" s="8"/>
       <c r="L108" s="8"/>
     </row>
-    <row r="109" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109" s="8"/>
       <c r="B109" s="8"/>
       <c r="C109" s="8"/>
@@ -9176,7 +9174,7 @@
       <c r="K109" s="8"/>
       <c r="L109" s="8"/>
     </row>
-    <row r="110" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" s="8"/>
       <c r="B110" s="8"/>
       <c r="C110" s="8"/>
@@ -9193,7 +9191,7 @@
       <c r="K110" s="8"/>
       <c r="L110" s="8"/>
     </row>
-    <row r="111" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A111" s="8"/>
       <c r="B111" s="8"/>
       <c r="C111" s="8"/>
@@ -9210,7 +9208,7 @@
       <c r="K111" s="8"/>
       <c r="L111" s="8"/>
     </row>
-    <row r="112" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112" s="8"/>
       <c r="B112" s="8"/>
       <c r="C112" s="8"/>
@@ -9228,13 +9226,7 @@
       <c r="L112" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="J1:J112" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="ToDo"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="E1:E112" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -9258,7 +9250,7 @@
         <v>12</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>13</v>
@@ -9432,14 +9424,14 @@
       </c>
       <c r="C10" s="4">
         <f>82-SUM(E$2:E10)</f>
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D10" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E10" s="2">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/Business Analysis/checkupp_sprint_plan_2026.xlsx
+++ b/Business Analysis/checkupp_sprint_plan_2026.xlsx
@@ -8,16 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Business Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB9CE57E-1583-4BD1-804B-D63B90208C71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90A638BA-5839-48FD-BCF3-0E9E521B30B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint 01" sheetId="1" r:id="rId1"/>
     <sheet name="Sprint 01 Burndown" sheetId="4" r:id="rId2"/>
+    <sheet name="Sprint 02" sheetId="5" r:id="rId3"/>
+    <sheet name="Sprint 02 Burndown" sheetId="6" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sprint 01'!$E$1:$E$112</definedName>
+    <definedName name="_xlchart.v1.0" hidden="1">'Sprint 02 Burndown'!$B$2:$B$10</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">'Sprint 02 Burndown'!$C$1</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">'Sprint 02 Burndown'!$C$2:$C$10</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">'Sprint 02 Burndown'!$D$1</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">'Sprint 02 Burndown'!$D$2:$D$10</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -57,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="101">
   <si>
     <t>Epic</t>
   </si>
@@ -5346,6 +5353,173 @@
   <si>
     <t>Done</t>
   </si>
+  <si>
+    <t>Document Wallet - Documents</t>
+  </si>
+  <si>
+    <t>Upload health documents</t>
+  </si>
+  <si>
+    <t>Implement Document Picker &amp; Upload State Management
+* **Target Files**:
+* `checkupp-mobile-main/app/(tabs)/wallet.tsx`
+* `checkupp-mobile-main/components/UploadModal.tsx`
+* **Description**:
+1. Integrate the `expo-document-picker` library into the Wallet screen to allow users to select single or multiple health documents (PDFs, images) from their local device.
+2. Update the existing `UploadModal.tsx` to handle the selected file objects, validating file size and MIME types locally before initiating an upload.
+3. Implement local UI state to show upload progress or a loading spinner (`checkupp-mobile-main/components/LoadingSpinner.tsx`) while files are being processed.
+* **Acceptance Criteria Covered**: US 6.1 (AC 1)</t>
+  </si>
+  <si>
+    <t>ToDo</t>
+  </si>
+  <si>
+    <t>Integrate Document Upload API Mutations &amp; Notifications
+* **Target Files**:
+* `checkupp-mobile-main/lib/features/documents/mutations.ts`
+* `checkupp-mobile-main/app/(tabs)/wallet.tsx`
+ `checkupp-mobile-main/components/CustomToast.tsx`
+* **Description**:
+1. Review and utilize the existing mutation hooks in `mutations.ts` to handle the 3-step upload process defined by the backend:
+* Call `/me/wallet/uploads/presign` to get an upload intent.
+* Upload the raw file buffer to `/me/wallet/uploads/pending` using the `objectKey`.
+* Call `/me/wallet/documents` to finalize the record in the database.
+2. Wrap the upload logic in a robust `try/catch` block.
+3. On success, trigger a confirmation message using the `CustomToast.tsx` component and invalidate the document list query to refresh the UI.
+4. On failure, trigger an error toast ("Upload failed, please try again") and ensure the UI allows the user to retry the specific failed document without affecting successful ones.
+* **Acceptance Criteria Covered**: US 6.1 (AC 2, 3, 4)</t>
+  </si>
+  <si>
+    <t>Upload health documents (Note: This covers the list AC of 6.1)</t>
+  </si>
+  <si>
+    <t>Implement Document List View
+* **Target Files**:
+* `checkupp-mobile-main/lib/features/documents/queries.ts`
+* `checkupp-mobile-main/app/(tabs)/wallet.tsx`
+* **Description**:
+1. Ensure `queries.ts` correctly fetches from `GET /me/wallet/documents`.
+2. Design and implement a modular `DocumentListItem` component within `wallet.tsx` (or a dedicated components folder) to map over the fetched data.
+3. Display the document name, upload date, and a "More Options" (three dots) menu containing icons for "View", "Download", "Share", and "Delete".
+4. Implement `checkupp-mobile-main/components/EmptyState.tsx` if the query returns an empty array.
+* **Acceptance Criteria Covered**: US 6.1 (AC 5, 6)</t>
+  </si>
+  <si>
+    <t>View health documents</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Implement Document Viewer Integration
+* **Target Files**:
+* `checkupp-mobile-main/app/(tabs)/wallet.tsx`
+* `checkupp-mobile-main/components/DocumentViewer.tsx`
+* **Description**:
+1. Wire up the "View" action from the document list to trigger the existing `DocumentViewer.tsx` component.
+2. Pass the `externalUrl` or `publicUrl` of the document to the viewer.
+3. Implement a fallback error boundary and toast notification ("Could not open file") if the URL is invalid or the device cannot render the file type.
+* **Acceptance Criteria Covered**: US 6.4 (AC 1, 2)
+</t>
+  </si>
+  <si>
+    <t>Share health documents</t>
+  </si>
+  <si>
+    <t>Implement Native Document Sharing
+* **Target Files**:
+* `checkupp-mobile-main/lib/utils/shareUtils.ts` (Existing or create new)
+* `checkupp-mobile-main/app/(tabs)/wallet.tsx`
+* **Description**:
+1. Implement a reusable function utilizing `expo-file-system` to securely download the document from its URL to a temporary local cache directory (`FileSystem.cacheDirectory`).
+2. Pass the local URI to `expo-sharing` (`Sharing.shareAsync()`) to trigger the device's native sharing drawer (WhatsApp, Email, etc.).
+3. Wrap in a `try/catch` block. On error, display the specific toast: "Something went wrong, please try again."
+* **Acceptance Criteria Covered**: US 6.2 (AC 1, 2, 3, 4)</t>
+  </si>
+  <si>
+    <t>Delete health documents</t>
+  </si>
+  <si>
+    <t>Implement Document Deletion Flow
+* **Target Files**:
+* `checkupp-mobile-main/app/(tabs)/wallet.tsx`
+* `checkupp-mobile-main/lib/features/documents/mutations.ts`
+* **Description**:
+1. Connect the "Delete" option in the list item to a React Native `Alert.alert` to display the confirmation prompt: "Are you sure you want to delete this file?".
+2. On confirmation, trigger the delete mutation (`DELETE /me/wallet/documents/:id`).
+3. On success, invalidate the React Query cache to automatically remove the item from the list.
+4. On failure, show the required error toast: "File could not be deleted, please try again", ensuring the item remains in the UI.
+* **Acceptance Criteria Covered**: US 6.3 (AC 1, 2, 3, 4, 5)</t>
+  </si>
+  <si>
+    <t>Document Wallet - Links</t>
+  </si>
+  <si>
+    <t>Add e-script links</t>
+  </si>
+  <si>
+    <t>Implement E-Script Link Submission Form
+* **Target Files**:
+* `checkupp-mobile-main/app/(tabs)/wallet.tsx`
+* `checkupp-mobile-main/components/FormField.tsx`
+* `checkupp-mobile-main/lib/features/documents/mutations.ts`
+* **Description**:
+1. Create a modal or inline form utilizing `FormField.tsx` to capture a URL and a text description.
+2. Use `Yup` (already in `package.json`) to validate that the input is a properly formatted URL.
+3. Create a React Query mutation invoking `POST /me/wallet/links` with the payload `{ title: description, documentType: "E-SCRIPT", link: url }`.
+4. Handle errors with a toast: "Link could not be saved, Try again." On success, invalidate the links query.
+* **Acceptance Criteria Covered**: US 7.1 (AC 1, 3)</t>
+  </si>
+  <si>
+    <t>7.1, 7.2</t>
+  </si>
+  <si>
+    <t>View e-script links</t>
+  </si>
+  <si>
+    <t>Implement Link List &amp; WebView
+* **Target Files**:
+* `checkupp-mobile-main/app/(tabs)/wallet.tsx`
+* `checkupp-mobile-main/lib/features/documents/queries.ts`
+* **Description**:
+1. Fetch the links using `GET /me/wallet/documents` filtered by `fileType=LINK` or `documentType=E-SCRIPT`.
+2. Render the links with their title/description and creation date. Include action buttons for View, Share, and Delete.
+3. Wire the "View" action to open the link using `expo-web-browser` (`WebBrowser.openBrowserAsync`).
+4. Wrap the view action in a `try/catch` returning the error toast: "Could not open Expanded View, try again".
+* **Acceptance Criteria Covered**: US 7.1 (AC 2, 4, 5), US 7.2 (AC 1)</t>
+  </si>
+  <si>
+    <t>7.3, 7.4</t>
+  </si>
+  <si>
+    <t>Share and delete e-script links</t>
+  </si>
+  <si>
+    <t>Implement Native Link Sharing &amp; Deletion
+* **Target Files**:
+* `checkupp-mobile-main/app/(tabs)/wallet.tsx`
+* `checkupp-mobile-main/lib/utils/shareUtils.ts`
+* **Description**:
+1. **Sharing**: Implement the share button using React Native's built-in `Share.share({ message: \`${description}: ${url}` })` method to invoke native sharing for text/links. Handle errors with the "Something went wrong..." toast.
+2. **Deletion**: Implement the delete flow using an `Alert.alert` ("Are you sure you want to delete this link?"). Hook it into the exact same delete mutation used for documents (`DELETE /me/wallet/documents/:id`). Handle errors with the "Link could not be deleted..." toast.
+* **Acceptance Criteria Covered**: US 7.3 (AC 1, 2, 3, 4, 5), US 7.4 (AC 1, 2, 3, 4, 5)</t>
+  </si>
+  <si>
+    <t>Global Backend Verification</t>
+  </si>
+  <si>
+    <t>Wallet automated testing</t>
+  </si>
+  <si>
+    <t>### Global Backend Verification Task
+*Note: The backend codebase already contains full implementations for the Wallet logic in `wallet.controller.ts`, `wallet.service.ts`, and `wallet.validation.ts`. This task ensures complete alignment with the new ACs and prevents regressions.*
+E2E Test Coverage for Wallet &amp; Link Actions
+* **Target Files**:
+* `checkupp-api-main/tests/modules/wallet/` (Directory to be created/populated)
+* `checkupp-api-main/src/modules/wallet/wallet.validation.ts`
+* **Description**:
+1. Write Supertest/Jest integration tests for `POST /me/wallet/documents`, `POST /me/wallet/links`, and `DELETE /me/wallet/documents/:id`.
+2. Verify that deletion securely handles `userId` scoping to prevent unauthorized deletion (tenant isolation).
+3. Verify that `createLinkSchema` strictly requires a valid URI pattern and returns a 400 Bad Request if the format is invalid.
+4. Verify that the `deleteDocument` service correctly unlinks the file from cloud storage using `cleanupUploadedFile` when a document is deleted.</t>
+  </si>
 </sst>
 </file>
 
@@ -5411,7 +5585,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5433,6 +5607,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5464,7 +5656,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5507,6 +5699,24 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5560,7 +5770,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-IN"/>
-              <a:t>Burndown</a:t>
+              <a:t>Sprint 01 - Burndown</a:t>
             </a:r>
             <a:r>
               <a:rPr lang="en-IN" baseline="0"/>
@@ -5827,7 +6037,7 @@
         <c:axId val="228576623"/>
         <c:axId val="228581423"/>
       </c:lineChart>
-      <c:dateAx>
+      <c:catAx>
         <c:axId val="228576623"/>
         <c:scaling>
           <c:orientation val="minMax"/>
@@ -5874,9 +6084,10 @@
         <c:crossAx val="228581423"/>
         <c:crosses val="autoZero"/>
         <c:auto val="0"/>
+        <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:baseTimeUnit val="days"/>
-      </c:dateAx>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
       <c:valAx>
         <c:axId val="228581423"/>
         <c:scaling>
@@ -6016,7 +6227,559 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-IN"/>
+              <a:t>Sprint 02 - Burndown</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-IN" baseline="0"/>
+              <a:t> Chart</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-IN"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sprint 02 Burndown'!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Actual Story Points Left</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Sprint 02 Burndown'!$B$2:$B$10</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yyyy</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>46251</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46252</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46253</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46254</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46255</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46258</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46259</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46260</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46261</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sprint 02 Burndown'!$C$2:$C$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>34</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4DC3-4944-9A66-86CC22E2D92F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Sprint 02 Burndown'!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Expected Story Points Left</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Sprint 02 Burndown'!$B$2:$B$10</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yyyy</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>46251</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46252</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>46253</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46254</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>46255</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46258</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>46259</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>46260</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46261</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sprint 02 Burndown'!$D$2:$D$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>29.75</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>25.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>21.25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>12.75</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4.25</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-4DC3-4944-9A66-86CC22E2D92F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1501547104"/>
+        <c:axId val="1501322672"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1501547104"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="m/d/yyyy" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1501322672"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="0"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1501322672"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1501547104"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -6572,6 +7335,522 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -6593,6 +7872,47 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A4606402-996D-6CA4-C8E9-5276D0F88F29}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>213360</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>350520</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{993740FE-4084-53D2-EA28-52B7CE8F44F2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9438,4 +10758,2276 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA30D3B6-4BBC-427B-918A-C301767B692F}">
+  <dimension ref="A1:L112"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.88671875" customWidth="1"/>
+    <col min="3" max="3" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.44140625" customWidth="1"/>
+    <col min="5" max="5" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="99.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="15">
+        <v>1</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" s="15">
+        <v>6.1</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="15">
+        <f t="array" ref="I2">_xlfn.SWITCH(H2,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="J2" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+    </row>
+    <row r="3" spans="1:12" ht="244.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="15">
+        <v>2</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" s="15">
+        <v>6.1</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="15">
+        <f t="array" ref="I3">_xlfn.SWITCH(H3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>5</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="K3" s="15"/>
+      <c r="L3" s="15"/>
+    </row>
+    <row r="4" spans="1:12" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="15">
+        <v>3</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" s="15">
+        <v>6.1</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" s="15">
+        <f t="array" ref="I4">_xlfn.SWITCH(H4,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+    </row>
+    <row r="5" spans="1:12" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="15">
+        <v>4</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" s="15">
+        <v>6.4</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" s="15">
+        <f t="array" ref="I5">_xlfn.SWITCH(H5,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>5</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="K5" s="15"/>
+      <c r="L5" s="15"/>
+    </row>
+    <row r="6" spans="1:12" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="15">
+        <v>5</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="C6" s="15">
+        <v>6.2</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6" s="15">
+        <f t="array" ref="I6">_xlfn.SWITCH(H6,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="J6" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+    </row>
+    <row r="7" spans="1:12" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="15">
+        <v>6</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" s="15">
+        <v>6.3</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="G7" s="15"/>
+      <c r="H7" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="15">
+        <f t="array" ref="I7">_xlfn.SWITCH(H7,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="K7" s="15"/>
+      <c r="L7" s="15"/>
+    </row>
+    <row r="8" spans="1:12" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="17">
+        <v>7</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="C8" s="17">
+        <v>7.1</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="I8" s="17">
+        <f t="array" ref="I8">_xlfn.SWITCH(H8,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="J8" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="K8" s="17"/>
+      <c r="L8" s="17"/>
+    </row>
+    <row r="9" spans="1:12" ht="144" x14ac:dyDescent="0.3">
+      <c r="A9" s="17">
+        <v>8</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="I9" s="17">
+        <f t="array" ref="I9">_xlfn.SWITCH(H9,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="J9" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="K9" s="17"/>
+      <c r="L9" s="17"/>
+    </row>
+    <row r="10" spans="1:12" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A10" s="17">
+        <v>9</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" s="17">
+        <f t="array" ref="I10">_xlfn.SWITCH(H10,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="J10" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="K10" s="17"/>
+      <c r="L10" s="17"/>
+    </row>
+    <row r="11" spans="1:12" ht="230.4" x14ac:dyDescent="0.3">
+      <c r="A11" s="19">
+        <v>10</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="I11" s="19">
+        <f t="array" ref="I11">_xlfn.SWITCH(H11,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>5</v>
+      </c>
+      <c r="J11" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8" t="str">
+        <f t="array" ref="I26">_xlfn.SWITCH(H26,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8" t="str">
+        <f t="array" ref="I27">_xlfn.SWITCH(H27,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="8"/>
+      <c r="I28" s="8" t="str">
+        <f t="array" ref="I28">_xlfn.SWITCH(H28,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8" t="str">
+        <f t="array" ref="I29">_xlfn.SWITCH(H29,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J29" s="8"/>
+      <c r="K29" s="8"/>
+      <c r="L29" s="8"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" s="8"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8" t="str">
+        <f t="array" ref="I30">_xlfn.SWITCH(H30,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J30" s="8"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="8"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" s="8"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="8" t="str">
+        <f t="array" ref="I31">_xlfn.SWITCH(H31,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J31" s="8"/>
+      <c r="K31" s="8"/>
+      <c r="L31" s="8"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A32" s="8"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="10"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="8" t="str">
+        <f t="array" ref="I32">_xlfn.SWITCH(H32,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J32" s="8"/>
+      <c r="K32" s="8"/>
+      <c r="L32" s="8"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A33" s="8"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8" t="str">
+        <f t="array" ref="I33">_xlfn.SWITCH(H33,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J33" s="8"/>
+      <c r="K33" s="8"/>
+      <c r="L33" s="8"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" s="8"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="8"/>
+      <c r="I34" s="8" t="str">
+        <f t="array" ref="I34">_xlfn.SWITCH(H34,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="8"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35" s="8"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="8" t="str">
+        <f t="array" ref="I35">_xlfn.SWITCH(H35,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J35" s="8"/>
+      <c r="K35" s="8"/>
+      <c r="L35" s="8"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36" s="8"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="8" t="str">
+        <f t="array" ref="I36">_xlfn.SWITCH(H36,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J36" s="8"/>
+      <c r="K36" s="8"/>
+      <c r="L36" s="8"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A37" s="8"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="8"/>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="8"/>
+      <c r="I37" s="8" t="str">
+        <f t="array" ref="I37">_xlfn.SWITCH(H37,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J37" s="8"/>
+      <c r="K37" s="8"/>
+      <c r="L37" s="8"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A38" s="8"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="8"/>
+      <c r="I38" s="8" t="str">
+        <f t="array" ref="I38">_xlfn.SWITCH(H38,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J38" s="8"/>
+      <c r="K38" s="8"/>
+      <c r="L38" s="8"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A39" s="8"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="8"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="8"/>
+      <c r="I39" s="8" t="str">
+        <f t="array" ref="I39">_xlfn.SWITCH(H39,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J39" s="8"/>
+      <c r="K39" s="8"/>
+      <c r="L39" s="8"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A40" s="8"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
+      <c r="I40" s="8" t="str">
+        <f t="array" ref="I40">_xlfn.SWITCH(H40,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J40" s="8"/>
+      <c r="K40" s="8"/>
+      <c r="L40" s="8"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A41" s="8"/>
+      <c r="B41" s="8"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="8"/>
+      <c r="I41" s="8" t="str">
+        <f t="array" ref="I41">_xlfn.SWITCH(H41,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J41" s="8"/>
+      <c r="K41" s="8"/>
+      <c r="L41" s="8"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A42" s="8"/>
+      <c r="B42" s="8"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="8"/>
+      <c r="E42" s="8"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="8"/>
+      <c r="H42" s="8"/>
+      <c r="I42" s="8" t="str">
+        <f t="array" ref="I42">_xlfn.SWITCH(H42,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J42" s="8"/>
+      <c r="K42" s="8"/>
+      <c r="L42" s="8"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A43" s="8"/>
+      <c r="B43" s="8"/>
+      <c r="C43" s="8"/>
+      <c r="D43" s="8"/>
+      <c r="E43" s="8"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="8"/>
+      <c r="I43" s="8" t="str">
+        <f t="array" ref="I43">_xlfn.SWITCH(H43,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J43" s="8"/>
+      <c r="K43" s="8"/>
+      <c r="L43" s="8"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A44" s="8"/>
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="9"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="8"/>
+      <c r="I44" s="8" t="str">
+        <f t="array" ref="I44">_xlfn.SWITCH(H44,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J44" s="8"/>
+      <c r="K44" s="8"/>
+      <c r="L44" s="8"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A45" s="8"/>
+      <c r="B45" s="8"/>
+      <c r="C45" s="8"/>
+      <c r="D45" s="8"/>
+      <c r="E45" s="8"/>
+      <c r="F45" s="9"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="8"/>
+      <c r="I45" s="8" t="str">
+        <f t="array" ref="I45">_xlfn.SWITCH(H45,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J45" s="8"/>
+      <c r="K45" s="8"/>
+      <c r="L45" s="8"/>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A46" s="8"/>
+      <c r="B46" s="8"/>
+      <c r="C46" s="8"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="8"/>
+      <c r="F46" s="9"/>
+      <c r="G46" s="8"/>
+      <c r="H46" s="8"/>
+      <c r="I46" s="8" t="str">
+        <f t="array" ref="I46">_xlfn.SWITCH(H46,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J46" s="8"/>
+      <c r="K46" s="8"/>
+      <c r="L46" s="8"/>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A47" s="8"/>
+      <c r="B47" s="8"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="8"/>
+      <c r="E47" s="8"/>
+      <c r="F47" s="9"/>
+      <c r="G47" s="8"/>
+      <c r="H47" s="8"/>
+      <c r="I47" s="8" t="str">
+        <f t="array" ref="I47">_xlfn.SWITCH(H47,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J47" s="8"/>
+      <c r="K47" s="8"/>
+      <c r="L47" s="8"/>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A48" s="8"/>
+      <c r="B48" s="8"/>
+      <c r="C48" s="8"/>
+      <c r="D48" s="8"/>
+      <c r="E48" s="8"/>
+      <c r="F48" s="9"/>
+      <c r="G48" s="8"/>
+      <c r="H48" s="8"/>
+      <c r="I48" s="8" t="str">
+        <f t="array" ref="I48">_xlfn.SWITCH(H48,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J48" s="8"/>
+      <c r="K48" s="8"/>
+      <c r="L48" s="8"/>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A49" s="8"/>
+      <c r="B49" s="8"/>
+      <c r="C49" s="8"/>
+      <c r="D49" s="8"/>
+      <c r="E49" s="8"/>
+      <c r="F49" s="9"/>
+      <c r="G49" s="8"/>
+      <c r="H49" s="8"/>
+      <c r="I49" s="8" t="str">
+        <f t="array" ref="I49">_xlfn.SWITCH(H49,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J49" s="8"/>
+      <c r="K49" s="8"/>
+      <c r="L49" s="8"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A50" s="8"/>
+      <c r="B50" s="8"/>
+      <c r="C50" s="8"/>
+      <c r="D50" s="8"/>
+      <c r="E50" s="8"/>
+      <c r="F50" s="9"/>
+      <c r="G50" s="8"/>
+      <c r="H50" s="8"/>
+      <c r="I50" s="8" t="str">
+        <f t="array" ref="I50">_xlfn.SWITCH(H50,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J50" s="8"/>
+      <c r="K50" s="8"/>
+      <c r="L50" s="8"/>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A51" s="8"/>
+      <c r="B51" s="8"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="10"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="8" t="str">
+        <f t="array" ref="I51">_xlfn.SWITCH(H51,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="8"/>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A52" s="8"/>
+      <c r="B52" s="8"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="10"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="8" t="str">
+        <f t="array" ref="I52">_xlfn.SWITCH(H52,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J52" s="8"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="8"/>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A53" s="8"/>
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="10"/>
+      <c r="G53" s="8"/>
+      <c r="H53" s="8"/>
+      <c r="I53" s="8" t="str">
+        <f t="array" ref="I53">_xlfn.SWITCH(H53,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J53" s="8"/>
+      <c r="K53" s="8"/>
+      <c r="L53" s="8"/>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A54" s="8"/>
+      <c r="B54" s="8"/>
+      <c r="C54" s="8"/>
+      <c r="D54" s="8"/>
+      <c r="E54" s="8"/>
+      <c r="F54" s="10"/>
+      <c r="G54" s="8"/>
+      <c r="H54" s="8"/>
+      <c r="I54" s="8" t="str">
+        <f t="array" ref="I54">_xlfn.SWITCH(H54,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J54" s="8"/>
+      <c r="K54" s="8"/>
+      <c r="L54" s="8"/>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A55" s="8"/>
+      <c r="B55" s="8"/>
+      <c r="C55" s="8"/>
+      <c r="D55" s="8"/>
+      <c r="E55" s="8"/>
+      <c r="F55" s="10"/>
+      <c r="G55" s="8"/>
+      <c r="H55" s="8"/>
+      <c r="I55" s="8" t="str">
+        <f t="array" ref="I55">_xlfn.SWITCH(H55,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J55" s="8"/>
+      <c r="K55" s="8"/>
+      <c r="L55" s="8"/>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A56" s="8"/>
+      <c r="B56" s="8"/>
+      <c r="C56" s="8"/>
+      <c r="D56" s="8"/>
+      <c r="E56" s="8"/>
+      <c r="F56" s="10"/>
+      <c r="G56" s="8"/>
+      <c r="H56" s="8"/>
+      <c r="I56" s="8" t="str">
+        <f t="array" ref="I56">_xlfn.SWITCH(H56,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J56" s="8"/>
+      <c r="K56" s="8"/>
+      <c r="L56" s="8"/>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A57" s="8"/>
+      <c r="B57" s="8"/>
+      <c r="C57" s="8"/>
+      <c r="D57" s="8"/>
+      <c r="E57" s="8"/>
+      <c r="F57" s="9"/>
+      <c r="G57" s="8"/>
+      <c r="H57" s="8"/>
+      <c r="I57" s="8" t="str">
+        <f t="array" ref="I57">_xlfn.SWITCH(H57,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J57" s="8"/>
+      <c r="K57" s="8"/>
+      <c r="L57" s="8"/>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A58" s="8"/>
+      <c r="B58" s="8"/>
+      <c r="C58" s="8"/>
+      <c r="D58" s="8"/>
+      <c r="E58" s="8"/>
+      <c r="F58" s="9"/>
+      <c r="G58" s="8"/>
+      <c r="H58" s="8"/>
+      <c r="I58" s="8" t="str">
+        <f t="array" ref="I58">_xlfn.SWITCH(H58,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J58" s="8"/>
+      <c r="K58" s="8"/>
+      <c r="L58" s="8"/>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A59" s="8"/>
+      <c r="B59" s="8"/>
+      <c r="C59" s="8"/>
+      <c r="D59" s="8"/>
+      <c r="E59" s="8"/>
+      <c r="F59" s="9"/>
+      <c r="G59" s="8"/>
+      <c r="H59" s="8"/>
+      <c r="I59" s="8" t="str">
+        <f t="array" ref="I59">_xlfn.SWITCH(H59,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J59" s="8"/>
+      <c r="K59" s="8"/>
+      <c r="L59" s="8"/>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A60" s="8"/>
+      <c r="B60" s="8"/>
+      <c r="C60" s="8"/>
+      <c r="D60" s="8"/>
+      <c r="E60" s="8"/>
+      <c r="F60" s="9"/>
+      <c r="G60" s="8"/>
+      <c r="H60" s="8"/>
+      <c r="I60" s="8" t="str">
+        <f t="array" ref="I60">_xlfn.SWITCH(H60,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J60" s="8"/>
+      <c r="K60" s="8"/>
+      <c r="L60" s="8"/>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A61" s="8"/>
+      <c r="B61" s="8"/>
+      <c r="C61" s="8"/>
+      <c r="D61" s="8"/>
+      <c r="E61" s="8"/>
+      <c r="F61" s="9"/>
+      <c r="G61" s="8"/>
+      <c r="H61" s="8"/>
+      <c r="I61" s="8" t="str">
+        <f t="array" ref="I61">_xlfn.SWITCH(H61,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J61" s="8"/>
+      <c r="K61" s="8"/>
+      <c r="L61" s="8"/>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A62" s="8"/>
+      <c r="B62" s="8"/>
+      <c r="C62" s="8"/>
+      <c r="D62" s="8"/>
+      <c r="E62" s="8"/>
+      <c r="F62" s="9"/>
+      <c r="G62" s="8"/>
+      <c r="H62" s="8"/>
+      <c r="I62" s="8" t="str">
+        <f t="array" ref="I62">_xlfn.SWITCH(H62,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J62" s="8"/>
+      <c r="K62" s="8"/>
+      <c r="L62" s="8"/>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A63" s="8"/>
+      <c r="B63" s="8"/>
+      <c r="C63" s="8"/>
+      <c r="D63" s="8"/>
+      <c r="E63" s="8"/>
+      <c r="F63" s="9"/>
+      <c r="G63" s="8"/>
+      <c r="H63" s="8"/>
+      <c r="I63" s="8" t="str">
+        <f t="array" ref="I63">_xlfn.SWITCH(H63,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J63" s="8"/>
+      <c r="K63" s="8"/>
+      <c r="L63" s="8"/>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A64" s="8"/>
+      <c r="B64" s="8"/>
+      <c r="C64" s="8"/>
+      <c r="D64" s="8"/>
+      <c r="E64" s="8"/>
+      <c r="F64" s="9"/>
+      <c r="G64" s="8"/>
+      <c r="H64" s="8"/>
+      <c r="I64" s="8" t="str">
+        <f t="array" ref="I64">_xlfn.SWITCH(H64,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J64" s="8"/>
+      <c r="K64" s="8"/>
+      <c r="L64" s="8"/>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A65" s="8"/>
+      <c r="B65" s="8"/>
+      <c r="C65" s="8"/>
+      <c r="D65" s="8"/>
+      <c r="E65" s="8"/>
+      <c r="F65" s="9"/>
+      <c r="G65" s="8"/>
+      <c r="H65" s="8"/>
+      <c r="I65" s="8" t="str">
+        <f t="array" ref="I65">_xlfn.SWITCH(H65,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J65" s="8"/>
+      <c r="K65" s="8"/>
+      <c r="L65" s="8"/>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A66" s="8"/>
+      <c r="B66" s="8"/>
+      <c r="C66" s="8"/>
+      <c r="D66" s="8"/>
+      <c r="E66" s="8"/>
+      <c r="F66" s="9"/>
+      <c r="G66" s="8"/>
+      <c r="H66" s="8"/>
+      <c r="I66" s="8" t="str">
+        <f t="array" ref="I66">_xlfn.SWITCH(H66,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J66" s="8"/>
+      <c r="K66" s="8"/>
+      <c r="L66" s="8"/>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A67" s="8"/>
+      <c r="B67" s="8"/>
+      <c r="C67" s="8"/>
+      <c r="D67" s="8"/>
+      <c r="E67" s="8"/>
+      <c r="F67" s="9"/>
+      <c r="G67" s="8"/>
+      <c r="H67" s="8"/>
+      <c r="I67" s="8" t="str">
+        <f t="array" ref="I67">_xlfn.SWITCH(H67,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J67" s="8"/>
+      <c r="K67" s="8"/>
+      <c r="L67" s="8"/>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A68" s="8"/>
+      <c r="B68" s="8"/>
+      <c r="C68" s="8"/>
+      <c r="D68" s="8"/>
+      <c r="E68" s="8"/>
+      <c r="F68" s="7"/>
+      <c r="G68" s="8"/>
+      <c r="H68" s="8"/>
+      <c r="I68" s="8" t="str">
+        <f t="array" ref="I68">_xlfn.SWITCH(H68,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J68" s="8"/>
+      <c r="K68" s="8"/>
+      <c r="L68" s="8"/>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A69" s="8"/>
+      <c r="B69" s="8"/>
+      <c r="C69" s="8"/>
+      <c r="D69" s="8"/>
+      <c r="E69" s="8"/>
+      <c r="F69" s="9"/>
+      <c r="G69" s="8"/>
+      <c r="H69" s="8"/>
+      <c r="I69" s="8" t="str">
+        <f t="array" ref="I69">_xlfn.SWITCH(H69,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J69" s="8"/>
+      <c r="K69" s="8"/>
+      <c r="L69" s="8"/>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A70" s="8"/>
+      <c r="B70" s="8"/>
+      <c r="C70" s="8"/>
+      <c r="D70" s="8"/>
+      <c r="E70" s="8"/>
+      <c r="F70" s="7"/>
+      <c r="G70" s="8"/>
+      <c r="H70" s="8"/>
+      <c r="I70" s="8" t="str">
+        <f t="array" ref="I70">_xlfn.SWITCH(H70,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J70" s="8"/>
+      <c r="K70" s="8"/>
+      <c r="L70" s="8"/>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A71" s="8"/>
+      <c r="B71" s="8"/>
+      <c r="C71" s="8"/>
+      <c r="D71" s="8"/>
+      <c r="E71" s="8"/>
+      <c r="F71" s="7"/>
+      <c r="G71" s="8"/>
+      <c r="H71" s="8"/>
+      <c r="I71" s="8" t="str">
+        <f t="array" ref="I71">_xlfn.SWITCH(H71,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J71" s="8"/>
+      <c r="K71" s="8"/>
+      <c r="L71" s="8"/>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A72" s="8"/>
+      <c r="B72" s="8"/>
+      <c r="C72" s="8"/>
+      <c r="D72" s="8"/>
+      <c r="E72" s="8"/>
+      <c r="F72" s="9"/>
+      <c r="G72" s="8"/>
+      <c r="H72" s="8"/>
+      <c r="I72" s="8" t="str">
+        <f t="array" ref="I72">_xlfn.SWITCH(H72,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J72" s="8"/>
+      <c r="K72" s="8"/>
+      <c r="L72" s="8"/>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A73" s="8"/>
+      <c r="B73" s="8"/>
+      <c r="C73" s="8"/>
+      <c r="D73" s="8"/>
+      <c r="E73" s="8"/>
+      <c r="F73" s="9"/>
+      <c r="G73" s="8"/>
+      <c r="H73" s="8"/>
+      <c r="I73" s="8" t="str">
+        <f t="array" ref="I73">_xlfn.SWITCH(H73,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J73" s="8"/>
+      <c r="K73" s="8"/>
+      <c r="L73" s="8"/>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A74" s="8"/>
+      <c r="B74" s="8"/>
+      <c r="C74" s="8"/>
+      <c r="D74" s="8"/>
+      <c r="E74" s="8"/>
+      <c r="F74" s="9"/>
+      <c r="G74" s="8"/>
+      <c r="H74" s="8"/>
+      <c r="I74" s="8" t="str">
+        <f t="array" ref="I74">_xlfn.SWITCH(H74,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J74" s="8"/>
+      <c r="K74" s="8"/>
+      <c r="L74" s="8"/>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A75" s="8"/>
+      <c r="B75" s="8"/>
+      <c r="C75" s="8"/>
+      <c r="D75" s="8"/>
+      <c r="E75" s="8"/>
+      <c r="F75" s="9"/>
+      <c r="G75" s="8"/>
+      <c r="H75" s="8"/>
+      <c r="I75" s="8" t="str">
+        <f t="array" ref="I75">_xlfn.SWITCH(H75,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J75" s="8"/>
+      <c r="K75" s="8"/>
+      <c r="L75" s="8"/>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A76" s="8"/>
+      <c r="B76" s="8"/>
+      <c r="C76" s="8"/>
+      <c r="D76" s="8"/>
+      <c r="E76" s="8"/>
+      <c r="F76" s="9"/>
+      <c r="G76" s="8"/>
+      <c r="H76" s="8"/>
+      <c r="I76" s="8" t="str">
+        <f t="array" ref="I76">_xlfn.SWITCH(H76,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J76" s="8"/>
+      <c r="K76" s="8"/>
+      <c r="L76" s="8"/>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A77" s="8"/>
+      <c r="B77" s="8"/>
+      <c r="C77" s="8"/>
+      <c r="D77" s="8"/>
+      <c r="E77" s="8"/>
+      <c r="F77" s="10"/>
+      <c r="G77" s="8"/>
+      <c r="H77" s="8"/>
+      <c r="I77" s="8" t="str">
+        <f t="array" ref="I77">_xlfn.SWITCH(H77,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J77" s="8"/>
+      <c r="K77" s="8"/>
+      <c r="L77" s="8"/>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A78" s="8"/>
+      <c r="B78" s="8"/>
+      <c r="C78" s="8"/>
+      <c r="D78" s="8"/>
+      <c r="E78" s="8"/>
+      <c r="F78" s="10"/>
+      <c r="G78" s="8"/>
+      <c r="H78" s="8"/>
+      <c r="I78" s="8" t="str">
+        <f t="array" ref="I78">_xlfn.SWITCH(H78,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J78" s="8"/>
+      <c r="K78" s="8"/>
+      <c r="L78" s="8"/>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A79" s="8"/>
+      <c r="B79" s="8"/>
+      <c r="C79" s="8"/>
+      <c r="D79" s="8"/>
+      <c r="E79" s="8"/>
+      <c r="F79" s="10"/>
+      <c r="G79" s="8"/>
+      <c r="H79" s="8"/>
+      <c r="I79" s="8" t="str">
+        <f t="array" ref="I79">_xlfn.SWITCH(H79,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J79" s="8"/>
+      <c r="K79" s="8"/>
+      <c r="L79" s="8"/>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A80" s="8"/>
+      <c r="B80" s="8"/>
+      <c r="C80" s="8"/>
+      <c r="D80" s="8"/>
+      <c r="E80" s="8"/>
+      <c r="F80" s="10"/>
+      <c r="G80" s="8"/>
+      <c r="H80" s="8"/>
+      <c r="I80" s="8" t="str">
+        <f t="array" ref="I80">_xlfn.SWITCH(H80,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J80" s="8"/>
+      <c r="K80" s="8"/>
+      <c r="L80" s="8"/>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A81" s="8"/>
+      <c r="B81" s="8"/>
+      <c r="C81" s="8"/>
+      <c r="D81" s="8"/>
+      <c r="E81" s="8"/>
+      <c r="F81" s="10"/>
+      <c r="G81" s="8"/>
+      <c r="H81" s="8"/>
+      <c r="I81" s="8" t="str">
+        <f t="array" ref="I81">_xlfn.SWITCH(H81,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J81" s="8"/>
+      <c r="K81" s="8"/>
+      <c r="L81" s="8"/>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A82" s="8"/>
+      <c r="B82" s="8"/>
+      <c r="C82" s="8"/>
+      <c r="D82" s="8"/>
+      <c r="E82" s="8"/>
+      <c r="F82" s="10"/>
+      <c r="G82" s="8"/>
+      <c r="H82" s="8"/>
+      <c r="I82" s="8" t="str">
+        <f t="array" ref="I82">_xlfn.SWITCH(H82,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J82" s="8"/>
+      <c r="K82" s="8"/>
+      <c r="L82" s="8"/>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A83" s="8"/>
+      <c r="B83" s="8"/>
+      <c r="C83" s="8"/>
+      <c r="D83" s="8"/>
+      <c r="E83" s="8"/>
+      <c r="F83" s="10"/>
+      <c r="G83" s="8"/>
+      <c r="H83" s="8"/>
+      <c r="I83" s="8" t="str">
+        <f t="array" ref="I83">_xlfn.SWITCH(H83,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J83" s="8"/>
+      <c r="K83" s="8"/>
+      <c r="L83" s="8"/>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A84" s="8"/>
+      <c r="B84" s="8"/>
+      <c r="C84" s="8"/>
+      <c r="D84" s="8"/>
+      <c r="E84" s="8"/>
+      <c r="F84" s="10"/>
+      <c r="G84" s="8"/>
+      <c r="H84" s="8"/>
+      <c r="I84" s="8" t="str">
+        <f t="array" ref="I84">_xlfn.SWITCH(H84,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J84" s="8"/>
+      <c r="K84" s="8"/>
+      <c r="L84" s="8"/>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A85" s="8"/>
+      <c r="B85" s="8"/>
+      <c r="C85" s="8"/>
+      <c r="D85" s="8"/>
+      <c r="E85" s="8"/>
+      <c r="F85" s="10"/>
+      <c r="G85" s="8"/>
+      <c r="H85" s="8"/>
+      <c r="I85" s="8" t="str">
+        <f t="array" ref="I85">_xlfn.SWITCH(H85,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J85" s="8"/>
+      <c r="K85" s="8"/>
+      <c r="L85" s="8"/>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A86" s="8"/>
+      <c r="B86" s="8"/>
+      <c r="C86" s="8"/>
+      <c r="D86" s="8"/>
+      <c r="E86" s="8"/>
+      <c r="F86" s="10"/>
+      <c r="G86" s="8"/>
+      <c r="H86" s="8"/>
+      <c r="I86" s="8" t="str">
+        <f t="array" ref="I86">_xlfn.SWITCH(H86,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J86" s="8"/>
+      <c r="K86" s="8"/>
+      <c r="L86" s="8"/>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A87" s="8"/>
+      <c r="B87" s="8"/>
+      <c r="C87" s="8"/>
+      <c r="D87" s="8"/>
+      <c r="E87" s="8"/>
+      <c r="F87" s="10"/>
+      <c r="G87" s="8"/>
+      <c r="H87" s="8"/>
+      <c r="I87" s="8" t="str">
+        <f t="array" ref="I87">_xlfn.SWITCH(H87,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J87" s="8"/>
+      <c r="K87" s="8"/>
+      <c r="L87" s="8"/>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A88" s="8"/>
+      <c r="B88" s="8"/>
+      <c r="C88" s="8"/>
+      <c r="D88" s="8"/>
+      <c r="E88" s="8"/>
+      <c r="F88" s="10"/>
+      <c r="G88" s="8"/>
+      <c r="H88" s="8"/>
+      <c r="I88" s="8" t="str">
+        <f t="array" ref="I88">_xlfn.SWITCH(H88,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J88" s="8"/>
+      <c r="K88" s="8"/>
+      <c r="L88" s="8"/>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A89" s="8"/>
+      <c r="B89" s="8"/>
+      <c r="C89" s="8"/>
+      <c r="D89" s="8"/>
+      <c r="E89" s="8"/>
+      <c r="F89" s="10"/>
+      <c r="G89" s="8"/>
+      <c r="H89" s="8"/>
+      <c r="I89" s="8" t="str">
+        <f t="array" ref="I89">_xlfn.SWITCH(H89,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J89" s="8"/>
+      <c r="K89" s="8"/>
+      <c r="L89" s="8"/>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A90" s="8"/>
+      <c r="B90" s="8"/>
+      <c r="C90" s="8"/>
+      <c r="D90" s="8"/>
+      <c r="E90" s="8"/>
+      <c r="F90" s="10"/>
+      <c r="G90" s="8"/>
+      <c r="H90" s="8"/>
+      <c r="I90" s="8" t="str">
+        <f t="array" ref="I90">_xlfn.SWITCH(H90,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J90" s="8"/>
+      <c r="K90" s="8"/>
+      <c r="L90" s="8"/>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A91" s="8"/>
+      <c r="B91" s="8"/>
+      <c r="C91" s="8"/>
+      <c r="D91" s="8"/>
+      <c r="E91" s="8"/>
+      <c r="F91" s="10"/>
+      <c r="G91" s="8"/>
+      <c r="H91" s="8"/>
+      <c r="I91" s="8" t="str">
+        <f t="array" ref="I91">_xlfn.SWITCH(H91,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J91" s="8"/>
+      <c r="K91" s="8"/>
+      <c r="L91" s="8"/>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A92" s="8"/>
+      <c r="B92" s="8"/>
+      <c r="C92" s="8"/>
+      <c r="D92" s="8"/>
+      <c r="E92" s="8"/>
+      <c r="F92" s="10"/>
+      <c r="G92" s="8"/>
+      <c r="H92" s="8"/>
+      <c r="I92" s="8" t="str">
+        <f t="array" ref="I92">_xlfn.SWITCH(H92,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J92" s="8"/>
+      <c r="K92" s="8"/>
+      <c r="L92" s="8"/>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A93" s="8"/>
+      <c r="B93" s="8"/>
+      <c r="C93" s="8"/>
+      <c r="D93" s="8"/>
+      <c r="E93" s="8"/>
+      <c r="F93" s="10"/>
+      <c r="G93" s="8"/>
+      <c r="H93" s="8"/>
+      <c r="I93" s="8" t="str">
+        <f t="array" ref="I93">_xlfn.SWITCH(H93,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J93" s="8"/>
+      <c r="K93" s="8"/>
+      <c r="L93" s="8"/>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A94" s="8"/>
+      <c r="B94" s="8"/>
+      <c r="C94" s="8"/>
+      <c r="D94" s="8"/>
+      <c r="E94" s="8"/>
+      <c r="F94" s="10"/>
+      <c r="G94" s="8"/>
+      <c r="H94" s="8"/>
+      <c r="I94" s="8" t="str">
+        <f t="array" ref="I94">_xlfn.SWITCH(H94,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J94" s="8"/>
+      <c r="K94" s="8"/>
+      <c r="L94" s="8"/>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A95" s="8"/>
+      <c r="B95" s="8"/>
+      <c r="C95" s="8"/>
+      <c r="D95" s="8"/>
+      <c r="E95" s="8"/>
+      <c r="F95" s="10"/>
+      <c r="G95" s="8"/>
+      <c r="H95" s="8"/>
+      <c r="I95" s="8" t="str">
+        <f t="array" ref="I95">_xlfn.SWITCH(H95,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J95" s="8"/>
+      <c r="K95" s="8"/>
+      <c r="L95" s="8"/>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A96" s="8"/>
+      <c r="B96" s="8"/>
+      <c r="C96" s="8"/>
+      <c r="D96" s="8"/>
+      <c r="E96" s="8"/>
+      <c r="F96" s="10"/>
+      <c r="G96" s="8"/>
+      <c r="H96" s="8"/>
+      <c r="I96" s="8" t="str">
+        <f t="array" ref="I96">_xlfn.SWITCH(H96,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J96" s="8"/>
+      <c r="K96" s="8"/>
+      <c r="L96" s="8"/>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A97" s="8"/>
+      <c r="B97" s="8"/>
+      <c r="C97" s="8"/>
+      <c r="D97" s="8"/>
+      <c r="E97" s="8"/>
+      <c r="F97" s="10"/>
+      <c r="G97" s="8"/>
+      <c r="H97" s="8"/>
+      <c r="I97" s="8" t="str">
+        <f t="array" ref="I97">_xlfn.SWITCH(H97,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J97" s="8"/>
+      <c r="K97" s="8"/>
+      <c r="L97" s="8"/>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A98" s="8"/>
+      <c r="B98" s="8"/>
+      <c r="C98" s="8"/>
+      <c r="D98" s="8"/>
+      <c r="E98" s="8"/>
+      <c r="F98" s="10"/>
+      <c r="G98" s="8"/>
+      <c r="H98" s="8"/>
+      <c r="I98" s="8" t="str">
+        <f t="array" ref="I98">_xlfn.SWITCH(H98,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J98" s="8"/>
+      <c r="K98" s="8"/>
+      <c r="L98" s="8"/>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A99" s="8"/>
+      <c r="B99" s="8"/>
+      <c r="C99" s="8"/>
+      <c r="D99" s="8"/>
+      <c r="E99" s="8"/>
+      <c r="F99" s="10"/>
+      <c r="G99" s="8"/>
+      <c r="H99" s="8"/>
+      <c r="I99" s="8" t="str">
+        <f t="array" ref="I99">_xlfn.SWITCH(H99,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J99" s="8"/>
+      <c r="K99" s="8"/>
+      <c r="L99" s="8"/>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A100" s="8"/>
+      <c r="B100" s="8"/>
+      <c r="C100" s="8"/>
+      <c r="D100" s="8"/>
+      <c r="E100" s="8"/>
+      <c r="F100" s="10"/>
+      <c r="G100" s="8"/>
+      <c r="H100" s="8"/>
+      <c r="I100" s="8" t="str">
+        <f t="array" ref="I100">_xlfn.SWITCH(H100,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J100" s="8"/>
+      <c r="K100" s="8"/>
+      <c r="L100" s="8"/>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A101" s="8"/>
+      <c r="B101" s="8"/>
+      <c r="C101" s="8"/>
+      <c r="D101" s="8"/>
+      <c r="E101" s="8"/>
+      <c r="F101" s="10"/>
+      <c r="G101" s="8"/>
+      <c r="H101" s="8"/>
+      <c r="I101" s="8" t="str">
+        <f t="array" ref="I101">_xlfn.SWITCH(H101,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J101" s="8"/>
+      <c r="K101" s="8"/>
+      <c r="L101" s="8"/>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A102" s="8"/>
+      <c r="B102" s="8"/>
+      <c r="C102" s="8"/>
+      <c r="D102" s="8"/>
+      <c r="E102" s="8"/>
+      <c r="F102" s="10"/>
+      <c r="G102" s="8"/>
+      <c r="H102" s="8"/>
+      <c r="I102" s="8" t="str">
+        <f t="array" ref="I102">_xlfn.SWITCH(H102,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J102" s="8"/>
+      <c r="K102" s="8"/>
+      <c r="L102" s="8"/>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A103" s="8"/>
+      <c r="B103" s="8"/>
+      <c r="C103" s="8"/>
+      <c r="D103" s="8"/>
+      <c r="E103" s="8"/>
+      <c r="F103" s="10"/>
+      <c r="G103" s="8"/>
+      <c r="H103" s="8"/>
+      <c r="I103" s="8" t="str">
+        <f t="array" ref="I103">_xlfn.SWITCH(H103,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J103" s="8"/>
+      <c r="K103" s="8"/>
+      <c r="L103" s="8"/>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A104" s="8"/>
+      <c r="B104" s="8"/>
+      <c r="C104" s="8"/>
+      <c r="D104" s="8"/>
+      <c r="E104" s="8"/>
+      <c r="F104" s="10"/>
+      <c r="G104" s="8"/>
+      <c r="H104" s="8"/>
+      <c r="I104" s="8" t="str">
+        <f t="array" ref="I104">_xlfn.SWITCH(H104,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J104" s="8"/>
+      <c r="K104" s="8"/>
+      <c r="L104" s="8"/>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A105" s="8"/>
+      <c r="B105" s="8"/>
+      <c r="C105" s="8"/>
+      <c r="D105" s="8"/>
+      <c r="E105" s="8"/>
+      <c r="F105" s="10"/>
+      <c r="G105" s="8"/>
+      <c r="H105" s="8"/>
+      <c r="I105" s="8" t="str">
+        <f t="array" ref="I105">_xlfn.SWITCH(H105,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J105" s="8"/>
+      <c r="K105" s="8"/>
+      <c r="L105" s="8"/>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A106" s="8"/>
+      <c r="B106" s="8"/>
+      <c r="C106" s="8"/>
+      <c r="D106" s="8"/>
+      <c r="E106" s="8"/>
+      <c r="F106" s="10"/>
+      <c r="G106" s="8"/>
+      <c r="H106" s="8"/>
+      <c r="I106" s="8" t="str">
+        <f t="array" ref="I106">_xlfn.SWITCH(H106,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J106" s="8"/>
+      <c r="K106" s="8"/>
+      <c r="L106" s="8"/>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A107" s="8"/>
+      <c r="B107" s="8"/>
+      <c r="C107" s="8"/>
+      <c r="D107" s="8"/>
+      <c r="E107" s="8"/>
+      <c r="F107" s="10"/>
+      <c r="G107" s="8"/>
+      <c r="H107" s="8"/>
+      <c r="I107" s="8" t="str">
+        <f t="array" ref="I107">_xlfn.SWITCH(H107,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J107" s="8"/>
+      <c r="K107" s="8"/>
+      <c r="L107" s="8"/>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A108" s="8"/>
+      <c r="B108" s="8"/>
+      <c r="C108" s="8"/>
+      <c r="D108" s="8"/>
+      <c r="E108" s="8"/>
+      <c r="F108" s="10"/>
+      <c r="G108" s="8"/>
+      <c r="H108" s="8"/>
+      <c r="I108" s="8" t="str">
+        <f t="array" ref="I108">_xlfn.SWITCH(H108,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J108" s="8"/>
+      <c r="K108" s="8"/>
+      <c r="L108" s="8"/>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A109" s="8"/>
+      <c r="B109" s="8"/>
+      <c r="C109" s="8"/>
+      <c r="D109" s="8"/>
+      <c r="E109" s="8"/>
+      <c r="F109" s="10"/>
+      <c r="G109" s="8"/>
+      <c r="H109" s="8"/>
+      <c r="I109" s="8" t="str">
+        <f t="array" ref="I109">_xlfn.SWITCH(H109,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J109" s="8"/>
+      <c r="K109" s="8"/>
+      <c r="L109" s="8"/>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A110" s="8"/>
+      <c r="B110" s="8"/>
+      <c r="C110" s="8"/>
+      <c r="D110" s="8"/>
+      <c r="E110" s="8"/>
+      <c r="F110" s="10"/>
+      <c r="G110" s="8"/>
+      <c r="H110" s="8"/>
+      <c r="I110" s="8" t="str">
+        <f t="array" ref="I110">_xlfn.SWITCH(H110,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J110" s="8"/>
+      <c r="K110" s="8"/>
+      <c r="L110" s="8"/>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A111" s="8"/>
+      <c r="B111" s="8"/>
+      <c r="C111" s="8"/>
+      <c r="D111" s="8"/>
+      <c r="E111" s="8"/>
+      <c r="F111" s="10"/>
+      <c r="G111" s="8"/>
+      <c r="H111" s="8"/>
+      <c r="I111" s="8" t="str">
+        <f t="array" ref="I111">_xlfn.SWITCH(H111,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J111" s="8"/>
+      <c r="K111" s="8"/>
+      <c r="L111" s="8"/>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A112" s="8"/>
+      <c r="B112" s="8"/>
+      <c r="C112" s="8"/>
+      <c r="D112" s="8"/>
+      <c r="E112" s="8"/>
+      <c r="F112" s="10"/>
+      <c r="G112" s="8"/>
+      <c r="H112" s="8"/>
+      <c r="I112" s="8" t="str">
+        <f t="array" ref="I112">_xlfn.SWITCH(H112,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J112" s="8"/>
+      <c r="K112" s="8"/>
+      <c r="L112" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47359ACD-20A0-40D8-BA3C-32B7C3C2E3F8}">
+  <dimension ref="A1:L10"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="4.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.77734375" style="5" customWidth="1"/>
+    <col min="4" max="4" width="10.77734375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="14">
+        <v>46251</v>
+      </c>
+      <c r="C2" s="4">
+        <f>34-SUM(E$2:E2)</f>
+        <v>34</v>
+      </c>
+      <c r="D2" s="1">
+        <f>34*(1-(A2/8))</f>
+        <v>34</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="14">
+        <v>46252</v>
+      </c>
+      <c r="C3" s="4">
+        <f>34-SUM(E$2:E3)</f>
+        <v>34</v>
+      </c>
+      <c r="D3" s="1">
+        <f t="shared" ref="D3:D10" si="0">34*(1-(A3/8))</f>
+        <v>29.75</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="14">
+        <v>46253</v>
+      </c>
+      <c r="C4" s="4">
+        <f>34-SUM(E$2:E4)</f>
+        <v>34</v>
+      </c>
+      <c r="D4" s="1">
+        <f t="shared" si="0"/>
+        <v>25.5</v>
+      </c>
+      <c r="E4" s="1">
+        <v>0</v>
+      </c>
+      <c r="L4" s="3"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="14">
+        <v>46254</v>
+      </c>
+      <c r="C5" s="4">
+        <f>34-SUM(E$2:E5)</f>
+        <v>34</v>
+      </c>
+      <c r="D5" s="1">
+        <f t="shared" si="0"/>
+        <v>21.25</v>
+      </c>
+      <c r="E5" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="14">
+        <v>46255</v>
+      </c>
+      <c r="C6" s="4">
+        <f>34-SUM(E$2:E6)</f>
+        <v>34</v>
+      </c>
+      <c r="D6" s="1">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="14">
+        <v>46258</v>
+      </c>
+      <c r="C7" s="4">
+        <f>34-SUM(E$2:E7)</f>
+        <v>34</v>
+      </c>
+      <c r="D7" s="1">
+        <f t="shared" si="0"/>
+        <v>12.75</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="14">
+        <v>46259</v>
+      </c>
+      <c r="C8" s="4">
+        <f>34-SUM(E$2:E8)</f>
+        <v>34</v>
+      </c>
+      <c r="D8" s="1">
+        <f t="shared" si="0"/>
+        <v>8.5</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="14">
+        <v>46260</v>
+      </c>
+      <c r="C9" s="4">
+        <f>34-SUM(E$2:E9)</f>
+        <v>34</v>
+      </c>
+      <c r="D9" s="1">
+        <f t="shared" si="0"/>
+        <v>4.25</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>8</v>
+      </c>
+      <c r="B10" s="14">
+        <v>46261</v>
+      </c>
+      <c r="C10" s="4">
+        <f>34-SUM(E$2:E10)</f>
+        <v>34</v>
+      </c>
+      <c r="D10" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/Business Analysis/checkupp_sprint_plan_2026.xlsx
+++ b/Business Analysis/checkupp_sprint_plan_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Business Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ANODIAM\CheckUpp\Business Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90A638BA-5839-48FD-BCF3-0E9E521B30B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9DFF801-27B8-44C8-8156-BCA7975288BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint 01" sheetId="1" r:id="rId1"/>
@@ -20,36 +20,20 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sprint 01'!$E$1:$E$112</definedName>
-    <definedName name="_xlchart.v1.0" hidden="1">'Sprint 02 Burndown'!$B$2:$B$10</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">'Sprint 02 Burndown'!$C$1</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">'Sprint 02 Burndown'!$C$2:$C$10</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">'Sprint 02 Burndown'!$D$1</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">'Sprint 02 Burndown'!$D$2:$D$10</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -64,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="101">
   <si>
     <t>Epic</t>
   </si>
@@ -6297,7 +6281,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-IN"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -6376,31 +6360,31 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>34</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>34</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>34</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>34</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>34</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>34</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>34</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>34</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>34</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6481,28 +6465,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>34</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>29.75</c:v>
+                  <c:v>28</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>25.5</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>21.25</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>17</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>12.75</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>8.5</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4.25</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -10836,7 +10820,9 @@
       <c r="F2" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="G2" s="15"/>
+      <c r="G2" s="15" t="s">
+        <v>21</v>
+      </c>
       <c r="H2" s="15" t="s">
         <v>27</v>
       </c>
@@ -10869,7 +10855,9 @@
       <c r="F3" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="G3" s="15"/>
+      <c r="G3" s="15" t="s">
+        <v>21</v>
+      </c>
       <c r="H3" s="15" t="s">
         <v>30</v>
       </c>
@@ -10902,7 +10890,9 @@
       <c r="F4" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="G4" s="15"/>
+      <c r="G4" s="15" t="s">
+        <v>21</v>
+      </c>
       <c r="H4" s="15" t="s">
         <v>27</v>
       </c>
@@ -10935,13 +10925,15 @@
       <c r="F5" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="G5" s="15"/>
+      <c r="G5" s="15" t="s">
+        <v>21</v>
+      </c>
       <c r="H5" s="15" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I5" s="15">
         <f t="array" ref="I5">_xlfn.SWITCH(H5,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J5" s="15" t="s">
         <v>79</v>
@@ -10968,7 +10960,9 @@
       <c r="F6" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="G6" s="15"/>
+      <c r="G6" s="15" t="s">
+        <v>21</v>
+      </c>
       <c r="H6" s="15" t="s">
         <v>27</v>
       </c>
@@ -11001,7 +10995,9 @@
       <c r="F7" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="G7" s="15"/>
+      <c r="G7" s="15" t="s">
+        <v>21</v>
+      </c>
       <c r="H7" s="15" t="s">
         <v>23</v>
       </c>
@@ -11034,11 +11030,13 @@
       <c r="F8" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="G8" s="17"/>
+      <c r="G8" s="17" t="s">
+        <v>29</v>
+      </c>
       <c r="H8" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="I8" s="17">
+      <c r="I8" s="15">
         <f t="array" ref="I8">_xlfn.SWITCH(H8,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
@@ -11067,11 +11065,13 @@
       <c r="F9" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="G9" s="17"/>
+      <c r="G9" s="17" t="s">
+        <v>29</v>
+      </c>
       <c r="H9" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="I9" s="17">
+      <c r="I9" s="15">
         <f t="array" ref="I9">_xlfn.SWITCH(H9,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
@@ -11100,11 +11100,13 @@
       <c r="F10" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="G10" s="17"/>
+      <c r="G10" s="17" t="s">
+        <v>29</v>
+      </c>
       <c r="H10" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="I10" s="17">
+      <c r="I10" s="15">
         <f t="array" ref="I10">_xlfn.SWITCH(H10,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
@@ -11131,11 +11133,13 @@
       <c r="F11" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="G11" s="19"/>
+      <c r="G11" s="19" t="s">
+        <v>29</v>
+      </c>
       <c r="H11" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="I11" s="19">
+      <c r="I11" s="15">
         <f t="array" ref="I11">_xlfn.SWITCH(H11,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
@@ -12862,12 +12866,12 @@
         <v>46251</v>
       </c>
       <c r="C2" s="4">
-        <f>34-SUM(E$2:E2)</f>
-        <v>34</v>
+        <f>32-SUM(E$2:E2)</f>
+        <v>32</v>
       </c>
       <c r="D2" s="1">
-        <f>34*(1-(A2/8))</f>
-        <v>34</v>
+        <f>32*(1-(A2/8))</f>
+        <v>32</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
@@ -12881,12 +12885,12 @@
         <v>46252</v>
       </c>
       <c r="C3" s="4">
-        <f>34-SUM(E$2:E3)</f>
-        <v>34</v>
+        <f>32-SUM(E$2:E3)</f>
+        <v>32</v>
       </c>
       <c r="D3" s="1">
-        <f t="shared" ref="D3:D10" si="0">34*(1-(A3/8))</f>
-        <v>29.75</v>
+        <f t="shared" ref="D3:D10" si="0">32*(1-(A3/8))</f>
+        <v>28</v>
       </c>
       <c r="E3" s="1">
         <v>0</v>
@@ -12900,12 +12904,12 @@
         <v>46253</v>
       </c>
       <c r="C4" s="4">
-        <f>34-SUM(E$2:E4)</f>
-        <v>34</v>
+        <f>32-SUM(E$2:E4)</f>
+        <v>32</v>
       </c>
       <c r="D4" s="1">
         <f t="shared" si="0"/>
-        <v>25.5</v>
+        <v>24</v>
       </c>
       <c r="E4" s="1">
         <v>0</v>
@@ -12920,12 +12924,12 @@
         <v>46254</v>
       </c>
       <c r="C5" s="4">
-        <f>34-SUM(E$2:E5)</f>
-        <v>34</v>
+        <f>32-SUM(E$2:E5)</f>
+        <v>32</v>
       </c>
       <c r="D5" s="1">
         <f t="shared" si="0"/>
-        <v>21.25</v>
+        <v>20</v>
       </c>
       <c r="E5" s="1">
         <v>0</v>
@@ -12939,12 +12943,12 @@
         <v>46255</v>
       </c>
       <c r="C6" s="4">
-        <f>34-SUM(E$2:E6)</f>
-        <v>34</v>
+        <f>32-SUM(E$2:E6)</f>
+        <v>32</v>
       </c>
       <c r="D6" s="1">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
@@ -12958,12 +12962,12 @@
         <v>46258</v>
       </c>
       <c r="C7" s="4">
-        <f>34-SUM(E$2:E7)</f>
-        <v>34</v>
+        <f>32-SUM(E$2:E7)</f>
+        <v>32</v>
       </c>
       <c r="D7" s="1">
         <f t="shared" si="0"/>
-        <v>12.75</v>
+        <v>12</v>
       </c>
       <c r="E7" s="1">
         <v>0</v>
@@ -12977,12 +12981,12 @@
         <v>46259</v>
       </c>
       <c r="C8" s="4">
-        <f>34-SUM(E$2:E8)</f>
-        <v>34</v>
+        <f>32-SUM(E$2:E8)</f>
+        <v>32</v>
       </c>
       <c r="D8" s="1">
         <f t="shared" si="0"/>
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="E8" s="1">
         <v>0</v>
@@ -12996,12 +13000,12 @@
         <v>46260</v>
       </c>
       <c r="C9" s="4">
-        <f>34-SUM(E$2:E9)</f>
-        <v>34</v>
+        <f>32-SUM(E$2:E9)</f>
+        <v>32</v>
       </c>
       <c r="D9" s="1">
         <f t="shared" si="0"/>
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
@@ -13015,8 +13019,8 @@
         <v>46261</v>
       </c>
       <c r="C10" s="4">
-        <f>34-SUM(E$2:E10)</f>
-        <v>34</v>
+        <f>32-SUM(E$2:E10)</f>
+        <v>32</v>
       </c>
       <c r="D10" s="1">
         <f t="shared" si="0"/>

--- a/Business Analysis/checkupp_sprint_plan_2026.xlsx
+++ b/Business Analysis/checkupp_sprint_plan_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ANODIAM\CheckUpp\Business Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9DFF801-27B8-44C8-8156-BCA7975288BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C71BA88-1BD8-429A-A2AC-E012F9D44E03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="118">
   <si>
     <t>Epic</t>
   </si>
@@ -5374,36 +5374,6 @@
 * **Acceptance Criteria Covered**: US 6.1 (AC 2, 3, 4)</t>
   </si>
   <si>
-    <t>Upload health documents (Note: This covers the list AC of 6.1)</t>
-  </si>
-  <si>
-    <t>Implement Document List View
-* **Target Files**:
-* `checkupp-mobile-main/lib/features/documents/queries.ts`
-* `checkupp-mobile-main/app/(tabs)/wallet.tsx`
-* **Description**:
-1. Ensure `queries.ts` correctly fetches from `GET /me/wallet/documents`.
-2. Design and implement a modular `DocumentListItem` component within `wallet.tsx` (or a dedicated components folder) to map over the fetched data.
-3. Display the document name, upload date, and a "More Options" (three dots) menu containing icons for "View", "Download", "Share", and "Delete".
-4. Implement `checkupp-mobile-main/components/EmptyState.tsx` if the query returns an empty array.
-* **Acceptance Criteria Covered**: US 6.1 (AC 5, 6)</t>
-  </si>
-  <si>
-    <t>View health documents</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Implement Document Viewer Integration
-* **Target Files**:
-* `checkupp-mobile-main/app/(tabs)/wallet.tsx`
-* `checkupp-mobile-main/components/DocumentViewer.tsx`
-* **Description**:
-1. Wire up the "View" action from the document list to trigger the existing `DocumentViewer.tsx` component.
-2. Pass the `externalUrl` or `publicUrl` of the document to the viewer.
-3. Implement a fallback error boundary and toast notification ("Could not open file") if the URL is invalid or the device cannot render the file type.
-* **Acceptance Criteria Covered**: US 6.4 (AC 1, 2)
-</t>
-  </si>
-  <si>
     <t>Share health documents</t>
   </si>
   <si>
@@ -5452,22 +5422,7 @@
 * **Acceptance Criteria Covered**: US 7.1 (AC 1, 3)</t>
   </si>
   <si>
-    <t>7.1, 7.2</t>
-  </si>
-  <si>
     <t>View e-script links</t>
-  </si>
-  <si>
-    <t>Implement Link List &amp; WebView
-* **Target Files**:
-* `checkupp-mobile-main/app/(tabs)/wallet.tsx`
-* `checkupp-mobile-main/lib/features/documents/queries.ts`
-* **Description**:
-1. Fetch the links using `GET /me/wallet/documents` filtered by `fileType=LINK` or `documentType=E-SCRIPT`.
-2. Render the links with their title/description and creation date. Include action buttons for View, Share, and Delete.
-3. Wire the "View" action to open the link using `expo-web-browser` (`WebBrowser.openBrowserAsync`).
-4. Wrap the view action in a `try/catch` returning the error toast: "Could not open Expanded View, try again".
-* **Acceptance Criteria Covered**: US 7.1 (AC 2, 4, 5), US 7.2 (AC 1)</t>
   </si>
   <si>
     <t>7.3, 7.4</t>
@@ -5503,6 +5458,173 @@
 2. Verify that deletion securely handles `userId` scoping to prevent unauthorized deletion (tenant isolation).
 3. Verify that `createLinkSchema` strictly requires a valid URI pattern and returns a 400 Bad Request if the format is invalid.
 4. Verify that the `deleteDocument` service correctly unlinks the file from cloud storage using `cleanupUploadedFile` when a document is deleted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Direct Document Download</t>
+  </si>
+  <si>
+    <t>6.1, 6.6</t>
+  </si>
+  <si>
+    <t>Document List View</t>
+  </si>
+  <si>
+    <t>Implement Document List View
+* **Target Files**:
+* `checkupp-mobile-main/lib/features/documents/queries.ts`
+* `checkupp-mobile-main/app/(tabs)/wallet.tsx`
+* **Description**:
+1. Ensure `queries.ts` correctly fetches from `GET /me/wallet/documents`.
+2. Design and implement a modular `DocumentListItem` component within `wallet.tsx` to map over the fetched data, displaying the document name and upload date.
+3. **Implement responsive card layout:**
+* **Large Screens:** Display standalone icons for "Share" and "Download", plus a vertical three-dot (kebab) menu. Expanding the kebab menu reveals "View" and "Delete".
+* **Small Screens (Edge Case):** Default to showing only the "Share" icon and the kebab menu. Expanding the menu reveals "View", "Download", and "Delete".
+4. Implement `checkupp-mobile-main/components/EmptyState.tsx` if the query returns an empty array.
+* **Acceptance Criteria Covered**: US 6.1 (AC 5, 6), US 6.6 (AC 1, 2, 3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Document Viewer Integration</t>
+  </si>
+  <si>
+    <t>Implement Document Viewer Integration
+* **Target Files**:
+* `checkupp-mobile-main/app/(tabs)/wallet.tsx`
+* `checkupp-mobile-main/components/DocumentViewer.tsx`
+* **Description**:
+1. Wire up the "View" action from the document list to trigger the existing `DocumentViewer.tsx` component.
+2. Pass the `externalUrl` or `publicUrl` of the document to the viewer.
+3. Implement a fallback error boundary and toast notification ("Could not open file") if the URL is invalid or the device cannot render the file type.
+4. **Enforce explicit removal:** Ensure the "Download" button is strictly removed or disabled within this view screen, as downloading is now an independent card action.
+* **Acceptance Criteria Covered**: US 6.4 (AC 1, 2, 3)</t>
+  </si>
+  <si>
+    <t>Implement Direct Document Download
+* **Target Files**:
+* `checkupp-mobile-main/app/(tabs)/wallet.tsx`
+* `checkupp-mobile-main/lib/utils/fileUtils.ts` (Existing or create new)
+* **Description**:
+1. Implement a download handler triggered directly from the "Download" option on the document card (or within its expanded menu).
+2. Utilize `expo-file-system` to securely fetch and save the document to the user's local device storage without requiring them to open it first.
+3. On success, trigger a `CustomToast.tsx` message displaying: "Download complete".
+4. On failure, trigger an error message prompting the user to try again.
+* **Acceptance Criteria Covered**: US 6.5 (AC 1, 2, 3, 4)</t>
+  </si>
+  <si>
+    <t>7.1, 7.2, 7.5</t>
+  </si>
+  <si>
+    <t>* **Target Files**:
+* `checkupp-mobile-main/app/(tabs)/wallet.tsx`
+* `checkupp-mobile-main/lib/features/documents/queries.ts`
+* **Description**:
+1. Fetch the links using `GET /me/wallet/documents` filtered by `fileType=LINK` or `documentType=E-SCRIPT`.
+2. Render the links with their title/description and creation date.
+3. **Implement responsive card layout:**
+* **Large Screens:** Display standalone buttons for "Share", "Open", and "Delete".
+* **Small Screens (Edge Case):** Display only the "Share" icon alongside a Hamburger Menu (three vertically stacked dots). Expanding the menu reveals "Open" and "Delete".
+4. Wire the "Open" action to open the link using `expo-web-browser` (`WebBrowser.openBrowserAsync`).
+5. Wrap the view action in a `try/catch` returning the error toast: "Could not open Expanded View, try again".
+* **Acceptance Criteria Covered**: US 7.1 (AC 2, 4, 5), US 7.2 (AC 1), US 7.5 (AC 1, 2, 3)</t>
+  </si>
+  <si>
+    <t>Cardiovascular Reading</t>
+  </si>
+  <si>
+    <t>Cardiovascular Camera Scanner UI &amp; Permission Handling</t>
+  </si>
+  <si>
+    <t>Cardiovascular Camera Scanner UI &amp; Permission Handling
+* **Target Files**:
+* `checkupp-mobile-main/app/(tabs)/cardiovascular.tsx`
+* `checkupp-mobile-main/components/camera/ScanMonitorModal.tsx`
+* **Description**:
+1. Add a "Scan Monitor" icon/button next to the manual input fields for Blood Pressure on the Cardiovascular screen.
+2. Implement `ScanMonitorModal.tsx` using `react-native-vision-camera` (or `expo-camera`).
+3. Include native camera permission checks with graceful permission fallback prompts.
+4. Design a full-screen camera modal with a centered "Target Bounding Box" overlay instructing the user to "Align your screen's numbers inside this box."
+5. Include a prominent manual "Cancel / Enter Manually" button to allow users to exit the camera view at any time.
+6. Cap camera frame processing at 15–30 fps via frame processor configuration to optimize device battery consumption and prevent thermal throttling.
+* **Acceptance Criteria Covered**: US 19.3 (AC 1, 2, 3, 4, 7)</t>
+  </si>
+  <si>
+    <t>OCR Processing, Frame Processor &amp; Form Auto-Fill</t>
+  </si>
+  <si>
+    <t>Blood Pressure ML Kit Extraction, Y-Coordinate Sorting &amp; Validation
+* **Target Files**:
+* `checkupp-mobile-main/lib/utils/ocrUtils.ts`
+* `checkupp-mobile-main/components/camera/ScanMonitorModal.tsx`
+* `checkupp-mobile-main/app/(tabs)/cardiovascular.tsx`
+* **Description**:
+1. Integrate Google ML Kit Text Recognition into the camera frame processor to extract numerical text strings dynamically.
+2. Implement vertical Y-coordinate sorting in `ocrUtils.ts`:
+* Highest Y-coordinate $\rightarrow$ Auto-fills **Systolic (mmHg)**
+* Middle Y-coordinate $\rightarrow$ Auto-fills **Diastolic (mmHg)**
+* Lowest Y-coordinate $\rightarrow$ Auto-fills **Heart Rate (BPM)**
+3. Close the camera modal upon successful extraction, populate the respective form fields, and display a Toast/Banner stating: `"Numbers scanned successfully. Please verify against your device."`
+4. Implement a 10-second timeout scanner loop. If no valid match is found within 10 seconds, trigger a prompt: `"Having trouble reading the screen. Ensure there is no glare, or switch to manual entry."` with an easy button to exit.
+* **Acceptance Criteria Covered**: US 19.3 (AC 5, 6, 8)</t>
+  </si>
+  <si>
+    <t>Diabetes Test</t>
+  </si>
+  <si>
+    <t>Single-Number OCR, Contextual Selection &amp; Auto-Fill</t>
+  </si>
+  <si>
+    <t>Glucometer ML Kit Scanning &amp; Contextual Reading Modal
+* **Target Files**:
+* `checkupp-mobile-main/app/(tabs)/diabetes.tsx`
+* `checkupp-mobile-main/components/camera/GlucometerScannerModal.tsx`
+* `checkupp-mobile-main/components/ReadingTypeBottomSheet.tsx`
+* **Description**:
+1. Place a "Scan Glucometer" button prominently at the top of the Blood Glucose section in the Diabetes form.
+2. Implement a focused scanner modal targeting single numbers (including decimals, e.g., 5.6 or 12.1) using regular expression matching.
+3. Upon capturing the valid glucose value, display `ReadingTypeBottomSheet.tsx` asking: `"What type of reading is this?"` with options:
+* Fasting Glucose
+* Random Glucose
+* Post-Meal Glucose
+4. Inject the scanned number specifically into the selected option's field and close the bottom sheet.
+5. Enforce human-in-the-loop confirmation where the user must manually tap "Save Reading" to commit to the backend.
+6. Add the 10-second scanner timeout alert with manual fallback options.
+* **Acceptance Criteria Covered**: US 20.3 - Glucometer (AC 1, 2, 3, 4, 5, 6, 7)</t>
+  </si>
+  <si>
+    <t>Contrast Pre-Processing, Regex Extraction &amp; Auto-Fill</t>
+  </si>
+  <si>
+    <t>Digital Weight Scale Camera Scanner with Image Pre-Processing
+* **Target Files**:
+* `checkupp-mobile-main/app/(tabs)/diabetes.tsx`
+* `checkupp-mobile-main/components/camera/ScaleScannerModal.tsx`
+* `checkupp-mobile-main/lib/utils/imageUtils.ts`
+* **Description**:
+1. Add a "Scan Scale" icon next to the Weight input field on the Diabetes form (and reusable shared modules).
+2. Implement `imageUtils.ts` threshold/contrast filter pre-processing on the captured camera frame to isolate glowing LCD digits from reflective or backlit scale surfaces before passing to ML Kit.
+3. Extract a 2-to-3 digit number (with or without a single decimal, e.g., 75.4 or 98) using Regex matching.
+4. Auto-fill the extracted value directly into the **Weight (kg)** field without triggering secondary contextual modals.
+5. Implement the 10-second timeout fallback alert ("Having trouble reading the screen...").
+* **Acceptance Criteria Covered**: US 20.3 - Weight Scale (AC 1, 2, 3, 4, 5)</t>
+  </si>
+  <si>
+    <t>Global Backend &amp; Validation Tasks</t>
+  </si>
+  <si>
+    <t>Controller, Validation &amp; Database Schema</t>
+  </si>
+  <si>
+    <t>Vitals &amp; Diabetes Measurement Ingestion Verification
+* **Target Files**:
+* `checkupp-api-main/src/modules/vitals/vitals.controller.ts`
+* `checkupp-api-main/src/modules/vitals/vitals.validation.ts`
+* `checkupp-api-main/tests/modules/vitals/vitals.test.ts`
+* **Description**:
+1. Ensure `vitals.validation.ts` accommodates auto-filled decimal and integer values strictly matching physiological sanity bounds (e.g., Systolic 50–250 mmHg, Weight 20–300 kg, Glucose 1–35 mmol/L or 20–600 mg/dL).
+2. Write unit and integration tests verifying that incoming payloads from both manual entry and camera-scanned flows validate identically and save correctly to user history.
+* **Acceptance Criteria Covered**: Cross-epic data integrity for US 19.3 &amp; US 20.3</t>
+  </si>
+  <si>
+    <t>Alekhya &amp; Atish</t>
   </si>
 </sst>
 </file>
@@ -5569,7 +5691,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5608,7 +5730,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5640,7 +5774,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5700,6 +5834,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6360,31 +6506,31 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>32</c:v>
+                  <c:v>54</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>32</c:v>
+                  <c:v>54</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>32</c:v>
+                  <c:v>54</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>32</c:v>
+                  <c:v>54</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>32</c:v>
+                  <c:v>54</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>32</c:v>
+                  <c:v>54</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>32</c:v>
+                  <c:v>54</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>32</c:v>
+                  <c:v>54</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>32</c:v>
+                  <c:v>54</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6465,28 +6611,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>32</c:v>
+                  <c:v>54</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>28</c:v>
+                  <c:v>47.25</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>24</c:v>
+                  <c:v>40.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>20</c:v>
+                  <c:v>33.75</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>16</c:v>
+                  <c:v>27</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>12</c:v>
+                  <c:v>20.25</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>8</c:v>
+                  <c:v>13.5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4</c:v>
+                  <c:v>6.75</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -10746,13 +10892,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA30D3B6-4BBC-427B-918A-C301767B692F}">
-  <dimension ref="A1:L112"/>
+  <dimension ref="A1:L113"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.44140625" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" customWidth="1"/>
+    <col min="3" max="3" width="7.6640625" customWidth="1"/>
+    <col min="4" max="4" width="11.109375" customWidth="1"/>
     <col min="5" max="5" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="99.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8" bestFit="1" customWidth="1"/>
@@ -10821,7 +10967,7 @@
         <v>78</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="H2" s="15" t="s">
         <v>27</v>
@@ -10856,7 +11002,7 @@
         <v>80</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="H3" s="15" t="s">
         <v>30</v>
@@ -10871,27 +11017,27 @@
       <c r="K3" s="15"/>
       <c r="L3" s="15"/>
     </row>
-    <row r="4" spans="1:12" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="216" x14ac:dyDescent="0.3">
       <c r="A4" s="15">
         <v>3</v>
       </c>
       <c r="B4" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="C4" s="15">
-        <v>6.1</v>
+      <c r="C4" s="15" t="s">
+        <v>96</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="E4" s="15" t="s">
         <v>20</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="H4" s="15" t="s">
         <v>27</v>
@@ -10906,7 +11052,7 @@
       <c r="K4" s="15"/>
       <c r="L4" s="15"/>
     </row>
-    <row r="5" spans="1:12" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A5" s="15">
         <v>4</v>
       </c>
@@ -10917,16 +11063,16 @@
         <v>6.4</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="E5" s="15" t="s">
         <v>20</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="H5" s="15" t="s">
         <v>27</v>
@@ -10952,16 +11098,16 @@
         <v>6.2</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E6" s="15" t="s">
         <v>20</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="H6" s="15" t="s">
         <v>27</v>
@@ -10987,16 +11133,16 @@
         <v>6.3</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E7" s="15" t="s">
         <v>20</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="H7" s="15" t="s">
         <v>23</v>
@@ -11011,67 +11157,67 @@
       <c r="K7" s="15"/>
       <c r="L7" s="15"/>
     </row>
-    <row r="8" spans="1:12" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="17">
+    <row r="8" spans="1:12" ht="99" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="15">
         <v>7</v>
       </c>
-      <c r="B8" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="C8" s="17">
-        <v>7.1</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="E8" s="17" t="s">
+      <c r="B8" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" s="15">
+        <v>6.5</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="E8" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="G8" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="H8" s="17" t="s">
+      <c r="F8" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="H8" s="15" t="s">
         <v>27</v>
       </c>
       <c r="I8" s="15">
         <f t="array" ref="I8">_xlfn.SWITCH(H8,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J8" s="17" t="s">
+      <c r="J8" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="K8" s="17"/>
-      <c r="L8" s="17"/>
-    </row>
-    <row r="9" spans="1:12" ht="144" x14ac:dyDescent="0.3">
+      <c r="K8" s="15"/>
+      <c r="L8" s="15"/>
+    </row>
+    <row r="9" spans="1:12" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A9" s="17">
         <v>8</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>92</v>
+        <v>85</v>
+      </c>
+      <c r="C9" s="17">
+        <v>7.1</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="E9" s="17" t="s">
         <v>20</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>29</v>
+        <v>117</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="I9" s="15">
+      <c r="I9" s="17">
         <f t="array" ref="I9">_xlfn.SWITCH(H9,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
@@ -11081,34 +11227,34 @@
       <c r="K9" s="17"/>
       <c r="L9" s="17"/>
     </row>
-    <row r="10" spans="1:12" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A10" s="17">
         <v>9</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E10" s="17" t="s">
         <v>20</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>29</v>
+        <v>117</v>
       </c>
       <c r="H10" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="I10" s="15">
+        <v>27</v>
+      </c>
+      <c r="I10" s="17">
         <f t="array" ref="I10">_xlfn.SWITCH(H10,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J10" s="17" t="s">
         <v>79</v>
@@ -11116,122 +11262,246 @@
       <c r="K10" s="17"/>
       <c r="L10" s="17"/>
     </row>
-    <row r="11" spans="1:12" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="19">
+    <row r="11" spans="1:12" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A11" s="17">
         <v>10</v>
       </c>
-      <c r="B11" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="E11" s="19" t="s">
+      <c r="B11" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="G11" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="H11" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="I11" s="17">
+        <f t="array" ref="I11">_xlfn.SWITCH(H11,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="J11" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="K11" s="17"/>
+      <c r="L11" s="17"/>
+    </row>
+    <row r="12" spans="1:12" ht="230.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="19">
+        <v>11</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="E12" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="F11" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="G11" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="H11" s="19" t="s">
+      <c r="F12" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="H12" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="I11" s="15">
-        <f t="array" ref="I11">_xlfn.SWITCH(H11,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="I12" s="19">
+        <f t="array" ref="I12">_xlfn.SWITCH(H12,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J11" s="19" t="s">
+      <c r="J12" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="K11" s="19"/>
-      <c r="L11" s="19"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+    </row>
+    <row r="13" spans="1:12" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="21">
+        <v>12</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="C13" s="21">
+        <v>19.3</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="G13" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="H13" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="I13" s="21">
+        <f t="array" ref="I13">_xlfn.SWITCH(H13,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="J13" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="K13" s="21"/>
+      <c r="L13" s="21"/>
+    </row>
+    <row r="14" spans="1:12" ht="244.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="21">
+        <v>13</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="C14" s="21">
+        <v>19.3</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="H14" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="I14" s="21">
+        <f t="array" ref="I14">_xlfn.SWITCH(H14,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>5</v>
+      </c>
+      <c r="J14" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="K14" s="21"/>
+      <c r="L14" s="21"/>
+    </row>
+    <row r="15" spans="1:12" ht="273.60000000000002" x14ac:dyDescent="0.3">
+      <c r="A15" s="21">
+        <v>14</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="C15" s="21">
+        <v>20.3</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="E15" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="G15" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="H15" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="I15" s="21">
+        <f t="array" ref="I15">_xlfn.SWITCH(H15,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>5</v>
+      </c>
+      <c r="J15" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="K15" s="21"/>
+      <c r="L15" s="21"/>
+    </row>
+    <row r="16" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="21">
+        <v>15</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="C16" s="21">
+        <v>20.3</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="G16" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="H16" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="I16" s="21">
+        <f t="array" ref="I16">_xlfn.SWITCH(H16,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="J16" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="K16" s="21"/>
+      <c r="L16" s="21"/>
+    </row>
+    <row r="17" spans="1:12" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A17" s="23">
+        <v>16</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23" t="s">
+        <v>115</v>
+      </c>
+      <c r="E17" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="F17" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="G17" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="H17" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="I17" s="23">
+        <f t="array" ref="I17">_xlfn.SWITCH(H17,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="J17" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="K17" s="23"/>
+      <c r="L17" s="23"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="8"/>
@@ -11354,10 +11624,7 @@
       <c r="F26" s="10"/>
       <c r="G26" s="8"/>
       <c r="H26" s="8"/>
-      <c r="I26" s="8" t="str">
-        <f t="array" ref="I26">_xlfn.SWITCH(H26,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
+      <c r="I26" s="8"/>
       <c r="J26" s="8"/>
       <c r="K26" s="8"/>
       <c r="L26" s="8"/>
@@ -11470,7 +11737,7 @@
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
       <c r="E33" s="8"/>
-      <c r="F33" s="7"/>
+      <c r="F33" s="10"/>
       <c r="G33" s="8"/>
       <c r="H33" s="8"/>
       <c r="I33" s="8" t="str">
@@ -11487,7 +11754,7 @@
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
       <c r="E34" s="8"/>
-      <c r="F34" s="9"/>
+      <c r="F34" s="7"/>
       <c r="G34" s="8"/>
       <c r="H34" s="8"/>
       <c r="I34" s="8" t="str">
@@ -11776,7 +12043,7 @@
       <c r="C51" s="8"/>
       <c r="D51" s="8"/>
       <c r="E51" s="8"/>
-      <c r="F51" s="10"/>
+      <c r="F51" s="9"/>
       <c r="G51" s="8"/>
       <c r="H51" s="8"/>
       <c r="I51" s="8" t="str">
@@ -11878,7 +12145,7 @@
       <c r="C57" s="8"/>
       <c r="D57" s="8"/>
       <c r="E57" s="8"/>
-      <c r="F57" s="9"/>
+      <c r="F57" s="10"/>
       <c r="G57" s="8"/>
       <c r="H57" s="8"/>
       <c r="I57" s="8" t="str">
@@ -12065,7 +12332,7 @@
       <c r="C68" s="8"/>
       <c r="D68" s="8"/>
       <c r="E68" s="8"/>
-      <c r="F68" s="7"/>
+      <c r="F68" s="9"/>
       <c r="G68" s="8"/>
       <c r="H68" s="8"/>
       <c r="I68" s="8" t="str">
@@ -12082,7 +12349,7 @@
       <c r="C69" s="8"/>
       <c r="D69" s="8"/>
       <c r="E69" s="8"/>
-      <c r="F69" s="9"/>
+      <c r="F69" s="7"/>
       <c r="G69" s="8"/>
       <c r="H69" s="8"/>
       <c r="I69" s="8" t="str">
@@ -12099,7 +12366,7 @@
       <c r="C70" s="8"/>
       <c r="D70" s="8"/>
       <c r="E70" s="8"/>
-      <c r="F70" s="7"/>
+      <c r="F70" s="9"/>
       <c r="G70" s="8"/>
       <c r="H70" s="8"/>
       <c r="I70" s="8" t="str">
@@ -12133,7 +12400,7 @@
       <c r="C72" s="8"/>
       <c r="D72" s="8"/>
       <c r="E72" s="8"/>
-      <c r="F72" s="9"/>
+      <c r="F72" s="7"/>
       <c r="G72" s="8"/>
       <c r="H72" s="8"/>
       <c r="I72" s="8" t="str">
@@ -12218,7 +12485,7 @@
       <c r="C77" s="8"/>
       <c r="D77" s="8"/>
       <c r="E77" s="8"/>
-      <c r="F77" s="10"/>
+      <c r="F77" s="9"/>
       <c r="G77" s="8"/>
       <c r="H77" s="8"/>
       <c r="I77" s="8" t="str">
@@ -12823,6 +13090,23 @@
       <c r="J112" s="8"/>
       <c r="K112" s="8"/>
       <c r="L112" s="8"/>
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A113" s="8"/>
+      <c r="B113" s="8"/>
+      <c r="C113" s="8"/>
+      <c r="D113" s="8"/>
+      <c r="E113" s="8"/>
+      <c r="F113" s="10"/>
+      <c r="G113" s="8"/>
+      <c r="H113" s="8"/>
+      <c r="I113" s="8" t="str">
+        <f t="array" ref="I113">_xlfn.SWITCH(H113,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J113" s="8"/>
+      <c r="K113" s="8"/>
+      <c r="L113" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12866,12 +13150,12 @@
         <v>46251</v>
       </c>
       <c r="C2" s="4">
-        <f>32-SUM(E$2:E2)</f>
-        <v>32</v>
+        <f>54-SUM(E$2:E2)</f>
+        <v>54</v>
       </c>
       <c r="D2" s="1">
-        <f>32*(1-(A2/8))</f>
-        <v>32</v>
+        <f>54*(1-(A2/8))</f>
+        <v>54</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
@@ -12885,12 +13169,12 @@
         <v>46252</v>
       </c>
       <c r="C3" s="4">
-        <f>32-SUM(E$2:E3)</f>
-        <v>32</v>
+        <f>54-SUM(E$2:E3)</f>
+        <v>54</v>
       </c>
       <c r="D3" s="1">
-        <f t="shared" ref="D3:D10" si="0">32*(1-(A3/8))</f>
-        <v>28</v>
+        <f t="shared" ref="D3:D10" si="0">54*(1-(A3/8))</f>
+        <v>47.25</v>
       </c>
       <c r="E3" s="1">
         <v>0</v>
@@ -12904,12 +13188,12 @@
         <v>46253</v>
       </c>
       <c r="C4" s="4">
-        <f>32-SUM(E$2:E4)</f>
-        <v>32</v>
+        <f>54-SUM(E$2:E4)</f>
+        <v>54</v>
       </c>
       <c r="D4" s="1">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>40.5</v>
       </c>
       <c r="E4" s="1">
         <v>0</v>
@@ -12924,12 +13208,12 @@
         <v>46254</v>
       </c>
       <c r="C5" s="4">
-        <f>32-SUM(E$2:E5)</f>
-        <v>32</v>
+        <f>54-SUM(E$2:E5)</f>
+        <v>54</v>
       </c>
       <c r="D5" s="1">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>33.75</v>
       </c>
       <c r="E5" s="1">
         <v>0</v>
@@ -12943,12 +13227,12 @@
         <v>46255</v>
       </c>
       <c r="C6" s="4">
-        <f>32-SUM(E$2:E6)</f>
-        <v>32</v>
+        <f>54-SUM(E$2:E6)</f>
+        <v>54</v>
       </c>
       <c r="D6" s="1">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
@@ -12962,12 +13246,12 @@
         <v>46258</v>
       </c>
       <c r="C7" s="4">
-        <f>32-SUM(E$2:E7)</f>
-        <v>32</v>
+        <f>54-SUM(E$2:E7)</f>
+        <v>54</v>
       </c>
       <c r="D7" s="1">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>20.25</v>
       </c>
       <c r="E7" s="1">
         <v>0</v>
@@ -12981,12 +13265,12 @@
         <v>46259</v>
       </c>
       <c r="C8" s="4">
-        <f>32-SUM(E$2:E8)</f>
-        <v>32</v>
+        <f>54-SUM(E$2:E8)</f>
+        <v>54</v>
       </c>
       <c r="D8" s="1">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>13.5</v>
       </c>
       <c r="E8" s="1">
         <v>0</v>
@@ -13000,12 +13284,12 @@
         <v>46260</v>
       </c>
       <c r="C9" s="4">
-        <f>32-SUM(E$2:E9)</f>
-        <v>32</v>
+        <f>54-SUM(E$2:E9)</f>
+        <v>54</v>
       </c>
       <c r="D9" s="1">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>6.75</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
@@ -13019,8 +13303,8 @@
         <v>46261</v>
       </c>
       <c r="C10" s="4">
-        <f>32-SUM(E$2:E10)</f>
-        <v>32</v>
+        <f>54-SUM(E$2:E10)</f>
+        <v>54</v>
       </c>
       <c r="D10" s="1">
         <f t="shared" si="0"/>

--- a/Business Analysis/checkupp_sprint_plan_2026.xlsx
+++ b/Business Analysis/checkupp_sprint_plan_2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ANODIAM\CheckUpp\Business Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Business Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C71BA88-1BD8-429A-A2AC-E012F9D44E03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5CB78D0-50AC-4087-955E-59A9E659A7A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,18 +22,29 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sprint 01'!$E$1:$E$112</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
       <extLst>
-        <ext xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
@@ -5550,22 +5561,6 @@
     <t>OCR Processing, Frame Processor &amp; Form Auto-Fill</t>
   </si>
   <si>
-    <t>Blood Pressure ML Kit Extraction, Y-Coordinate Sorting &amp; Validation
-* **Target Files**:
-* `checkupp-mobile-main/lib/utils/ocrUtils.ts`
-* `checkupp-mobile-main/components/camera/ScanMonitorModal.tsx`
-* `checkupp-mobile-main/app/(tabs)/cardiovascular.tsx`
-* **Description**:
-1. Integrate Google ML Kit Text Recognition into the camera frame processor to extract numerical text strings dynamically.
-2. Implement vertical Y-coordinate sorting in `ocrUtils.ts`:
-* Highest Y-coordinate $\rightarrow$ Auto-fills **Systolic (mmHg)**
-* Middle Y-coordinate $\rightarrow$ Auto-fills **Diastolic (mmHg)**
-* Lowest Y-coordinate $\rightarrow$ Auto-fills **Heart Rate (BPM)**
-3. Close the camera modal upon successful extraction, populate the respective form fields, and display a Toast/Banner stating: `"Numbers scanned successfully. Please verify against your device."`
-4. Implement a 10-second timeout scanner loop. If no valid match is found within 10 seconds, trigger a prompt: `"Having trouble reading the screen. Ensure there is no glare, or switch to manual entry."` with an easy button to exit.
-* **Acceptance Criteria Covered**: US 19.3 (AC 5, 6, 8)</t>
-  </si>
-  <si>
     <t>Diabetes Test</t>
   </si>
   <si>
@@ -5625,6 +5620,22 @@
   </si>
   <si>
     <t>Alekhya &amp; Atish</t>
+  </si>
+  <si>
+    <t>Blood Pressure ML Kit Extraction, Y-Coordinate Sorting &amp; Validation
+* **Target Files**:
+* `checkupp-mobile-main/lib/utils/ocrUtils.ts`
+* `checkupp-mobile-main/components/camera/ScanMonitorModal.tsx`
+* `checkupp-mobile-main/app/(tabs)/cardiovascular.tsx`
+* **Description**:
+1. Integrate Google ML Kit Text Recognition into the camera frame processor to extract numerical text strings dynamically.
+2. Implement vertical Y-coordinate sorting in `ocrUtils.ts`:
+* Highest Y-coordinate -&gt; Auto-fills **Systolic (mmHg)**
+* Middle Y-coordinate -&gt; Auto-fills **Diastolic (mmHg)**
+* Lowest Y-coordinate -&gt; Auto-fills **Heart Rate (BPM)**
+3. Close the camera modal upon successful extraction, populate the respective form fields, and display a Toast/Banner stating: `"Numbers scanned successfully. Please verify against your device."`
+4. Implement a 10-second timeout scanner loop. If no valid match is found within 10 seconds, trigger a prompt: `"Having trouble reading the screen. Ensure there is no glare, or switch to manual entry."` with an easy button to exit.
+* **Acceptance Criteria Covered**: US 19.3 (AC 5, 6, 8)</t>
   </si>
 </sst>
 </file>
@@ -10967,7 +10978,7 @@
         <v>78</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H2" s="15" t="s">
         <v>27</v>
@@ -11002,7 +11013,7 @@
         <v>80</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H3" s="15" t="s">
         <v>30</v>
@@ -11037,7 +11048,7 @@
         <v>98</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H4" s="15" t="s">
         <v>27</v>
@@ -11072,7 +11083,7 @@
         <v>100</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H5" s="15" t="s">
         <v>27</v>
@@ -11107,7 +11118,7 @@
         <v>82</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H6" s="15" t="s">
         <v>27</v>
@@ -11142,7 +11153,7 @@
         <v>84</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H7" s="15" t="s">
         <v>23</v>
@@ -11177,7 +11188,7 @@
         <v>101</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H8" s="15" t="s">
         <v>27</v>
@@ -11212,7 +11223,7 @@
         <v>87</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>27</v>
@@ -11247,7 +11258,7 @@
         <v>103</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>27</v>
@@ -11282,7 +11293,7 @@
         <v>91</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H11" s="17" t="s">
         <v>23</v>
@@ -11315,7 +11326,7 @@
         <v>94</v>
       </c>
       <c r="G12" s="19" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H12" s="19" t="s">
         <v>30</v>
@@ -11330,7 +11341,7 @@
       <c r="K12" s="19"/>
       <c r="L12" s="19"/>
     </row>
-    <row r="13" spans="1:12" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A13" s="21">
         <v>12</v>
       </c>
@@ -11382,7 +11393,7 @@
         <v>20</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="G14" s="21" t="s">
         <v>24</v>
@@ -11405,19 +11416,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C15" s="21">
         <v>20.3</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E15" s="21" t="s">
         <v>20</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G15" s="21" t="s">
         <v>24</v>
@@ -11440,19 +11451,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C16" s="21">
         <v>20.3</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E16" s="21" t="s">
         <v>20</v>
       </c>
       <c r="F16" s="22" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G16" s="21" t="s">
         <v>24</v>
@@ -11475,17 +11486,17 @@
         <v>16</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C17" s="23"/>
       <c r="D17" s="23" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E17" s="23" t="s">
         <v>22</v>
       </c>
       <c r="F17" s="24" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G17" s="23" t="s">
         <v>24</v>

--- a/Business Analysis/checkupp_sprint_plan_2026.xlsx
+++ b/Business Analysis/checkupp_sprint_plan_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Business Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5CB78D0-50AC-4087-955E-59A9E659A7A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CA2C8B7-F614-444B-8762-C8F096F11AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10907,11 +10907,11 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" customWidth="1"/>
-    <col min="3" max="3" width="7.6640625" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.109375" customWidth="1"/>
     <col min="5" max="5" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="99.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="99.44140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6" bestFit="1" customWidth="1"/>
@@ -10958,7 +10958,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A2" s="15">
         <v>1</v>
       </c>
@@ -11168,7 +11168,7 @@
       <c r="K7" s="15"/>
       <c r="L7" s="15"/>
     </row>
-    <row r="8" spans="1:12" ht="99" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A8" s="15">
         <v>7</v>
       </c>

--- a/Business Analysis/checkupp_sprint_plan_2026.xlsx
+++ b/Business Analysis/checkupp_sprint_plan_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Business Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CheckUpp\Business Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CA2C8B7-F614-444B-8762-C8F096F11AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FA343AF-9CCF-419A-9A25-3D66D9729CF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="1224" windowWidth="21600" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint 01" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="130">
   <si>
     <t>Epic</t>
   </si>
@@ -5636,6 +5636,110 @@
 3. Close the camera modal upon successful extraction, populate the respective form fields, and display a Toast/Banner stating: `"Numbers scanned successfully. Please verify against your device."`
 4. Implement a 10-second timeout scanner loop. If no valid match is found within 10 seconds, trigger a prompt: `"Having trouble reading the screen. Ensure there is no glare, or switch to manual entry."` with an easy button to exit.
 * **Acceptance Criteria Covered**: US 19.3 (AC 5, 6, 8)</t>
+  </si>
+  <si>
+    <t>Live-scan digital blood pressure monitor</t>
+  </si>
+  <si>
+    <t>Implement Blood Pressure OCR Extraction and Y-Coordinate Mapping with Jest TDD
+Target Files:
+• checkupp-mobile-main/lib/scanner/bloodPressureScanner.js
+• checkupp-mobile-main/__tests__/cardiovascular/scan-monitor-image.test.js
+Description:
+1. Reuse the existing Google ML Kit Text Recognition integration.
+2. Extract three valid numeric values from the BP monitor OCR response.
+3. Sort OCR candidates using their vertical bounding-box position and map them to Systolic, Diastolic and Heart Rate according to the agreed screen-coordinate convention.
+4. Ignore unrelated values such as date, time, memory number and unit labels.
+5. Ensure shuffled ML Kit OCR results produce the same final BP values.
+6. Return null when one or more required readings cannot be reliably identified.
+7. Add Jest tests for normal, shuffled, incomplete, irrelevant and malformed OCR results.
+Acceptance Criteria Covered: US 19.3 – Extraction Logic (Y-Coordinate Sorting)</t>
+  </si>
+  <si>
+    <t>Live-scan digital glucometer</t>
+  </si>
+  <si>
+    <t>Implement Glucometer Single-Value OCR Extraction and Regex Validation with Jest TDD
+Target Files:
+• checkupp-mobile-main/lib/scanner/glucoseScanner.js
+• checkupp-mobile-main/__tests__/diabetes/scan-glucometer-image.test.js
+Description:
+1. Reuse Google ML Kit Text Recognition to process the glucometer display.
+2. Extract one glucose value using regex validation.
+3. Support values such as 5, 5.6, 12 and 12.1.
+4. Ignore unrelated date, time, memory and unit values.
+5. Select the primary LCD value when multiple numeric OCR results are present.
+6. Reject malformed values, multiple decimal points, negative values, alphabetic text and empty OCR results.
+7. Add Jest tests covering normal, dark, glare, blur, multiple-number and invalid-value scenarios.
+Acceptance Criteria Covered: US 20.3 – Extraction Logic (Regex) and scan accuracy</t>
+  </si>
+  <si>
+    <t>Live-scan digital weighing scale</t>
+  </si>
+  <si>
+    <t>Implement Digital Weighing Scale LCD OCR and Weight Validation with Jest TDD
+Target Files:
+• checkupp-mobile-main/lib/scanner/weightScanner.js
+• checkupp-mobile-main/__tests__/diabetes/scan-digital-scale-image.test.js
+Description:
+1. Implement OCR-based scanning specifically for the supplied digital LCD weighing scale; do not implement analog needle detection.
+2. Extract values such as 68, 68.7, 68.70, 98 and 98.40.
+3. Support OCR values containing the kg suffix, such as 68.70 kg and 68.70kg.
+4. Validate the extracted value before auto-fill using a regex such as ^\\d{2,3}(?:\\.\\d{1,2})?$.
+5. Reject negative, alphabetic, malformed, multiple-decimal, impossible and four-digit values.
+6. Use the supplied digital-scale image displaying 68.70 kg as the reference test scenario.
+7. Add Jest tests for normal, dark, glare, blur, rotation, obstruction and malformed OCR cases.
+Acceptance Criteria Covered: US 20.4 – Extraction Logic and Auto-Fill</t>
+  </si>
+  <si>
+    <t>Shared Scanner</t>
+  </si>
+  <si>
+    <t>19.3 / 20.3 / 20.4</t>
+  </si>
+  <si>
+    <t>Shared camera scanning</t>
+  </si>
+  <si>
+    <t>Implement Shared Camera Performance, Permission and Timeout Handling with Jest TDD
+Target Files:
+• checkupp-mobile-main/lib/scanner/deviceScanner.js
+• Existing camera component under checkupp-mobile-main/components/
+• checkupp-mobile-main/__tests__/scanner/scanner-edge-cases.test.js
+Description:
+1. Reuse the existing native camera permission implementation.
+2. Handle already-granted, requested, denied and revoked camera permissions gracefully.
+3. Limit ML Kit frame processing to 15–30 FPS instead of processing every camera frame.
+4. Start a 10-second timeout whenever a scanner opens.
+5. Cancel the timeout after successful detection, cancellation or scanner closure.
+6. Display the exact timeout message: "Having trouble reading the screen. Ensure there is no glare, or switch to manual entry."
+7. Provide an easy exit/manual-entry action after timeout.
+8. Add Jest fake-timer and mocked-permission tests.
+Acceptance Criteria Covered: US 19.3 – Permissions, Performance, Timeout; US 20.3 – Timeout; US 20.4 – Timeout</t>
+  </si>
+  <si>
+    <t>Implement Image Quality, Bounding-Box Filtering and Multi-Frame Stability with Jest TDD
+Target Files:
+• checkupp-mobile-main/lib/scanner/bloodPressureScanner.js
+• checkupp-mobile-main/lib/scanner/glucoseScanner.js
+• checkupp-mobile-main/lib/scanner/weightScanner.js
+• checkupp-mobile-main/__tests__/cardiovascular/scan-monitor-image.test.js
+• checkupp-mobile-main/__tests__/diabetes/scan-glucometer-image.test.js
+• checkupp-mobile-main/__tests__/diabetes/scan-digital-scale-image.test.js
+Description:
+1. Filter OCR results so only values inside the appropriate target bounding box are considered.
+2. Ignore numbers outside the target region and unrelated OCR text.
+3. Handle rotated OCR coordinates after normalization.
+4. Reject unreadable values caused by severe glare, blur or obstruction when confidence is insufficient.
+5. Implement multi-frame stability so a measurement must remain consistent before auto-fill.
+6. Treat equivalent weight formats such as 68.7 and 68.70 as the same numeric value.
+7. Reject fluctuating OCR results and insufficient frames.
+8. Ensure failed or uncertain scans never overwrite manually entered values.
+9. Add Jest tests for lighting, glare, blur, rotation, obstruction, target-box failures, unstable readings and false-positive protection.
+Acceptance Criteria Covered: US 19.3 – Extraction Reliability; US 20.3 – Scan Reliability; US 20.4 – Lighting/Contrast and Extraction Reliability</t>
+  </si>
+  <si>
+    <t>Shared measurement reliability</t>
   </si>
 </sst>
 </file>
@@ -8074,10 +8178,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -11514,72 +11614,164 @@
       <c r="K17" s="23"/>
       <c r="L17" s="23"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
+    <row r="18" spans="1:12" ht="244.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="8">
+        <v>17</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="C18" s="8">
+        <v>19.3</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I18" s="8">
+        <f t="array" ref="I18">_xlfn.SWITCH(H18,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>5</v>
+      </c>
       <c r="J18" s="8"/>
       <c r="K18" s="8"/>
       <c r="L18" s="8"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
+    <row r="19" spans="1:12" ht="230.4" x14ac:dyDescent="0.3">
+      <c r="A19" s="8">
+        <v>18</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C19">
+        <v>20.3</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I19" s="8">
+        <f t="array" ref="I19">_xlfn.SWITCH(H19,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>5</v>
+      </c>
       <c r="J19" s="8"/>
       <c r="K19" s="8"/>
       <c r="L19" s="8"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
+    <row r="20" spans="1:12" ht="244.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="8">
+        <v>19</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C20" s="8">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I20" s="8">
+        <v>5</v>
+      </c>
       <c r="J20" s="8"/>
       <c r="K20" s="8"/>
       <c r="L20" s="8"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
+    <row r="21" spans="1:12" ht="273.60000000000002" x14ac:dyDescent="0.3">
+      <c r="A21" s="8">
+        <v>20</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C21" t="s">
+        <v>125</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I21" s="8">
+        <v>5</v>
+      </c>
       <c r="J21" s="8"/>
       <c r="K21" s="8"/>
       <c r="L21" s="8"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
+    <row r="22" spans="1:12" ht="345.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="8">
+        <v>21</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I22" s="8">
+        <v>5</v>
+      </c>
       <c r="J22" s="8"/>
       <c r="K22" s="8"/>
       <c r="L22" s="8"/>

--- a/Business Analysis/checkupp_sprint_plan_2026.xlsx
+++ b/Business Analysis/checkupp_sprint_plan_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CheckUpp\Business Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Business Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FA343AF-9CCF-419A-9A25-3D66D9729CF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80902876-C959-46A9-A58F-7A22EA245052}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1224" windowWidth="21600" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint 01" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="119">
   <si>
     <t>Epic</t>
   </si>
@@ -5352,190 +5352,7 @@
     <t>Document Wallet - Documents</t>
   </si>
   <si>
-    <t>Upload health documents</t>
-  </si>
-  <si>
-    <t>Implement Document Picker &amp; Upload State Management
-* **Target Files**:
-* `checkupp-mobile-main/app/(tabs)/wallet.tsx`
-* `checkupp-mobile-main/components/UploadModal.tsx`
-* **Description**:
-1. Integrate the `expo-document-picker` library into the Wallet screen to allow users to select single or multiple health documents (PDFs, images) from their local device.
-2. Update the existing `UploadModal.tsx` to handle the selected file objects, validating file size and MIME types locally before initiating an upload.
-3. Implement local UI state to show upload progress or a loading spinner (`checkupp-mobile-main/components/LoadingSpinner.tsx`) while files are being processed.
-* **Acceptance Criteria Covered**: US 6.1 (AC 1)</t>
-  </si>
-  <si>
     <t>ToDo</t>
-  </si>
-  <si>
-    <t>Integrate Document Upload API Mutations &amp; Notifications
-* **Target Files**:
-* `checkupp-mobile-main/lib/features/documents/mutations.ts`
-* `checkupp-mobile-main/app/(tabs)/wallet.tsx`
- `checkupp-mobile-main/components/CustomToast.tsx`
-* **Description**:
-1. Review and utilize the existing mutation hooks in `mutations.ts` to handle the 3-step upload process defined by the backend:
-* Call `/me/wallet/uploads/presign` to get an upload intent.
-* Upload the raw file buffer to `/me/wallet/uploads/pending` using the `objectKey`.
-* Call `/me/wallet/documents` to finalize the record in the database.
-2. Wrap the upload logic in a robust `try/catch` block.
-3. On success, trigger a confirmation message using the `CustomToast.tsx` component and invalidate the document list query to refresh the UI.
-4. On failure, trigger an error toast ("Upload failed, please try again") and ensure the UI allows the user to retry the specific failed document without affecting successful ones.
-* **Acceptance Criteria Covered**: US 6.1 (AC 2, 3, 4)</t>
-  </si>
-  <si>
-    <t>Share health documents</t>
-  </si>
-  <si>
-    <t>Implement Native Document Sharing
-* **Target Files**:
-* `checkupp-mobile-main/lib/utils/shareUtils.ts` (Existing or create new)
-* `checkupp-mobile-main/app/(tabs)/wallet.tsx`
-* **Description**:
-1. Implement a reusable function utilizing `expo-file-system` to securely download the document from its URL to a temporary local cache directory (`FileSystem.cacheDirectory`).
-2. Pass the local URI to `expo-sharing` (`Sharing.shareAsync()`) to trigger the device's native sharing drawer (WhatsApp, Email, etc.).
-3. Wrap in a `try/catch` block. On error, display the specific toast: "Something went wrong, please try again."
-* **Acceptance Criteria Covered**: US 6.2 (AC 1, 2, 3, 4)</t>
-  </si>
-  <si>
-    <t>Delete health documents</t>
-  </si>
-  <si>
-    <t>Implement Document Deletion Flow
-* **Target Files**:
-* `checkupp-mobile-main/app/(tabs)/wallet.tsx`
-* `checkupp-mobile-main/lib/features/documents/mutations.ts`
-* **Description**:
-1. Connect the "Delete" option in the list item to a React Native `Alert.alert` to display the confirmation prompt: "Are you sure you want to delete this file?".
-2. On confirmation, trigger the delete mutation (`DELETE /me/wallet/documents/:id`).
-3. On success, invalidate the React Query cache to automatically remove the item from the list.
-4. On failure, show the required error toast: "File could not be deleted, please try again", ensuring the item remains in the UI.
-* **Acceptance Criteria Covered**: US 6.3 (AC 1, 2, 3, 4, 5)</t>
-  </si>
-  <si>
-    <t>Document Wallet - Links</t>
-  </si>
-  <si>
-    <t>Add e-script links</t>
-  </si>
-  <si>
-    <t>Implement E-Script Link Submission Form
-* **Target Files**:
-* `checkupp-mobile-main/app/(tabs)/wallet.tsx`
-* `checkupp-mobile-main/components/FormField.tsx`
-* `checkupp-mobile-main/lib/features/documents/mutations.ts`
-* **Description**:
-1. Create a modal or inline form utilizing `FormField.tsx` to capture a URL and a text description.
-2. Use `Yup` (already in `package.json`) to validate that the input is a properly formatted URL.
-3. Create a React Query mutation invoking `POST /me/wallet/links` with the payload `{ title: description, documentType: "E-SCRIPT", link: url }`.
-4. Handle errors with a toast: "Link could not be saved, Try again." On success, invalidate the links query.
-* **Acceptance Criteria Covered**: US 7.1 (AC 1, 3)</t>
-  </si>
-  <si>
-    <t>View e-script links</t>
-  </si>
-  <si>
-    <t>7.3, 7.4</t>
-  </si>
-  <si>
-    <t>Share and delete e-script links</t>
-  </si>
-  <si>
-    <t>Implement Native Link Sharing &amp; Deletion
-* **Target Files**:
-* `checkupp-mobile-main/app/(tabs)/wallet.tsx`
-* `checkupp-mobile-main/lib/utils/shareUtils.ts`
-* **Description**:
-1. **Sharing**: Implement the share button using React Native's built-in `Share.share({ message: \`${description}: ${url}` })` method to invoke native sharing for text/links. Handle errors with the "Something went wrong..." toast.
-2. **Deletion**: Implement the delete flow using an `Alert.alert` ("Are you sure you want to delete this link?"). Hook it into the exact same delete mutation used for documents (`DELETE /me/wallet/documents/:id`). Handle errors with the "Link could not be deleted..." toast.
-* **Acceptance Criteria Covered**: US 7.3 (AC 1, 2, 3, 4, 5), US 7.4 (AC 1, 2, 3, 4, 5)</t>
-  </si>
-  <si>
-    <t>Global Backend Verification</t>
-  </si>
-  <si>
-    <t>Wallet automated testing</t>
-  </si>
-  <si>
-    <t>### Global Backend Verification Task
-*Note: The backend codebase already contains full implementations for the Wallet logic in `wallet.controller.ts`, `wallet.service.ts`, and `wallet.validation.ts`. This task ensures complete alignment with the new ACs and prevents regressions.*
-E2E Test Coverage for Wallet &amp; Link Actions
-* **Target Files**:
-* `checkupp-api-main/tests/modules/wallet/` (Directory to be created/populated)
-* `checkupp-api-main/src/modules/wallet/wallet.validation.ts`
-* **Description**:
-1. Write Supertest/Jest integration tests for `POST /me/wallet/documents`, `POST /me/wallet/links`, and `DELETE /me/wallet/documents/:id`.
-2. Verify that deletion securely handles `userId` scoping to prevent unauthorized deletion (tenant isolation).
-3. Verify that `createLinkSchema` strictly requires a valid URI pattern and returns a 400 Bad Request if the format is invalid.
-4. Verify that the `deleteDocument` service correctly unlinks the file from cloud storage using `cleanupUploadedFile` when a document is deleted.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Direct Document Download</t>
-  </si>
-  <si>
-    <t>6.1, 6.6</t>
-  </si>
-  <si>
-    <t>Document List View</t>
-  </si>
-  <si>
-    <t>Implement Document List View
-* **Target Files**:
-* `checkupp-mobile-main/lib/features/documents/queries.ts`
-* `checkupp-mobile-main/app/(tabs)/wallet.tsx`
-* **Description**:
-1. Ensure `queries.ts` correctly fetches from `GET /me/wallet/documents`.
-2. Design and implement a modular `DocumentListItem` component within `wallet.tsx` to map over the fetched data, displaying the document name and upload date.
-3. **Implement responsive card layout:**
-* **Large Screens:** Display standalone icons for "Share" and "Download", plus a vertical three-dot (kebab) menu. Expanding the kebab menu reveals "View" and "Delete".
-* **Small Screens (Edge Case):** Default to showing only the "Share" icon and the kebab menu. Expanding the menu reveals "View", "Download", and "Delete".
-4. Implement `checkupp-mobile-main/components/EmptyState.tsx` if the query returns an empty array.
-* **Acceptance Criteria Covered**: US 6.1 (AC 5, 6), US 6.6 (AC 1, 2, 3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Document Viewer Integration</t>
-  </si>
-  <si>
-    <t>Implement Document Viewer Integration
-* **Target Files**:
-* `checkupp-mobile-main/app/(tabs)/wallet.tsx`
-* `checkupp-mobile-main/components/DocumentViewer.tsx`
-* **Description**:
-1. Wire up the "View" action from the document list to trigger the existing `DocumentViewer.tsx` component.
-2. Pass the `externalUrl` or `publicUrl` of the document to the viewer.
-3. Implement a fallback error boundary and toast notification ("Could not open file") if the URL is invalid or the device cannot render the file type.
-4. **Enforce explicit removal:** Ensure the "Download" button is strictly removed or disabled within this view screen, as downloading is now an independent card action.
-* **Acceptance Criteria Covered**: US 6.4 (AC 1, 2, 3)</t>
-  </si>
-  <si>
-    <t>Implement Direct Document Download
-* **Target Files**:
-* `checkupp-mobile-main/app/(tabs)/wallet.tsx`
-* `checkupp-mobile-main/lib/utils/fileUtils.ts` (Existing or create new)
-* **Description**:
-1. Implement a download handler triggered directly from the "Download" option on the document card (or within its expanded menu).
-2. Utilize `expo-file-system` to securely fetch and save the document to the user's local device storage without requiring them to open it first.
-3. On success, trigger a `CustomToast.tsx` message displaying: "Download complete".
-4. On failure, trigger an error message prompting the user to try again.
-* **Acceptance Criteria Covered**: US 6.5 (AC 1, 2, 3, 4)</t>
-  </si>
-  <si>
-    <t>7.1, 7.2, 7.5</t>
-  </si>
-  <si>
-    <t>* **Target Files**:
-* `checkupp-mobile-main/app/(tabs)/wallet.tsx`
-* `checkupp-mobile-main/lib/features/documents/queries.ts`
-* **Description**:
-1. Fetch the links using `GET /me/wallet/documents` filtered by `fileType=LINK` or `documentType=E-SCRIPT`.
-2. Render the links with their title/description and creation date.
-3. **Implement responsive card layout:**
-* **Large Screens:** Display standalone buttons for "Share", "Open", and "Delete".
-* **Small Screens (Edge Case):** Display only the "Share" icon alongside a Hamburger Menu (three vertically stacked dots). Expanding the menu reveals "Open" and "Delete".
-4. Wire the "Open" action to open the link using `expo-web-browser` (`WebBrowser.openBrowserAsync`).
-5. Wrap the view action in a `try/catch` returning the error toast: "Could not open Expanded View, try again".
-* **Acceptance Criteria Covered**: US 7.1 (AC 2, 4, 5), US 7.2 (AC 1), US 7.5 (AC 1, 2, 3)</t>
   </si>
   <si>
     <t>Cardiovascular Reading</t>
@@ -5695,9 +5512,6 @@
     <t>Shared Scanner</t>
   </si>
   <si>
-    <t>19.3 / 20.3 / 20.4</t>
-  </si>
-  <si>
     <t>Shared camera scanning</t>
   </si>
   <si>
@@ -5740,6 +5554,216 @@
   </si>
   <si>
     <t>Shared measurement reliability</t>
+  </si>
+  <si>
+    <t>6.1, 6.3, 7.1, 7.4</t>
+  </si>
+  <si>
+    <t>6.1, 6.3, 7.4</t>
+  </si>
+  <si>
+    <t>6.2, 6.3, 6.4, 6.5, 6.6, 7.2, 7.3, 7.4, 7.5</t>
+  </si>
+  <si>
+    <t>6.3, 6.6, 7.5</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Refactor FileCard component to implement 3-Dot (Kebab) Action Menu &amp; Share Button
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Target Files:Modify: checkupp-mobile/app/(tabs)/wallet.tsx (Inside the FileCard declaration)  
+Ambiguity-Free Technical Specification:
+Refactor the FileCard component. The outermost wrapper must be a View (not TouchableOpacity) to prevent touch-target conflicts.
+In the "Actions" flex row, render a prominent primary TouchableOpacity for "Share" (e.g., green styling).Render a secondary TouchableOpacity for the kebab menu (MaterialCommunityIcons name="dots-vertical").
+Implement handleMoreOptions using React Native's Alert.alert. If item.fileType === 'link', show options: [Open, Delete, Cancel]. If it is a document/image, show: [View, Download, Delete, Cancel]. Wire these to the respective prop callbacks (onView, onDelete, onDownload).</t>
+    </r>
+  </si>
+  <si>
+    <t>Document Wallet</t>
+  </si>
+  <si>
+    <t>6.2, 7.3</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Implement secure local download &amp; save to device logic
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Target Files:Create: checkupp-mobile/hooks/useDocumentDownload.ts
+Ambiguity-Free Technical Specification:
+Create a hook returning { downloadItem, isDownloading }.
+Utilize FileSystem.downloadAsync to pull the file to FileSystem.documentDirectory (iOS) or a public folder via Android intents.For images, leverage expo-media-library to save directly to the camera roll (MediaLibrary.saveToLibraryAsync).  Fire success toasts ("Download complete") or error toasts ("Download failed, please try again").</t>
+    </r>
+  </si>
+  <si>
+    <t>6.4, 7.2, 7.4</t>
+  </si>
+  <si>
+    <t>19.3,  20.3,  20.4</t>
+  </si>
+  <si>
+    <t>19.3, 20.3, 20.4</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">TDD - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Automated Jest test suite for Firebase Storage upload/delete &amp; Link creation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Target Files:Create: checkupp-api/tests/modules/wallet/wallet.test.ts
+Ambiguity-Free Technical Specification:
+Initialize a Jest test suite using supertest against the Express app. Mock the Firebase Admin Storage bucket module and ensure the mocked bucket targets an Australian region configuration (australia-southeast1).
+Test Case 1 (US 6.1): Mock a file buffer upload to PUT /me/wallet/uploads/pending. Assert that the mocked Firebase bucket upload function is called and a 201 response is returned with the cloud URL.
+Test Case 2 (US 7.1): POST to /me/wallet/links with a valid e-script URL. Assert a 201 response and verify the database record contains fileType: LINK and the proper external URL 
+Test Case 3 (US 6.3, 7.4): DELETE /me/wallet/documents/:id. Assert that the database record is removed and an immutable AuditLog entry is written. For physical documents, assert that the mocked Firebase bucket delete method is invoked.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">TDD - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Automated Jest test suite for 3-Dot Menu, Native Sharing &amp; Local Downloads</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Target Files:Create: checkupp-mobile/tests/wallet/walletCardInteractions.test.js
+Ambiguity-Free Technical Specification:
+Setup tests using @testing-library/react-native. Mock expo-file-system, expo-sharing, and React Native's Share and Alert modules.  
+Test Case 1 (US 6.6, 7.5): Render the FileCard component. Assert the explicit "View" and "Delete" buttons are absent, and the "Share" icon + "3-dot" icon are present.
+Test Case 2 (US 6.3, 7.4): Simulate press on the 3-dot menu. Assert Alert.alert (or ActionSheet) is called with "View/Open", "Download" (only for documents, not links/e-scipts), "Delete", and "Cancel".
+Test Case 3 (US 6.2, 7.3): Simulate press on the "Share" button for a document. Assert FileSystem.downloadAsync is called, followed by Sharing.shareAsync. For an e-script, assert Share.share is called with the URL.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Refactor wallet.service.ts to stream uploads to Australian Firebase Storage bucket with Audit Logging
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Target Files:Modify: checkupp-api/src/modules/wallet/wallet.service.ts
+Ambiguity-Free Technical Specification:
+Remove Local Disk Storage: Remove the local fs.writeFile and fs.unlink implementation inside uploadPendingFile and cleanupUploadedFile.
+ Firebase Storage Initialization: Initialize firebase-admin/storage pointing explicitly to the Australian storage bucket region (e.g., process.env.FIREBASE_STORAGE_BUCKET initialized in australia-southeast1).
+Upload Logic (US 6.1): In uploadPendingFile, stream the incoming fileBuffer directly into the Firebase Storage bucket with the correct mimeType and AES-256 encryption at rest. Return the secure public cloud URL.
+Delete Logic (US 6.3, 7.4): In cleanupUploadedFile, call bucket.file(objectKey).delete() to physically wipe the file from the cloud bucket when the database record is deleted. Catch and suppress 404 errors if the file is already missing.
+Audit Middleware Compliance: Ensure all uploads and deletions continue to pass through the controller-level tryCreateAuditLog wrapper to maintain immutable tracking.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Implement useDocumentShare Hook for cross-platform native app sharing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Target Files:
+Create: checkupp-mobile/hooks/useDocumentShare.ts
+Ambiguity-Free Technical Specification:
+Create a custom React hook returning { shareItem, isSharing }.
+e-Script/Link Logic (US 7.3): If item.fileType === "link", immediately invoke React Native's Share.share({ message: ... ${item.file}, url: item.file }).
+Document Logic (US 6.2): If item.fileType is image/file, invoke expo-file-system downloadAsync to temporarily cache the remote cloud URL locally to FileSystem.cacheDirectory. Pass the local URI to Sharing.shareAsync().
+Implement error handling with a toast notification: showToast("Something went wrong, please try again", "error").</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Integrate Viewer Modals, Browser linking, and Delete Confirmation flows</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Target Files: Modify: checkupp-mobile/app/(tabs)/wallet.tsx
+Ambiguity-Free Technical Specification:
+Wire the onView callback from the 3-dot menu. If the item is an image, set state to open the existing ImageViewer. If it is a PDF/Document, open the DocumentViewer. If it is an e-script link, invoke WebBrowser.openBrowserAsync().
+Wire the onDelete callback. It must trigger Alert.alert("Are you sure you want to delete this file?") before calling deleteDocument.mutateAsync(id).
+Ensure the UI updates to deleted card or triggers a refetch upon successful deletion.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -5806,7 +5830,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5834,18 +5858,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5889,7 +5901,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5951,16 +5963,7 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6621,31 +6624,31 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>54</c:v>
+                  <c:v>65</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>54</c:v>
+                  <c:v>65</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>54</c:v>
+                  <c:v>65</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>54</c:v>
+                  <c:v>65</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>54</c:v>
+                  <c:v>65</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>54</c:v>
+                  <c:v>65</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>54</c:v>
+                  <c:v>65</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>54</c:v>
+                  <c:v>65</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>54</c:v>
+                  <c:v>65</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6726,28 +6729,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>54</c:v>
+                  <c:v>65</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>47.25</c:v>
+                  <c:v>56.875</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>40.5</c:v>
+                  <c:v>48.75</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>33.75</c:v>
+                  <c:v>40.625</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>27</c:v>
+                  <c:v>32.5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>20.25</c:v>
+                  <c:v>24.375</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>13.5</c:v>
+                  <c:v>16.25</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>6.75</c:v>
+                  <c:v>8.125</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -11003,7 +11006,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA30D3B6-4BBC-427B-918A-C301767B692F}">
-  <dimension ref="A1:L113"/>
+  <dimension ref="A1:L109"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
@@ -11063,22 +11066,20 @@
         <v>1</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="C2" s="15">
-        <v>6.1</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>77</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2" s="15"/>
       <c r="E2" s="15" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>116</v>
+        <v>29</v>
       </c>
       <c r="H2" s="15" t="s">
         <v>27</v>
@@ -11088,137 +11089,129 @@
         <v>3</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K2" s="15"/>
       <c r="L2" s="15"/>
     </row>
-    <row r="3" spans="1:12" ht="244.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A3" s="15">
         <v>2</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="C3" s="15">
-        <v>6.1</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>77</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="D3" s="15"/>
       <c r="E3" s="15" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>116</v>
+        <v>29</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I3" s="15">
         <f t="array" ref="I3">_xlfn.SWITCH(H3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K3" s="15"/>
       <c r="L3" s="15"/>
     </row>
-    <row r="4" spans="1:12" ht="216" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A4" s="15">
         <v>3</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>97</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="D4" s="15"/>
       <c r="E4" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="16" t="s">
-        <v>98</v>
+        <v>22</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>116</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>116</v>
+        <v>29</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I4" s="15">
         <f t="array" ref="I4">_xlfn.SWITCH(H4,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K4" s="15"/>
       <c r="L4" s="15"/>
     </row>
-    <row r="5" spans="1:12" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="144" x14ac:dyDescent="0.3">
       <c r="A5" s="15">
         <v>4</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" s="15">
-        <v>6.4</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>99</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="D5" s="15"/>
       <c r="E5" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="16" t="s">
-        <v>100</v>
+      <c r="F5" s="21" t="s">
+        <v>107</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>116</v>
+        <v>29</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="I5" s="15">
         <f t="array" ref="I5">_xlfn.SWITCH(H5,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J5" s="15" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K5" s="15"/>
       <c r="L5" s="15"/>
     </row>
-    <row r="6" spans="1:12" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="144" x14ac:dyDescent="0.3">
       <c r="A6" s="15">
         <v>5</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="C6" s="15">
-        <v>6.2</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>81</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="D6" s="15"/>
       <c r="E6" s="15" t="s">
         <v>20</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>116</v>
+        <v>29</v>
       </c>
       <c r="H6" s="15" t="s">
         <v>27</v>
@@ -11228,32 +11221,30 @@
         <v>3</v>
       </c>
       <c r="J6" s="15" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K6" s="15"/>
       <c r="L6" s="15"/>
     </row>
-    <row r="7" spans="1:12" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A7" s="15">
         <v>6</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="C7" s="15">
-        <v>6.3</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>83</v>
-      </c>
+        <v>6.5</v>
+      </c>
+      <c r="D7" s="15"/>
       <c r="E7" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="16" t="s">
-        <v>84</v>
+      <c r="F7" s="21" t="s">
+        <v>110</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>116</v>
+        <v>29</v>
       </c>
       <c r="H7" s="15" t="s">
         <v>23</v>
@@ -11263,32 +11254,30 @@
         <v>2</v>
       </c>
       <c r="J7" s="15" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K7" s="15"/>
       <c r="L7" s="15"/>
     </row>
-    <row r="8" spans="1:12" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A8" s="15">
         <v>7</v>
       </c>
       <c r="B8" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="C8" s="15">
-        <v>6.5</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>95</v>
-      </c>
+      <c r="C8" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="D8" s="15"/>
       <c r="E8" s="15" t="s">
         <v>20</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>116</v>
+        <v>90</v>
       </c>
       <c r="H8" s="15" t="s">
         <v>27</v>
@@ -11298,32 +11287,32 @@
         <v>3</v>
       </c>
       <c r="J8" s="15" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K8" s="15"/>
       <c r="L8" s="15"/>
     </row>
-    <row r="9" spans="1:12" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A9" s="17">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C9" s="17">
-        <v>7.1</v>
+        <v>19.3</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="E9" s="17" t="s">
         <v>20</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>116</v>
+        <v>24</v>
       </c>
       <c r="H9" s="17" t="s">
         <v>27</v>
@@ -11333,305 +11322,297 @@
         <v>3</v>
       </c>
       <c r="J9" s="17" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K9" s="17"/>
       <c r="L9" s="17"/>
     </row>
-    <row r="10" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A10" s="17">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>102</v>
+        <v>78</v>
+      </c>
+      <c r="C10" s="17">
+        <v>19.3</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="E10" s="17" t="s">
         <v>20</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>116</v>
+        <v>24</v>
       </c>
       <c r="H10" s="17" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I10" s="17">
         <f t="array" ref="I10">_xlfn.SWITCH(H10,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J10" s="17" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K10" s="17"/>
       <c r="L10" s="17"/>
     </row>
-    <row r="11" spans="1:12" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A11" s="17">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>89</v>
+        <v>82</v>
+      </c>
+      <c r="C11" s="17">
+        <v>20.3</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="E11" s="17" t="s">
         <v>20</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>116</v>
+        <v>24</v>
       </c>
       <c r="H11" s="17" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I11" s="17">
         <f t="array" ref="I11">_xlfn.SWITCH(H11,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J11" s="17" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K11" s="17"/>
       <c r="L11" s="17"/>
     </row>
-    <row r="12" spans="1:12" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="19">
-        <v>11</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19" t="s">
-        <v>93</v>
-      </c>
-      <c r="E12" s="19" t="s">
+    <row r="12" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="17">
+        <v>15</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12" s="17">
+        <v>20.3</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="H12" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="I12" s="17">
+        <f t="array" ref="I12">_xlfn.SWITCH(H12,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="J12" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="K12" s="17"/>
+      <c r="L12" s="17"/>
+    </row>
+    <row r="13" spans="1:12" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A13" s="19">
+        <v>16</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="E13" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="G12" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="H12" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="I12" s="19">
-        <f t="array" ref="I12">_xlfn.SWITCH(H12,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>5</v>
-      </c>
-      <c r="J12" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="K12" s="19"/>
-      <c r="L12" s="19"/>
-    </row>
-    <row r="13" spans="1:12" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="21">
-        <v>12</v>
-      </c>
-      <c r="B13" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="C13" s="21">
-        <v>19.3</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="E13" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="F13" s="22" t="s">
-        <v>106</v>
-      </c>
-      <c r="G13" s="21" t="s">
+      <c r="F13" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="G13" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="H13" s="21" t="s">
+      <c r="H13" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="I13" s="21">
+      <c r="I13" s="19">
         <f t="array" ref="I13">_xlfn.SWITCH(H13,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J13" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="K13" s="21"/>
-      <c r="L13" s="21"/>
+      <c r="J13" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
     </row>
     <row r="14" spans="1:12" ht="244.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="21">
-        <v>13</v>
-      </c>
-      <c r="B14" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="C14" s="21">
+      <c r="A14" s="8">
+        <v>17</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" s="8">
         <v>19.3</v>
       </c>
-      <c r="D14" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="E14" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="F14" s="22" t="s">
-        <v>117</v>
-      </c>
-      <c r="G14" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="H14" s="21" t="s">
+      <c r="D14" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H14" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="I14" s="21">
+      <c r="I14" s="8">
         <f t="array" ref="I14">_xlfn.SWITCH(H14,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J14" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="K14" s="21"/>
-      <c r="L14" s="21"/>
-    </row>
-    <row r="15" spans="1:12" ht="273.60000000000002" x14ac:dyDescent="0.3">
-      <c r="A15" s="21">
-        <v>14</v>
-      </c>
-      <c r="B15" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="C15" s="21">
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+    </row>
+    <row r="15" spans="1:12" ht="230.4" x14ac:dyDescent="0.3">
+      <c r="A15" s="8">
+        <v>18</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C15" s="8">
         <v>20.3</v>
       </c>
-      <c r="D15" s="21" t="s">
-        <v>109</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="F15" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="G15" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="H15" s="21" t="s">
+      <c r="D15" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H15" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="I15" s="21">
+      <c r="I15" s="8">
         <f t="array" ref="I15">_xlfn.SWITCH(H15,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J15" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="K15" s="21"/>
-      <c r="L15" s="21"/>
-    </row>
-    <row r="16" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="21">
-        <v>15</v>
-      </c>
-      <c r="B16" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="C16" s="21">
-        <v>20.3</v>
-      </c>
-      <c r="D16" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="E16" s="21" t="s">
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+    </row>
+    <row r="16" spans="1:12" ht="244.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="8">
+        <v>19</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C16" s="8">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I16" s="8">
+        <v>5</v>
+      </c>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+    </row>
+    <row r="17" spans="1:12" ht="273.60000000000002" x14ac:dyDescent="0.3">
+      <c r="A17" s="8">
         <v>20</v>
       </c>
-      <c r="F16" s="22" t="s">
+      <c r="B17" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="G16" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="H16" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="I16" s="21">
-        <f t="array" ref="I16">_xlfn.SWITCH(H16,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J16" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="K16" s="21"/>
-      <c r="L16" s="21"/>
-    </row>
-    <row r="17" spans="1:12" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="23">
-        <v>16</v>
-      </c>
-      <c r="B17" s="23" t="s">
+      <c r="D17" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I17" s="8">
+        <v>5</v>
+      </c>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+    </row>
+    <row r="18" spans="1:12" ht="345.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="8">
+        <v>21</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="C17" s="23"/>
-      <c r="D17" s="23" t="s">
-        <v>114</v>
-      </c>
-      <c r="E17" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="F17" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="G17" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="H17" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="I17" s="23">
-        <f t="array" ref="I17">_xlfn.SWITCH(H17,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J17" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="K17" s="23"/>
-      <c r="L17" s="23"/>
-    </row>
-    <row r="18" spans="1:12" ht="244.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="8">
-        <v>17</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="C18" s="8">
-        <v>19.3</v>
-      </c>
       <c r="D18" s="8" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>31</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="G18" s="8" t="s">
         <v>29</v>
@@ -11640,138 +11621,64 @@
         <v>30</v>
       </c>
       <c r="I18" s="8">
-        <f t="array" ref="I18">_xlfn.SWITCH(H18,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
       <c r="J18" s="8"/>
       <c r="K18" s="8"/>
       <c r="L18" s="8"/>
     </row>
-    <row r="19" spans="1:12" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="8">
-        <v>18</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="C19">
-        <v>20.3</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="I19" s="8">
-        <f t="array" ref="I19">_xlfn.SWITCH(H19,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>5</v>
-      </c>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
       <c r="J19" s="8"/>
       <c r="K19" s="8"/>
       <c r="L19" s="8"/>
     </row>
-    <row r="20" spans="1:12" ht="244.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="8">
-        <v>19</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="C20" s="8">
-        <v>20.399999999999999</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="I20" s="8">
-        <v>5</v>
-      </c>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
       <c r="J20" s="8"/>
       <c r="K20" s="8"/>
       <c r="L20" s="8"/>
     </row>
-    <row r="21" spans="1:12" ht="273.60000000000002" x14ac:dyDescent="0.3">
-      <c r="A21" s="8">
-        <v>20</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="C21" t="s">
-        <v>125</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="I21" s="8">
-        <v>5</v>
-      </c>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
       <c r="J21" s="8"/>
       <c r="K21" s="8"/>
       <c r="L21" s="8"/>
     </row>
-    <row r="22" spans="1:12" ht="345.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="8">
-        <v>21</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="F22" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="I22" s="8">
-        <v>5</v>
-      </c>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
       <c r="J22" s="8"/>
       <c r="K22" s="8"/>
       <c r="L22" s="8"/>
@@ -11785,7 +11692,10 @@
       <c r="F23" s="10"/>
       <c r="G23" s="8"/>
       <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
+      <c r="I23" s="8" t="str">
+        <f t="array" ref="I23">_xlfn.SWITCH(H23,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
       <c r="J23" s="8"/>
       <c r="K23" s="8"/>
       <c r="L23" s="8"/>
@@ -11799,7 +11709,10 @@
       <c r="F24" s="10"/>
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
+      <c r="I24" s="8" t="str">
+        <f t="array" ref="I24">_xlfn.SWITCH(H24,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
       <c r="J24" s="8"/>
       <c r="K24" s="8"/>
       <c r="L24" s="8"/>
@@ -11813,7 +11726,10 @@
       <c r="F25" s="10"/>
       <c r="G25" s="8"/>
       <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
+      <c r="I25" s="8" t="str">
+        <f t="array" ref="I25">_xlfn.SWITCH(H25,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
       <c r="J25" s="8"/>
       <c r="K25" s="8"/>
       <c r="L25" s="8"/>
@@ -11827,7 +11743,10 @@
       <c r="F26" s="10"/>
       <c r="G26" s="8"/>
       <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
+      <c r="I26" s="8" t="str">
+        <f t="array" ref="I26">_xlfn.SWITCH(H26,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
       <c r="J26" s="8"/>
       <c r="K26" s="8"/>
       <c r="L26" s="8"/>
@@ -11889,7 +11808,7 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="10"/>
+      <c r="F30" s="7"/>
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
       <c r="I30" s="8" t="str">
@@ -11906,7 +11825,7 @@
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
       <c r="E31" s="8"/>
-      <c r="F31" s="10"/>
+      <c r="F31" s="9"/>
       <c r="G31" s="8"/>
       <c r="H31" s="8"/>
       <c r="I31" s="8" t="str">
@@ -11923,7 +11842,7 @@
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
       <c r="E32" s="8"/>
-      <c r="F32" s="10"/>
+      <c r="F32" s="9"/>
       <c r="G32" s="8"/>
       <c r="H32" s="8"/>
       <c r="I32" s="8" t="str">
@@ -11940,7 +11859,7 @@
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
       <c r="E33" s="8"/>
-      <c r="F33" s="10"/>
+      <c r="F33" s="9"/>
       <c r="G33" s="8"/>
       <c r="H33" s="8"/>
       <c r="I33" s="8" t="str">
@@ -11957,7 +11876,7 @@
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
       <c r="E34" s="8"/>
-      <c r="F34" s="7"/>
+      <c r="F34" s="9"/>
       <c r="G34" s="8"/>
       <c r="H34" s="8"/>
       <c r="I34" s="8" t="str">
@@ -12195,7 +12114,7 @@
       <c r="C48" s="8"/>
       <c r="D48" s="8"/>
       <c r="E48" s="8"/>
-      <c r="F48" s="9"/>
+      <c r="F48" s="10"/>
       <c r="G48" s="8"/>
       <c r="H48" s="8"/>
       <c r="I48" s="8" t="str">
@@ -12212,7 +12131,7 @@
       <c r="C49" s="8"/>
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
-      <c r="F49" s="9"/>
+      <c r="F49" s="10"/>
       <c r="G49" s="8"/>
       <c r="H49" s="8"/>
       <c r="I49" s="8" t="str">
@@ -12229,7 +12148,7 @@
       <c r="C50" s="8"/>
       <c r="D50" s="8"/>
       <c r="E50" s="8"/>
-      <c r="F50" s="9"/>
+      <c r="F50" s="10"/>
       <c r="G50" s="8"/>
       <c r="H50" s="8"/>
       <c r="I50" s="8" t="str">
@@ -12246,7 +12165,7 @@
       <c r="C51" s="8"/>
       <c r="D51" s="8"/>
       <c r="E51" s="8"/>
-      <c r="F51" s="9"/>
+      <c r="F51" s="10"/>
       <c r="G51" s="8"/>
       <c r="H51" s="8"/>
       <c r="I51" s="8" t="str">
@@ -12297,7 +12216,7 @@
       <c r="C54" s="8"/>
       <c r="D54" s="8"/>
       <c r="E54" s="8"/>
-      <c r="F54" s="10"/>
+      <c r="F54" s="9"/>
       <c r="G54" s="8"/>
       <c r="H54" s="8"/>
       <c r="I54" s="8" t="str">
@@ -12314,7 +12233,7 @@
       <c r="C55" s="8"/>
       <c r="D55" s="8"/>
       <c r="E55" s="8"/>
-      <c r="F55" s="10"/>
+      <c r="F55" s="9"/>
       <c r="G55" s="8"/>
       <c r="H55" s="8"/>
       <c r="I55" s="8" t="str">
@@ -12331,7 +12250,7 @@
       <c r="C56" s="8"/>
       <c r="D56" s="8"/>
       <c r="E56" s="8"/>
-      <c r="F56" s="10"/>
+      <c r="F56" s="9"/>
       <c r="G56" s="8"/>
       <c r="H56" s="8"/>
       <c r="I56" s="8" t="str">
@@ -12348,7 +12267,7 @@
       <c r="C57" s="8"/>
       <c r="D57" s="8"/>
       <c r="E57" s="8"/>
-      <c r="F57" s="10"/>
+      <c r="F57" s="9"/>
       <c r="G57" s="8"/>
       <c r="H57" s="8"/>
       <c r="I57" s="8" t="str">
@@ -12484,7 +12403,7 @@
       <c r="C65" s="8"/>
       <c r="D65" s="8"/>
       <c r="E65" s="8"/>
-      <c r="F65" s="9"/>
+      <c r="F65" s="7"/>
       <c r="G65" s="8"/>
       <c r="H65" s="8"/>
       <c r="I65" s="8" t="str">
@@ -12518,7 +12437,7 @@
       <c r="C67" s="8"/>
       <c r="D67" s="8"/>
       <c r="E67" s="8"/>
-      <c r="F67" s="9"/>
+      <c r="F67" s="7"/>
       <c r="G67" s="8"/>
       <c r="H67" s="8"/>
       <c r="I67" s="8" t="str">
@@ -12535,7 +12454,7 @@
       <c r="C68" s="8"/>
       <c r="D68" s="8"/>
       <c r="E68" s="8"/>
-      <c r="F68" s="9"/>
+      <c r="F68" s="7"/>
       <c r="G68" s="8"/>
       <c r="H68" s="8"/>
       <c r="I68" s="8" t="str">
@@ -12552,7 +12471,7 @@
       <c r="C69" s="8"/>
       <c r="D69" s="8"/>
       <c r="E69" s="8"/>
-      <c r="F69" s="7"/>
+      <c r="F69" s="9"/>
       <c r="G69" s="8"/>
       <c r="H69" s="8"/>
       <c r="I69" s="8" t="str">
@@ -12586,7 +12505,7 @@
       <c r="C71" s="8"/>
       <c r="D71" s="8"/>
       <c r="E71" s="8"/>
-      <c r="F71" s="7"/>
+      <c r="F71" s="9"/>
       <c r="G71" s="8"/>
       <c r="H71" s="8"/>
       <c r="I71" s="8" t="str">
@@ -12603,7 +12522,7 @@
       <c r="C72" s="8"/>
       <c r="D72" s="8"/>
       <c r="E72" s="8"/>
-      <c r="F72" s="7"/>
+      <c r="F72" s="9"/>
       <c r="G72" s="8"/>
       <c r="H72" s="8"/>
       <c r="I72" s="8" t="str">
@@ -12637,7 +12556,7 @@
       <c r="C74" s="8"/>
       <c r="D74" s="8"/>
       <c r="E74" s="8"/>
-      <c r="F74" s="9"/>
+      <c r="F74" s="10"/>
       <c r="G74" s="8"/>
       <c r="H74" s="8"/>
       <c r="I74" s="8" t="str">
@@ -12654,7 +12573,7 @@
       <c r="C75" s="8"/>
       <c r="D75" s="8"/>
       <c r="E75" s="8"/>
-      <c r="F75" s="9"/>
+      <c r="F75" s="10"/>
       <c r="G75" s="8"/>
       <c r="H75" s="8"/>
       <c r="I75" s="8" t="str">
@@ -12671,7 +12590,7 @@
       <c r="C76" s="8"/>
       <c r="D76" s="8"/>
       <c r="E76" s="8"/>
-      <c r="F76" s="9"/>
+      <c r="F76" s="10"/>
       <c r="G76" s="8"/>
       <c r="H76" s="8"/>
       <c r="I76" s="8" t="str">
@@ -12688,7 +12607,7 @@
       <c r="C77" s="8"/>
       <c r="D77" s="8"/>
       <c r="E77" s="8"/>
-      <c r="F77" s="9"/>
+      <c r="F77" s="10"/>
       <c r="G77" s="8"/>
       <c r="H77" s="8"/>
       <c r="I77" s="8" t="str">
@@ -13242,74 +13161,6 @@
       <c r="J109" s="8"/>
       <c r="K109" s="8"/>
       <c r="L109" s="8"/>
-    </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A110" s="8"/>
-      <c r="B110" s="8"/>
-      <c r="C110" s="8"/>
-      <c r="D110" s="8"/>
-      <c r="E110" s="8"/>
-      <c r="F110" s="10"/>
-      <c r="G110" s="8"/>
-      <c r="H110" s="8"/>
-      <c r="I110" s="8" t="str">
-        <f t="array" ref="I110">_xlfn.SWITCH(H110,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J110" s="8"/>
-      <c r="K110" s="8"/>
-      <c r="L110" s="8"/>
-    </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A111" s="8"/>
-      <c r="B111" s="8"/>
-      <c r="C111" s="8"/>
-      <c r="D111" s="8"/>
-      <c r="E111" s="8"/>
-      <c r="F111" s="10"/>
-      <c r="G111" s="8"/>
-      <c r="H111" s="8"/>
-      <c r="I111" s="8" t="str">
-        <f t="array" ref="I111">_xlfn.SWITCH(H111,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J111" s="8"/>
-      <c r="K111" s="8"/>
-      <c r="L111" s="8"/>
-    </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A112" s="8"/>
-      <c r="B112" s="8"/>
-      <c r="C112" s="8"/>
-      <c r="D112" s="8"/>
-      <c r="E112" s="8"/>
-      <c r="F112" s="10"/>
-      <c r="G112" s="8"/>
-      <c r="H112" s="8"/>
-      <c r="I112" s="8" t="str">
-        <f t="array" ref="I112">_xlfn.SWITCH(H112,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J112" s="8"/>
-      <c r="K112" s="8"/>
-      <c r="L112" s="8"/>
-    </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A113" s="8"/>
-      <c r="B113" s="8"/>
-      <c r="C113" s="8"/>
-      <c r="D113" s="8"/>
-      <c r="E113" s="8"/>
-      <c r="F113" s="10"/>
-      <c r="G113" s="8"/>
-      <c r="H113" s="8"/>
-      <c r="I113" s="8" t="str">
-        <f t="array" ref="I113">_xlfn.SWITCH(H113,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J113" s="8"/>
-      <c r="K113" s="8"/>
-      <c r="L113" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13353,12 +13204,12 @@
         <v>46251</v>
       </c>
       <c r="C2" s="4">
-        <f>54-SUM(E$2:E2)</f>
-        <v>54</v>
+        <f>65-SUM(E$2:E2)</f>
+        <v>65</v>
       </c>
       <c r="D2" s="1">
-        <f>54*(1-(A2/8))</f>
-        <v>54</v>
+        <f>65*(1-(A2/8))</f>
+        <v>65</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
@@ -13372,12 +13223,12 @@
         <v>46252</v>
       </c>
       <c r="C3" s="4">
-        <f>54-SUM(E$2:E3)</f>
-        <v>54</v>
+        <f>65-SUM(E$2:E3)</f>
+        <v>65</v>
       </c>
       <c r="D3" s="1">
-        <f t="shared" ref="D3:D10" si="0">54*(1-(A3/8))</f>
-        <v>47.25</v>
+        <f t="shared" ref="D3:D10" si="0">65*(1-(A3/8))</f>
+        <v>56.875</v>
       </c>
       <c r="E3" s="1">
         <v>0</v>
@@ -13391,12 +13242,12 @@
         <v>46253</v>
       </c>
       <c r="C4" s="4">
-        <f>54-SUM(E$2:E4)</f>
-        <v>54</v>
+        <f>65-SUM(E$2:E4)</f>
+        <v>65</v>
       </c>
       <c r="D4" s="1">
         <f t="shared" si="0"/>
-        <v>40.5</v>
+        <v>48.75</v>
       </c>
       <c r="E4" s="1">
         <v>0</v>
@@ -13411,12 +13262,12 @@
         <v>46254</v>
       </c>
       <c r="C5" s="4">
-        <f>54-SUM(E$2:E5)</f>
-        <v>54</v>
+        <f>65-SUM(E$2:E5)</f>
+        <v>65</v>
       </c>
       <c r="D5" s="1">
         <f t="shared" si="0"/>
-        <v>33.75</v>
+        <v>40.625</v>
       </c>
       <c r="E5" s="1">
         <v>0</v>
@@ -13430,12 +13281,12 @@
         <v>46255</v>
       </c>
       <c r="C6" s="4">
-        <f>54-SUM(E$2:E6)</f>
-        <v>54</v>
+        <f>65-SUM(E$2:E6)</f>
+        <v>65</v>
       </c>
       <c r="D6" s="1">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>32.5</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
@@ -13449,12 +13300,12 @@
         <v>46258</v>
       </c>
       <c r="C7" s="4">
-        <f>54-SUM(E$2:E7)</f>
-        <v>54</v>
+        <f>65-SUM(E$2:E7)</f>
+        <v>65</v>
       </c>
       <c r="D7" s="1">
         <f t="shared" si="0"/>
-        <v>20.25</v>
+        <v>24.375</v>
       </c>
       <c r="E7" s="1">
         <v>0</v>
@@ -13468,12 +13319,12 @@
         <v>46259</v>
       </c>
       <c r="C8" s="4">
-        <f>54-SUM(E$2:E8)</f>
-        <v>54</v>
+        <f>65-SUM(E$2:E8)</f>
+        <v>65</v>
       </c>
       <c r="D8" s="1">
         <f t="shared" si="0"/>
-        <v>13.5</v>
+        <v>16.25</v>
       </c>
       <c r="E8" s="1">
         <v>0</v>
@@ -13487,12 +13338,12 @@
         <v>46260</v>
       </c>
       <c r="C9" s="4">
-        <f>54-SUM(E$2:E9)</f>
-        <v>54</v>
+        <f>65-SUM(E$2:E9)</f>
+        <v>65</v>
       </c>
       <c r="D9" s="1">
         <f t="shared" si="0"/>
-        <v>6.75</v>
+        <v>8.125</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
@@ -13506,8 +13357,8 @@
         <v>46261</v>
       </c>
       <c r="C10" s="4">
-        <f>54-SUM(E$2:E10)</f>
-        <v>54</v>
+        <f>65-SUM(E$2:E10)</f>
+        <v>65</v>
       </c>
       <c r="D10" s="1">
         <f t="shared" si="0"/>

--- a/Business Analysis/checkupp_sprint_plan_2026.xlsx
+++ b/Business Analysis/checkupp_sprint_plan_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Business Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80902876-C959-46A9-A58F-7A22EA245052}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15694944-5DD9-4300-B3D5-3C1B585492C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint 01" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="121">
   <si>
     <t>Epic</t>
   </si>
@@ -5763,6 +5763,71 @@
 Wire the onView callback from the 3-dot menu. If the item is an image, set state to open the existing ImageViewer. If it is a PDF/Document, open the DocumentViewer. If it is an e-script link, invoke WebBrowser.openBrowserAsync().
 Wire the onDelete callback. It must trigger Alert.alert("Are you sure you want to delete this file?") before calling deleteDocument.mutateAsync(id).
 Ensure the UI updates to deleted card or triggers a refetch upon successful deletion.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Backend TDD Suite: Firebase Storage &amp; Links
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Setup &amp; Teardown:
+Initialize the Jest test suite using supertest against the Express server.
+Mock the firebase-admin/storage module to intercept bucket uploads and deletes.
+Implement ruthless beforeEach and afterAll database purges to guarantee deterministic test runs.
+US 6.1: Document Upload (Firebase Stream)
+Success: Send a valid file buffer payload to POST /me/wallet/documents. Assert a 201 Created response. Assert the mocked Firebase bucket upload function is invoked and the database record correctly saves the fileType: FILE and public cloud URL.  
+Edge Case (Missing Fields): Send a payload missing documentType. Assert the Joi gateway validation blocks it and returns a 400 Bad Request.  
+Edge Case (Cloud Failure): Force the mocked Firebase upload to throw an error. Assert the API returns a graceful 500 without creating an orphaned database record.
+US 7.1: e-Script Link Creation
+Success: POST /me/wallet/links with a valid URL and title. Assert a 201 Created response and verify the database record saves fileType: LINK.  
+Edge Case (Whitespace Validation): Send a URL containing only blank spaces. Assert Joi's .trim().min(1) intercepts the request and throws a 400 Bad Request.  
+US 6.3 &amp; 7.4: Deletion &amp; Tenant Isolation
+Success (Document): DELETE /me/wallet/documents/:id. Assert a 200 OK response. Assert the mocked Firebase bucket delete() method is called and the database record is removed.
+Success (Link): DELETE /me/wallet/documents/:id (targeting a link). Assert the database record is removed but the Firebase bucket delete() method is not called.
+Edge Case (Tenant Isolation): Attempt to delete a document ID using a different user's mocked JWT token. Assert a 404 Not Found to guarantee multi-tenant security scoping.
+Audit Logging (All Modifications)
+Success: Following a successful creation or deletion, query the test database to assert an immutable AuditLog row was created with the correct actorId, action, and timestamp.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Frontend TDD Suite: UI, Sharing &amp; Caching</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+US 6.6 &amp; 7.5: Decluttered Card Layout (checkupp-mobile/tests/DocumentWallet/FileCard.test.tsx)
+Success: Render the FileCard component. Assert that explicit standalone "View", "Download", and "Delete" text/buttons are completely absent from the DOM.
+Success: Assert that the primary "Share" icon and the secondary "3-dot" kebab menu icon are rendered correctly on the card.
+US 6.3, 6.5 &amp; 7.4: 3-Dot Action Menu (Alert/ActionSheet) (checkupp-mobile/tests/DocumentWallet/FileCard.test.tsx)
+Success (Document): Simulate a press on the 3-dot menu for a document payload. Assert Alert.alert triggers with exactly four options: "View", "Download", "Delete", and "Cancel".
+Success (Link): Simulate a press on the 3-dot menu for an e-script payload. Assert Alert.alert triggers with exactly three options: "Open", "Delete", and "Cancel".
+Edge Case (Delete Cancellation): Trigger the "Delete" option, then press "Cancel" on the subsequent confirmation prompt. Assert the deleteDocument mutation is never fired.
+US 6.2 &amp; 7.3: Cross-Platform Native Sharing (checkupp-mobile/tests/hooks/useDocumentShare.test.ts)
+Success (Link): Simulate a press on the "Share" button for an e-script. Assert React Native's Share.share is invoked immediately with the text/URL payload.
+Success (Document): Simulate a press on the "Share" button for a document. Assert a loading spinner renders. Assert FileSystem.downloadAsync is called with the remote Firebase URL. Assert Sharing.shareAsync is subsequently called with the resulting local URI.
+Edge Case (Unsupported Device): Force the mocked Sharing.isAvailableAsync() to return false. Assert a Toast is displayed notifying the user that sharing is unavailable.
+US 6.5: Download Document (checkupp-mobile/tests/hooks/useDocumentDownload.test.ts)
+Success: Verify that pressing the Download button invokes FileSystem.downloadAsync to permanently save the file to local device storage.
+Edge Case (Network Drop): Simulate a failure during FileSystem.downloadAsync. Assert the loading spinner reverts to the share icon and the "Something went wrong, please try again" error toast fires.
+US 6.4 &amp; 7.2: Viewer Integrations (checkupp-mobile/tests/DocumentWallet/FileCard.test.tsx)
+Success (Image): Simulate selecting "View" on an image document. Assert the ImageViewer modal becomes visible.
+Success (PDF): Simulate selecting "View" on a PDF document. Assert the DocumentViewer modal becomes visible.
+Success (Link): Simulate selecting "Open" on an e-script link. Assert WebBrowser.openBrowserAsync is called with the specific URL.</t>
     </r>
   </si>
 </sst>
@@ -6624,31 +6689,31 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>65</c:v>
+                  <c:v>75</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>65</c:v>
+                  <c:v>75</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>65</c:v>
+                  <c:v>75</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>65</c:v>
+                  <c:v>75</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>65</c:v>
+                  <c:v>75</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>65</c:v>
+                  <c:v>75</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>65</c:v>
+                  <c:v>75</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>65</c:v>
+                  <c:v>75</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>65</c:v>
+                  <c:v>75</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6729,28 +6794,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>65</c:v>
+                  <c:v>75</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>56.875</c:v>
+                  <c:v>65.625</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>48.75</c:v>
+                  <c:v>56.25</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>40.625</c:v>
+                  <c:v>46.875</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>32.5</c:v>
+                  <c:v>37.5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>24.375</c:v>
+                  <c:v>28.125</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>16.25</c:v>
+                  <c:v>18.75</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8.125</c:v>
+                  <c:v>9.375</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -11006,7 +11071,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA30D3B6-4BBC-427B-918A-C301767B692F}">
-  <dimension ref="A1:L109"/>
+  <dimension ref="A1:L111"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
@@ -11127,22 +11192,20 @@
       <c r="K3" s="15"/>
       <c r="L3" s="15"/>
     </row>
-    <row r="4" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="15">
-        <v>3</v>
-      </c>
+    <row r="4" spans="1:12" ht="403.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="15"/>
       <c r="B4" s="15" t="s">
         <v>108</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D4" s="15"/>
       <c r="E4" s="15" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F4" s="21" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G4" s="15" t="s">
         <v>29</v>
@@ -11154,71 +11217,65 @@
         <f t="array" ref="I4">_xlfn.SWITCH(H4,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J4" s="15" t="s">
-        <v>77</v>
-      </c>
+      <c r="J4" s="15"/>
       <c r="K4" s="15"/>
       <c r="L4" s="15"/>
     </row>
-    <row r="5" spans="1:12" ht="144" x14ac:dyDescent="0.3">
-      <c r="A5" s="15">
-        <v>4</v>
-      </c>
+    <row r="5" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="15"/>
       <c r="B5" s="15" t="s">
         <v>108</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D5" s="15"/>
       <c r="E5" s="15" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="G5" s="15" t="s">
         <v>29</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="I5" s="15">
         <f t="array" ref="I5">_xlfn.SWITCH(H5,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>2</v>
-      </c>
-      <c r="J5" s="15" t="s">
-        <v>77</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="J5" s="15"/>
       <c r="K5" s="15"/>
       <c r="L5" s="15"/>
     </row>
-    <row r="6" spans="1:12" ht="144" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A6" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B6" s="15" t="s">
         <v>108</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D6" s="15"/>
       <c r="E6" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="16" t="s">
-        <v>117</v>
+        <v>22</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>116</v>
       </c>
       <c r="G6" s="15" t="s">
         <v>29</v>
       </c>
       <c r="H6" s="15" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I6" s="15">
         <f t="array" ref="I6">_xlfn.SWITCH(H6,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J6" s="15" t="s">
         <v>77</v>
@@ -11226,22 +11283,22 @@
       <c r="K6" s="15"/>
       <c r="L6" s="15"/>
     </row>
-    <row r="7" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="144" x14ac:dyDescent="0.3">
       <c r="A7" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B7" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="C7" s="15">
-        <v>6.5</v>
+      <c r="C7" s="15" t="s">
+        <v>106</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="15" t="s">
         <v>20</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="G7" s="15" t="s">
         <v>29</v>
@@ -11259,25 +11316,25 @@
       <c r="K7" s="15"/>
       <c r="L7" s="15"/>
     </row>
-    <row r="8" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="144" x14ac:dyDescent="0.3">
       <c r="A8" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D8" s="15"/>
       <c r="E8" s="15" t="s">
         <v>20</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="H8" s="15" t="s">
         <v>27</v>
@@ -11292,104 +11349,100 @@
       <c r="K8" s="15"/>
       <c r="L8" s="15"/>
     </row>
-    <row r="9" spans="1:12" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="17">
+    <row r="9" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="15">
+        <v>6</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="C9" s="15">
+        <v>6.5</v>
+      </c>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9" s="15">
+        <f t="array" ref="I9">_xlfn.SWITCH(H9,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="K9" s="15"/>
+      <c r="L9" s="15"/>
+    </row>
+    <row r="10" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="15">
+        <v>7</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="H10" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="I10" s="15">
+        <f t="array" ref="I10">_xlfn.SWITCH(H10,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="J10" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
+    </row>
+    <row r="11" spans="1:12" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="17">
         <v>12</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B11" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C11" s="17">
         <v>19.3</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D11" s="17" t="s">
         <v>79</v>
-      </c>
-      <c r="E9" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="G9" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="H9" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="I9" s="17">
-        <f t="array" ref="I9">_xlfn.SWITCH(H9,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J9" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="K9" s="17"/>
-      <c r="L9" s="17"/>
-    </row>
-    <row r="10" spans="1:12" ht="244.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="17">
-        <v>13</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="C10" s="17">
-        <v>19.3</v>
-      </c>
-      <c r="D10" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="E10" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="G10" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="H10" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="I10" s="17">
-        <f t="array" ref="I10">_xlfn.SWITCH(H10,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>5</v>
-      </c>
-      <c r="J10" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
-    </row>
-    <row r="11" spans="1:12" ht="273.60000000000002" x14ac:dyDescent="0.3">
-      <c r="A11" s="17">
-        <v>14</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="C11" s="17">
-        <v>20.3</v>
-      </c>
-      <c r="D11" s="17" t="s">
-        <v>83</v>
       </c>
       <c r="E11" s="17" t="s">
         <v>20</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G11" s="17" t="s">
         <v>24</v>
       </c>
       <c r="H11" s="17" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I11" s="17">
         <f t="array" ref="I11">_xlfn.SWITCH(H11,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J11" s="17" t="s">
         <v>77</v>
@@ -11397,34 +11450,34 @@
       <c r="K11" s="17"/>
       <c r="L11" s="17"/>
     </row>
-    <row r="12" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A12" s="17">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C12" s="17">
-        <v>20.3</v>
+        <v>19.3</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E12" s="17" t="s">
         <v>20</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G12" s="17" t="s">
         <v>24</v>
       </c>
       <c r="H12" s="17" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I12" s="17">
         <f t="array" ref="I12">_xlfn.SWITCH(H12,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J12" s="17" t="s">
         <v>77</v>
@@ -11432,123 +11485,127 @@
       <c r="K12" s="17"/>
       <c r="L12" s="17"/>
     </row>
-    <row r="13" spans="1:12" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="19">
+    <row r="13" spans="1:12" ht="273.60000000000002" x14ac:dyDescent="0.3">
+      <c r="A13" s="17">
+        <v>14</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" s="17">
+        <v>20.3</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="G13" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="H13" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="I13" s="17">
+        <f t="array" ref="I13">_xlfn.SWITCH(H13,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>5</v>
+      </c>
+      <c r="J13" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="K13" s="17"/>
+      <c r="L13" s="17"/>
+    </row>
+    <row r="14" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A14" s="17">
+        <v>15</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="C14" s="17">
+        <v>20.3</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="G14" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="H14" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="I14" s="17">
+        <f t="array" ref="I14">_xlfn.SWITCH(H14,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>3</v>
+      </c>
+      <c r="J14" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="K14" s="17"/>
+      <c r="L14" s="17"/>
+    </row>
+    <row r="15" spans="1:12" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A15" s="19">
         <v>16</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B15" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19" t="s">
+      <c r="C15" s="19"/>
+      <c r="D15" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E15" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="20" t="s">
+      <c r="F15" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="G13" s="19" t="s">
+      <c r="G15" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="H13" s="19" t="s">
+      <c r="H15" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="I13" s="19">
-        <f t="array" ref="I13">_xlfn.SWITCH(H13,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+      <c r="I15" s="19">
+        <f t="array" ref="I15">_xlfn.SWITCH(H15,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J13" s="19" t="s">
+      <c r="J15" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="K13" s="19"/>
-      <c r="L13" s="19"/>
-    </row>
-    <row r="14" spans="1:12" ht="244.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="8">
-        <v>17</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="C14" s="8">
-        <v>19.3</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="I14" s="8">
-        <f t="array" ref="I14">_xlfn.SWITCH(H14,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>5</v>
-      </c>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
-    </row>
-    <row r="15" spans="1:12" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="8">
-        <v>18</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="C15" s="8">
-        <v>20.3</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="I15" s="8">
-        <f t="array" ref="I15">_xlfn.SWITCH(H15,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>5</v>
-      </c>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="19"/>
     </row>
     <row r="16" spans="1:12" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C16" s="8">
-        <v>20.399999999999999</v>
+        <v>19.3</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>31</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="G16" s="8" t="s">
         <v>29</v>
@@ -11557,30 +11614,31 @@
         <v>30</v>
       </c>
       <c r="I16" s="8">
+        <f t="array" ref="I16">_xlfn.SWITCH(H16,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
       <c r="J16" s="8"/>
       <c r="K16" s="8"/>
       <c r="L16" s="8"/>
     </row>
-    <row r="17" spans="1:12" ht="273.60000000000002" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>112</v>
+        <v>82</v>
+      </c>
+      <c r="C17" s="8">
+        <v>20.3</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>31</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G17" s="8" t="s">
         <v>29</v>
@@ -11589,30 +11647,31 @@
         <v>30</v>
       </c>
       <c r="I17" s="8">
+        <f t="array" ref="I17">_xlfn.SWITCH(H17,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
       <c r="J17" s="8"/>
       <c r="K17" s="8"/>
       <c r="L17" s="8"/>
     </row>
-    <row r="18" spans="1:12" ht="345.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>113</v>
+        <v>82</v>
+      </c>
+      <c r="C18" s="8">
+        <v>20.399999999999999</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>31</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G18" s="8" t="s">
         <v>29</v>
@@ -11627,30 +11686,66 @@
       <c r="K18" s="8"/>
       <c r="L18" s="8"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
+    <row r="19" spans="1:12" ht="273.60000000000002" x14ac:dyDescent="0.3">
+      <c r="A19" s="8">
+        <v>20</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I19" s="8">
+        <v>5</v>
+      </c>
       <c r="J19" s="8"/>
       <c r="K19" s="8"/>
       <c r="L19" s="8"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
+    <row r="20" spans="1:12" ht="345.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="8">
+        <v>21</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I20" s="8">
+        <v>5</v>
+      </c>
       <c r="J20" s="8"/>
       <c r="K20" s="8"/>
       <c r="L20" s="8"/>
@@ -11692,10 +11787,7 @@
       <c r="F23" s="10"/>
       <c r="G23" s="8"/>
       <c r="H23" s="8"/>
-      <c r="I23" s="8" t="str">
-        <f t="array" ref="I23">_xlfn.SWITCH(H23,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
+      <c r="I23" s="8"/>
       <c r="J23" s="8"/>
       <c r="K23" s="8"/>
       <c r="L23" s="8"/>
@@ -11709,10 +11801,7 @@
       <c r="F24" s="10"/>
       <c r="G24" s="8"/>
       <c r="H24" s="8"/>
-      <c r="I24" s="8" t="str">
-        <f t="array" ref="I24">_xlfn.SWITCH(H24,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
+      <c r="I24" s="8"/>
       <c r="J24" s="8"/>
       <c r="K24" s="8"/>
       <c r="L24" s="8"/>
@@ -11808,7 +11897,7 @@
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
       <c r="E30" s="8"/>
-      <c r="F30" s="7"/>
+      <c r="F30" s="10"/>
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
       <c r="I30" s="8" t="str">
@@ -11825,7 +11914,7 @@
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
       <c r="E31" s="8"/>
-      <c r="F31" s="9"/>
+      <c r="F31" s="10"/>
       <c r="G31" s="8"/>
       <c r="H31" s="8"/>
       <c r="I31" s="8" t="str">
@@ -11842,7 +11931,7 @@
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
       <c r="E32" s="8"/>
-      <c r="F32" s="9"/>
+      <c r="F32" s="7"/>
       <c r="G32" s="8"/>
       <c r="H32" s="8"/>
       <c r="I32" s="8" t="str">
@@ -12114,7 +12203,7 @@
       <c r="C48" s="8"/>
       <c r="D48" s="8"/>
       <c r="E48" s="8"/>
-      <c r="F48" s="10"/>
+      <c r="F48" s="9"/>
       <c r="G48" s="8"/>
       <c r="H48" s="8"/>
       <c r="I48" s="8" t="str">
@@ -12131,7 +12220,7 @@
       <c r="C49" s="8"/>
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
-      <c r="F49" s="10"/>
+      <c r="F49" s="9"/>
       <c r="G49" s="8"/>
       <c r="H49" s="8"/>
       <c r="I49" s="8" t="str">
@@ -12216,7 +12305,7 @@
       <c r="C54" s="8"/>
       <c r="D54" s="8"/>
       <c r="E54" s="8"/>
-      <c r="F54" s="9"/>
+      <c r="F54" s="10"/>
       <c r="G54" s="8"/>
       <c r="H54" s="8"/>
       <c r="I54" s="8" t="str">
@@ -12233,7 +12322,7 @@
       <c r="C55" s="8"/>
       <c r="D55" s="8"/>
       <c r="E55" s="8"/>
-      <c r="F55" s="9"/>
+      <c r="F55" s="10"/>
       <c r="G55" s="8"/>
       <c r="H55" s="8"/>
       <c r="I55" s="8" t="str">
@@ -12403,7 +12492,7 @@
       <c r="C65" s="8"/>
       <c r="D65" s="8"/>
       <c r="E65" s="8"/>
-      <c r="F65" s="7"/>
+      <c r="F65" s="9"/>
       <c r="G65" s="8"/>
       <c r="H65" s="8"/>
       <c r="I65" s="8" t="str">
@@ -12454,7 +12543,7 @@
       <c r="C68" s="8"/>
       <c r="D68" s="8"/>
       <c r="E68" s="8"/>
-      <c r="F68" s="7"/>
+      <c r="F68" s="9"/>
       <c r="G68" s="8"/>
       <c r="H68" s="8"/>
       <c r="I68" s="8" t="str">
@@ -12471,7 +12560,7 @@
       <c r="C69" s="8"/>
       <c r="D69" s="8"/>
       <c r="E69" s="8"/>
-      <c r="F69" s="9"/>
+      <c r="F69" s="7"/>
       <c r="G69" s="8"/>
       <c r="H69" s="8"/>
       <c r="I69" s="8" t="str">
@@ -12488,7 +12577,7 @@
       <c r="C70" s="8"/>
       <c r="D70" s="8"/>
       <c r="E70" s="8"/>
-      <c r="F70" s="9"/>
+      <c r="F70" s="7"/>
       <c r="G70" s="8"/>
       <c r="H70" s="8"/>
       <c r="I70" s="8" t="str">
@@ -12556,7 +12645,7 @@
       <c r="C74" s="8"/>
       <c r="D74" s="8"/>
       <c r="E74" s="8"/>
-      <c r="F74" s="10"/>
+      <c r="F74" s="9"/>
       <c r="G74" s="8"/>
       <c r="H74" s="8"/>
       <c r="I74" s="8" t="str">
@@ -12573,7 +12662,7 @@
       <c r="C75" s="8"/>
       <c r="D75" s="8"/>
       <c r="E75" s="8"/>
-      <c r="F75" s="10"/>
+      <c r="F75" s="9"/>
       <c r="G75" s="8"/>
       <c r="H75" s="8"/>
       <c r="I75" s="8" t="str">
@@ -13161,6 +13250,40 @@
       <c r="J109" s="8"/>
       <c r="K109" s="8"/>
       <c r="L109" s="8"/>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A110" s="8"/>
+      <c r="B110" s="8"/>
+      <c r="C110" s="8"/>
+      <c r="D110" s="8"/>
+      <c r="E110" s="8"/>
+      <c r="F110" s="10"/>
+      <c r="G110" s="8"/>
+      <c r="H110" s="8"/>
+      <c r="I110" s="8" t="str">
+        <f t="array" ref="I110">_xlfn.SWITCH(H110,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J110" s="8"/>
+      <c r="K110" s="8"/>
+      <c r="L110" s="8"/>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A111" s="8"/>
+      <c r="B111" s="8"/>
+      <c r="C111" s="8"/>
+      <c r="D111" s="8"/>
+      <c r="E111" s="8"/>
+      <c r="F111" s="10"/>
+      <c r="G111" s="8"/>
+      <c r="H111" s="8"/>
+      <c r="I111" s="8" t="str">
+        <f t="array" ref="I111">_xlfn.SWITCH(H111,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
+      <c r="J111" s="8"/>
+      <c r="K111" s="8"/>
+      <c r="L111" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13204,12 +13327,12 @@
         <v>46251</v>
       </c>
       <c r="C2" s="4">
-        <f>65-SUM(E$2:E2)</f>
-        <v>65</v>
+        <f>75-SUM(E$2:E2)</f>
+        <v>75</v>
       </c>
       <c r="D2" s="1">
-        <f>65*(1-(A2/8))</f>
-        <v>65</v>
+        <f>75*(1-(A2/8))</f>
+        <v>75</v>
       </c>
       <c r="E2" s="1">
         <v>0</v>
@@ -13223,12 +13346,12 @@
         <v>46252</v>
       </c>
       <c r="C3" s="4">
-        <f>65-SUM(E$2:E3)</f>
-        <v>65</v>
+        <f>75-SUM(E$2:E3)</f>
+        <v>75</v>
       </c>
       <c r="D3" s="1">
-        <f t="shared" ref="D3:D10" si="0">65*(1-(A3/8))</f>
-        <v>56.875</v>
+        <f t="shared" ref="D3:D10" si="0">75*(1-(A3/8))</f>
+        <v>65.625</v>
       </c>
       <c r="E3" s="1">
         <v>0</v>
@@ -13242,12 +13365,12 @@
         <v>46253</v>
       </c>
       <c r="C4" s="4">
-        <f>65-SUM(E$2:E4)</f>
-        <v>65</v>
+        <f>75-SUM(E$2:E4)</f>
+        <v>75</v>
       </c>
       <c r="D4" s="1">
         <f t="shared" si="0"/>
-        <v>48.75</v>
+        <v>56.25</v>
       </c>
       <c r="E4" s="1">
         <v>0</v>
@@ -13262,12 +13385,12 @@
         <v>46254</v>
       </c>
       <c r="C5" s="4">
-        <f>65-SUM(E$2:E5)</f>
-        <v>65</v>
+        <f>75-SUM(E$2:E5)</f>
+        <v>75</v>
       </c>
       <c r="D5" s="1">
         <f t="shared" si="0"/>
-        <v>40.625</v>
+        <v>46.875</v>
       </c>
       <c r="E5" s="1">
         <v>0</v>
@@ -13281,12 +13404,12 @@
         <v>46255</v>
       </c>
       <c r="C6" s="4">
-        <f>65-SUM(E$2:E6)</f>
-        <v>65</v>
+        <f>75-SUM(E$2:E6)</f>
+        <v>75</v>
       </c>
       <c r="D6" s="1">
         <f t="shared" si="0"/>
-        <v>32.5</v>
+        <v>37.5</v>
       </c>
       <c r="E6" s="1">
         <v>0</v>
@@ -13300,12 +13423,12 @@
         <v>46258</v>
       </c>
       <c r="C7" s="4">
-        <f>65-SUM(E$2:E7)</f>
-        <v>65</v>
+        <f>75-SUM(E$2:E7)</f>
+        <v>75</v>
       </c>
       <c r="D7" s="1">
         <f t="shared" si="0"/>
-        <v>24.375</v>
+        <v>28.125</v>
       </c>
       <c r="E7" s="1">
         <v>0</v>
@@ -13319,12 +13442,12 @@
         <v>46259</v>
       </c>
       <c r="C8" s="4">
-        <f>65-SUM(E$2:E8)</f>
-        <v>65</v>
+        <f>75-SUM(E$2:E8)</f>
+        <v>75</v>
       </c>
       <c r="D8" s="1">
         <f t="shared" si="0"/>
-        <v>16.25</v>
+        <v>18.75</v>
       </c>
       <c r="E8" s="1">
         <v>0</v>
@@ -13338,12 +13461,12 @@
         <v>46260</v>
       </c>
       <c r="C9" s="4">
-        <f>65-SUM(E$2:E9)</f>
-        <v>65</v>
+        <f>75-SUM(E$2:E9)</f>
+        <v>75</v>
       </c>
       <c r="D9" s="1">
         <f t="shared" si="0"/>
-        <v>8.125</v>
+        <v>9.375</v>
       </c>
       <c r="E9" s="1">
         <v>0</v>
@@ -13357,8 +13480,8 @@
         <v>46261</v>
       </c>
       <c r="C10" s="4">
-        <f>65-SUM(E$2:E10)</f>
-        <v>65</v>
+        <f>75-SUM(E$2:E10)</f>
+        <v>75</v>
       </c>
       <c r="D10" s="1">
         <f t="shared" si="0"/>

--- a/Business Analysis/checkupp_sprint_plan_2026.xlsx
+++ b/Business Analysis/checkupp_sprint_plan_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Business Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15694944-5DD9-4300-B3D5-3C1B585492C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FE696C6-D790-467D-9513-75CA5AD684B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint 01" sheetId="1" r:id="rId1"/>
@@ -5767,38 +5767,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Backend TDD Suite: Firebase Storage &amp; Links
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Setup &amp; Teardown:
-Initialize the Jest test suite using supertest against the Express server.
-Mock the firebase-admin/storage module to intercept bucket uploads and deletes.
-Implement ruthless beforeEach and afterAll database purges to guarantee deterministic test runs.
-US 6.1: Document Upload (Firebase Stream)
-Success: Send a valid file buffer payload to POST /me/wallet/documents. Assert a 201 Created response. Assert the mocked Firebase bucket upload function is invoked and the database record correctly saves the fileType: FILE and public cloud URL.  
-Edge Case (Missing Fields): Send a payload missing documentType. Assert the Joi gateway validation blocks it and returns a 400 Bad Request.  
-Edge Case (Cloud Failure): Force the mocked Firebase upload to throw an error. Assert the API returns a graceful 500 without creating an orphaned database record.
-US 7.1: e-Script Link Creation
-Success: POST /me/wallet/links with a valid URL and title. Assert a 201 Created response and verify the database record saves fileType: LINK.  
-Edge Case (Whitespace Validation): Send a URL containing only blank spaces. Assert Joi's .trim().min(1) intercepts the request and throws a 400 Bad Request.  
-US 6.3 &amp; 7.4: Deletion &amp; Tenant Isolation
-Success (Document): DELETE /me/wallet/documents/:id. Assert a 200 OK response. Assert the mocked Firebase bucket delete() method is called and the database record is removed.
-Success (Link): DELETE /me/wallet/documents/:id (targeting a link). Assert the database record is removed but the Firebase bucket delete() method is not called.
-Edge Case (Tenant Isolation): Attempt to delete a document ID using a different user's mocked JWT token. Assert a 404 Not Found to guarantee multi-tenant security scoping.
-Audit Logging (All Modifications)
-Success: Following a successful creation or deletion, query the test database to assert an immutable AuditLog row was created with the correct actorId, action, and timestamp.</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>Frontend TDD Suite: UI, Sharing &amp; Caching</t>
     </r>
     <r>
@@ -5828,6 +5796,38 @@
 Success (Image): Simulate selecting "View" on an image document. Assert the ImageViewer modal becomes visible.
 Success (PDF): Simulate selecting "View" on a PDF document. Assert the DocumentViewer modal becomes visible.
 Success (Link): Simulate selecting "Open" on an e-script link. Assert WebBrowser.openBrowserAsync is called with the specific URL.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Backend TDD Suite: Firebase Storage &amp; Links
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Setup &amp; Teardown: (checkupp-api/tests/modules/wallet/wallet.test.ts)
+Initialize the Jest test suite using supertest against the Express server.
+Mock the firebase-admin/storage module to intercept bucket uploads and deletes.
+Implement ruthless beforeEach and afterAll database purges to guarantee deterministic test runs.
+US 6.1: Document Upload (Firebase Stream)
+Success: Send a valid file buffer payload to POST /me/wallet/documents. Assert a 201 Created response. Assert the mocked Firebase bucket upload function is invoked and the database record correctly saves the fileType: FILE and public cloud URL.  
+Edge Case (Missing Fields): Send a payload missing documentType. Assert the Joi gateway validation blocks it and returns a 400 Bad Request.  
+Edge Case (Cloud Failure): Force the mocked Firebase upload to throw an error. Assert the API returns a graceful 500 without creating an orphaned database record.
+US 7.1: e-Script Link Creation
+Success: POST /me/wallet/links with a valid URL and title. Assert a 201 Created response and verify the database record saves fileType: LINK.  
+Edge Case (Whitespace Validation): Send a URL containing only blank spaces. Assert Joi's .trim().min(1) intercepts the request and throws a 400 Bad Request.  
+US 6.3 &amp; 7.4: Deletion &amp; Tenant Isolation
+Success (Document): DELETE /me/wallet/documents/:id. Assert a 200 OK response. Assert the mocked Firebase bucket delete() method is called and the database record is removed.
+Success (Link): DELETE /me/wallet/documents/:id (targeting a link). Assert the database record is removed but the Firebase bucket delete() method is not called.
+Edge Case (Tenant Isolation): Attempt to delete a document ID using a different user's mocked JWT token. Assert a 404 Not Found to guarantee multi-tenant security scoping.
+Audit Logging (All Modifications)
+Success: Following a successful creation or deletion, query the test database to assert an immutable AuditLog row was created with the correct actorId, action, and timestamp.</t>
     </r>
   </si>
 </sst>
@@ -11193,7 +11193,9 @@
       <c r="L3" s="15"/>
     </row>
     <row r="4" spans="1:12" ht="403.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="15"/>
+      <c r="A4" s="15">
+        <v>3</v>
+      </c>
       <c r="B4" s="15" t="s">
         <v>108</v>
       </c>
@@ -11205,7 +11207,7 @@
         <v>31</v>
       </c>
       <c r="F4" s="21" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G4" s="15" t="s">
         <v>29</v>
@@ -11222,7 +11224,9 @@
       <c r="L4" s="15"/>
     </row>
     <row r="5" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="15"/>
+      <c r="A5" s="15">
+        <v>4</v>
+      </c>
       <c r="B5" s="15" t="s">
         <v>108</v>
       </c>
@@ -11234,7 +11238,7 @@
         <v>31</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G5" s="15" t="s">
         <v>29</v>
@@ -11252,7 +11256,7 @@
     </row>
     <row r="6" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A6" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B6" s="15" t="s">
         <v>108</v>
@@ -11285,7 +11289,7 @@
     </row>
     <row r="7" spans="1:12" ht="144" x14ac:dyDescent="0.3">
       <c r="A7" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B7" s="15" t="s">
         <v>108</v>
@@ -11318,7 +11322,7 @@
     </row>
     <row r="8" spans="1:12" ht="144" x14ac:dyDescent="0.3">
       <c r="A8" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B8" s="15" t="s">
         <v>108</v>
@@ -11351,7 +11355,7 @@
     </row>
     <row r="9" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A9" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>108</v>
@@ -11384,7 +11388,7 @@
     </row>
     <row r="10" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A10" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>76</v>
@@ -11416,8 +11420,8 @@
       <c r="L10" s="15"/>
     </row>
     <row r="11" spans="1:12" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="17">
-        <v>12</v>
+      <c r="A11" s="15">
+        <v>10</v>
       </c>
       <c r="B11" s="17" t="s">
         <v>78</v>
@@ -11451,8 +11455,8 @@
       <c r="L11" s="17"/>
     </row>
     <row r="12" spans="1:12" ht="244.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="17">
-        <v>13</v>
+      <c r="A12" s="15">
+        <v>11</v>
       </c>
       <c r="B12" s="17" t="s">
         <v>78</v>
@@ -11486,8 +11490,8 @@
       <c r="L12" s="17"/>
     </row>
     <row r="13" spans="1:12" ht="273.60000000000002" x14ac:dyDescent="0.3">
-      <c r="A13" s="17">
-        <v>14</v>
+      <c r="A13" s="15">
+        <v>12</v>
       </c>
       <c r="B13" s="17" t="s">
         <v>82</v>
@@ -11521,8 +11525,8 @@
       <c r="L13" s="17"/>
     </row>
     <row r="14" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A14" s="17">
-        <v>15</v>
+      <c r="A14" s="15">
+        <v>13</v>
       </c>
       <c r="B14" s="17" t="s">
         <v>82</v>
@@ -11556,8 +11560,8 @@
       <c r="L14" s="17"/>
     </row>
     <row r="15" spans="1:12" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="19">
-        <v>16</v>
+      <c r="A15" s="15">
+        <v>14</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>87</v>
@@ -11589,8 +11593,8 @@
       <c r="L15" s="19"/>
     </row>
     <row r="16" spans="1:12" ht="244.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="8">
-        <v>17</v>
+      <c r="A16" s="15">
+        <v>15</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>78</v>
@@ -11622,8 +11626,8 @@
       <c r="L16" s="8"/>
     </row>
     <row r="17" spans="1:12" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="8">
-        <v>18</v>
+      <c r="A17" s="15">
+        <v>16</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>82</v>
@@ -11655,8 +11659,8 @@
       <c r="L17" s="8"/>
     </row>
     <row r="18" spans="1:12" ht="244.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="8">
-        <v>19</v>
+      <c r="A18" s="15">
+        <v>17</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>82</v>
@@ -11687,8 +11691,8 @@
       <c r="L18" s="8"/>
     </row>
     <row r="19" spans="1:12" ht="273.60000000000002" x14ac:dyDescent="0.3">
-      <c r="A19" s="8">
-        <v>20</v>
+      <c r="A19" s="15">
+        <v>18</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>98</v>
@@ -11719,8 +11723,8 @@
       <c r="L19" s="8"/>
     </row>
     <row r="20" spans="1:12" ht="345.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="8">
-        <v>21</v>
+      <c r="A20" s="15">
+        <v>19</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>98</v>

--- a/Business Analysis/checkupp_sprint_plan_2026.xlsx
+++ b/Business Analysis/checkupp_sprint_plan_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Business Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FE696C6-D790-467D-9513-75CA5AD684B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9841AB54-7BFF-463E-BFAA-CC799CFC4226}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="120">
   <si>
     <t>Epic</t>
   </si>
@@ -5347,9 +5347,6 @@
   </si>
   <si>
     <t>Done</t>
-  </si>
-  <si>
-    <t>Document Wallet - Documents</t>
   </si>
   <si>
     <t>ToDo</t>
@@ -11131,17 +11128,17 @@
         <v>1</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15" t="s">
         <v>31</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G2" s="15" t="s">
         <v>29</v>
@@ -11154,7 +11151,7 @@
         <v>3</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K2" s="15"/>
       <c r="L2" s="15"/>
@@ -11164,17 +11161,17 @@
         <v>2</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D3" s="15"/>
       <c r="E3" s="15" t="s">
         <v>31</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G3" s="15" t="s">
         <v>29</v>
@@ -11187,7 +11184,7 @@
         <v>3</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K3" s="15"/>
       <c r="L3" s="15"/>
@@ -11197,17 +11194,17 @@
         <v>3</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D4" s="15"/>
       <c r="E4" s="15" t="s">
         <v>31</v>
       </c>
       <c r="F4" s="21" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G4" s="15" t="s">
         <v>29</v>
@@ -11228,17 +11225,17 @@
         <v>4</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D5" s="15"/>
       <c r="E5" s="15" t="s">
         <v>31</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G5" s="15" t="s">
         <v>29</v>
@@ -11259,17 +11256,17 @@
         <v>5</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D6" s="15"/>
       <c r="E6" s="15" t="s">
         <v>22</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G6" s="15" t="s">
         <v>29</v>
@@ -11282,7 +11279,7 @@
         <v>5</v>
       </c>
       <c r="J6" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K6" s="15"/>
       <c r="L6" s="15"/>
@@ -11292,17 +11289,17 @@
         <v>6</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="15" t="s">
         <v>20</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G7" s="15" t="s">
         <v>29</v>
@@ -11315,7 +11312,7 @@
         <v>2</v>
       </c>
       <c r="J7" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K7" s="15"/>
       <c r="L7" s="15"/>
@@ -11325,17 +11322,17 @@
         <v>7</v>
       </c>
       <c r="B8" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="C8" s="15" t="s">
         <v>108</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>109</v>
       </c>
       <c r="D8" s="15"/>
       <c r="E8" s="15" t="s">
         <v>20</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G8" s="15" t="s">
         <v>29</v>
@@ -11348,7 +11345,7 @@
         <v>3</v>
       </c>
       <c r="J8" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K8" s="15"/>
       <c r="L8" s="15"/>
@@ -11358,7 +11355,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C9" s="15">
         <v>6.5</v>
@@ -11368,7 +11365,7 @@
         <v>20</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G9" s="15" t="s">
         <v>29</v>
@@ -11381,7 +11378,7 @@
         <v>2</v>
       </c>
       <c r="J9" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K9" s="15"/>
       <c r="L9" s="15"/>
@@ -11391,20 +11388,20 @@
         <v>9</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>76</v>
+        <v>107</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D10" s="15"/>
       <c r="E10" s="15" t="s">
         <v>20</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H10" s="15" t="s">
         <v>27</v>
@@ -11414,29 +11411,29 @@
         <v>3</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K10" s="15"/>
       <c r="L10" s="15"/>
     </row>
     <row r="11" spans="1:12" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="15">
+      <c r="A11" s="17">
         <v>10</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C11" s="17">
         <v>19.3</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E11" s="17" t="s">
         <v>20</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G11" s="17" t="s">
         <v>24</v>
@@ -11449,29 +11446,29 @@
         <v>3</v>
       </c>
       <c r="J11" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K11" s="17"/>
       <c r="L11" s="17"/>
     </row>
     <row r="12" spans="1:12" ht="244.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="15">
+      <c r="A12" s="17">
         <v>11</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C12" s="17">
         <v>19.3</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E12" s="17" t="s">
         <v>20</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G12" s="17" t="s">
         <v>24</v>
@@ -11484,29 +11481,29 @@
         <v>5</v>
       </c>
       <c r="J12" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K12" s="17"/>
       <c r="L12" s="17"/>
     </row>
     <row r="13" spans="1:12" ht="273.60000000000002" x14ac:dyDescent="0.3">
-      <c r="A13" s="15">
+      <c r="A13" s="17">
         <v>12</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C13" s="17">
         <v>20.3</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E13" s="17" t="s">
         <v>20</v>
       </c>
       <c r="F13" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G13" s="17" t="s">
         <v>24</v>
@@ -11519,29 +11516,29 @@
         <v>5</v>
       </c>
       <c r="J13" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K13" s="17"/>
       <c r="L13" s="17"/>
     </row>
     <row r="14" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A14" s="15">
+      <c r="A14" s="17">
         <v>13</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C14" s="17">
         <v>20.3</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E14" s="17" t="s">
         <v>20</v>
       </c>
       <c r="F14" s="18" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G14" s="17" t="s">
         <v>24</v>
@@ -11554,27 +11551,27 @@
         <v>3</v>
       </c>
       <c r="J14" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K14" s="17"/>
       <c r="L14" s="17"/>
     </row>
     <row r="15" spans="1:12" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="15">
+      <c r="A15" s="19">
         <v>14</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C15" s="19"/>
       <c r="D15" s="19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E15" s="19" t="s">
         <v>22</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G15" s="19" t="s">
         <v>24</v>
@@ -11587,29 +11584,29 @@
         <v>3</v>
       </c>
       <c r="J15" s="19" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K15" s="19"/>
       <c r="L15" s="19"/>
     </row>
     <row r="16" spans="1:12" ht="244.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="15">
+      <c r="A16" s="8">
         <v>15</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C16" s="8">
         <v>19.3</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>31</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G16" s="8" t="s">
         <v>29</v>
@@ -11626,23 +11623,23 @@
       <c r="L16" s="8"/>
     </row>
     <row r="17" spans="1:12" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="15">
+      <c r="A17" s="8">
         <v>16</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C17" s="8">
         <v>20.3</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>31</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G17" s="8" t="s">
         <v>29</v>
@@ -11659,23 +11656,23 @@
       <c r="L17" s="8"/>
     </row>
     <row r="18" spans="1:12" ht="244.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="15">
+      <c r="A18" s="8">
         <v>17</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C18" s="8">
         <v>20.399999999999999</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>31</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G18" s="8" t="s">
         <v>29</v>
@@ -11691,23 +11688,23 @@
       <c r="L18" s="8"/>
     </row>
     <row r="19" spans="1:12" ht="273.60000000000002" x14ac:dyDescent="0.3">
-      <c r="A19" s="15">
+      <c r="A19" s="8">
         <v>18</v>
       </c>
       <c r="B19" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="D19" s="8" t="s">
         <v>98</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>99</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>31</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G19" s="8" t="s">
         <v>29</v>
@@ -11723,23 +11720,23 @@
       <c r="L19" s="8"/>
     </row>
     <row r="20" spans="1:12" ht="345.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="15">
+      <c r="A20" s="8">
         <v>19</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E20" s="8" t="s">
         <v>31</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G20" s="8" t="s">
         <v>29</v>

--- a/Business Analysis/checkupp_sprint_plan_2026.xlsx
+++ b/Business Analysis/checkupp_sprint_plan_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Business Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9841AB54-7BFF-463E-BFAA-CC799CFC4226}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBAE6161-9D0C-475D-B5AB-1CB4A12B3B0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="119">
   <si>
     <t>Epic</t>
   </si>
@@ -5358,20 +5358,6 @@
     <t>Cardiovascular Camera Scanner UI &amp; Permission Handling</t>
   </si>
   <si>
-    <t>Cardiovascular Camera Scanner UI &amp; Permission Handling
-* **Target Files**:
-* `checkupp-mobile-main/app/(tabs)/cardiovascular.tsx`
-* `checkupp-mobile-main/components/camera/ScanMonitorModal.tsx`
-* **Description**:
-1. Add a "Scan Monitor" icon/button next to the manual input fields for Blood Pressure on the Cardiovascular screen.
-2. Implement `ScanMonitorModal.tsx` using `react-native-vision-camera` (or `expo-camera`).
-3. Include native camera permission checks with graceful permission fallback prompts.
-4. Design a full-screen camera modal with a centered "Target Bounding Box" overlay instructing the user to "Align your screen's numbers inside this box."
-5. Include a prominent manual "Cancel / Enter Manually" button to allow users to exit the camera view at any time.
-6. Cap camera frame processing at 15–30 fps via frame processor configuration to optimize device battery consumption and prevent thermal throttling.
-* **Acceptance Criteria Covered**: US 19.3 (AC 1, 2, 3, 4, 7)</t>
-  </si>
-  <si>
     <t>OCR Processing, Frame Processor &amp; Form Auto-Fill</t>
   </si>
   <si>
@@ -5379,24 +5365,6 @@
   </si>
   <si>
     <t>Single-Number OCR, Contextual Selection &amp; Auto-Fill</t>
-  </si>
-  <si>
-    <t>Glucometer ML Kit Scanning &amp; Contextual Reading Modal
-* **Target Files**:
-* `checkupp-mobile-main/app/(tabs)/diabetes.tsx`
-* `checkupp-mobile-main/components/camera/GlucometerScannerModal.tsx`
-* `checkupp-mobile-main/components/ReadingTypeBottomSheet.tsx`
-* **Description**:
-1. Place a "Scan Glucometer" button prominently at the top of the Blood Glucose section in the Diabetes form.
-2. Implement a focused scanner modal targeting single numbers (including decimals, e.g., 5.6 or 12.1) using regular expression matching.
-3. Upon capturing the valid glucose value, display `ReadingTypeBottomSheet.tsx` asking: `"What type of reading is this?"` with options:
-* Fasting Glucose
-* Random Glucose
-* Post-Meal Glucose
-4. Inject the scanned number specifically into the selected option's field and close the bottom sheet.
-5. Enforce human-in-the-loop confirmation where the user must manually tap "Save Reading" to commit to the backend.
-6. Add the 10-second scanner timeout alert with manual fallback options.
-* **Acceptance Criteria Covered**: US 20.3 - Glucometer (AC 1, 2, 3, 4, 5, 6, 7)</t>
   </si>
   <si>
     <t>Contrast Pre-Processing, Regex Extraction &amp; Auto-Fill</t>
@@ -5431,25 +5399,6 @@
 1. Ensure `vitals.validation.ts` accommodates auto-filled decimal and integer values strictly matching physiological sanity bounds (e.g., Systolic 50–250 mmHg, Weight 20–300 kg, Glucose 1–35 mmol/L or 20–600 mg/dL).
 2. Write unit and integration tests verifying that incoming payloads from both manual entry and camera-scanned flows validate identically and save correctly to user history.
 * **Acceptance Criteria Covered**: Cross-epic data integrity for US 19.3 &amp; US 20.3</t>
-  </si>
-  <si>
-    <t>Alekhya &amp; Atish</t>
-  </si>
-  <si>
-    <t>Blood Pressure ML Kit Extraction, Y-Coordinate Sorting &amp; Validation
-* **Target Files**:
-* `checkupp-mobile-main/lib/utils/ocrUtils.ts`
-* `checkupp-mobile-main/components/camera/ScanMonitorModal.tsx`
-* `checkupp-mobile-main/app/(tabs)/cardiovascular.tsx`
-* **Description**:
-1. Integrate Google ML Kit Text Recognition into the camera frame processor to extract numerical text strings dynamically.
-2. Implement vertical Y-coordinate sorting in `ocrUtils.ts`:
-* Highest Y-coordinate -&gt; Auto-fills **Systolic (mmHg)**
-* Middle Y-coordinate -&gt; Auto-fills **Diastolic (mmHg)**
-* Lowest Y-coordinate -&gt; Auto-fills **Heart Rate (BPM)**
-3. Close the camera modal upon successful extraction, populate the respective form fields, and display a Toast/Banner stating: `"Numbers scanned successfully. Please verify against your device."`
-4. Implement a 10-second timeout scanner loop. If no valid match is found within 10 seconds, trigger a prompt: `"Having trouble reading the screen. Ensure there is no glare, or switch to manual entry."` with an easy button to exit.
-* **Acceptance Criteria Covered**: US 19.3 (AC 5, 6, 8)</t>
   </si>
   <si>
     <t>Live-scan digital blood pressure monitor</t>
@@ -5512,23 +5461,6 @@
     <t>Shared camera scanning</t>
   </si>
   <si>
-    <t>Implement Shared Camera Performance, Permission and Timeout Handling with Jest TDD
-Target Files:
-• checkupp-mobile-main/lib/scanner/deviceScanner.js
-• Existing camera component under checkupp-mobile-main/components/
-• checkupp-mobile-main/__tests__/scanner/scanner-edge-cases.test.js
-Description:
-1. Reuse the existing native camera permission implementation.
-2. Handle already-granted, requested, denied and revoked camera permissions gracefully.
-3. Limit ML Kit frame processing to 15–30 FPS instead of processing every camera frame.
-4. Start a 10-second timeout whenever a scanner opens.
-5. Cancel the timeout after successful detection, cancellation or scanner closure.
-6. Display the exact timeout message: "Having trouble reading the screen. Ensure there is no glare, or switch to manual entry."
-7. Provide an easy exit/manual-entry action after timeout.
-8. Add Jest fake-timer and mocked-permission tests.
-Acceptance Criteria Covered: US 19.3 – Permissions, Performance, Timeout; US 20.3 – Timeout; US 20.4 – Timeout</t>
-  </si>
-  <si>
     <t>Implement Image Quality, Bounding-Box Filtering and Multi-Frame Stability with Jest TDD
 Target Files:
 • checkupp-mobile-main/lib/scanner/bloodPressureScanner.js
@@ -5826,6 +5758,78 @@
 Audit Logging (All Modifications)
 Success: Following a successful creation or deletion, query the test database to assert an immutable AuditLog row was created with the correct actorId, action, and timestamp.</t>
     </r>
+  </si>
+  <si>
+    <t>Cardiovascular Camera Scanner UI, Permission Handling &amp; Torch Toggle
+* **Target Files**:
+* `checkupp-mobile-main/app/(tabs)/cardiovascular.tsx`
+* `checkupp-mobile-main/components/camera/ScanMonitorModal.tsx`
+* **Description**:
+1. Add a "Scan Monitor" icon/button next to the manual input fields for Blood Pressure on the Cardiovascular screen.
+2. Implement `ScanMonitorModal.tsx` using `react-native-vision-camera` (or `expo-camera`).
+3. Include native camera permission checks with graceful permission fallback prompts.
+4. Design a full-screen camera modal with a centered "Target Bounding Box" overlay instructing the user to "Align your screen's numbers inside this box."
+5. Include a prominent manual "Cancel / Enter Manually" button to allow users to exit the camera view at any time.
+6. Cap camera frame processing at 15–30 fps via frame processor configuration to optimize device battery consumption and prevent thermal throttling.
+7. Add an interactive Torch/Flashlight toggle button overlay on the scanner interface to illuminate dark physical environments, bound to the camera torch property.
+* **Acceptance Criteria Covered**: US 19.3 (AC 1, 2, 3, 4, 7)</t>
+  </si>
+  <si>
+    <t>Blood Pressure ML Kit Extraction, Pre-Processing, Y-Coordinate Sorting &amp; Validation
+* **Target Files**:
+* `checkupp-mobile-main/lib/utils/ocrUtils.ts`
+* `checkupp-mobile/lib/utils/imageUtils.ts
+* `checkupp-mobile-main/components/camera/ScanMonitorModal.tsx`
+* `checkupp-mobile-main/app/(tabs)/cardiovascular.tsx`
+* **Description**:
+0. Apply imageUtils.ts grayscale and adaptive threshold/contrast filtering to the camera frame buffer before ML Kit processing to strip screen reflections and isolate glowing LCD digits.
+1. Integrate Google ML Kit Text Recognition into the camera frame processor to extract numerical text strings dynamically.
+2. Implement vertical Y-coordinate sorting in `ocrUtils.ts`:
+* Highest Y-coordinate -&gt; Auto-fills **Systolic (mmHg)**
+* Middle Y-coordinate -&gt; Auto-fills **Diastolic (mmHg)**
+* Lowest Y-coordinate -&gt; Auto-fills **Heart Rate (BPM)**
+3. Close the camera modal upon successful extraction, populate the respective form fields, and display a Toast stating: `"Numbers scanned successfully. Please verify against your device."`
+4. Implement a 10-second timeout scanner loop. If no valid match is found within 10 seconds, trigger a prompt: `"Having trouble reading the screen. Ensure there is no glare, or switch to manual entry."` with an easy button to exit.
+* **Acceptance Criteria Covered**: US 19.3 (AC 5, 6, 8)</t>
+  </si>
+  <si>
+    <t>Glucometer ML Kit Scanning with Frame Pre-Processing &amp; Contextual Reading Modal
+* **Target Files**:
+* `checkupp-mobile-main/app/(tabs)/diabetes.tsx`
+* `checkupp-mobile/lib/utils/imageUtils.ts
+* `checkupp-mobile-main/components/camera/GlucometerScannerModal.tsx`
+* `checkupp-mobile-main/components/ReadingTypeBottomSheet.tsx`
+* **Description**:
+1. Place a "Scan Glucometer" button prominently at the top of the Blood Glucose section in the Diabetes form.
+2. Apply imageUtils.ts threshold/contrast pre-processing to the camera frame to eliminate screen glare before passing to ML Kit.
+3. Implement a focused scanner modal targeting single numbers (including decimals, e.g., 5.6 or 12.1) using regular expression matching.
+4. Upon capturing the valid glucose value, display `ReadingTypeBottomSheet.tsx` asking: `"What type of reading is this?"` with options:
+* Fasting Glucose
+* Random Glucose
+* Post-Meal Glucose
+5. Inject the scanned number specifically into the selected option's field and close the bottom sheet.
+6. Enforce human-in-the-loop confirmation where the user must manually tap "Save Reading" to commit to the backend.
+7. Add the 10-second scanner timeout alert with manual fallback options.
+* **Acceptance Criteria Covered**: US 20.3 - Glucometer (AC 1, 2, 3, 4, 5, 6, 7)</t>
+  </si>
+  <si>
+    <t>Implement Shared Camera Performance, Permission, Timeout Handling &amp; Privacy with Jest TDD
+Target Files:
+• checkupp-mobile-main/lib/scanner/deviceScanner.js
+• checkupp-mobile/components/camera/ScanMonitorModal.tsx
+• checkupp-mobile-main/__tests__/scanner/scanner-edge-cases.test.js
+Description:
+1. Reuse the existing native camera permission implementation.
+2. Handle already-granted, requested, denied and revoked camera permissions gracefully.
+3. Limit ML Kit frame processing to 15–30 FPS instead of processing every camera frame.
+4. Start a 10-second timeout whenever a scanner opens.
+5. Cancel the timeout after successful detection, cancellation or scanner closure.
+6. Display the exact timeout message: "Having trouble reading the screen. Ensure there is no glare, or switch to manual entry."
+7. Provide an easy exit/manual-entry action after timeout.
+8. Add Jest fake-timer and mocked-permission tests.
+9. Add Jest tests verifying that toggling the Torch/Flashlight UI control updates the native camera torch state property correctly.
+10. Add a test assertion verifying that scanner execution operates 100% locally via on-device ML Kit with zero outbound HTTP/network requests initiated during the scan cycle.
+Acceptance Criteria Covered: US 19.3 – Permissions, Performance, Timeout; US 20.3 – Timeout; US 20.4 – Timeout</t>
   </si>
 </sst>
 </file>
@@ -5892,7 +5896,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5935,6 +5939,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -5963,19 +5973,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6004,9 +6008,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6027,6 +6028,24 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8531,2325 +8550,2325 @@
   <dimension ref="A1:L112"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.88671875" style="12" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" style="12" customWidth="1"/>
-    <col min="3" max="3" width="13.21875" style="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.6640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5546875" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="52.6640625" style="13" customWidth="1"/>
-    <col min="7" max="7" width="12.109375" style="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.88671875" style="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.33203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.77734375" style="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5546875" style="12" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.44140625" style="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.88671875" style="12"/>
+    <col min="1" max="1" width="6.88671875" style="10" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" style="10" customWidth="1"/>
+    <col min="3" max="3" width="13.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="52.6640625" style="11" customWidth="1"/>
+    <col min="7" max="7" width="12.109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.88671875" style="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.33203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.77734375" style="10" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.5546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.44140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.88671875" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:12" s="9" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="49.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8">
+      <c r="A2" s="6">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="6">
         <v>0.1</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="8" cm="1">
+      <c r="I2" s="6" cm="1">
         <f t="array" ref="I2">_xlfn.SWITCH(H2,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
     </row>
     <row r="3" spans="1:12" ht="408.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="8">
+      <c r="A3" s="6">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="6">
         <v>1.1000000000000001</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="8" cm="1">
+      <c r="I3" s="6" cm="1">
         <f t="array" ref="I3">_xlfn.SWITCH(H3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="1:12" ht="408.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="8">
+      <c r="A4" s="6">
         <v>3</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="8" cm="1">
+      <c r="I4" s="6" cm="1">
         <f t="array" ref="I4">_xlfn.SWITCH(H4,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>1</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J4" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
     </row>
     <row r="5" spans="1:12" ht="408.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="8">
+      <c r="A5" s="6">
         <v>4</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="I5" s="8" cm="1">
+      <c r="I5" s="6" cm="1">
         <f t="array" ref="I5">_xlfn.SWITCH(H5,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="J5" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
     </row>
     <row r="6" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="8">
+      <c r="A6" s="6">
         <v>5</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8">
+      <c r="B6" s="6"/>
+      <c r="C6" s="6">
         <v>1.6</v>
       </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8" t="s">
+      <c r="D6" s="6"/>
+      <c r="E6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="I6" s="8" cm="1">
+      <c r="I6" s="6" cm="1">
         <f t="array" ref="I6">_xlfn.SWITCH(H6,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="J6" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
     </row>
     <row r="7" spans="1:12" ht="272.39999999999998" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="8">
+      <c r="A7" s="6">
         <v>6</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="H7" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="I7" s="8" cm="1">
+      <c r="I7" s="6" cm="1">
         <f t="array" ref="I7">_xlfn.SWITCH(H7,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="J7" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
     </row>
     <row r="8" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="8">
+      <c r="A8" s="6">
         <v>7</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="I8" s="8" cm="1">
+      <c r="I8" s="6" cm="1">
         <f t="array" ref="I8">_xlfn.SWITCH(H8,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J8" s="8" t="s">
+      <c r="J8" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
     </row>
     <row r="9" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="8">
+      <c r="A9" s="6">
         <v>8</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I9" s="8" cm="1">
+      <c r="I9" s="6" cm="1">
         <f t="array" ref="I9">_xlfn.SWITCH(H9,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J9" s="8" t="s">
+      <c r="J9" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
     </row>
     <row r="10" spans="1:12" ht="396" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="8">
+      <c r="A10" s="6">
         <v>9</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G10" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="H10" s="8" t="s">
+      <c r="H10" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="I10" s="8" cm="1">
+      <c r="I10" s="6" cm="1">
         <f t="array" ref="I10">_xlfn.SWITCH(H10,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J10" s="8" t="s">
+      <c r="J10" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
     </row>
     <row r="11" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="8">
+      <c r="A11" s="6">
         <v>10</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="H11" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="I11" s="8" cm="1">
+      <c r="I11" s="6" cm="1">
         <f t="array" ref="I11">_xlfn.SWITCH(H11,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J11" s="8" t="s">
+      <c r="J11" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
     </row>
     <row r="12" spans="1:12" ht="408.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="8">
+      <c r="A12" s="6">
         <v>11</v>
       </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8" t="s">
+      <c r="B12" s="6"/>
+      <c r="C12" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8" t="s">
+      <c r="D12" s="6"/>
+      <c r="E12" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="H12" s="8" t="s">
+      <c r="H12" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="I12" s="8" cm="1">
+      <c r="I12" s="6" cm="1">
         <f t="array" ref="I12">_xlfn.SWITCH(H12,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J12" s="8" t="s">
+      <c r="J12" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
     </row>
     <row r="13" spans="1:12" ht="302.39999999999998" x14ac:dyDescent="0.3">
-      <c r="A13" s="8">
+      <c r="A13" s="6">
         <v>12</v>
       </c>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8">
+      <c r="B13" s="6"/>
+      <c r="C13" s="6">
         <v>1.8</v>
       </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8" t="s">
+      <c r="D13" s="6"/>
+      <c r="E13" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="G13" s="8" t="s">
+      <c r="G13" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="H13" s="8" t="s">
+      <c r="H13" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I13" s="8" cm="1">
+      <c r="I13" s="6" cm="1">
         <f t="array" ref="I13">_xlfn.SWITCH(H13,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J13" s="8" t="s">
+      <c r="J13" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
     </row>
     <row r="14" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="8">
+      <c r="A14" s="6">
         <v>13</v>
       </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8" t="s">
+      <c r="B14" s="6"/>
+      <c r="C14" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F14" s="10" t="s">
+      <c r="F14" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="G14" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="H14" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="I14" s="8" cm="1">
+      <c r="I14" s="6" cm="1">
         <f t="array" ref="I14">_xlfn.SWITCH(H14,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J14" s="8" t="s">
+      <c r="J14" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
     </row>
     <row r="15" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="8">
+      <c r="A15" s="6">
         <v>14</v>
       </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8" t="s">
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F15" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="G15" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H15" s="8" t="s">
+      <c r="H15" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="I15" s="8" cm="1">
+      <c r="I15" s="6" cm="1">
         <f t="array" ref="I15">_xlfn.SWITCH(H15,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J15" s="8" t="s">
+      <c r="J15" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="K15" s="8" t="s">
+      <c r="K15" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="L15" s="8"/>
+      <c r="L15" s="6"/>
     </row>
     <row r="16" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="8">
+      <c r="A16" s="6">
         <v>15</v>
       </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8" t="s">
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F16" s="10" t="s">
+      <c r="F16" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="G16" s="8" t="s">
+      <c r="G16" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H16" s="8" t="s">
+      <c r="H16" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="I16" s="8" cm="1">
+      <c r="I16" s="6" cm="1">
         <f t="array" ref="I16">_xlfn.SWITCH(H16,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J16" s="8" t="s">
+      <c r="J16" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="K16" s="8" t="s">
+      <c r="K16" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="L16" s="8"/>
+      <c r="L16" s="6"/>
     </row>
     <row r="17" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="8">
+      <c r="A17" s="6">
         <v>16</v>
       </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8">
+      <c r="B17" s="6"/>
+      <c r="C17" s="6">
         <v>18.5</v>
       </c>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8" t="s">
+      <c r="D17" s="6"/>
+      <c r="E17" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F17" s="10" t="s">
+      <c r="F17" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="G17" s="8" t="s">
+      <c r="G17" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H17" s="8" t="s">
+      <c r="H17" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="I17" s="8" cm="1">
+      <c r="I17" s="6" cm="1">
         <f t="array" ref="I17">_xlfn.SWITCH(H17,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J17" s="8" t="s">
+      <c r="J17" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="K17" s="8" t="s">
+      <c r="K17" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="L17" s="8"/>
+      <c r="L17" s="6"/>
     </row>
     <row r="18" spans="1:12" ht="315.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="8">
+      <c r="A18" s="6">
         <v>17</v>
       </c>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8" t="s">
+      <c r="B18" s="6"/>
+      <c r="C18" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8" t="s">
+      <c r="D18" s="6"/>
+      <c r="E18" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F18" s="10" t="s">
+      <c r="F18" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="G18" s="8" t="s">
+      <c r="G18" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="H18" s="8" t="s">
+      <c r="H18" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="I18" s="8" cm="1">
+      <c r="I18" s="6" cm="1">
         <f t="array" ref="I18">_xlfn.SWITCH(H18,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J18" s="8" t="s">
+      <c r="J18" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="K18" s="8"/>
-      <c r="L18" s="8"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
     </row>
     <row r="19" spans="1:12" ht="383.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="8">
+      <c r="A19" s="6">
         <v>18</v>
       </c>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8">
+      <c r="B19" s="6"/>
+      <c r="C19" s="6">
         <v>18.100000000000001</v>
       </c>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8" t="s">
+      <c r="D19" s="6"/>
+      <c r="E19" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="F19" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="G19" s="8" t="s">
+      <c r="G19" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="H19" s="8" t="s">
+      <c r="H19" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I19" s="8" cm="1">
+      <c r="I19" s="6" cm="1">
         <f t="array" ref="I19">_xlfn.SWITCH(H19,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J19" s="8" t="s">
+      <c r="J19" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
     </row>
     <row r="20" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="8">
+      <c r="A20" s="6">
         <v>19</v>
       </c>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8">
+      <c r="B20" s="6"/>
+      <c r="C20" s="6">
         <v>18.2</v>
       </c>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8" t="s">
+      <c r="D20" s="6"/>
+      <c r="E20" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F20" s="10" t="s">
+      <c r="F20" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="G20" s="8" t="s">
+      <c r="G20" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="H20" s="8" t="s">
+      <c r="H20" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="I20" s="8" cm="1">
+      <c r="I20" s="6" cm="1">
         <f t="array" ref="I20">_xlfn.SWITCH(H20,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J20" s="8" t="s">
+      <c r="J20" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="K20" s="8"/>
-      <c r="L20" s="8"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
     </row>
     <row r="21" spans="1:12" ht="360" x14ac:dyDescent="0.3">
-      <c r="A21" s="8">
+      <c r="A21" s="6">
         <v>20</v>
       </c>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8">
+      <c r="B21" s="6"/>
+      <c r="C21" s="6">
         <v>18.3</v>
       </c>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8" t="s">
+      <c r="D21" s="6"/>
+      <c r="E21" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F21" s="10" t="s">
+      <c r="F21" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="G21" s="8" t="s">
+      <c r="G21" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="H21" s="8" t="s">
+      <c r="H21" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="I21" s="8" cm="1">
+      <c r="I21" s="6" cm="1">
         <f t="array" ref="I21">_xlfn.SWITCH(H21,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J21" s="8" t="s">
+      <c r="J21" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="K21" s="8"/>
-      <c r="L21" s="8"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6"/>
     </row>
     <row r="22" spans="1:12" ht="409.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="8">
+      <c r="A22" s="6">
         <v>21</v>
       </c>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8" t="s">
+      <c r="B22" s="6"/>
+      <c r="C22" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8" t="s">
+      <c r="D22" s="6"/>
+      <c r="E22" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F22" s="10" t="s">
+      <c r="F22" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="G22" s="8" t="s">
+      <c r="G22" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="H22" s="8" t="s">
+      <c r="H22" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="I22" s="8" cm="1">
+      <c r="I22" s="6" cm="1">
         <f t="array" ref="I22">_xlfn.SWITCH(H22,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J22" s="8" t="s">
+      <c r="J22" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="K22" s="8"/>
-      <c r="L22" s="8"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
     </row>
     <row r="23" spans="1:12" ht="316.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="8">
+      <c r="A23" s="6">
         <v>22</v>
       </c>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8">
+      <c r="B23" s="6"/>
+      <c r="C23" s="6">
         <v>18.399999999999999</v>
       </c>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8" t="s">
+      <c r="D23" s="6"/>
+      <c r="E23" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F23" s="10" t="s">
+      <c r="F23" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="G23" s="8" t="s">
+      <c r="G23" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="H23" s="8" t="s">
+      <c r="H23" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="I23" s="8" cm="1">
+      <c r="I23" s="6" cm="1">
         <f t="array" ref="I23">_xlfn.SWITCH(H23,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J23" s="8" t="s">
+      <c r="J23" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="K23" s="8"/>
-      <c r="L23" s="8"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6"/>
     </row>
     <row r="24" spans="1:12" ht="403.2" x14ac:dyDescent="0.3">
-      <c r="A24" s="8">
+      <c r="A24" s="6">
         <v>23</v>
       </c>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8">
+      <c r="B24" s="6"/>
+      <c r="C24" s="6">
         <v>18.5</v>
       </c>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8" t="s">
+      <c r="D24" s="6"/>
+      <c r="E24" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F24" s="10" t="s">
+      <c r="F24" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="G24" s="8" t="s">
+      <c r="G24" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="H24" s="8" t="s">
+      <c r="H24" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="I24" s="8" cm="1">
+      <c r="I24" s="6" cm="1">
         <f t="array" ref="I24">_xlfn.SWITCH(H24,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J24" s="8" t="s">
+      <c r="J24" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="K24" s="8"/>
-      <c r="L24" s="8"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6"/>
     </row>
     <row r="25" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="8">
+      <c r="A25" s="6">
         <v>24</v>
       </c>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8" t="s">
+      <c r="B25" s="6"/>
+      <c r="C25" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8" t="s">
+      <c r="D25" s="6"/>
+      <c r="E25" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F25" s="10" t="s">
+      <c r="F25" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="G25" s="8" t="s">
+      <c r="G25" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="H25" s="8" t="s">
+      <c r="H25" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="I25" s="8" cm="1">
+      <c r="I25" s="6" cm="1">
         <f t="array" ref="I25">_xlfn.SWITCH(H25,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J25" s="8" t="s">
+      <c r="J25" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="K25" s="8"/>
-      <c r="L25" s="8"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="6"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="8" t="str" cm="1">
+      <c r="A26" s="6"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6" t="str" cm="1">
         <f t="array" ref="I26">_xlfn.SWITCH(H26,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J26" s="8"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="8"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="8"/>
-      <c r="I27" s="8" t="str" cm="1">
+      <c r="A27" s="6"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6" t="str" cm="1">
         <f t="array" ref="I27">_xlfn.SWITCH(H27,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J27" s="8"/>
-      <c r="K27" s="8"/>
-      <c r="L27" s="8"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="6"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="8"/>
-      <c r="I28" s="8" t="str" cm="1">
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="6" t="str" cm="1">
         <f t="array" ref="I28">_xlfn.SWITCH(H28,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J28" s="8"/>
-      <c r="K28" s="8"/>
-      <c r="L28" s="8"/>
+      <c r="J28" s="6"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="6"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8" t="str" cm="1">
+      <c r="A29" s="6"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6" t="str" cm="1">
         <f t="array" ref="I29">_xlfn.SWITCH(H29,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J29" s="8"/>
-      <c r="K29" s="8"/>
-      <c r="L29" s="8"/>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="6"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="8"/>
-      <c r="I30" s="8" t="str" cm="1">
+      <c r="A30" s="6"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6" t="str" cm="1">
         <f t="array" ref="I30">_xlfn.SWITCH(H30,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J30" s="8"/>
-      <c r="K30" s="8"/>
-      <c r="L30" s="8"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
+      <c r="L30" s="6"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
-      <c r="I31" s="8" t="str" cm="1">
+      <c r="A31" s="6"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6" t="str" cm="1">
         <f t="array" ref="I31">_xlfn.SWITCH(H31,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J31" s="8"/>
-      <c r="K31" s="8"/>
-      <c r="L31" s="8"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" s="8"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="8"/>
-      <c r="I32" s="8" t="str" cm="1">
+      <c r="A32" s="6"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6" t="str" cm="1">
         <f t="array" ref="I32">_xlfn.SWITCH(H32,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J32" s="8"/>
-      <c r="K32" s="8"/>
-      <c r="L32" s="8"/>
+      <c r="J32" s="6"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="6"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A33" s="8"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="8"/>
-      <c r="I33" s="8" t="str" cm="1">
+      <c r="A33" s="6"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6" t="str" cm="1">
         <f t="array" ref="I33">_xlfn.SWITCH(H33,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J33" s="8"/>
-      <c r="K33" s="8"/>
-      <c r="L33" s="8"/>
+      <c r="J33" s="6"/>
+      <c r="K33" s="6"/>
+      <c r="L33" s="6"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34" s="8"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="8"/>
-      <c r="H34" s="8"/>
-      <c r="I34" s="8" t="str" cm="1">
+      <c r="A34" s="6"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6" t="str" cm="1">
         <f t="array" ref="I34">_xlfn.SWITCH(H34,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J34" s="8"/>
-      <c r="K34" s="8"/>
-      <c r="L34" s="8"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="6"/>
+      <c r="L34" s="6"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A35" s="8"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="8"/>
-      <c r="H35" s="8"/>
-      <c r="I35" s="8" t="str" cm="1">
+      <c r="A35" s="6"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="6" t="str" cm="1">
         <f t="array" ref="I35">_xlfn.SWITCH(H35,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J35" s="8"/>
-      <c r="K35" s="8"/>
-      <c r="L35" s="8"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="6"/>
+      <c r="L35" s="6"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" s="8"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="8"/>
-      <c r="H36" s="8"/>
-      <c r="I36" s="8" t="str" cm="1">
+      <c r="A36" s="6"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6" t="str" cm="1">
         <f t="array" ref="I36">_xlfn.SWITCH(H36,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J36" s="8"/>
-      <c r="K36" s="8"/>
-      <c r="L36" s="8"/>
+      <c r="J36" s="6"/>
+      <c r="K36" s="6"/>
+      <c r="L36" s="6"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A37" s="8"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="8"/>
-      <c r="H37" s="8"/>
-      <c r="I37" s="8" t="str" cm="1">
+      <c r="A37" s="6"/>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6" t="str" cm="1">
         <f t="array" ref="I37">_xlfn.SWITCH(H37,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J37" s="8"/>
-      <c r="K37" s="8"/>
-      <c r="L37" s="8"/>
+      <c r="J37" s="6"/>
+      <c r="K37" s="6"/>
+      <c r="L37" s="6"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A38" s="8"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="8"/>
-      <c r="H38" s="8"/>
-      <c r="I38" s="8" t="str" cm="1">
+      <c r="A38" s="6"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6" t="str" cm="1">
         <f t="array" ref="I38">_xlfn.SWITCH(H38,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J38" s="8"/>
-      <c r="K38" s="8"/>
-      <c r="L38" s="8"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="6"/>
+      <c r="L38" s="6"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A39" s="8"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="8"/>
-      <c r="H39" s="8"/>
-      <c r="I39" s="8" t="str" cm="1">
+      <c r="A39" s="6"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6" t="str" cm="1">
         <f t="array" ref="I39">_xlfn.SWITCH(H39,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J39" s="8"/>
-      <c r="K39" s="8"/>
-      <c r="L39" s="8"/>
+      <c r="J39" s="6"/>
+      <c r="K39" s="6"/>
+      <c r="L39" s="6"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A40" s="8"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="8"/>
-      <c r="H40" s="8"/>
-      <c r="I40" s="8" t="str" cm="1">
+      <c r="A40" s="6"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="6" t="str" cm="1">
         <f t="array" ref="I40">_xlfn.SWITCH(H40,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J40" s="8"/>
-      <c r="K40" s="8"/>
-      <c r="L40" s="8"/>
+      <c r="J40" s="6"/>
+      <c r="K40" s="6"/>
+      <c r="L40" s="6"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A41" s="8"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="8"/>
-      <c r="H41" s="8"/>
-      <c r="I41" s="8" t="str" cm="1">
+      <c r="A41" s="6"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="6"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="6" t="str" cm="1">
         <f t="array" ref="I41">_xlfn.SWITCH(H41,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J41" s="8"/>
-      <c r="K41" s="8"/>
-      <c r="L41" s="8"/>
+      <c r="J41" s="6"/>
+      <c r="K41" s="6"/>
+      <c r="L41" s="6"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A42" s="8"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="8"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="8"/>
-      <c r="H42" s="8"/>
-      <c r="I42" s="8" t="str" cm="1">
+      <c r="A42" s="6"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="7"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6" t="str" cm="1">
         <f t="array" ref="I42">_xlfn.SWITCH(H42,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J42" s="8"/>
-      <c r="K42" s="8"/>
-      <c r="L42" s="8"/>
+      <c r="J42" s="6"/>
+      <c r="K42" s="6"/>
+      <c r="L42" s="6"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43" s="8"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="8"/>
-      <c r="H43" s="8"/>
-      <c r="I43" s="8" t="str" cm="1">
+      <c r="A43" s="6"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="7"/>
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="6" t="str" cm="1">
         <f t="array" ref="I43">_xlfn.SWITCH(H43,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J43" s="8"/>
-      <c r="K43" s="8"/>
-      <c r="L43" s="8"/>
+      <c r="J43" s="6"/>
+      <c r="K43" s="6"/>
+      <c r="L43" s="6"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A44" s="8"/>
-      <c r="B44" s="8"/>
-      <c r="C44" s="8"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="8"/>
-      <c r="H44" s="8"/>
-      <c r="I44" s="8" t="str" cm="1">
+      <c r="A44" s="6"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="7"/>
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="6" t="str" cm="1">
         <f t="array" ref="I44">_xlfn.SWITCH(H44,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J44" s="8"/>
-      <c r="K44" s="8"/>
-      <c r="L44" s="8"/>
+      <c r="J44" s="6"/>
+      <c r="K44" s="6"/>
+      <c r="L44" s="6"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A45" s="8"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="8"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="8"/>
-      <c r="H45" s="8"/>
-      <c r="I45" s="8" t="str" cm="1">
+      <c r="A45" s="6"/>
+      <c r="B45" s="6"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="6"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="6" t="str" cm="1">
         <f t="array" ref="I45">_xlfn.SWITCH(H45,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J45" s="8"/>
-      <c r="K45" s="8"/>
-      <c r="L45" s="8"/>
+      <c r="J45" s="6"/>
+      <c r="K45" s="6"/>
+      <c r="L45" s="6"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A46" s="8"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="8"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="8"/>
-      <c r="H46" s="8"/>
-      <c r="I46" s="8" t="str" cm="1">
+      <c r="A46" s="6"/>
+      <c r="B46" s="6"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="7"/>
+      <c r="G46" s="6"/>
+      <c r="H46" s="6"/>
+      <c r="I46" s="6" t="str" cm="1">
         <f t="array" ref="I46">_xlfn.SWITCH(H46,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J46" s="8"/>
-      <c r="K46" s="8"/>
-      <c r="L46" s="8"/>
+      <c r="J46" s="6"/>
+      <c r="K46" s="6"/>
+      <c r="L46" s="6"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A47" s="8"/>
-      <c r="B47" s="8"/>
-      <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="8"/>
-      <c r="H47" s="8"/>
-      <c r="I47" s="8" t="str" cm="1">
+      <c r="A47" s="6"/>
+      <c r="B47" s="6"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="7"/>
+      <c r="G47" s="6"/>
+      <c r="H47" s="6"/>
+      <c r="I47" s="6" t="str" cm="1">
         <f t="array" ref="I47">_xlfn.SWITCH(H47,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J47" s="8"/>
-      <c r="K47" s="8"/>
-      <c r="L47" s="8"/>
+      <c r="J47" s="6"/>
+      <c r="K47" s="6"/>
+      <c r="L47" s="6"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A48" s="8"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="8"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="8"/>
-      <c r="H48" s="8"/>
-      <c r="I48" s="8" t="str" cm="1">
+      <c r="A48" s="6"/>
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="7"/>
+      <c r="G48" s="6"/>
+      <c r="H48" s="6"/>
+      <c r="I48" s="6" t="str" cm="1">
         <f t="array" ref="I48">_xlfn.SWITCH(H48,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J48" s="8"/>
-      <c r="K48" s="8"/>
-      <c r="L48" s="8"/>
+      <c r="J48" s="6"/>
+      <c r="K48" s="6"/>
+      <c r="L48" s="6"/>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A49" s="8"/>
-      <c r="B49" s="8"/>
-      <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="8"/>
-      <c r="H49" s="8"/>
-      <c r="I49" s="8" t="str" cm="1">
+      <c r="A49" s="6"/>
+      <c r="B49" s="6"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="7"/>
+      <c r="G49" s="6"/>
+      <c r="H49" s="6"/>
+      <c r="I49" s="6" t="str" cm="1">
         <f t="array" ref="I49">_xlfn.SWITCH(H49,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J49" s="8"/>
-      <c r="K49" s="8"/>
-      <c r="L49" s="8"/>
+      <c r="J49" s="6"/>
+      <c r="K49" s="6"/>
+      <c r="L49" s="6"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A50" s="8"/>
-      <c r="B50" s="8"/>
-      <c r="C50" s="8"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="8"/>
-      <c r="H50" s="8"/>
-      <c r="I50" s="8" t="str" cm="1">
+      <c r="A50" s="6"/>
+      <c r="B50" s="6"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="7"/>
+      <c r="G50" s="6"/>
+      <c r="H50" s="6"/>
+      <c r="I50" s="6" t="str" cm="1">
         <f t="array" ref="I50">_xlfn.SWITCH(H50,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J50" s="8"/>
-      <c r="K50" s="8"/>
-      <c r="L50" s="8"/>
+      <c r="J50" s="6"/>
+      <c r="K50" s="6"/>
+      <c r="L50" s="6"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A51" s="8"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="8"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="10"/>
-      <c r="G51" s="8"/>
-      <c r="H51" s="8"/>
-      <c r="I51" s="8" t="str" cm="1">
+      <c r="A51" s="6"/>
+      <c r="B51" s="6"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="8"/>
+      <c r="G51" s="6"/>
+      <c r="H51" s="6"/>
+      <c r="I51" s="6" t="str" cm="1">
         <f t="array" ref="I51">_xlfn.SWITCH(H51,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J51" s="8"/>
-      <c r="K51" s="8"/>
-      <c r="L51" s="8"/>
+      <c r="J51" s="6"/>
+      <c r="K51" s="6"/>
+      <c r="L51" s="6"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A52" s="8"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="8"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="10"/>
-      <c r="G52" s="8"/>
-      <c r="H52" s="8"/>
-      <c r="I52" s="8" t="str" cm="1">
+      <c r="A52" s="6"/>
+      <c r="B52" s="6"/>
+      <c r="C52" s="6"/>
+      <c r="D52" s="6"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="8"/>
+      <c r="G52" s="6"/>
+      <c r="H52" s="6"/>
+      <c r="I52" s="6" t="str" cm="1">
         <f t="array" ref="I52">_xlfn.SWITCH(H52,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J52" s="8"/>
-      <c r="K52" s="8"/>
-      <c r="L52" s="8"/>
+      <c r="J52" s="6"/>
+      <c r="K52" s="6"/>
+      <c r="L52" s="6"/>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A53" s="8"/>
-      <c r="B53" s="8"/>
-      <c r="C53" s="8"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="10"/>
-      <c r="G53" s="8"/>
-      <c r="H53" s="8"/>
-      <c r="I53" s="8" t="str" cm="1">
+      <c r="A53" s="6"/>
+      <c r="B53" s="6"/>
+      <c r="C53" s="6"/>
+      <c r="D53" s="6"/>
+      <c r="E53" s="6"/>
+      <c r="F53" s="8"/>
+      <c r="G53" s="6"/>
+      <c r="H53" s="6"/>
+      <c r="I53" s="6" t="str" cm="1">
         <f t="array" ref="I53">_xlfn.SWITCH(H53,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J53" s="8"/>
-      <c r="K53" s="8"/>
-      <c r="L53" s="8"/>
+      <c r="J53" s="6"/>
+      <c r="K53" s="6"/>
+      <c r="L53" s="6"/>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A54" s="8"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="8"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="10"/>
-      <c r="G54" s="8"/>
-      <c r="H54" s="8"/>
-      <c r="I54" s="8" t="str" cm="1">
+      <c r="A54" s="6"/>
+      <c r="B54" s="6"/>
+      <c r="C54" s="6"/>
+      <c r="D54" s="6"/>
+      <c r="E54" s="6"/>
+      <c r="F54" s="8"/>
+      <c r="G54" s="6"/>
+      <c r="H54" s="6"/>
+      <c r="I54" s="6" t="str" cm="1">
         <f t="array" ref="I54">_xlfn.SWITCH(H54,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J54" s="8"/>
-      <c r="K54" s="8"/>
-      <c r="L54" s="8"/>
+      <c r="J54" s="6"/>
+      <c r="K54" s="6"/>
+      <c r="L54" s="6"/>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A55" s="8"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="8"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="10"/>
-      <c r="G55" s="8"/>
-      <c r="H55" s="8"/>
-      <c r="I55" s="8" t="str" cm="1">
+      <c r="A55" s="6"/>
+      <c r="B55" s="6"/>
+      <c r="C55" s="6"/>
+      <c r="D55" s="6"/>
+      <c r="E55" s="6"/>
+      <c r="F55" s="8"/>
+      <c r="G55" s="6"/>
+      <c r="H55" s="6"/>
+      <c r="I55" s="6" t="str" cm="1">
         <f t="array" ref="I55">_xlfn.SWITCH(H55,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J55" s="8"/>
-      <c r="K55" s="8"/>
-      <c r="L55" s="8"/>
+      <c r="J55" s="6"/>
+      <c r="K55" s="6"/>
+      <c r="L55" s="6"/>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A56" s="8"/>
-      <c r="B56" s="8"/>
-      <c r="C56" s="8"/>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="10"/>
-      <c r="G56" s="8"/>
-      <c r="H56" s="8"/>
-      <c r="I56" s="8" t="str" cm="1">
+      <c r="A56" s="6"/>
+      <c r="B56" s="6"/>
+      <c r="C56" s="6"/>
+      <c r="D56" s="6"/>
+      <c r="E56" s="6"/>
+      <c r="F56" s="8"/>
+      <c r="G56" s="6"/>
+      <c r="H56" s="6"/>
+      <c r="I56" s="6" t="str" cm="1">
         <f t="array" ref="I56">_xlfn.SWITCH(H56,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J56" s="8"/>
-      <c r="K56" s="8"/>
-      <c r="L56" s="8"/>
+      <c r="J56" s="6"/>
+      <c r="K56" s="6"/>
+      <c r="L56" s="6"/>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A57" s="8"/>
-      <c r="B57" s="8"/>
-      <c r="C57" s="8"/>
-      <c r="D57" s="8"/>
-      <c r="E57" s="8"/>
-      <c r="F57" s="9"/>
-      <c r="G57" s="8"/>
-      <c r="H57" s="8"/>
-      <c r="I57" s="8" t="str" cm="1">
+      <c r="A57" s="6"/>
+      <c r="B57" s="6"/>
+      <c r="C57" s="6"/>
+      <c r="D57" s="6"/>
+      <c r="E57" s="6"/>
+      <c r="F57" s="7"/>
+      <c r="G57" s="6"/>
+      <c r="H57" s="6"/>
+      <c r="I57" s="6" t="str" cm="1">
         <f t="array" ref="I57">_xlfn.SWITCH(H57,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J57" s="8"/>
-      <c r="K57" s="8"/>
-      <c r="L57" s="8"/>
+      <c r="J57" s="6"/>
+      <c r="K57" s="6"/>
+      <c r="L57" s="6"/>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A58" s="8"/>
-      <c r="B58" s="8"/>
-      <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="9"/>
-      <c r="G58" s="8"/>
-      <c r="H58" s="8"/>
-      <c r="I58" s="8" t="str" cm="1">
+      <c r="A58" s="6"/>
+      <c r="B58" s="6"/>
+      <c r="C58" s="6"/>
+      <c r="D58" s="6"/>
+      <c r="E58" s="6"/>
+      <c r="F58" s="7"/>
+      <c r="G58" s="6"/>
+      <c r="H58" s="6"/>
+      <c r="I58" s="6" t="str" cm="1">
         <f t="array" ref="I58">_xlfn.SWITCH(H58,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J58" s="8"/>
-      <c r="K58" s="8"/>
-      <c r="L58" s="8"/>
+      <c r="J58" s="6"/>
+      <c r="K58" s="6"/>
+      <c r="L58" s="6"/>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A59" s="8"/>
-      <c r="B59" s="8"/>
-      <c r="C59" s="8"/>
-      <c r="D59" s="8"/>
-      <c r="E59" s="8"/>
-      <c r="F59" s="9"/>
-      <c r="G59" s="8"/>
-      <c r="H59" s="8"/>
-      <c r="I59" s="8" t="str" cm="1">
+      <c r="A59" s="6"/>
+      <c r="B59" s="6"/>
+      <c r="C59" s="6"/>
+      <c r="D59" s="6"/>
+      <c r="E59" s="6"/>
+      <c r="F59" s="7"/>
+      <c r="G59" s="6"/>
+      <c r="H59" s="6"/>
+      <c r="I59" s="6" t="str" cm="1">
         <f t="array" ref="I59">_xlfn.SWITCH(H59,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J59" s="8"/>
-      <c r="K59" s="8"/>
-      <c r="L59" s="8"/>
+      <c r="J59" s="6"/>
+      <c r="K59" s="6"/>
+      <c r="L59" s="6"/>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A60" s="8"/>
-      <c r="B60" s="8"/>
-      <c r="C60" s="8"/>
-      <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
-      <c r="F60" s="9"/>
-      <c r="G60" s="8"/>
-      <c r="H60" s="8"/>
-      <c r="I60" s="8" t="str" cm="1">
+      <c r="A60" s="6"/>
+      <c r="B60" s="6"/>
+      <c r="C60" s="6"/>
+      <c r="D60" s="6"/>
+      <c r="E60" s="6"/>
+      <c r="F60" s="7"/>
+      <c r="G60" s="6"/>
+      <c r="H60" s="6"/>
+      <c r="I60" s="6" t="str" cm="1">
         <f t="array" ref="I60">_xlfn.SWITCH(H60,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J60" s="8"/>
-      <c r="K60" s="8"/>
-      <c r="L60" s="8"/>
+      <c r="J60" s="6"/>
+      <c r="K60" s="6"/>
+      <c r="L60" s="6"/>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A61" s="8"/>
-      <c r="B61" s="8"/>
-      <c r="C61" s="8"/>
-      <c r="D61" s="8"/>
-      <c r="E61" s="8"/>
-      <c r="F61" s="9"/>
-      <c r="G61" s="8"/>
-      <c r="H61" s="8"/>
-      <c r="I61" s="8" t="str" cm="1">
+      <c r="A61" s="6"/>
+      <c r="B61" s="6"/>
+      <c r="C61" s="6"/>
+      <c r="D61" s="6"/>
+      <c r="E61" s="6"/>
+      <c r="F61" s="7"/>
+      <c r="G61" s="6"/>
+      <c r="H61" s="6"/>
+      <c r="I61" s="6" t="str" cm="1">
         <f t="array" ref="I61">_xlfn.SWITCH(H61,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J61" s="8"/>
-      <c r="K61" s="8"/>
-      <c r="L61" s="8"/>
+      <c r="J61" s="6"/>
+      <c r="K61" s="6"/>
+      <c r="L61" s="6"/>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A62" s="8"/>
-      <c r="B62" s="8"/>
-      <c r="C62" s="8"/>
-      <c r="D62" s="8"/>
-      <c r="E62" s="8"/>
-      <c r="F62" s="9"/>
-      <c r="G62" s="8"/>
-      <c r="H62" s="8"/>
-      <c r="I62" s="8" t="str" cm="1">
+      <c r="A62" s="6"/>
+      <c r="B62" s="6"/>
+      <c r="C62" s="6"/>
+      <c r="D62" s="6"/>
+      <c r="E62" s="6"/>
+      <c r="F62" s="7"/>
+      <c r="G62" s="6"/>
+      <c r="H62" s="6"/>
+      <c r="I62" s="6" t="str" cm="1">
         <f t="array" ref="I62">_xlfn.SWITCH(H62,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J62" s="8"/>
-      <c r="K62" s="8"/>
-      <c r="L62" s="8"/>
+      <c r="J62" s="6"/>
+      <c r="K62" s="6"/>
+      <c r="L62" s="6"/>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A63" s="8"/>
-      <c r="B63" s="8"/>
-      <c r="C63" s="8"/>
-      <c r="D63" s="8"/>
-      <c r="E63" s="8"/>
-      <c r="F63" s="9"/>
-      <c r="G63" s="8"/>
-      <c r="H63" s="8"/>
-      <c r="I63" s="8" t="str" cm="1">
+      <c r="A63" s="6"/>
+      <c r="B63" s="6"/>
+      <c r="C63" s="6"/>
+      <c r="D63" s="6"/>
+      <c r="E63" s="6"/>
+      <c r="F63" s="7"/>
+      <c r="G63" s="6"/>
+      <c r="H63" s="6"/>
+      <c r="I63" s="6" t="str" cm="1">
         <f t="array" ref="I63">_xlfn.SWITCH(H63,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J63" s="8"/>
-      <c r="K63" s="8"/>
-      <c r="L63" s="8"/>
+      <c r="J63" s="6"/>
+      <c r="K63" s="6"/>
+      <c r="L63" s="6"/>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A64" s="8"/>
-      <c r="B64" s="8"/>
-      <c r="C64" s="8"/>
-      <c r="D64" s="8"/>
-      <c r="E64" s="8"/>
-      <c r="F64" s="9"/>
-      <c r="G64" s="8"/>
-      <c r="H64" s="8"/>
-      <c r="I64" s="8" t="str" cm="1">
+      <c r="A64" s="6"/>
+      <c r="B64" s="6"/>
+      <c r="C64" s="6"/>
+      <c r="D64" s="6"/>
+      <c r="E64" s="6"/>
+      <c r="F64" s="7"/>
+      <c r="G64" s="6"/>
+      <c r="H64" s="6"/>
+      <c r="I64" s="6" t="str" cm="1">
         <f t="array" ref="I64">_xlfn.SWITCH(H64,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J64" s="8"/>
-      <c r="K64" s="8"/>
-      <c r="L64" s="8"/>
+      <c r="J64" s="6"/>
+      <c r="K64" s="6"/>
+      <c r="L64" s="6"/>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A65" s="8"/>
-      <c r="B65" s="8"/>
-      <c r="C65" s="8"/>
-      <c r="D65" s="8"/>
-      <c r="E65" s="8"/>
-      <c r="F65" s="9"/>
-      <c r="G65" s="8"/>
-      <c r="H65" s="8"/>
-      <c r="I65" s="8" t="str" cm="1">
+      <c r="A65" s="6"/>
+      <c r="B65" s="6"/>
+      <c r="C65" s="6"/>
+      <c r="D65" s="6"/>
+      <c r="E65" s="6"/>
+      <c r="F65" s="7"/>
+      <c r="G65" s="6"/>
+      <c r="H65" s="6"/>
+      <c r="I65" s="6" t="str" cm="1">
         <f t="array" ref="I65">_xlfn.SWITCH(H65,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J65" s="8"/>
-      <c r="K65" s="8"/>
-      <c r="L65" s="8"/>
+      <c r="J65" s="6"/>
+      <c r="K65" s="6"/>
+      <c r="L65" s="6"/>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A66" s="8"/>
-      <c r="B66" s="8"/>
-      <c r="C66" s="8"/>
-      <c r="D66" s="8"/>
-      <c r="E66" s="8"/>
-      <c r="F66" s="9"/>
-      <c r="G66" s="8"/>
-      <c r="H66" s="8"/>
-      <c r="I66" s="8" t="str" cm="1">
+      <c r="A66" s="6"/>
+      <c r="B66" s="6"/>
+      <c r="C66" s="6"/>
+      <c r="D66" s="6"/>
+      <c r="E66" s="6"/>
+      <c r="F66" s="7"/>
+      <c r="G66" s="6"/>
+      <c r="H66" s="6"/>
+      <c r="I66" s="6" t="str" cm="1">
         <f t="array" ref="I66">_xlfn.SWITCH(H66,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J66" s="8"/>
-      <c r="K66" s="8"/>
-      <c r="L66" s="8"/>
+      <c r="J66" s="6"/>
+      <c r="K66" s="6"/>
+      <c r="L66" s="6"/>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A67" s="8"/>
-      <c r="B67" s="8"/>
-      <c r="C67" s="8"/>
-      <c r="D67" s="8"/>
-      <c r="E67" s="8"/>
-      <c r="F67" s="9"/>
-      <c r="G67" s="8"/>
-      <c r="H67" s="8"/>
-      <c r="I67" s="8" t="str" cm="1">
+      <c r="A67" s="6"/>
+      <c r="B67" s="6"/>
+      <c r="C67" s="6"/>
+      <c r="D67" s="6"/>
+      <c r="E67" s="6"/>
+      <c r="F67" s="7"/>
+      <c r="G67" s="6"/>
+      <c r="H67" s="6"/>
+      <c r="I67" s="6" t="str" cm="1">
         <f t="array" ref="I67">_xlfn.SWITCH(H67,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J67" s="8"/>
-      <c r="K67" s="8"/>
-      <c r="L67" s="8"/>
+      <c r="J67" s="6"/>
+      <c r="K67" s="6"/>
+      <c r="L67" s="6"/>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A68" s="8"/>
-      <c r="B68" s="8"/>
-      <c r="C68" s="8"/>
-      <c r="D68" s="8"/>
-      <c r="E68" s="8"/>
-      <c r="F68" s="7"/>
-      <c r="G68" s="8"/>
-      <c r="H68" s="8"/>
-      <c r="I68" s="8" t="str" cm="1">
+      <c r="A68" s="6"/>
+      <c r="B68" s="6"/>
+      <c r="C68" s="6"/>
+      <c r="D68" s="6"/>
+      <c r="E68" s="6"/>
+      <c r="F68" s="5"/>
+      <c r="G68" s="6"/>
+      <c r="H68" s="6"/>
+      <c r="I68" s="6" t="str" cm="1">
         <f t="array" ref="I68">_xlfn.SWITCH(H68,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J68" s="8"/>
-      <c r="K68" s="8"/>
-      <c r="L68" s="8"/>
+      <c r="J68" s="6"/>
+      <c r="K68" s="6"/>
+      <c r="L68" s="6"/>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A69" s="8"/>
-      <c r="B69" s="8"/>
-      <c r="C69" s="8"/>
-      <c r="D69" s="8"/>
-      <c r="E69" s="8"/>
-      <c r="F69" s="9"/>
-      <c r="G69" s="8"/>
-      <c r="H69" s="8"/>
-      <c r="I69" s="8" t="str" cm="1">
+      <c r="A69" s="6"/>
+      <c r="B69" s="6"/>
+      <c r="C69" s="6"/>
+      <c r="D69" s="6"/>
+      <c r="E69" s="6"/>
+      <c r="F69" s="7"/>
+      <c r="G69" s="6"/>
+      <c r="H69" s="6"/>
+      <c r="I69" s="6" t="str" cm="1">
         <f t="array" ref="I69">_xlfn.SWITCH(H69,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J69" s="8"/>
-      <c r="K69" s="8"/>
-      <c r="L69" s="8"/>
+      <c r="J69" s="6"/>
+      <c r="K69" s="6"/>
+      <c r="L69" s="6"/>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A70" s="8"/>
-      <c r="B70" s="8"/>
-      <c r="C70" s="8"/>
-      <c r="D70" s="8"/>
-      <c r="E70" s="8"/>
-      <c r="F70" s="7"/>
-      <c r="G70" s="8"/>
-      <c r="H70" s="8"/>
-      <c r="I70" s="8" t="str" cm="1">
+      <c r="A70" s="6"/>
+      <c r="B70" s="6"/>
+      <c r="C70" s="6"/>
+      <c r="D70" s="6"/>
+      <c r="E70" s="6"/>
+      <c r="F70" s="5"/>
+      <c r="G70" s="6"/>
+      <c r="H70" s="6"/>
+      <c r="I70" s="6" t="str" cm="1">
         <f t="array" ref="I70">_xlfn.SWITCH(H70,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J70" s="8"/>
-      <c r="K70" s="8"/>
-      <c r="L70" s="8"/>
+      <c r="J70" s="6"/>
+      <c r="K70" s="6"/>
+      <c r="L70" s="6"/>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A71" s="8"/>
-      <c r="B71" s="8"/>
-      <c r="C71" s="8"/>
-      <c r="D71" s="8"/>
-      <c r="E71" s="8"/>
-      <c r="F71" s="7"/>
-      <c r="G71" s="8"/>
-      <c r="H71" s="8"/>
-      <c r="I71" s="8" t="str" cm="1">
+      <c r="A71" s="6"/>
+      <c r="B71" s="6"/>
+      <c r="C71" s="6"/>
+      <c r="D71" s="6"/>
+      <c r="E71" s="6"/>
+      <c r="F71" s="5"/>
+      <c r="G71" s="6"/>
+      <c r="H71" s="6"/>
+      <c r="I71" s="6" t="str" cm="1">
         <f t="array" ref="I71">_xlfn.SWITCH(H71,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J71" s="8"/>
-      <c r="K71" s="8"/>
-      <c r="L71" s="8"/>
+      <c r="J71" s="6"/>
+      <c r="K71" s="6"/>
+      <c r="L71" s="6"/>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A72" s="8"/>
-      <c r="B72" s="8"/>
-      <c r="C72" s="8"/>
-      <c r="D72" s="8"/>
-      <c r="E72" s="8"/>
-      <c r="F72" s="9"/>
-      <c r="G72" s="8"/>
-      <c r="H72" s="8"/>
-      <c r="I72" s="8" t="str" cm="1">
+      <c r="A72" s="6"/>
+      <c r="B72" s="6"/>
+      <c r="C72" s="6"/>
+      <c r="D72" s="6"/>
+      <c r="E72" s="6"/>
+      <c r="F72" s="7"/>
+      <c r="G72" s="6"/>
+      <c r="H72" s="6"/>
+      <c r="I72" s="6" t="str" cm="1">
         <f t="array" ref="I72">_xlfn.SWITCH(H72,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J72" s="8"/>
-      <c r="K72" s="8"/>
-      <c r="L72" s="8"/>
+      <c r="J72" s="6"/>
+      <c r="K72" s="6"/>
+      <c r="L72" s="6"/>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A73" s="8"/>
-      <c r="B73" s="8"/>
-      <c r="C73" s="8"/>
-      <c r="D73" s="8"/>
-      <c r="E73" s="8"/>
-      <c r="F73" s="9"/>
-      <c r="G73" s="8"/>
-      <c r="H73" s="8"/>
-      <c r="I73" s="8" t="str" cm="1">
+      <c r="A73" s="6"/>
+      <c r="B73" s="6"/>
+      <c r="C73" s="6"/>
+      <c r="D73" s="6"/>
+      <c r="E73" s="6"/>
+      <c r="F73" s="7"/>
+      <c r="G73" s="6"/>
+      <c r="H73" s="6"/>
+      <c r="I73" s="6" t="str" cm="1">
         <f t="array" ref="I73">_xlfn.SWITCH(H73,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J73" s="8"/>
-      <c r="K73" s="8"/>
-      <c r="L73" s="8"/>
+      <c r="J73" s="6"/>
+      <c r="K73" s="6"/>
+      <c r="L73" s="6"/>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A74" s="8"/>
-      <c r="B74" s="8"/>
-      <c r="C74" s="8"/>
-      <c r="D74" s="8"/>
-      <c r="E74" s="8"/>
-      <c r="F74" s="9"/>
-      <c r="G74" s="8"/>
-      <c r="H74" s="8"/>
-      <c r="I74" s="8" t="str" cm="1">
+      <c r="A74" s="6"/>
+      <c r="B74" s="6"/>
+      <c r="C74" s="6"/>
+      <c r="D74" s="6"/>
+      <c r="E74" s="6"/>
+      <c r="F74" s="7"/>
+      <c r="G74" s="6"/>
+      <c r="H74" s="6"/>
+      <c r="I74" s="6" t="str" cm="1">
         <f t="array" ref="I74">_xlfn.SWITCH(H74,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J74" s="8"/>
-      <c r="K74" s="8"/>
-      <c r="L74" s="8"/>
+      <c r="J74" s="6"/>
+      <c r="K74" s="6"/>
+      <c r="L74" s="6"/>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A75" s="8"/>
-      <c r="B75" s="8"/>
-      <c r="C75" s="8"/>
-      <c r="D75" s="8"/>
-      <c r="E75" s="8"/>
-      <c r="F75" s="9"/>
-      <c r="G75" s="8"/>
-      <c r="H75" s="8"/>
-      <c r="I75" s="8" t="str" cm="1">
+      <c r="A75" s="6"/>
+      <c r="B75" s="6"/>
+      <c r="C75" s="6"/>
+      <c r="D75" s="6"/>
+      <c r="E75" s="6"/>
+      <c r="F75" s="7"/>
+      <c r="G75" s="6"/>
+      <c r="H75" s="6"/>
+      <c r="I75" s="6" t="str" cm="1">
         <f t="array" ref="I75">_xlfn.SWITCH(H75,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J75" s="8"/>
-      <c r="K75" s="8"/>
-      <c r="L75" s="8"/>
+      <c r="J75" s="6"/>
+      <c r="K75" s="6"/>
+      <c r="L75" s="6"/>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A76" s="8"/>
-      <c r="B76" s="8"/>
-      <c r="C76" s="8"/>
-      <c r="D76" s="8"/>
-      <c r="E76" s="8"/>
-      <c r="F76" s="9"/>
-      <c r="G76" s="8"/>
-      <c r="H76" s="8"/>
-      <c r="I76" s="8" t="str" cm="1">
+      <c r="A76" s="6"/>
+      <c r="B76" s="6"/>
+      <c r="C76" s="6"/>
+      <c r="D76" s="6"/>
+      <c r="E76" s="6"/>
+      <c r="F76" s="7"/>
+      <c r="G76" s="6"/>
+      <c r="H76" s="6"/>
+      <c r="I76" s="6" t="str" cm="1">
         <f t="array" ref="I76">_xlfn.SWITCH(H76,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J76" s="8"/>
-      <c r="K76" s="8"/>
-      <c r="L76" s="8"/>
+      <c r="J76" s="6"/>
+      <c r="K76" s="6"/>
+      <c r="L76" s="6"/>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A77" s="8"/>
-      <c r="B77" s="8"/>
-      <c r="C77" s="8"/>
-      <c r="D77" s="8"/>
-      <c r="E77" s="8"/>
-      <c r="F77" s="10"/>
-      <c r="G77" s="8"/>
-      <c r="H77" s="8"/>
-      <c r="I77" s="8" t="str" cm="1">
+      <c r="A77" s="6"/>
+      <c r="B77" s="6"/>
+      <c r="C77" s="6"/>
+      <c r="D77" s="6"/>
+      <c r="E77" s="6"/>
+      <c r="F77" s="8"/>
+      <c r="G77" s="6"/>
+      <c r="H77" s="6"/>
+      <c r="I77" s="6" t="str" cm="1">
         <f t="array" ref="I77">_xlfn.SWITCH(H77,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J77" s="8"/>
-      <c r="K77" s="8"/>
-      <c r="L77" s="8"/>
+      <c r="J77" s="6"/>
+      <c r="K77" s="6"/>
+      <c r="L77" s="6"/>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A78" s="8"/>
-      <c r="B78" s="8"/>
-      <c r="C78" s="8"/>
-      <c r="D78" s="8"/>
-      <c r="E78" s="8"/>
-      <c r="F78" s="10"/>
-      <c r="G78" s="8"/>
-      <c r="H78" s="8"/>
-      <c r="I78" s="8" t="str" cm="1">
+      <c r="A78" s="6"/>
+      <c r="B78" s="6"/>
+      <c r="C78" s="6"/>
+      <c r="D78" s="6"/>
+      <c r="E78" s="6"/>
+      <c r="F78" s="8"/>
+      <c r="G78" s="6"/>
+      <c r="H78" s="6"/>
+      <c r="I78" s="6" t="str" cm="1">
         <f t="array" ref="I78">_xlfn.SWITCH(H78,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J78" s="8"/>
-      <c r="K78" s="8"/>
-      <c r="L78" s="8"/>
+      <c r="J78" s="6"/>
+      <c r="K78" s="6"/>
+      <c r="L78" s="6"/>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A79" s="8"/>
-      <c r="B79" s="8"/>
-      <c r="C79" s="8"/>
-      <c r="D79" s="8"/>
-      <c r="E79" s="8"/>
-      <c r="F79" s="10"/>
-      <c r="G79" s="8"/>
-      <c r="H79" s="8"/>
-      <c r="I79" s="8" t="str" cm="1">
+      <c r="A79" s="6"/>
+      <c r="B79" s="6"/>
+      <c r="C79" s="6"/>
+      <c r="D79" s="6"/>
+      <c r="E79" s="6"/>
+      <c r="F79" s="8"/>
+      <c r="G79" s="6"/>
+      <c r="H79" s="6"/>
+      <c r="I79" s="6" t="str" cm="1">
         <f t="array" ref="I79">_xlfn.SWITCH(H79,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J79" s="8"/>
-      <c r="K79" s="8"/>
-      <c r="L79" s="8"/>
+      <c r="J79" s="6"/>
+      <c r="K79" s="6"/>
+      <c r="L79" s="6"/>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A80" s="8"/>
-      <c r="B80" s="8"/>
-      <c r="C80" s="8"/>
-      <c r="D80" s="8"/>
-      <c r="E80" s="8"/>
-      <c r="F80" s="10"/>
-      <c r="G80" s="8"/>
-      <c r="H80" s="8"/>
-      <c r="I80" s="8" t="str" cm="1">
+      <c r="A80" s="6"/>
+      <c r="B80" s="6"/>
+      <c r="C80" s="6"/>
+      <c r="D80" s="6"/>
+      <c r="E80" s="6"/>
+      <c r="F80" s="8"/>
+      <c r="G80" s="6"/>
+      <c r="H80" s="6"/>
+      <c r="I80" s="6" t="str" cm="1">
         <f t="array" ref="I80">_xlfn.SWITCH(H80,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J80" s="8"/>
-      <c r="K80" s="8"/>
-      <c r="L80" s="8"/>
+      <c r="J80" s="6"/>
+      <c r="K80" s="6"/>
+      <c r="L80" s="6"/>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A81" s="8"/>
-      <c r="B81" s="8"/>
-      <c r="C81" s="8"/>
-      <c r="D81" s="8"/>
-      <c r="E81" s="8"/>
-      <c r="F81" s="10"/>
-      <c r="G81" s="8"/>
-      <c r="H81" s="8"/>
-      <c r="I81" s="8" t="str" cm="1">
+      <c r="A81" s="6"/>
+      <c r="B81" s="6"/>
+      <c r="C81" s="6"/>
+      <c r="D81" s="6"/>
+      <c r="E81" s="6"/>
+      <c r="F81" s="8"/>
+      <c r="G81" s="6"/>
+      <c r="H81" s="6"/>
+      <c r="I81" s="6" t="str" cm="1">
         <f t="array" ref="I81">_xlfn.SWITCH(H81,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J81" s="8"/>
-      <c r="K81" s="8"/>
-      <c r="L81" s="8"/>
+      <c r="J81" s="6"/>
+      <c r="K81" s="6"/>
+      <c r="L81" s="6"/>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A82" s="8"/>
-      <c r="B82" s="8"/>
-      <c r="C82" s="8"/>
-      <c r="D82" s="8"/>
-      <c r="E82" s="8"/>
-      <c r="F82" s="10"/>
-      <c r="G82" s="8"/>
-      <c r="H82" s="8"/>
-      <c r="I82" s="8" t="str" cm="1">
+      <c r="A82" s="6"/>
+      <c r="B82" s="6"/>
+      <c r="C82" s="6"/>
+      <c r="D82" s="6"/>
+      <c r="E82" s="6"/>
+      <c r="F82" s="8"/>
+      <c r="G82" s="6"/>
+      <c r="H82" s="6"/>
+      <c r="I82" s="6" t="str" cm="1">
         <f t="array" ref="I82">_xlfn.SWITCH(H82,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J82" s="8"/>
-      <c r="K82" s="8"/>
-      <c r="L82" s="8"/>
+      <c r="J82" s="6"/>
+      <c r="K82" s="6"/>
+      <c r="L82" s="6"/>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A83" s="8"/>
-      <c r="B83" s="8"/>
-      <c r="C83" s="8"/>
-      <c r="D83" s="8"/>
-      <c r="E83" s="8"/>
-      <c r="F83" s="10"/>
-      <c r="G83" s="8"/>
-      <c r="H83" s="8"/>
-      <c r="I83" s="8" t="str" cm="1">
+      <c r="A83" s="6"/>
+      <c r="B83" s="6"/>
+      <c r="C83" s="6"/>
+      <c r="D83" s="6"/>
+      <c r="E83" s="6"/>
+      <c r="F83" s="8"/>
+      <c r="G83" s="6"/>
+      <c r="H83" s="6"/>
+      <c r="I83" s="6" t="str" cm="1">
         <f t="array" ref="I83">_xlfn.SWITCH(H83,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J83" s="8"/>
-      <c r="K83" s="8"/>
-      <c r="L83" s="8"/>
+      <c r="J83" s="6"/>
+      <c r="K83" s="6"/>
+      <c r="L83" s="6"/>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A84" s="8"/>
-      <c r="B84" s="8"/>
-      <c r="C84" s="8"/>
-      <c r="D84" s="8"/>
-      <c r="E84" s="8"/>
-      <c r="F84" s="10"/>
-      <c r="G84" s="8"/>
-      <c r="H84" s="8"/>
-      <c r="I84" s="8" t="str" cm="1">
+      <c r="A84" s="6"/>
+      <c r="B84" s="6"/>
+      <c r="C84" s="6"/>
+      <c r="D84" s="6"/>
+      <c r="E84" s="6"/>
+      <c r="F84" s="8"/>
+      <c r="G84" s="6"/>
+      <c r="H84" s="6"/>
+      <c r="I84" s="6" t="str" cm="1">
         <f t="array" ref="I84">_xlfn.SWITCH(H84,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J84" s="8"/>
-      <c r="K84" s="8"/>
-      <c r="L84" s="8"/>
+      <c r="J84" s="6"/>
+      <c r="K84" s="6"/>
+      <c r="L84" s="6"/>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A85" s="8"/>
-      <c r="B85" s="8"/>
-      <c r="C85" s="8"/>
-      <c r="D85" s="8"/>
-      <c r="E85" s="8"/>
-      <c r="F85" s="10"/>
-      <c r="G85" s="8"/>
-      <c r="H85" s="8"/>
-      <c r="I85" s="8" t="str" cm="1">
+      <c r="A85" s="6"/>
+      <c r="B85" s="6"/>
+      <c r="C85" s="6"/>
+      <c r="D85" s="6"/>
+      <c r="E85" s="6"/>
+      <c r="F85" s="8"/>
+      <c r="G85" s="6"/>
+      <c r="H85" s="6"/>
+      <c r="I85" s="6" t="str" cm="1">
         <f t="array" ref="I85">_xlfn.SWITCH(H85,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J85" s="8"/>
-      <c r="K85" s="8"/>
-      <c r="L85" s="8"/>
+      <c r="J85" s="6"/>
+      <c r="K85" s="6"/>
+      <c r="L85" s="6"/>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A86" s="8"/>
-      <c r="B86" s="8"/>
-      <c r="C86" s="8"/>
-      <c r="D86" s="8"/>
-      <c r="E86" s="8"/>
-      <c r="F86" s="10"/>
-      <c r="G86" s="8"/>
-      <c r="H86" s="8"/>
-      <c r="I86" s="8" t="str" cm="1">
+      <c r="A86" s="6"/>
+      <c r="B86" s="6"/>
+      <c r="C86" s="6"/>
+      <c r="D86" s="6"/>
+      <c r="E86" s="6"/>
+      <c r="F86" s="8"/>
+      <c r="G86" s="6"/>
+      <c r="H86" s="6"/>
+      <c r="I86" s="6" t="str" cm="1">
         <f t="array" ref="I86">_xlfn.SWITCH(H86,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J86" s="8"/>
-      <c r="K86" s="8"/>
-      <c r="L86" s="8"/>
+      <c r="J86" s="6"/>
+      <c r="K86" s="6"/>
+      <c r="L86" s="6"/>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A87" s="8"/>
-      <c r="B87" s="8"/>
-      <c r="C87" s="8"/>
-      <c r="D87" s="8"/>
-      <c r="E87" s="8"/>
-      <c r="F87" s="10"/>
-      <c r="G87" s="8"/>
-      <c r="H87" s="8"/>
-      <c r="I87" s="8" t="str" cm="1">
+      <c r="A87" s="6"/>
+      <c r="B87" s="6"/>
+      <c r="C87" s="6"/>
+      <c r="D87" s="6"/>
+      <c r="E87" s="6"/>
+      <c r="F87" s="8"/>
+      <c r="G87" s="6"/>
+      <c r="H87" s="6"/>
+      <c r="I87" s="6" t="str" cm="1">
         <f t="array" ref="I87">_xlfn.SWITCH(H87,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J87" s="8"/>
-      <c r="K87" s="8"/>
-      <c r="L87" s="8"/>
+      <c r="J87" s="6"/>
+      <c r="K87" s="6"/>
+      <c r="L87" s="6"/>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A88" s="8"/>
-      <c r="B88" s="8"/>
-      <c r="C88" s="8"/>
-      <c r="D88" s="8"/>
-      <c r="E88" s="8"/>
-      <c r="F88" s="10"/>
-      <c r="G88" s="8"/>
-      <c r="H88" s="8"/>
-      <c r="I88" s="8" t="str" cm="1">
+      <c r="A88" s="6"/>
+      <c r="B88" s="6"/>
+      <c r="C88" s="6"/>
+      <c r="D88" s="6"/>
+      <c r="E88" s="6"/>
+      <c r="F88" s="8"/>
+      <c r="G88" s="6"/>
+      <c r="H88" s="6"/>
+      <c r="I88" s="6" t="str" cm="1">
         <f t="array" ref="I88">_xlfn.SWITCH(H88,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J88" s="8"/>
-      <c r="K88" s="8"/>
-      <c r="L88" s="8"/>
+      <c r="J88" s="6"/>
+      <c r="K88" s="6"/>
+      <c r="L88" s="6"/>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A89" s="8"/>
-      <c r="B89" s="8"/>
-      <c r="C89" s="8"/>
-      <c r="D89" s="8"/>
-      <c r="E89" s="8"/>
-      <c r="F89" s="10"/>
-      <c r="G89" s="8"/>
-      <c r="H89" s="8"/>
-      <c r="I89" s="8" t="str" cm="1">
+      <c r="A89" s="6"/>
+      <c r="B89" s="6"/>
+      <c r="C89" s="6"/>
+      <c r="D89" s="6"/>
+      <c r="E89" s="6"/>
+      <c r="F89" s="8"/>
+      <c r="G89" s="6"/>
+      <c r="H89" s="6"/>
+      <c r="I89" s="6" t="str" cm="1">
         <f t="array" ref="I89">_xlfn.SWITCH(H89,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J89" s="8"/>
-      <c r="K89" s="8"/>
-      <c r="L89" s="8"/>
+      <c r="J89" s="6"/>
+      <c r="K89" s="6"/>
+      <c r="L89" s="6"/>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A90" s="8"/>
-      <c r="B90" s="8"/>
-      <c r="C90" s="8"/>
-      <c r="D90" s="8"/>
-      <c r="E90" s="8"/>
-      <c r="F90" s="10"/>
-      <c r="G90" s="8"/>
-      <c r="H90" s="8"/>
-      <c r="I90" s="8" t="str" cm="1">
+      <c r="A90" s="6"/>
+      <c r="B90" s="6"/>
+      <c r="C90" s="6"/>
+      <c r="D90" s="6"/>
+      <c r="E90" s="6"/>
+      <c r="F90" s="8"/>
+      <c r="G90" s="6"/>
+      <c r="H90" s="6"/>
+      <c r="I90" s="6" t="str" cm="1">
         <f t="array" ref="I90">_xlfn.SWITCH(H90,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J90" s="8"/>
-      <c r="K90" s="8"/>
-      <c r="L90" s="8"/>
+      <c r="J90" s="6"/>
+      <c r="K90" s="6"/>
+      <c r="L90" s="6"/>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A91" s="8"/>
-      <c r="B91" s="8"/>
-      <c r="C91" s="8"/>
-      <c r="D91" s="8"/>
-      <c r="E91" s="8"/>
-      <c r="F91" s="10"/>
-      <c r="G91" s="8"/>
-      <c r="H91" s="8"/>
-      <c r="I91" s="8" t="str" cm="1">
+      <c r="A91" s="6"/>
+      <c r="B91" s="6"/>
+      <c r="C91" s="6"/>
+      <c r="D91" s="6"/>
+      <c r="E91" s="6"/>
+      <c r="F91" s="8"/>
+      <c r="G91" s="6"/>
+      <c r="H91" s="6"/>
+      <c r="I91" s="6" t="str" cm="1">
         <f t="array" ref="I91">_xlfn.SWITCH(H91,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J91" s="8"/>
-      <c r="K91" s="8"/>
-      <c r="L91" s="8"/>
+      <c r="J91" s="6"/>
+      <c r="K91" s="6"/>
+      <c r="L91" s="6"/>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A92" s="8"/>
-      <c r="B92" s="8"/>
-      <c r="C92" s="8"/>
-      <c r="D92" s="8"/>
-      <c r="E92" s="8"/>
-      <c r="F92" s="10"/>
-      <c r="G92" s="8"/>
-      <c r="H92" s="8"/>
-      <c r="I92" s="8" t="str" cm="1">
+      <c r="A92" s="6"/>
+      <c r="B92" s="6"/>
+      <c r="C92" s="6"/>
+      <c r="D92" s="6"/>
+      <c r="E92" s="6"/>
+      <c r="F92" s="8"/>
+      <c r="G92" s="6"/>
+      <c r="H92" s="6"/>
+      <c r="I92" s="6" t="str" cm="1">
         <f t="array" ref="I92">_xlfn.SWITCH(H92,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J92" s="8"/>
-      <c r="K92" s="8"/>
-      <c r="L92" s="8"/>
+      <c r="J92" s="6"/>
+      <c r="K92" s="6"/>
+      <c r="L92" s="6"/>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A93" s="8"/>
-      <c r="B93" s="8"/>
-      <c r="C93" s="8"/>
-      <c r="D93" s="8"/>
-      <c r="E93" s="8"/>
-      <c r="F93" s="10"/>
-      <c r="G93" s="8"/>
-      <c r="H93" s="8"/>
-      <c r="I93" s="8" t="str" cm="1">
+      <c r="A93" s="6"/>
+      <c r="B93" s="6"/>
+      <c r="C93" s="6"/>
+      <c r="D93" s="6"/>
+      <c r="E93" s="6"/>
+      <c r="F93" s="8"/>
+      <c r="G93" s="6"/>
+      <c r="H93" s="6"/>
+      <c r="I93" s="6" t="str" cm="1">
         <f t="array" ref="I93">_xlfn.SWITCH(H93,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J93" s="8"/>
-      <c r="K93" s="8"/>
-      <c r="L93" s="8"/>
+      <c r="J93" s="6"/>
+      <c r="K93" s="6"/>
+      <c r="L93" s="6"/>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A94" s="8"/>
-      <c r="B94" s="8"/>
-      <c r="C94" s="8"/>
-      <c r="D94" s="8"/>
-      <c r="E94" s="8"/>
-      <c r="F94" s="10"/>
-      <c r="G94" s="8"/>
-      <c r="H94" s="8"/>
-      <c r="I94" s="8" t="str" cm="1">
+      <c r="A94" s="6"/>
+      <c r="B94" s="6"/>
+      <c r="C94" s="6"/>
+      <c r="D94" s="6"/>
+      <c r="E94" s="6"/>
+      <c r="F94" s="8"/>
+      <c r="G94" s="6"/>
+      <c r="H94" s="6"/>
+      <c r="I94" s="6" t="str" cm="1">
         <f t="array" ref="I94">_xlfn.SWITCH(H94,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J94" s="8"/>
-      <c r="K94" s="8"/>
-      <c r="L94" s="8"/>
+      <c r="J94" s="6"/>
+      <c r="K94" s="6"/>
+      <c r="L94" s="6"/>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A95" s="8"/>
-      <c r="B95" s="8"/>
-      <c r="C95" s="8"/>
-      <c r="D95" s="8"/>
-      <c r="E95" s="8"/>
-      <c r="F95" s="10"/>
-      <c r="G95" s="8"/>
-      <c r="H95" s="8"/>
-      <c r="I95" s="8" t="str" cm="1">
+      <c r="A95" s="6"/>
+      <c r="B95" s="6"/>
+      <c r="C95" s="6"/>
+      <c r="D95" s="6"/>
+      <c r="E95" s="6"/>
+      <c r="F95" s="8"/>
+      <c r="G95" s="6"/>
+      <c r="H95" s="6"/>
+      <c r="I95" s="6" t="str" cm="1">
         <f t="array" ref="I95">_xlfn.SWITCH(H95,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J95" s="8"/>
-      <c r="K95" s="8"/>
-      <c r="L95" s="8"/>
+      <c r="J95" s="6"/>
+      <c r="K95" s="6"/>
+      <c r="L95" s="6"/>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A96" s="8"/>
-      <c r="B96" s="8"/>
-      <c r="C96" s="8"/>
-      <c r="D96" s="8"/>
-      <c r="E96" s="8"/>
-      <c r="F96" s="10"/>
-      <c r="G96" s="8"/>
-      <c r="H96" s="8"/>
-      <c r="I96" s="8" t="str" cm="1">
+      <c r="A96" s="6"/>
+      <c r="B96" s="6"/>
+      <c r="C96" s="6"/>
+      <c r="D96" s="6"/>
+      <c r="E96" s="6"/>
+      <c r="F96" s="8"/>
+      <c r="G96" s="6"/>
+      <c r="H96" s="6"/>
+      <c r="I96" s="6" t="str" cm="1">
         <f t="array" ref="I96">_xlfn.SWITCH(H96,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J96" s="8"/>
-      <c r="K96" s="8"/>
-      <c r="L96" s="8"/>
+      <c r="J96" s="6"/>
+      <c r="K96" s="6"/>
+      <c r="L96" s="6"/>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A97" s="8"/>
-      <c r="B97" s="8"/>
-      <c r="C97" s="8"/>
-      <c r="D97" s="8"/>
-      <c r="E97" s="8"/>
-      <c r="F97" s="10"/>
-      <c r="G97" s="8"/>
-      <c r="H97" s="8"/>
-      <c r="I97" s="8" t="str" cm="1">
+      <c r="A97" s="6"/>
+      <c r="B97" s="6"/>
+      <c r="C97" s="6"/>
+      <c r="D97" s="6"/>
+      <c r="E97" s="6"/>
+      <c r="F97" s="8"/>
+      <c r="G97" s="6"/>
+      <c r="H97" s="6"/>
+      <c r="I97" s="6" t="str" cm="1">
         <f t="array" ref="I97">_xlfn.SWITCH(H97,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J97" s="8"/>
-      <c r="K97" s="8"/>
-      <c r="L97" s="8"/>
+      <c r="J97" s="6"/>
+      <c r="K97" s="6"/>
+      <c r="L97" s="6"/>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A98" s="8"/>
-      <c r="B98" s="8"/>
-      <c r="C98" s="8"/>
-      <c r="D98" s="8"/>
-      <c r="E98" s="8"/>
-      <c r="F98" s="10"/>
-      <c r="G98" s="8"/>
-      <c r="H98" s="8"/>
-      <c r="I98" s="8" t="str" cm="1">
+      <c r="A98" s="6"/>
+      <c r="B98" s="6"/>
+      <c r="C98" s="6"/>
+      <c r="D98" s="6"/>
+      <c r="E98" s="6"/>
+      <c r="F98" s="8"/>
+      <c r="G98" s="6"/>
+      <c r="H98" s="6"/>
+      <c r="I98" s="6" t="str" cm="1">
         <f t="array" ref="I98">_xlfn.SWITCH(H98,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J98" s="8"/>
-      <c r="K98" s="8"/>
-      <c r="L98" s="8"/>
+      <c r="J98" s="6"/>
+      <c r="K98" s="6"/>
+      <c r="L98" s="6"/>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A99" s="8"/>
-      <c r="B99" s="8"/>
-      <c r="C99" s="8"/>
-      <c r="D99" s="8"/>
-      <c r="E99" s="8"/>
-      <c r="F99" s="10"/>
-      <c r="G99" s="8"/>
-      <c r="H99" s="8"/>
-      <c r="I99" s="8" t="str" cm="1">
+      <c r="A99" s="6"/>
+      <c r="B99" s="6"/>
+      <c r="C99" s="6"/>
+      <c r="D99" s="6"/>
+      <c r="E99" s="6"/>
+      <c r="F99" s="8"/>
+      <c r="G99" s="6"/>
+      <c r="H99" s="6"/>
+      <c r="I99" s="6" t="str" cm="1">
         <f t="array" ref="I99">_xlfn.SWITCH(H99,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J99" s="8"/>
-      <c r="K99" s="8"/>
-      <c r="L99" s="8"/>
+      <c r="J99" s="6"/>
+      <c r="K99" s="6"/>
+      <c r="L99" s="6"/>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A100" s="8"/>
-      <c r="B100" s="8"/>
-      <c r="C100" s="8"/>
-      <c r="D100" s="8"/>
-      <c r="E100" s="8"/>
-      <c r="F100" s="10"/>
-      <c r="G100" s="8"/>
-      <c r="H100" s="8"/>
-      <c r="I100" s="8" t="str" cm="1">
+      <c r="A100" s="6"/>
+      <c r="B100" s="6"/>
+      <c r="C100" s="6"/>
+      <c r="D100" s="6"/>
+      <c r="E100" s="6"/>
+      <c r="F100" s="8"/>
+      <c r="G100" s="6"/>
+      <c r="H100" s="6"/>
+      <c r="I100" s="6" t="str" cm="1">
         <f t="array" ref="I100">_xlfn.SWITCH(H100,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J100" s="8"/>
-      <c r="K100" s="8"/>
-      <c r="L100" s="8"/>
+      <c r="J100" s="6"/>
+      <c r="K100" s="6"/>
+      <c r="L100" s="6"/>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A101" s="8"/>
-      <c r="B101" s="8"/>
-      <c r="C101" s="8"/>
-      <c r="D101" s="8"/>
-      <c r="E101" s="8"/>
-      <c r="F101" s="10"/>
-      <c r="G101" s="8"/>
-      <c r="H101" s="8"/>
-      <c r="I101" s="8" t="str" cm="1">
+      <c r="A101" s="6"/>
+      <c r="B101" s="6"/>
+      <c r="C101" s="6"/>
+      <c r="D101" s="6"/>
+      <c r="E101" s="6"/>
+      <c r="F101" s="8"/>
+      <c r="G101" s="6"/>
+      <c r="H101" s="6"/>
+      <c r="I101" s="6" t="str" cm="1">
         <f t="array" ref="I101">_xlfn.SWITCH(H101,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J101" s="8"/>
-      <c r="K101" s="8"/>
-      <c r="L101" s="8"/>
+      <c r="J101" s="6"/>
+      <c r="K101" s="6"/>
+      <c r="L101" s="6"/>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A102" s="8"/>
-      <c r="B102" s="8"/>
-      <c r="C102" s="8"/>
-      <c r="D102" s="8"/>
-      <c r="E102" s="8"/>
-      <c r="F102" s="10"/>
-      <c r="G102" s="8"/>
-      <c r="H102" s="8"/>
-      <c r="I102" s="8" t="str" cm="1">
+      <c r="A102" s="6"/>
+      <c r="B102" s="6"/>
+      <c r="C102" s="6"/>
+      <c r="D102" s="6"/>
+      <c r="E102" s="6"/>
+      <c r="F102" s="8"/>
+      <c r="G102" s="6"/>
+      <c r="H102" s="6"/>
+      <c r="I102" s="6" t="str" cm="1">
         <f t="array" ref="I102">_xlfn.SWITCH(H102,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J102" s="8"/>
-      <c r="K102" s="8"/>
-      <c r="L102" s="8"/>
+      <c r="J102" s="6"/>
+      <c r="K102" s="6"/>
+      <c r="L102" s="6"/>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A103" s="8"/>
-      <c r="B103" s="8"/>
-      <c r="C103" s="8"/>
-      <c r="D103" s="8"/>
-      <c r="E103" s="8"/>
-      <c r="F103" s="10"/>
-      <c r="G103" s="8"/>
-      <c r="H103" s="8"/>
-      <c r="I103" s="8" t="str" cm="1">
+      <c r="A103" s="6"/>
+      <c r="B103" s="6"/>
+      <c r="C103" s="6"/>
+      <c r="D103" s="6"/>
+      <c r="E103" s="6"/>
+      <c r="F103" s="8"/>
+      <c r="G103" s="6"/>
+      <c r="H103" s="6"/>
+      <c r="I103" s="6" t="str" cm="1">
         <f t="array" ref="I103">_xlfn.SWITCH(H103,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J103" s="8"/>
-      <c r="K103" s="8"/>
-      <c r="L103" s="8"/>
+      <c r="J103" s="6"/>
+      <c r="K103" s="6"/>
+      <c r="L103" s="6"/>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A104" s="8"/>
-      <c r="B104" s="8"/>
-      <c r="C104" s="8"/>
-      <c r="D104" s="8"/>
-      <c r="E104" s="8"/>
-      <c r="F104" s="10"/>
-      <c r="G104" s="8"/>
-      <c r="H104" s="8"/>
-      <c r="I104" s="8" t="str" cm="1">
+      <c r="A104" s="6"/>
+      <c r="B104" s="6"/>
+      <c r="C104" s="6"/>
+      <c r="D104" s="6"/>
+      <c r="E104" s="6"/>
+      <c r="F104" s="8"/>
+      <c r="G104" s="6"/>
+      <c r="H104" s="6"/>
+      <c r="I104" s="6" t="str" cm="1">
         <f t="array" ref="I104">_xlfn.SWITCH(H104,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J104" s="8"/>
-      <c r="K104" s="8"/>
-      <c r="L104" s="8"/>
+      <c r="J104" s="6"/>
+      <c r="K104" s="6"/>
+      <c r="L104" s="6"/>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A105" s="8"/>
-      <c r="B105" s="8"/>
-      <c r="C105" s="8"/>
-      <c r="D105" s="8"/>
-      <c r="E105" s="8"/>
-      <c r="F105" s="10"/>
-      <c r="G105" s="8"/>
-      <c r="H105" s="8"/>
-      <c r="I105" s="8" t="str" cm="1">
+      <c r="A105" s="6"/>
+      <c r="B105" s="6"/>
+      <c r="C105" s="6"/>
+      <c r="D105" s="6"/>
+      <c r="E105" s="6"/>
+      <c r="F105" s="8"/>
+      <c r="G105" s="6"/>
+      <c r="H105" s="6"/>
+      <c r="I105" s="6" t="str" cm="1">
         <f t="array" ref="I105">_xlfn.SWITCH(H105,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J105" s="8"/>
-      <c r="K105" s="8"/>
-      <c r="L105" s="8"/>
+      <c r="J105" s="6"/>
+      <c r="K105" s="6"/>
+      <c r="L105" s="6"/>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A106" s="8"/>
-      <c r="B106" s="8"/>
-      <c r="C106" s="8"/>
-      <c r="D106" s="8"/>
-      <c r="E106" s="8"/>
-      <c r="F106" s="10"/>
-      <c r="G106" s="8"/>
-      <c r="H106" s="8"/>
-      <c r="I106" s="8" t="str" cm="1">
+      <c r="A106" s="6"/>
+      <c r="B106" s="6"/>
+      <c r="C106" s="6"/>
+      <c r="D106" s="6"/>
+      <c r="E106" s="6"/>
+      <c r="F106" s="8"/>
+      <c r="G106" s="6"/>
+      <c r="H106" s="6"/>
+      <c r="I106" s="6" t="str" cm="1">
         <f t="array" ref="I106">_xlfn.SWITCH(H106,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J106" s="8"/>
-      <c r="K106" s="8"/>
-      <c r="L106" s="8"/>
+      <c r="J106" s="6"/>
+      <c r="K106" s="6"/>
+      <c r="L106" s="6"/>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A107" s="8"/>
-      <c r="B107" s="8"/>
-      <c r="C107" s="8"/>
-      <c r="D107" s="8"/>
-      <c r="E107" s="8"/>
-      <c r="F107" s="10"/>
-      <c r="G107" s="8"/>
-      <c r="H107" s="8"/>
-      <c r="I107" s="8" t="str" cm="1">
+      <c r="A107" s="6"/>
+      <c r="B107" s="6"/>
+      <c r="C107" s="6"/>
+      <c r="D107" s="6"/>
+      <c r="E107" s="6"/>
+      <c r="F107" s="8"/>
+      <c r="G107" s="6"/>
+      <c r="H107" s="6"/>
+      <c r="I107" s="6" t="str" cm="1">
         <f t="array" ref="I107">_xlfn.SWITCH(H107,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J107" s="8"/>
-      <c r="K107" s="8"/>
-      <c r="L107" s="8"/>
+      <c r="J107" s="6"/>
+      <c r="K107" s="6"/>
+      <c r="L107" s="6"/>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A108" s="8"/>
-      <c r="B108" s="8"/>
-      <c r="C108" s="8"/>
-      <c r="D108" s="8"/>
-      <c r="E108" s="8"/>
-      <c r="F108" s="10"/>
-      <c r="G108" s="8"/>
-      <c r="H108" s="8"/>
-      <c r="I108" s="8" t="str" cm="1">
+      <c r="A108" s="6"/>
+      <c r="B108" s="6"/>
+      <c r="C108" s="6"/>
+      <c r="D108" s="6"/>
+      <c r="E108" s="6"/>
+      <c r="F108" s="8"/>
+      <c r="G108" s="6"/>
+      <c r="H108" s="6"/>
+      <c r="I108" s="6" t="str" cm="1">
         <f t="array" ref="I108">_xlfn.SWITCH(H108,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J108" s="8"/>
-      <c r="K108" s="8"/>
-      <c r="L108" s="8"/>
+      <c r="J108" s="6"/>
+      <c r="K108" s="6"/>
+      <c r="L108" s="6"/>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A109" s="8"/>
-      <c r="B109" s="8"/>
-      <c r="C109" s="8"/>
-      <c r="D109" s="8"/>
-      <c r="E109" s="8"/>
-      <c r="F109" s="10"/>
-      <c r="G109" s="8"/>
-      <c r="H109" s="8"/>
-      <c r="I109" s="8" t="str" cm="1">
+      <c r="A109" s="6"/>
+      <c r="B109" s="6"/>
+      <c r="C109" s="6"/>
+      <c r="D109" s="6"/>
+      <c r="E109" s="6"/>
+      <c r="F109" s="8"/>
+      <c r="G109" s="6"/>
+      <c r="H109" s="6"/>
+      <c r="I109" s="6" t="str" cm="1">
         <f t="array" ref="I109">_xlfn.SWITCH(H109,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J109" s="8"/>
-      <c r="K109" s="8"/>
-      <c r="L109" s="8"/>
+      <c r="J109" s="6"/>
+      <c r="K109" s="6"/>
+      <c r="L109" s="6"/>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A110" s="8"/>
-      <c r="B110" s="8"/>
-      <c r="C110" s="8"/>
-      <c r="D110" s="8"/>
-      <c r="E110" s="8"/>
-      <c r="F110" s="10"/>
-      <c r="G110" s="8"/>
-      <c r="H110" s="8"/>
-      <c r="I110" s="8" t="str" cm="1">
+      <c r="A110" s="6"/>
+      <c r="B110" s="6"/>
+      <c r="C110" s="6"/>
+      <c r="D110" s="6"/>
+      <c r="E110" s="6"/>
+      <c r="F110" s="8"/>
+      <c r="G110" s="6"/>
+      <c r="H110" s="6"/>
+      <c r="I110" s="6" t="str" cm="1">
         <f t="array" ref="I110">_xlfn.SWITCH(H110,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J110" s="8"/>
-      <c r="K110" s="8"/>
-      <c r="L110" s="8"/>
+      <c r="J110" s="6"/>
+      <c r="K110" s="6"/>
+      <c r="L110" s="6"/>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A111" s="8"/>
-      <c r="B111" s="8"/>
-      <c r="C111" s="8"/>
-      <c r="D111" s="8"/>
-      <c r="E111" s="8"/>
-      <c r="F111" s="10"/>
-      <c r="G111" s="8"/>
-      <c r="H111" s="8"/>
-      <c r="I111" s="8" t="str" cm="1">
+      <c r="A111" s="6"/>
+      <c r="B111" s="6"/>
+      <c r="C111" s="6"/>
+      <c r="D111" s="6"/>
+      <c r="E111" s="6"/>
+      <c r="F111" s="8"/>
+      <c r="G111" s="6"/>
+      <c r="H111" s="6"/>
+      <c r="I111" s="6" t="str" cm="1">
         <f t="array" ref="I111">_xlfn.SWITCH(H111,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J111" s="8"/>
-      <c r="K111" s="8"/>
-      <c r="L111" s="8"/>
+      <c r="J111" s="6"/>
+      <c r="K111" s="6"/>
+      <c r="L111" s="6"/>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A112" s="8"/>
-      <c r="B112" s="8"/>
-      <c r="C112" s="8"/>
-      <c r="D112" s="8"/>
-      <c r="E112" s="8"/>
-      <c r="F112" s="10"/>
-      <c r="G112" s="8"/>
-      <c r="H112" s="8"/>
-      <c r="I112" s="8" t="str" cm="1">
+      <c r="A112" s="6"/>
+      <c r="B112" s="6"/>
+      <c r="C112" s="6"/>
+      <c r="D112" s="6"/>
+      <c r="E112" s="6"/>
+      <c r="F112" s="8"/>
+      <c r="G112" s="6"/>
+      <c r="H112" s="6"/>
+      <c r="I112" s="6" t="str" cm="1">
         <f t="array" ref="I112">_xlfn.SWITCH(H112,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J112" s="8"/>
-      <c r="K112" s="8"/>
-      <c r="L112" s="8"/>
+      <c r="J112" s="6"/>
+      <c r="K112" s="6"/>
+      <c r="L112" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="E1:E112" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -10864,199 +10883,199 @@
   <dimension ref="A1:L10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.77734375" style="5" customWidth="1"/>
-    <col min="4" max="4" width="10.77734375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="4.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.77734375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="10.77734375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="24" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
+      <c r="A2" s="19">
         <v>0</v>
       </c>
-      <c r="B2" s="14">
+      <c r="B2" s="20">
         <v>46237</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="21">
         <f>82-SUM(E$2:E2)</f>
         <v>82</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="22">
         <f xml:space="preserve"> 82*(1-1/8*A2)</f>
         <v>82</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
+      <c r="A3" s="19">
         <v>1</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="20">
         <v>46238</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="21">
         <f>82-SUM(E$2:E3)</f>
         <v>74</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="22">
         <f t="shared" ref="D3:D10" si="0" xml:space="preserve"> 82*(1-1/8*A3)</f>
         <v>71.75</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="19">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
+      <c r="A4" s="19">
         <v>2</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="20">
         <v>46239</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="21">
         <f>82-SUM(E$2:E4)</f>
         <v>66</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="22">
         <f t="shared" si="0"/>
         <v>61.5</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="19">
         <v>8</v>
       </c>
-      <c r="L4" s="3"/>
+      <c r="L4" s="2"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
+      <c r="A5" s="19">
         <v>3</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="20">
         <v>46240</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="21">
         <f>82-SUM(E$2:E5)</f>
         <v>66</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="22">
         <f t="shared" si="0"/>
         <v>51.25</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
+      <c r="A6" s="19">
         <v>4</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="20">
         <v>46241</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="21">
         <f>82-SUM(E$2:E6)</f>
         <v>66</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="22">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
+      <c r="A7" s="19">
         <v>5</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="20">
         <v>46244</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="21">
         <f>82-SUM(E$2:E7)</f>
         <v>62</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="22">
         <f t="shared" si="0"/>
         <v>30.75</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="19">
         <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
+      <c r="A8" s="19">
         <v>6</v>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="20">
         <v>46245</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="21">
         <f>82-SUM(E$2:E8)</f>
         <v>52</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="22">
         <f t="shared" si="0"/>
         <v>20.5</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="19">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
+      <c r="A9" s="19">
         <v>7</v>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="20">
         <v>46246</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="21">
         <f>82-SUM(E$2:E9)</f>
         <v>37</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="22">
         <f t="shared" si="0"/>
         <v>10.25</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="19">
         <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
+      <c r="A10" s="19">
         <v>8</v>
       </c>
-      <c r="B10" s="14">
+      <c r="B10" s="20">
         <v>46247</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="21">
         <f>82-SUM(E$2:E10)</f>
         <v>0</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" s="22">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="19">
         <v>37</v>
       </c>
     </row>
@@ -11086,2205 +11105,2205 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="15">
+      <c r="A2" s="12">
         <v>1</v>
       </c>
-      <c r="B2" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C2" s="15" t="s">
+      <c r="B2" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15" t="s">
+      <c r="C2" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="G2" s="15" t="s">
+      <c r="F2" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="G2" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="15">
+      <c r="I2" s="12">
         <f t="array" ref="I2">_xlfn.SWITCH(H2,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="J2" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
     </row>
     <row r="3" spans="1:12" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="15">
+      <c r="A3" s="12">
         <v>2</v>
       </c>
-      <c r="B3" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15" t="s">
+      <c r="B3" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="G3" s="15" t="s">
+      <c r="F3" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="H3" s="15" t="s">
+      <c r="H3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="15">
+      <c r="I3" s="12">
         <f t="array" ref="I3">_xlfn.SWITCH(H3,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J3" s="15" t="s">
+      <c r="J3" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="K3" s="15"/>
-      <c r="L3" s="15"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
     </row>
     <row r="4" spans="1:12" ht="403.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="15">
+      <c r="A4" s="12">
         <v>3</v>
       </c>
-      <c r="B4" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C4" s="15" t="s">
+      <c r="B4" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15" t="s">
+      <c r="C4" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="G4" s="15" t="s">
+      <c r="F4" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="G4" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="H4" s="15" t="s">
+      <c r="H4" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="15">
+      <c r="I4" s="12">
         <f t="array" ref="I4">_xlfn.SWITCH(H4,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="12"/>
     </row>
     <row r="5" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="15">
+      <c r="A5" s="12">
         <v>4</v>
       </c>
-      <c r="B5" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15" t="s">
+      <c r="B5" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="G5" s="15" t="s">
+      <c r="F5" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="G5" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="I5" s="15">
+      <c r="I5" s="12">
         <f t="array" ref="I5">_xlfn.SWITCH(H5,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
     </row>
     <row r="6" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="15">
+      <c r="A6" s="12">
         <v>5</v>
       </c>
-      <c r="B6" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15" t="s">
+      <c r="B6" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="21" t="s">
-        <v>115</v>
-      </c>
-      <c r="G6" s="15" t="s">
+      <c r="F6" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="G6" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="H6" s="15" t="s">
+      <c r="H6" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="I6" s="15">
+      <c r="I6" s="12">
         <f t="array" ref="I6">_xlfn.SWITCH(H6,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J6" s="15" t="s">
+      <c r="J6" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="K6" s="15"/>
-      <c r="L6" s="15"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
     </row>
     <row r="7" spans="1:12" ht="144" x14ac:dyDescent="0.3">
-      <c r="A7" s="15">
+      <c r="A7" s="12">
         <v>6</v>
       </c>
-      <c r="B7" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15" t="s">
+      <c r="B7" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="G7" s="15" t="s">
+      <c r="F7" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="G7" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="H7" s="15" t="s">
+      <c r="H7" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="I7" s="15">
+      <c r="I7" s="12">
         <f t="array" ref="I7">_xlfn.SWITCH(H7,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J7" s="15" t="s">
+      <c r="J7" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="K7" s="15"/>
-      <c r="L7" s="15"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="12"/>
     </row>
     <row r="8" spans="1:12" ht="144" x14ac:dyDescent="0.3">
-      <c r="A8" s="15">
+      <c r="A8" s="12">
         <v>7</v>
       </c>
-      <c r="B8" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15" t="s">
+      <c r="B8" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="G8" s="15" t="s">
+      <c r="F8" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="G8" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="H8" s="15" t="s">
+      <c r="H8" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="I8" s="15">
+      <c r="I8" s="12">
         <f t="array" ref="I8">_xlfn.SWITCH(H8,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J8" s="15" t="s">
+      <c r="J8" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="K8" s="15"/>
-      <c r="L8" s="15"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
     </row>
     <row r="9" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="15">
+      <c r="A9" s="12">
         <v>8</v>
       </c>
-      <c r="B9" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C9" s="15">
+      <c r="B9" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="C9" s="12">
         <v>6.5</v>
       </c>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15" t="s">
+      <c r="D9" s="12"/>
+      <c r="E9" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="21" t="s">
-        <v>109</v>
-      </c>
-      <c r="G9" s="15" t="s">
+      <c r="F9" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="G9" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="H9" s="15" t="s">
+      <c r="H9" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="I9" s="15">
+      <c r="I9" s="12">
         <f t="array" ref="I9">_xlfn.SWITCH(H9,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>2</v>
       </c>
-      <c r="J9" s="15" t="s">
+      <c r="J9" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="K9" s="15"/>
-      <c r="L9" s="15"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="12"/>
     </row>
     <row r="10" spans="1:12" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="15">
+      <c r="A10" s="12">
         <v>9</v>
       </c>
-      <c r="B10" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15" t="s">
+      <c r="B10" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F10" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="G10" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="H10" s="15" t="s">
+      <c r="F10" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="I10" s="15">
+      <c r="I10" s="12">
         <f t="array" ref="I10">_xlfn.SWITCH(H10,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J10" s="15" t="s">
+      <c r="J10" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15"/>
-    </row>
-    <row r="11" spans="1:12" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="17">
+      <c r="K10" s="12"/>
+      <c r="L10" s="12"/>
+    </row>
+    <row r="11" spans="1:12" ht="230.4" x14ac:dyDescent="0.3">
+      <c r="A11" s="14">
         <v>10</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="14">
         <v>19.3</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="E11" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="G11" s="17" t="s">
+      <c r="F11" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="G11" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="H11" s="17" t="s">
+      <c r="H11" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="I11" s="17">
+      <c r="I11" s="14">
         <f t="array" ref="I11">_xlfn.SWITCH(H11,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J11" s="17" t="s">
+      <c r="J11" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
-    </row>
-    <row r="12" spans="1:12" ht="244.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="17">
+      <c r="K11" s="14"/>
+      <c r="L11" s="14"/>
+    </row>
+    <row r="12" spans="1:12" ht="288" x14ac:dyDescent="0.3">
+      <c r="A12" s="14">
         <v>11</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="14">
         <v>19.3</v>
       </c>
-      <c r="D12" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="E12" s="17" t="s">
+      <c r="D12" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="E12" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="G12" s="17" t="s">
+      <c r="F12" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="G12" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="H12" s="17" t="s">
+      <c r="H12" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="I12" s="17">
+      <c r="I12" s="14">
         <f t="array" ref="I12">_xlfn.SWITCH(H12,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J12" s="17" t="s">
+      <c r="J12" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="K12" s="17"/>
-      <c r="L12" s="17"/>
-    </row>
-    <row r="13" spans="1:12" ht="273.60000000000002" x14ac:dyDescent="0.3">
-      <c r="A13" s="17">
+      <c r="K12" s="14"/>
+      <c r="L12" s="14"/>
+    </row>
+    <row r="13" spans="1:12" ht="316.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="14">
         <v>12</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13" s="14">
+        <v>20.3</v>
+      </c>
+      <c r="D13" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="C13" s="17">
-        <v>20.3</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="E13" s="17" t="s">
+      <c r="E13" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="G13" s="17" t="s">
+      <c r="F13" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="G13" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="H13" s="17" t="s">
+      <c r="H13" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="I13" s="17">
+      <c r="I13" s="14">
         <f t="array" ref="I13">_xlfn.SWITCH(H13,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J13" s="17" t="s">
+      <c r="J13" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="K13" s="17"/>
-      <c r="L13" s="17"/>
+      <c r="K13" s="14"/>
+      <c r="L13" s="14"/>
     </row>
     <row r="14" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A14" s="17">
+      <c r="A14" s="14">
         <v>13</v>
       </c>
-      <c r="B14" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="C14" s="17">
+      <c r="B14" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" s="14">
         <v>20.3</v>
       </c>
-      <c r="D14" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="E14" s="17" t="s">
+      <c r="D14" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="E14" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="F14" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="G14" s="17" t="s">
+      <c r="F14" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="G14" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="H14" s="17" t="s">
+      <c r="H14" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="I14" s="17">
+      <c r="I14" s="14">
         <f t="array" ref="I14">_xlfn.SWITCH(H14,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J14" s="17" t="s">
+      <c r="J14" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="K14" s="17"/>
-      <c r="L14" s="17"/>
+      <c r="K14" s="14"/>
+      <c r="L14" s="14"/>
     </row>
     <row r="15" spans="1:12" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="19">
+      <c r="A15" s="16">
         <v>14</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="E15" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="F15" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="G15" s="19" t="s">
+      <c r="G15" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="H15" s="19" t="s">
+      <c r="H15" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="I15" s="19">
+      <c r="I15" s="16">
         <f t="array" ref="I15">_xlfn.SWITCH(H15,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>3</v>
       </c>
-      <c r="J15" s="19" t="s">
+      <c r="J15" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="K15" s="19"/>
-      <c r="L15" s="19"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
     </row>
     <row r="16" spans="1:12" ht="244.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="8">
+      <c r="A16" s="6">
         <v>15</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="6">
         <v>19.3</v>
       </c>
-      <c r="D16" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="E16" s="8" t="s">
+      <c r="D16" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="E16" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F16" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="G16" s="8" t="s">
+      <c r="F16" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="G16" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="H16" s="8" t="s">
+      <c r="H16" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="I16" s="8">
+      <c r="I16" s="6">
         <f t="array" ref="I16">_xlfn.SWITCH(H16,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
     </row>
     <row r="17" spans="1:12" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="8">
+      <c r="A17" s="6">
         <v>16</v>
       </c>
-      <c r="B17" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C17" s="8">
+      <c r="B17" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C17" s="6">
         <v>20.3</v>
       </c>
-      <c r="D17" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="E17" s="8" t="s">
+      <c r="D17" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F17" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="G17" s="8" t="s">
+      <c r="F17" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="G17" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="H17" s="8" t="s">
+      <c r="H17" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="I17" s="8">
+      <c r="I17" s="6">
         <f t="array" ref="I17">_xlfn.SWITCH(H17,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
     </row>
     <row r="18" spans="1:12" ht="244.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="8">
+      <c r="A18" s="6">
         <v>17</v>
       </c>
-      <c r="B18" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C18" s="8">
+      <c r="B18" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C18" s="6">
         <v>20.399999999999999</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I18" s="6">
+        <v>5</v>
+      </c>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+    </row>
+    <row r="19" spans="1:12" ht="316.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="6">
+        <v>18</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I19" s="6">
+        <v>5</v>
+      </c>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
+    </row>
+    <row r="20" spans="1:12" ht="345.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="6">
+        <v>19</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="E18" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="G18" s="8" t="s">
+      <c r="G20" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="H18" s="8" t="s">
+      <c r="H20" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="I18" s="8">
+      <c r="I20" s="6">
         <v>5</v>
       </c>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
-      <c r="L18" s="8"/>
-    </row>
-    <row r="19" spans="1:12" ht="273.60000000000002" x14ac:dyDescent="0.3">
-      <c r="A19" s="8">
-        <v>18</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="I19" s="8">
-        <v>5</v>
-      </c>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-    </row>
-    <row r="20" spans="1:12" ht="345.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="8">
-        <v>19</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="I20" s="8">
-        <v>5</v>
-      </c>
-      <c r="J20" s="8"/>
-      <c r="K20" s="8"/>
-      <c r="L20" s="8"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-      <c r="J21" s="8"/>
-      <c r="K21" s="8"/>
-      <c r="L21" s="8"/>
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-      <c r="J22" s="8"/>
-      <c r="K22" s="8"/>
-      <c r="L22" s="8"/>
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
-      <c r="J23" s="8"/>
-      <c r="K23" s="8"/>
-      <c r="L23" s="8"/>
+      <c r="A23" s="6"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="8"/>
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8" t="str">
+      <c r="A25" s="6"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6" t="str">
         <f t="array" ref="I25">_xlfn.SWITCH(H25,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J25" s="8"/>
-      <c r="K25" s="8"/>
-      <c r="L25" s="8"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="6"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="8" t="str">
+      <c r="A26" s="6"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6" t="str">
         <f t="array" ref="I26">_xlfn.SWITCH(H26,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J26" s="8"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="8"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="8"/>
-      <c r="I27" s="8" t="str">
+      <c r="A27" s="6"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6" t="str">
         <f t="array" ref="I27">_xlfn.SWITCH(H27,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J27" s="8"/>
-      <c r="K27" s="8"/>
-      <c r="L27" s="8"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="6"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="8"/>
-      <c r="I28" s="8" t="str">
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="6" t="str">
         <f t="array" ref="I28">_xlfn.SWITCH(H28,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J28" s="8"/>
-      <c r="K28" s="8"/>
-      <c r="L28" s="8"/>
+      <c r="J28" s="6"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="6"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8" t="str">
+      <c r="A29" s="6"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6" t="str">
         <f t="array" ref="I29">_xlfn.SWITCH(H29,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J29" s="8"/>
-      <c r="K29" s="8"/>
-      <c r="L29" s="8"/>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="6"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="8"/>
-      <c r="I30" s="8" t="str">
+      <c r="A30" s="6"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6" t="str">
         <f t="array" ref="I30">_xlfn.SWITCH(H30,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J30" s="8"/>
-      <c r="K30" s="8"/>
-      <c r="L30" s="8"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
+      <c r="L30" s="6"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
-      <c r="I31" s="8" t="str">
+      <c r="A31" s="6"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6" t="str">
         <f t="array" ref="I31">_xlfn.SWITCH(H31,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J31" s="8"/>
-      <c r="K31" s="8"/>
-      <c r="L31" s="8"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A32" s="8"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="8"/>
-      <c r="I32" s="8" t="str">
+      <c r="A32" s="6"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6" t="str">
         <f t="array" ref="I32">_xlfn.SWITCH(H32,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J32" s="8"/>
-      <c r="K32" s="8"/>
-      <c r="L32" s="8"/>
+      <c r="J32" s="6"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="6"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A33" s="8"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="8"/>
-      <c r="I33" s="8" t="str">
+      <c r="A33" s="6"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6" t="str">
         <f t="array" ref="I33">_xlfn.SWITCH(H33,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J33" s="8"/>
-      <c r="K33" s="8"/>
-      <c r="L33" s="8"/>
+      <c r="J33" s="6"/>
+      <c r="K33" s="6"/>
+      <c r="L33" s="6"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A34" s="8"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="8"/>
-      <c r="H34" s="8"/>
-      <c r="I34" s="8" t="str">
+      <c r="A34" s="6"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6" t="str">
         <f t="array" ref="I34">_xlfn.SWITCH(H34,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J34" s="8"/>
-      <c r="K34" s="8"/>
-      <c r="L34" s="8"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="6"/>
+      <c r="L34" s="6"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A35" s="8"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="8"/>
-      <c r="H35" s="8"/>
-      <c r="I35" s="8" t="str">
+      <c r="A35" s="6"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="6" t="str">
         <f t="array" ref="I35">_xlfn.SWITCH(H35,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J35" s="8"/>
-      <c r="K35" s="8"/>
-      <c r="L35" s="8"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="6"/>
+      <c r="L35" s="6"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" s="8"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="8"/>
-      <c r="H36" s="8"/>
-      <c r="I36" s="8" t="str">
+      <c r="A36" s="6"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6" t="str">
         <f t="array" ref="I36">_xlfn.SWITCH(H36,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J36" s="8"/>
-      <c r="K36" s="8"/>
-      <c r="L36" s="8"/>
+      <c r="J36" s="6"/>
+      <c r="K36" s="6"/>
+      <c r="L36" s="6"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A37" s="8"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="8"/>
-      <c r="H37" s="8"/>
-      <c r="I37" s="8" t="str">
+      <c r="A37" s="6"/>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6" t="str">
         <f t="array" ref="I37">_xlfn.SWITCH(H37,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J37" s="8"/>
-      <c r="K37" s="8"/>
-      <c r="L37" s="8"/>
+      <c r="J37" s="6"/>
+      <c r="K37" s="6"/>
+      <c r="L37" s="6"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A38" s="8"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="8"/>
-      <c r="H38" s="8"/>
-      <c r="I38" s="8" t="str">
+      <c r="A38" s="6"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6" t="str">
         <f t="array" ref="I38">_xlfn.SWITCH(H38,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J38" s="8"/>
-      <c r="K38" s="8"/>
-      <c r="L38" s="8"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="6"/>
+      <c r="L38" s="6"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A39" s="8"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="8"/>
-      <c r="H39" s="8"/>
-      <c r="I39" s="8" t="str">
+      <c r="A39" s="6"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6" t="str">
         <f t="array" ref="I39">_xlfn.SWITCH(H39,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J39" s="8"/>
-      <c r="K39" s="8"/>
-      <c r="L39" s="8"/>
+      <c r="J39" s="6"/>
+      <c r="K39" s="6"/>
+      <c r="L39" s="6"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A40" s="8"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="8"/>
-      <c r="H40" s="8"/>
-      <c r="I40" s="8" t="str">
+      <c r="A40" s="6"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="6" t="str">
         <f t="array" ref="I40">_xlfn.SWITCH(H40,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J40" s="8"/>
-      <c r="K40" s="8"/>
-      <c r="L40" s="8"/>
+      <c r="J40" s="6"/>
+      <c r="K40" s="6"/>
+      <c r="L40" s="6"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A41" s="8"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="8"/>
-      <c r="H41" s="8"/>
-      <c r="I41" s="8" t="str">
+      <c r="A41" s="6"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="6"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="6" t="str">
         <f t="array" ref="I41">_xlfn.SWITCH(H41,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J41" s="8"/>
-      <c r="K41" s="8"/>
-      <c r="L41" s="8"/>
+      <c r="J41" s="6"/>
+      <c r="K41" s="6"/>
+      <c r="L41" s="6"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A42" s="8"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="8"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="8"/>
-      <c r="H42" s="8"/>
-      <c r="I42" s="8" t="str">
+      <c r="A42" s="6"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="7"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6" t="str">
         <f t="array" ref="I42">_xlfn.SWITCH(H42,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J42" s="8"/>
-      <c r="K42" s="8"/>
-      <c r="L42" s="8"/>
+      <c r="J42" s="6"/>
+      <c r="K42" s="6"/>
+      <c r="L42" s="6"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A43" s="8"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="8"/>
-      <c r="H43" s="8"/>
-      <c r="I43" s="8" t="str">
+      <c r="A43" s="6"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="7"/>
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="6" t="str">
         <f t="array" ref="I43">_xlfn.SWITCH(H43,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J43" s="8"/>
-      <c r="K43" s="8"/>
-      <c r="L43" s="8"/>
+      <c r="J43" s="6"/>
+      <c r="K43" s="6"/>
+      <c r="L43" s="6"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A44" s="8"/>
-      <c r="B44" s="8"/>
-      <c r="C44" s="8"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="8"/>
-      <c r="H44" s="8"/>
-      <c r="I44" s="8" t="str">
+      <c r="A44" s="6"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="7"/>
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="6" t="str">
         <f t="array" ref="I44">_xlfn.SWITCH(H44,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J44" s="8"/>
-      <c r="K44" s="8"/>
-      <c r="L44" s="8"/>
+      <c r="J44" s="6"/>
+      <c r="K44" s="6"/>
+      <c r="L44" s="6"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A45" s="8"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="8"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="8"/>
-      <c r="H45" s="8"/>
-      <c r="I45" s="8" t="str">
+      <c r="A45" s="6"/>
+      <c r="B45" s="6"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="6"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="6" t="str">
         <f t="array" ref="I45">_xlfn.SWITCH(H45,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J45" s="8"/>
-      <c r="K45" s="8"/>
-      <c r="L45" s="8"/>
+      <c r="J45" s="6"/>
+      <c r="K45" s="6"/>
+      <c r="L45" s="6"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A46" s="8"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="8"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="9"/>
-      <c r="G46" s="8"/>
-      <c r="H46" s="8"/>
-      <c r="I46" s="8" t="str">
+      <c r="A46" s="6"/>
+      <c r="B46" s="6"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="7"/>
+      <c r="G46" s="6"/>
+      <c r="H46" s="6"/>
+      <c r="I46" s="6" t="str">
         <f t="array" ref="I46">_xlfn.SWITCH(H46,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J46" s="8"/>
-      <c r="K46" s="8"/>
-      <c r="L46" s="8"/>
+      <c r="J46" s="6"/>
+      <c r="K46" s="6"/>
+      <c r="L46" s="6"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A47" s="8"/>
-      <c r="B47" s="8"/>
-      <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="8"/>
-      <c r="H47" s="8"/>
-      <c r="I47" s="8" t="str">
+      <c r="A47" s="6"/>
+      <c r="B47" s="6"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="7"/>
+      <c r="G47" s="6"/>
+      <c r="H47" s="6"/>
+      <c r="I47" s="6" t="str">
         <f t="array" ref="I47">_xlfn.SWITCH(H47,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J47" s="8"/>
-      <c r="K47" s="8"/>
-      <c r="L47" s="8"/>
+      <c r="J47" s="6"/>
+      <c r="K47" s="6"/>
+      <c r="L47" s="6"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A48" s="8"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="8"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="8"/>
-      <c r="H48" s="8"/>
-      <c r="I48" s="8" t="str">
+      <c r="A48" s="6"/>
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="7"/>
+      <c r="G48" s="6"/>
+      <c r="H48" s="6"/>
+      <c r="I48" s="6" t="str">
         <f t="array" ref="I48">_xlfn.SWITCH(H48,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J48" s="8"/>
-      <c r="K48" s="8"/>
-      <c r="L48" s="8"/>
+      <c r="J48" s="6"/>
+      <c r="K48" s="6"/>
+      <c r="L48" s="6"/>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A49" s="8"/>
-      <c r="B49" s="8"/>
-      <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="8"/>
-      <c r="H49" s="8"/>
-      <c r="I49" s="8" t="str">
+      <c r="A49" s="6"/>
+      <c r="B49" s="6"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="7"/>
+      <c r="G49" s="6"/>
+      <c r="H49" s="6"/>
+      <c r="I49" s="6" t="str">
         <f t="array" ref="I49">_xlfn.SWITCH(H49,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J49" s="8"/>
-      <c r="K49" s="8"/>
-      <c r="L49" s="8"/>
+      <c r="J49" s="6"/>
+      <c r="K49" s="6"/>
+      <c r="L49" s="6"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A50" s="8"/>
-      <c r="B50" s="8"/>
-      <c r="C50" s="8"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="10"/>
-      <c r="G50" s="8"/>
-      <c r="H50" s="8"/>
-      <c r="I50" s="8" t="str">
+      <c r="A50" s="6"/>
+      <c r="B50" s="6"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="8"/>
+      <c r="G50" s="6"/>
+      <c r="H50" s="6"/>
+      <c r="I50" s="6" t="str">
         <f t="array" ref="I50">_xlfn.SWITCH(H50,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J50" s="8"/>
-      <c r="K50" s="8"/>
-      <c r="L50" s="8"/>
+      <c r="J50" s="6"/>
+      <c r="K50" s="6"/>
+      <c r="L50" s="6"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A51" s="8"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="8"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="10"/>
-      <c r="G51" s="8"/>
-      <c r="H51" s="8"/>
-      <c r="I51" s="8" t="str">
+      <c r="A51" s="6"/>
+      <c r="B51" s="6"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="8"/>
+      <c r="G51" s="6"/>
+      <c r="H51" s="6"/>
+      <c r="I51" s="6" t="str">
         <f t="array" ref="I51">_xlfn.SWITCH(H51,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J51" s="8"/>
-      <c r="K51" s="8"/>
-      <c r="L51" s="8"/>
+      <c r="J51" s="6"/>
+      <c r="K51" s="6"/>
+      <c r="L51" s="6"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A52" s="8"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="8"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="10"/>
-      <c r="G52" s="8"/>
-      <c r="H52" s="8"/>
-      <c r="I52" s="8" t="str">
+      <c r="A52" s="6"/>
+      <c r="B52" s="6"/>
+      <c r="C52" s="6"/>
+      <c r="D52" s="6"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="8"/>
+      <c r="G52" s="6"/>
+      <c r="H52" s="6"/>
+      <c r="I52" s="6" t="str">
         <f t="array" ref="I52">_xlfn.SWITCH(H52,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J52" s="8"/>
-      <c r="K52" s="8"/>
-      <c r="L52" s="8"/>
+      <c r="J52" s="6"/>
+      <c r="K52" s="6"/>
+      <c r="L52" s="6"/>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A53" s="8"/>
-      <c r="B53" s="8"/>
-      <c r="C53" s="8"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="10"/>
-      <c r="G53" s="8"/>
-      <c r="H53" s="8"/>
-      <c r="I53" s="8" t="str">
+      <c r="A53" s="6"/>
+      <c r="B53" s="6"/>
+      <c r="C53" s="6"/>
+      <c r="D53" s="6"/>
+      <c r="E53" s="6"/>
+      <c r="F53" s="8"/>
+      <c r="G53" s="6"/>
+      <c r="H53" s="6"/>
+      <c r="I53" s="6" t="str">
         <f t="array" ref="I53">_xlfn.SWITCH(H53,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J53" s="8"/>
-      <c r="K53" s="8"/>
-      <c r="L53" s="8"/>
+      <c r="J53" s="6"/>
+      <c r="K53" s="6"/>
+      <c r="L53" s="6"/>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A54" s="8"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="8"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="10"/>
-      <c r="G54" s="8"/>
-      <c r="H54" s="8"/>
-      <c r="I54" s="8" t="str">
+      <c r="A54" s="6"/>
+      <c r="B54" s="6"/>
+      <c r="C54" s="6"/>
+      <c r="D54" s="6"/>
+      <c r="E54" s="6"/>
+      <c r="F54" s="8"/>
+      <c r="G54" s="6"/>
+      <c r="H54" s="6"/>
+      <c r="I54" s="6" t="str">
         <f t="array" ref="I54">_xlfn.SWITCH(H54,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J54" s="8"/>
-      <c r="K54" s="8"/>
-      <c r="L54" s="8"/>
+      <c r="J54" s="6"/>
+      <c r="K54" s="6"/>
+      <c r="L54" s="6"/>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A55" s="8"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="8"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="10"/>
-      <c r="G55" s="8"/>
-      <c r="H55" s="8"/>
-      <c r="I55" s="8" t="str">
+      <c r="A55" s="6"/>
+      <c r="B55" s="6"/>
+      <c r="C55" s="6"/>
+      <c r="D55" s="6"/>
+      <c r="E55" s="6"/>
+      <c r="F55" s="8"/>
+      <c r="G55" s="6"/>
+      <c r="H55" s="6"/>
+      <c r="I55" s="6" t="str">
         <f t="array" ref="I55">_xlfn.SWITCH(H55,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J55" s="8"/>
-      <c r="K55" s="8"/>
-      <c r="L55" s="8"/>
+      <c r="J55" s="6"/>
+      <c r="K55" s="6"/>
+      <c r="L55" s="6"/>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A56" s="8"/>
-      <c r="B56" s="8"/>
-      <c r="C56" s="8"/>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="9"/>
-      <c r="G56" s="8"/>
-      <c r="H56" s="8"/>
-      <c r="I56" s="8" t="str">
+      <c r="A56" s="6"/>
+      <c r="B56" s="6"/>
+      <c r="C56" s="6"/>
+      <c r="D56" s="6"/>
+      <c r="E56" s="6"/>
+      <c r="F56" s="7"/>
+      <c r="G56" s="6"/>
+      <c r="H56" s="6"/>
+      <c r="I56" s="6" t="str">
         <f t="array" ref="I56">_xlfn.SWITCH(H56,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J56" s="8"/>
-      <c r="K56" s="8"/>
-      <c r="L56" s="8"/>
+      <c r="J56" s="6"/>
+      <c r="K56" s="6"/>
+      <c r="L56" s="6"/>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A57" s="8"/>
-      <c r="B57" s="8"/>
-      <c r="C57" s="8"/>
-      <c r="D57" s="8"/>
-      <c r="E57" s="8"/>
-      <c r="F57" s="9"/>
-      <c r="G57" s="8"/>
-      <c r="H57" s="8"/>
-      <c r="I57" s="8" t="str">
+      <c r="A57" s="6"/>
+      <c r="B57" s="6"/>
+      <c r="C57" s="6"/>
+      <c r="D57" s="6"/>
+      <c r="E57" s="6"/>
+      <c r="F57" s="7"/>
+      <c r="G57" s="6"/>
+      <c r="H57" s="6"/>
+      <c r="I57" s="6" t="str">
         <f t="array" ref="I57">_xlfn.SWITCH(H57,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J57" s="8"/>
-      <c r="K57" s="8"/>
-      <c r="L57" s="8"/>
+      <c r="J57" s="6"/>
+      <c r="K57" s="6"/>
+      <c r="L57" s="6"/>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A58" s="8"/>
-      <c r="B58" s="8"/>
-      <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="9"/>
-      <c r="G58" s="8"/>
-      <c r="H58" s="8"/>
-      <c r="I58" s="8" t="str">
+      <c r="A58" s="6"/>
+      <c r="B58" s="6"/>
+      <c r="C58" s="6"/>
+      <c r="D58" s="6"/>
+      <c r="E58" s="6"/>
+      <c r="F58" s="7"/>
+      <c r="G58" s="6"/>
+      <c r="H58" s="6"/>
+      <c r="I58" s="6" t="str">
         <f t="array" ref="I58">_xlfn.SWITCH(H58,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J58" s="8"/>
-      <c r="K58" s="8"/>
-      <c r="L58" s="8"/>
+      <c r="J58" s="6"/>
+      <c r="K58" s="6"/>
+      <c r="L58" s="6"/>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A59" s="8"/>
-      <c r="B59" s="8"/>
-      <c r="C59" s="8"/>
-      <c r="D59" s="8"/>
-      <c r="E59" s="8"/>
-      <c r="F59" s="9"/>
-      <c r="G59" s="8"/>
-      <c r="H59" s="8"/>
-      <c r="I59" s="8" t="str">
+      <c r="A59" s="6"/>
+      <c r="B59" s="6"/>
+      <c r="C59" s="6"/>
+      <c r="D59" s="6"/>
+      <c r="E59" s="6"/>
+      <c r="F59" s="7"/>
+      <c r="G59" s="6"/>
+      <c r="H59" s="6"/>
+      <c r="I59" s="6" t="str">
         <f t="array" ref="I59">_xlfn.SWITCH(H59,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J59" s="8"/>
-      <c r="K59" s="8"/>
-      <c r="L59" s="8"/>
+      <c r="J59" s="6"/>
+      <c r="K59" s="6"/>
+      <c r="L59" s="6"/>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A60" s="8"/>
-      <c r="B60" s="8"/>
-      <c r="C60" s="8"/>
-      <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
-      <c r="F60" s="9"/>
-      <c r="G60" s="8"/>
-      <c r="H60" s="8"/>
-      <c r="I60" s="8" t="str">
+      <c r="A60" s="6"/>
+      <c r="B60" s="6"/>
+      <c r="C60" s="6"/>
+      <c r="D60" s="6"/>
+      <c r="E60" s="6"/>
+      <c r="F60" s="7"/>
+      <c r="G60" s="6"/>
+      <c r="H60" s="6"/>
+      <c r="I60" s="6" t="str">
         <f t="array" ref="I60">_xlfn.SWITCH(H60,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J60" s="8"/>
-      <c r="K60" s="8"/>
-      <c r="L60" s="8"/>
+      <c r="J60" s="6"/>
+      <c r="K60" s="6"/>
+      <c r="L60" s="6"/>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A61" s="8"/>
-      <c r="B61" s="8"/>
-      <c r="C61" s="8"/>
-      <c r="D61" s="8"/>
-      <c r="E61" s="8"/>
-      <c r="F61" s="9"/>
-      <c r="G61" s="8"/>
-      <c r="H61" s="8"/>
-      <c r="I61" s="8" t="str">
+      <c r="A61" s="6"/>
+      <c r="B61" s="6"/>
+      <c r="C61" s="6"/>
+      <c r="D61" s="6"/>
+      <c r="E61" s="6"/>
+      <c r="F61" s="7"/>
+      <c r="G61" s="6"/>
+      <c r="H61" s="6"/>
+      <c r="I61" s="6" t="str">
         <f t="array" ref="I61">_xlfn.SWITCH(H61,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J61" s="8"/>
-      <c r="K61" s="8"/>
-      <c r="L61" s="8"/>
+      <c r="J61" s="6"/>
+      <c r="K61" s="6"/>
+      <c r="L61" s="6"/>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A62" s="8"/>
-      <c r="B62" s="8"/>
-      <c r="C62" s="8"/>
-      <c r="D62" s="8"/>
-      <c r="E62" s="8"/>
-      <c r="F62" s="9"/>
-      <c r="G62" s="8"/>
-      <c r="H62" s="8"/>
-      <c r="I62" s="8" t="str">
+      <c r="A62" s="6"/>
+      <c r="B62" s="6"/>
+      <c r="C62" s="6"/>
+      <c r="D62" s="6"/>
+      <c r="E62" s="6"/>
+      <c r="F62" s="7"/>
+      <c r="G62" s="6"/>
+      <c r="H62" s="6"/>
+      <c r="I62" s="6" t="str">
         <f t="array" ref="I62">_xlfn.SWITCH(H62,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J62" s="8"/>
-      <c r="K62" s="8"/>
-      <c r="L62" s="8"/>
+      <c r="J62" s="6"/>
+      <c r="K62" s="6"/>
+      <c r="L62" s="6"/>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A63" s="8"/>
-      <c r="B63" s="8"/>
-      <c r="C63" s="8"/>
-      <c r="D63" s="8"/>
-      <c r="E63" s="8"/>
-      <c r="F63" s="9"/>
-      <c r="G63" s="8"/>
-      <c r="H63" s="8"/>
-      <c r="I63" s="8" t="str">
+      <c r="A63" s="6"/>
+      <c r="B63" s="6"/>
+      <c r="C63" s="6"/>
+      <c r="D63" s="6"/>
+      <c r="E63" s="6"/>
+      <c r="F63" s="7"/>
+      <c r="G63" s="6"/>
+      <c r="H63" s="6"/>
+      <c r="I63" s="6" t="str">
         <f t="array" ref="I63">_xlfn.SWITCH(H63,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J63" s="8"/>
-      <c r="K63" s="8"/>
-      <c r="L63" s="8"/>
+      <c r="J63" s="6"/>
+      <c r="K63" s="6"/>
+      <c r="L63" s="6"/>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A64" s="8"/>
-      <c r="B64" s="8"/>
-      <c r="C64" s="8"/>
-      <c r="D64" s="8"/>
-      <c r="E64" s="8"/>
-      <c r="F64" s="9"/>
-      <c r="G64" s="8"/>
-      <c r="H64" s="8"/>
-      <c r="I64" s="8" t="str">
+      <c r="A64" s="6"/>
+      <c r="B64" s="6"/>
+      <c r="C64" s="6"/>
+      <c r="D64" s="6"/>
+      <c r="E64" s="6"/>
+      <c r="F64" s="7"/>
+      <c r="G64" s="6"/>
+      <c r="H64" s="6"/>
+      <c r="I64" s="6" t="str">
         <f t="array" ref="I64">_xlfn.SWITCH(H64,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J64" s="8"/>
-      <c r="K64" s="8"/>
-      <c r="L64" s="8"/>
+      <c r="J64" s="6"/>
+      <c r="K64" s="6"/>
+      <c r="L64" s="6"/>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A65" s="8"/>
-      <c r="B65" s="8"/>
-      <c r="C65" s="8"/>
-      <c r="D65" s="8"/>
-      <c r="E65" s="8"/>
-      <c r="F65" s="9"/>
-      <c r="G65" s="8"/>
-      <c r="H65" s="8"/>
-      <c r="I65" s="8" t="str">
+      <c r="A65" s="6"/>
+      <c r="B65" s="6"/>
+      <c r="C65" s="6"/>
+      <c r="D65" s="6"/>
+      <c r="E65" s="6"/>
+      <c r="F65" s="7"/>
+      <c r="G65" s="6"/>
+      <c r="H65" s="6"/>
+      <c r="I65" s="6" t="str">
         <f t="array" ref="I65">_xlfn.SWITCH(H65,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J65" s="8"/>
-      <c r="K65" s="8"/>
-      <c r="L65" s="8"/>
+      <c r="J65" s="6"/>
+      <c r="K65" s="6"/>
+      <c r="L65" s="6"/>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A66" s="8"/>
-      <c r="B66" s="8"/>
-      <c r="C66" s="8"/>
-      <c r="D66" s="8"/>
-      <c r="E66" s="8"/>
-      <c r="F66" s="9"/>
-      <c r="G66" s="8"/>
-      <c r="H66" s="8"/>
-      <c r="I66" s="8" t="str">
+      <c r="A66" s="6"/>
+      <c r="B66" s="6"/>
+      <c r="C66" s="6"/>
+      <c r="D66" s="6"/>
+      <c r="E66" s="6"/>
+      <c r="F66" s="7"/>
+      <c r="G66" s="6"/>
+      <c r="H66" s="6"/>
+      <c r="I66" s="6" t="str">
         <f t="array" ref="I66">_xlfn.SWITCH(H66,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J66" s="8"/>
-      <c r="K66" s="8"/>
-      <c r="L66" s="8"/>
+      <c r="J66" s="6"/>
+      <c r="K66" s="6"/>
+      <c r="L66" s="6"/>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A67" s="8"/>
-      <c r="B67" s="8"/>
-      <c r="C67" s="8"/>
-      <c r="D67" s="8"/>
-      <c r="E67" s="8"/>
-      <c r="F67" s="7"/>
-      <c r="G67" s="8"/>
-      <c r="H67" s="8"/>
-      <c r="I67" s="8" t="str">
+      <c r="A67" s="6"/>
+      <c r="B67" s="6"/>
+      <c r="C67" s="6"/>
+      <c r="D67" s="6"/>
+      <c r="E67" s="6"/>
+      <c r="F67" s="5"/>
+      <c r="G67" s="6"/>
+      <c r="H67" s="6"/>
+      <c r="I67" s="6" t="str">
         <f t="array" ref="I67">_xlfn.SWITCH(H67,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J67" s="8"/>
-      <c r="K67" s="8"/>
-      <c r="L67" s="8"/>
+      <c r="J67" s="6"/>
+      <c r="K67" s="6"/>
+      <c r="L67" s="6"/>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A68" s="8"/>
-      <c r="B68" s="8"/>
-      <c r="C68" s="8"/>
-      <c r="D68" s="8"/>
-      <c r="E68" s="8"/>
-      <c r="F68" s="9"/>
-      <c r="G68" s="8"/>
-      <c r="H68" s="8"/>
-      <c r="I68" s="8" t="str">
+      <c r="A68" s="6"/>
+      <c r="B68" s="6"/>
+      <c r="C68" s="6"/>
+      <c r="D68" s="6"/>
+      <c r="E68" s="6"/>
+      <c r="F68" s="7"/>
+      <c r="G68" s="6"/>
+      <c r="H68" s="6"/>
+      <c r="I68" s="6" t="str">
         <f t="array" ref="I68">_xlfn.SWITCH(H68,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J68" s="8"/>
-      <c r="K68" s="8"/>
-      <c r="L68" s="8"/>
+      <c r="J68" s="6"/>
+      <c r="K68" s="6"/>
+      <c r="L68" s="6"/>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A69" s="8"/>
-      <c r="B69" s="8"/>
-      <c r="C69" s="8"/>
-      <c r="D69" s="8"/>
-      <c r="E69" s="8"/>
-      <c r="F69" s="7"/>
-      <c r="G69" s="8"/>
-      <c r="H69" s="8"/>
-      <c r="I69" s="8" t="str">
+      <c r="A69" s="6"/>
+      <c r="B69" s="6"/>
+      <c r="C69" s="6"/>
+      <c r="D69" s="6"/>
+      <c r="E69" s="6"/>
+      <c r="F69" s="5"/>
+      <c r="G69" s="6"/>
+      <c r="H69" s="6"/>
+      <c r="I69" s="6" t="str">
         <f t="array" ref="I69">_xlfn.SWITCH(H69,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J69" s="8"/>
-      <c r="K69" s="8"/>
-      <c r="L69" s="8"/>
+      <c r="J69" s="6"/>
+      <c r="K69" s="6"/>
+      <c r="L69" s="6"/>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A70" s="8"/>
-      <c r="B70" s="8"/>
-      <c r="C70" s="8"/>
-      <c r="D70" s="8"/>
-      <c r="E70" s="8"/>
-      <c r="F70" s="7"/>
-      <c r="G70" s="8"/>
-      <c r="H70" s="8"/>
-      <c r="I70" s="8" t="str">
+      <c r="A70" s="6"/>
+      <c r="B70" s="6"/>
+      <c r="C70" s="6"/>
+      <c r="D70" s="6"/>
+      <c r="E70" s="6"/>
+      <c r="F70" s="5"/>
+      <c r="G70" s="6"/>
+      <c r="H70" s="6"/>
+      <c r="I70" s="6" t="str">
         <f t="array" ref="I70">_xlfn.SWITCH(H70,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J70" s="8"/>
-      <c r="K70" s="8"/>
-      <c r="L70" s="8"/>
+      <c r="J70" s="6"/>
+      <c r="K70" s="6"/>
+      <c r="L70" s="6"/>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A71" s="8"/>
-      <c r="B71" s="8"/>
-      <c r="C71" s="8"/>
-      <c r="D71" s="8"/>
-      <c r="E71" s="8"/>
-      <c r="F71" s="9"/>
-      <c r="G71" s="8"/>
-      <c r="H71" s="8"/>
-      <c r="I71" s="8" t="str">
+      <c r="A71" s="6"/>
+      <c r="B71" s="6"/>
+      <c r="C71" s="6"/>
+      <c r="D71" s="6"/>
+      <c r="E71" s="6"/>
+      <c r="F71" s="7"/>
+      <c r="G71" s="6"/>
+      <c r="H71" s="6"/>
+      <c r="I71" s="6" t="str">
         <f t="array" ref="I71">_xlfn.SWITCH(H71,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J71" s="8"/>
-      <c r="K71" s="8"/>
-      <c r="L71" s="8"/>
+      <c r="J71" s="6"/>
+      <c r="K71" s="6"/>
+      <c r="L71" s="6"/>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A72" s="8"/>
-      <c r="B72" s="8"/>
-      <c r="C72" s="8"/>
-      <c r="D72" s="8"/>
-      <c r="E72" s="8"/>
-      <c r="F72" s="9"/>
-      <c r="G72" s="8"/>
-      <c r="H72" s="8"/>
-      <c r="I72" s="8" t="str">
+      <c r="A72" s="6"/>
+      <c r="B72" s="6"/>
+      <c r="C72" s="6"/>
+      <c r="D72" s="6"/>
+      <c r="E72" s="6"/>
+      <c r="F72" s="7"/>
+      <c r="G72" s="6"/>
+      <c r="H72" s="6"/>
+      <c r="I72" s="6" t="str">
         <f t="array" ref="I72">_xlfn.SWITCH(H72,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J72" s="8"/>
-      <c r="K72" s="8"/>
-      <c r="L72" s="8"/>
+      <c r="J72" s="6"/>
+      <c r="K72" s="6"/>
+      <c r="L72" s="6"/>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A73" s="8"/>
-      <c r="B73" s="8"/>
-      <c r="C73" s="8"/>
-      <c r="D73" s="8"/>
-      <c r="E73" s="8"/>
-      <c r="F73" s="9"/>
-      <c r="G73" s="8"/>
-      <c r="H73" s="8"/>
-      <c r="I73" s="8" t="str">
+      <c r="A73" s="6"/>
+      <c r="B73" s="6"/>
+      <c r="C73" s="6"/>
+      <c r="D73" s="6"/>
+      <c r="E73" s="6"/>
+      <c r="F73" s="7"/>
+      <c r="G73" s="6"/>
+      <c r="H73" s="6"/>
+      <c r="I73" s="6" t="str">
         <f t="array" ref="I73">_xlfn.SWITCH(H73,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J73" s="8"/>
-      <c r="K73" s="8"/>
-      <c r="L73" s="8"/>
+      <c r="J73" s="6"/>
+      <c r="K73" s="6"/>
+      <c r="L73" s="6"/>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A74" s="8"/>
-      <c r="B74" s="8"/>
-      <c r="C74" s="8"/>
-      <c r="D74" s="8"/>
-      <c r="E74" s="8"/>
-      <c r="F74" s="9"/>
-      <c r="G74" s="8"/>
-      <c r="H74" s="8"/>
-      <c r="I74" s="8" t="str">
+      <c r="A74" s="6"/>
+      <c r="B74" s="6"/>
+      <c r="C74" s="6"/>
+      <c r="D74" s="6"/>
+      <c r="E74" s="6"/>
+      <c r="F74" s="7"/>
+      <c r="G74" s="6"/>
+      <c r="H74" s="6"/>
+      <c r="I74" s="6" t="str">
         <f t="array" ref="I74">_xlfn.SWITCH(H74,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J74" s="8"/>
-      <c r="K74" s="8"/>
-      <c r="L74" s="8"/>
+      <c r="J74" s="6"/>
+      <c r="K74" s="6"/>
+      <c r="L74" s="6"/>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A75" s="8"/>
-      <c r="B75" s="8"/>
-      <c r="C75" s="8"/>
-      <c r="D75" s="8"/>
-      <c r="E75" s="8"/>
-      <c r="F75" s="9"/>
-      <c r="G75" s="8"/>
-      <c r="H75" s="8"/>
-      <c r="I75" s="8" t="str">
+      <c r="A75" s="6"/>
+      <c r="B75" s="6"/>
+      <c r="C75" s="6"/>
+      <c r="D75" s="6"/>
+      <c r="E75" s="6"/>
+      <c r="F75" s="7"/>
+      <c r="G75" s="6"/>
+      <c r="H75" s="6"/>
+      <c r="I75" s="6" t="str">
         <f t="array" ref="I75">_xlfn.SWITCH(H75,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J75" s="8"/>
-      <c r="K75" s="8"/>
-      <c r="L75" s="8"/>
+      <c r="J75" s="6"/>
+      <c r="K75" s="6"/>
+      <c r="L75" s="6"/>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A76" s="8"/>
-      <c r="B76" s="8"/>
-      <c r="C76" s="8"/>
-      <c r="D76" s="8"/>
-      <c r="E76" s="8"/>
-      <c r="F76" s="10"/>
-      <c r="G76" s="8"/>
-      <c r="H76" s="8"/>
-      <c r="I76" s="8" t="str">
+      <c r="A76" s="6"/>
+      <c r="B76" s="6"/>
+      <c r="C76" s="6"/>
+      <c r="D76" s="6"/>
+      <c r="E76" s="6"/>
+      <c r="F76" s="8"/>
+      <c r="G76" s="6"/>
+      <c r="H76" s="6"/>
+      <c r="I76" s="6" t="str">
         <f t="array" ref="I76">_xlfn.SWITCH(H76,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J76" s="8"/>
-      <c r="K76" s="8"/>
-      <c r="L76" s="8"/>
+      <c r="J76" s="6"/>
+      <c r="K76" s="6"/>
+      <c r="L76" s="6"/>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A77" s="8"/>
-      <c r="B77" s="8"/>
-      <c r="C77" s="8"/>
-      <c r="D77" s="8"/>
-      <c r="E77" s="8"/>
-      <c r="F77" s="10"/>
-      <c r="G77" s="8"/>
-      <c r="H77" s="8"/>
-      <c r="I77" s="8" t="str">
+      <c r="A77" s="6"/>
+      <c r="B77" s="6"/>
+      <c r="C77" s="6"/>
+      <c r="D77" s="6"/>
+      <c r="E77" s="6"/>
+      <c r="F77" s="8"/>
+      <c r="G77" s="6"/>
+      <c r="H77" s="6"/>
+      <c r="I77" s="6" t="str">
         <f t="array" ref="I77">_xlfn.SWITCH(H77,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J77" s="8"/>
-      <c r="K77" s="8"/>
-      <c r="L77" s="8"/>
+      <c r="J77" s="6"/>
+      <c r="K77" s="6"/>
+      <c r="L77" s="6"/>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A78" s="8"/>
-      <c r="B78" s="8"/>
-      <c r="C78" s="8"/>
-      <c r="D78" s="8"/>
-      <c r="E78" s="8"/>
-      <c r="F78" s="10"/>
-      <c r="G78" s="8"/>
-      <c r="H78" s="8"/>
-      <c r="I78" s="8" t="str">
+      <c r="A78" s="6"/>
+      <c r="B78" s="6"/>
+      <c r="C78" s="6"/>
+      <c r="D78" s="6"/>
+      <c r="E78" s="6"/>
+      <c r="F78" s="8"/>
+      <c r="G78" s="6"/>
+      <c r="H78" s="6"/>
+      <c r="I78" s="6" t="str">
         <f t="array" ref="I78">_xlfn.SWITCH(H78,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J78" s="8"/>
-      <c r="K78" s="8"/>
-      <c r="L78" s="8"/>
+      <c r="J78" s="6"/>
+      <c r="K78" s="6"/>
+      <c r="L78" s="6"/>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A79" s="8"/>
-      <c r="B79" s="8"/>
-      <c r="C79" s="8"/>
-      <c r="D79" s="8"/>
-      <c r="E79" s="8"/>
-      <c r="F79" s="10"/>
-      <c r="G79" s="8"/>
-      <c r="H79" s="8"/>
-      <c r="I79" s="8" t="str">
+      <c r="A79" s="6"/>
+      <c r="B79" s="6"/>
+      <c r="C79" s="6"/>
+      <c r="D79" s="6"/>
+      <c r="E79" s="6"/>
+      <c r="F79" s="8"/>
+      <c r="G79" s="6"/>
+      <c r="H79" s="6"/>
+      <c r="I79" s="6" t="str">
         <f t="array" ref="I79">_xlfn.SWITCH(H79,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J79" s="8"/>
-      <c r="K79" s="8"/>
-      <c r="L79" s="8"/>
+      <c r="J79" s="6"/>
+      <c r="K79" s="6"/>
+      <c r="L79" s="6"/>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A80" s="8"/>
-      <c r="B80" s="8"/>
-      <c r="C80" s="8"/>
-      <c r="D80" s="8"/>
-      <c r="E80" s="8"/>
-      <c r="F80" s="10"/>
-      <c r="G80" s="8"/>
-      <c r="H80" s="8"/>
-      <c r="I80" s="8" t="str">
+      <c r="A80" s="6"/>
+      <c r="B80" s="6"/>
+      <c r="C80" s="6"/>
+      <c r="D80" s="6"/>
+      <c r="E80" s="6"/>
+      <c r="F80" s="8"/>
+      <c r="G80" s="6"/>
+      <c r="H80" s="6"/>
+      <c r="I80" s="6" t="str">
         <f t="array" ref="I80">_xlfn.SWITCH(H80,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J80" s="8"/>
-      <c r="K80" s="8"/>
-      <c r="L80" s="8"/>
+      <c r="J80" s="6"/>
+      <c r="K80" s="6"/>
+      <c r="L80" s="6"/>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A81" s="8"/>
-      <c r="B81" s="8"/>
-      <c r="C81" s="8"/>
-      <c r="D81" s="8"/>
-      <c r="E81" s="8"/>
-      <c r="F81" s="10"/>
-      <c r="G81" s="8"/>
-      <c r="H81" s="8"/>
-      <c r="I81" s="8" t="str">
+      <c r="A81" s="6"/>
+      <c r="B81" s="6"/>
+      <c r="C81" s="6"/>
+      <c r="D81" s="6"/>
+      <c r="E81" s="6"/>
+      <c r="F81" s="8"/>
+      <c r="G81" s="6"/>
+      <c r="H81" s="6"/>
+      <c r="I81" s="6" t="str">
         <f t="array" ref="I81">_xlfn.SWITCH(H81,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J81" s="8"/>
-      <c r="K81" s="8"/>
-      <c r="L81" s="8"/>
+      <c r="J81" s="6"/>
+      <c r="K81" s="6"/>
+      <c r="L81" s="6"/>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A82" s="8"/>
-      <c r="B82" s="8"/>
-      <c r="C82" s="8"/>
-      <c r="D82" s="8"/>
-      <c r="E82" s="8"/>
-      <c r="F82" s="10"/>
-      <c r="G82" s="8"/>
-      <c r="H82" s="8"/>
-      <c r="I82" s="8" t="str">
+      <c r="A82" s="6"/>
+      <c r="B82" s="6"/>
+      <c r="C82" s="6"/>
+      <c r="D82" s="6"/>
+      <c r="E82" s="6"/>
+      <c r="F82" s="8"/>
+      <c r="G82" s="6"/>
+      <c r="H82" s="6"/>
+      <c r="I82" s="6" t="str">
         <f t="array" ref="I82">_xlfn.SWITCH(H82,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J82" s="8"/>
-      <c r="K82" s="8"/>
-      <c r="L82" s="8"/>
+      <c r="J82" s="6"/>
+      <c r="K82" s="6"/>
+      <c r="L82" s="6"/>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A83" s="8"/>
-      <c r="B83" s="8"/>
-      <c r="C83" s="8"/>
-      <c r="D83" s="8"/>
-      <c r="E83" s="8"/>
-      <c r="F83" s="10"/>
-      <c r="G83" s="8"/>
-      <c r="H83" s="8"/>
-      <c r="I83" s="8" t="str">
+      <c r="A83" s="6"/>
+      <c r="B83" s="6"/>
+      <c r="C83" s="6"/>
+      <c r="D83" s="6"/>
+      <c r="E83" s="6"/>
+      <c r="F83" s="8"/>
+      <c r="G83" s="6"/>
+      <c r="H83" s="6"/>
+      <c r="I83" s="6" t="str">
         <f t="array" ref="I83">_xlfn.SWITCH(H83,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J83" s="8"/>
-      <c r="K83" s="8"/>
-      <c r="L83" s="8"/>
+      <c r="J83" s="6"/>
+      <c r="K83" s="6"/>
+      <c r="L83" s="6"/>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A84" s="8"/>
-      <c r="B84" s="8"/>
-      <c r="C84" s="8"/>
-      <c r="D84" s="8"/>
-      <c r="E84" s="8"/>
-      <c r="F84" s="10"/>
-      <c r="G84" s="8"/>
-      <c r="H84" s="8"/>
-      <c r="I84" s="8" t="str">
+      <c r="A84" s="6"/>
+      <c r="B84" s="6"/>
+      <c r="C84" s="6"/>
+      <c r="D84" s="6"/>
+      <c r="E84" s="6"/>
+      <c r="F84" s="8"/>
+      <c r="G84" s="6"/>
+      <c r="H84" s="6"/>
+      <c r="I84" s="6" t="str">
         <f t="array" ref="I84">_xlfn.SWITCH(H84,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J84" s="8"/>
-      <c r="K84" s="8"/>
-      <c r="L84" s="8"/>
+      <c r="J84" s="6"/>
+      <c r="K84" s="6"/>
+      <c r="L84" s="6"/>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A85" s="8"/>
-      <c r="B85" s="8"/>
-      <c r="C85" s="8"/>
-      <c r="D85" s="8"/>
-      <c r="E85" s="8"/>
-      <c r="F85" s="10"/>
-      <c r="G85" s="8"/>
-      <c r="H85" s="8"/>
-      <c r="I85" s="8" t="str">
+      <c r="A85" s="6"/>
+      <c r="B85" s="6"/>
+      <c r="C85" s="6"/>
+      <c r="D85" s="6"/>
+      <c r="E85" s="6"/>
+      <c r="F85" s="8"/>
+      <c r="G85" s="6"/>
+      <c r="H85" s="6"/>
+      <c r="I85" s="6" t="str">
         <f t="array" ref="I85">_xlfn.SWITCH(H85,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J85" s="8"/>
-      <c r="K85" s="8"/>
-      <c r="L85" s="8"/>
+      <c r="J85" s="6"/>
+      <c r="K85" s="6"/>
+      <c r="L85" s="6"/>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A86" s="8"/>
-      <c r="B86" s="8"/>
-      <c r="C86" s="8"/>
-      <c r="D86" s="8"/>
-      <c r="E86" s="8"/>
-      <c r="F86" s="10"/>
-      <c r="G86" s="8"/>
-      <c r="H86" s="8"/>
-      <c r="I86" s="8" t="str">
+      <c r="A86" s="6"/>
+      <c r="B86" s="6"/>
+      <c r="C86" s="6"/>
+      <c r="D86" s="6"/>
+      <c r="E86" s="6"/>
+      <c r="F86" s="8"/>
+      <c r="G86" s="6"/>
+      <c r="H86" s="6"/>
+      <c r="I86" s="6" t="str">
         <f t="array" ref="I86">_xlfn.SWITCH(H86,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J86" s="8"/>
-      <c r="K86" s="8"/>
-      <c r="L86" s="8"/>
+      <c r="J86" s="6"/>
+      <c r="K86" s="6"/>
+      <c r="L86" s="6"/>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A87" s="8"/>
-      <c r="B87" s="8"/>
-      <c r="C87" s="8"/>
-      <c r="D87" s="8"/>
-      <c r="E87" s="8"/>
-      <c r="F87" s="10"/>
-      <c r="G87" s="8"/>
-      <c r="H87" s="8"/>
-      <c r="I87" s="8" t="str">
+      <c r="A87" s="6"/>
+      <c r="B87" s="6"/>
+      <c r="C87" s="6"/>
+      <c r="D87" s="6"/>
+      <c r="E87" s="6"/>
+      <c r="F87" s="8"/>
+      <c r="G87" s="6"/>
+      <c r="H87" s="6"/>
+      <c r="I87" s="6" t="str">
         <f t="array" ref="I87">_xlfn.SWITCH(H87,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J87" s="8"/>
-      <c r="K87" s="8"/>
-      <c r="L87" s="8"/>
+      <c r="J87" s="6"/>
+      <c r="K87" s="6"/>
+      <c r="L87" s="6"/>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A88" s="8"/>
-      <c r="B88" s="8"/>
-      <c r="C88" s="8"/>
-      <c r="D88" s="8"/>
-      <c r="E88" s="8"/>
-      <c r="F88" s="10"/>
-      <c r="G88" s="8"/>
-      <c r="H88" s="8"/>
-      <c r="I88" s="8" t="str">
+      <c r="A88" s="6"/>
+      <c r="B88" s="6"/>
+      <c r="C88" s="6"/>
+      <c r="D88" s="6"/>
+      <c r="E88" s="6"/>
+      <c r="F88" s="8"/>
+      <c r="G88" s="6"/>
+      <c r="H88" s="6"/>
+      <c r="I88" s="6" t="str">
         <f t="array" ref="I88">_xlfn.SWITCH(H88,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J88" s="8"/>
-      <c r="K88" s="8"/>
-      <c r="L88" s="8"/>
+      <c r="J88" s="6"/>
+      <c r="K88" s="6"/>
+      <c r="L88" s="6"/>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A89" s="8"/>
-      <c r="B89" s="8"/>
-      <c r="C89" s="8"/>
-      <c r="D89" s="8"/>
-      <c r="E89" s="8"/>
-      <c r="F89" s="10"/>
-      <c r="G89" s="8"/>
-      <c r="H89" s="8"/>
-      <c r="I89" s="8" t="str">
+      <c r="A89" s="6"/>
+      <c r="B89" s="6"/>
+      <c r="C89" s="6"/>
+      <c r="D89" s="6"/>
+      <c r="E89" s="6"/>
+      <c r="F89" s="8"/>
+      <c r="G89" s="6"/>
+      <c r="H89" s="6"/>
+      <c r="I89" s="6" t="str">
         <f t="array" ref="I89">_xlfn.SWITCH(H89,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J89" s="8"/>
-      <c r="K89" s="8"/>
-      <c r="L89" s="8"/>
+      <c r="J89" s="6"/>
+      <c r="K89" s="6"/>
+      <c r="L89" s="6"/>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A90" s="8"/>
-      <c r="B90" s="8"/>
-      <c r="C90" s="8"/>
-      <c r="D90" s="8"/>
-      <c r="E90" s="8"/>
-      <c r="F90" s="10"/>
-      <c r="G90" s="8"/>
-      <c r="H90" s="8"/>
-      <c r="I90" s="8" t="str">
+      <c r="A90" s="6"/>
+      <c r="B90" s="6"/>
+      <c r="C90" s="6"/>
+      <c r="D90" s="6"/>
+      <c r="E90" s="6"/>
+      <c r="F90" s="8"/>
+      <c r="G90" s="6"/>
+      <c r="H90" s="6"/>
+      <c r="I90" s="6" t="str">
         <f t="array" ref="I90">_xlfn.SWITCH(H90,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J90" s="8"/>
-      <c r="K90" s="8"/>
-      <c r="L90" s="8"/>
+      <c r="J90" s="6"/>
+      <c r="K90" s="6"/>
+      <c r="L90" s="6"/>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A91" s="8"/>
-      <c r="B91" s="8"/>
-      <c r="C91" s="8"/>
-      <c r="D91" s="8"/>
-      <c r="E91" s="8"/>
-      <c r="F91" s="10"/>
-      <c r="G91" s="8"/>
-      <c r="H91" s="8"/>
-      <c r="I91" s="8" t="str">
+      <c r="A91" s="6"/>
+      <c r="B91" s="6"/>
+      <c r="C91" s="6"/>
+      <c r="D91" s="6"/>
+      <c r="E91" s="6"/>
+      <c r="F91" s="8"/>
+      <c r="G91" s="6"/>
+      <c r="H91" s="6"/>
+      <c r="I91" s="6" t="str">
         <f t="array" ref="I91">_xlfn.SWITCH(H91,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J91" s="8"/>
-      <c r="K91" s="8"/>
-      <c r="L91" s="8"/>
+      <c r="J91" s="6"/>
+      <c r="K91" s="6"/>
+      <c r="L91" s="6"/>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A92" s="8"/>
-      <c r="B92" s="8"/>
-      <c r="C92" s="8"/>
-      <c r="D92" s="8"/>
-      <c r="E92" s="8"/>
-      <c r="F92" s="10"/>
-      <c r="G92" s="8"/>
-      <c r="H92" s="8"/>
-      <c r="I92" s="8" t="str">
+      <c r="A92" s="6"/>
+      <c r="B92" s="6"/>
+      <c r="C92" s="6"/>
+      <c r="D92" s="6"/>
+      <c r="E92" s="6"/>
+      <c r="F92" s="8"/>
+      <c r="G92" s="6"/>
+      <c r="H92" s="6"/>
+      <c r="I92" s="6" t="str">
         <f t="array" ref="I92">_xlfn.SWITCH(H92,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J92" s="8"/>
-      <c r="K92" s="8"/>
-      <c r="L92" s="8"/>
+      <c r="J92" s="6"/>
+      <c r="K92" s="6"/>
+      <c r="L92" s="6"/>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A93" s="8"/>
-      <c r="B93" s="8"/>
-      <c r="C93" s="8"/>
-      <c r="D93" s="8"/>
-      <c r="E93" s="8"/>
-      <c r="F93" s="10"/>
-      <c r="G93" s="8"/>
-      <c r="H93" s="8"/>
-      <c r="I93" s="8" t="str">
+      <c r="A93" s="6"/>
+      <c r="B93" s="6"/>
+      <c r="C93" s="6"/>
+      <c r="D93" s="6"/>
+      <c r="E93" s="6"/>
+      <c r="F93" s="8"/>
+      <c r="G93" s="6"/>
+      <c r="H93" s="6"/>
+      <c r="I93" s="6" t="str">
         <f t="array" ref="I93">_xlfn.SWITCH(H93,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J93" s="8"/>
-      <c r="K93" s="8"/>
-      <c r="L93" s="8"/>
+      <c r="J93" s="6"/>
+      <c r="K93" s="6"/>
+      <c r="L93" s="6"/>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A94" s="8"/>
-      <c r="B94" s="8"/>
-      <c r="C94" s="8"/>
-      <c r="D94" s="8"/>
-      <c r="E94" s="8"/>
-      <c r="F94" s="10"/>
-      <c r="G94" s="8"/>
-      <c r="H94" s="8"/>
-      <c r="I94" s="8" t="str">
+      <c r="A94" s="6"/>
+      <c r="B94" s="6"/>
+      <c r="C94" s="6"/>
+      <c r="D94" s="6"/>
+      <c r="E94" s="6"/>
+      <c r="F94" s="8"/>
+      <c r="G94" s="6"/>
+      <c r="H94" s="6"/>
+      <c r="I94" s="6" t="str">
         <f t="array" ref="I94">_xlfn.SWITCH(H94,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J94" s="8"/>
-      <c r="K94" s="8"/>
-      <c r="L94" s="8"/>
+      <c r="J94" s="6"/>
+      <c r="K94" s="6"/>
+      <c r="L94" s="6"/>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A95" s="8"/>
-      <c r="B95" s="8"/>
-      <c r="C95" s="8"/>
-      <c r="D95" s="8"/>
-      <c r="E95" s="8"/>
-      <c r="F95" s="10"/>
-      <c r="G95" s="8"/>
-      <c r="H95" s="8"/>
-      <c r="I95" s="8" t="str">
+      <c r="A95" s="6"/>
+      <c r="B95" s="6"/>
+      <c r="C95" s="6"/>
+      <c r="D95" s="6"/>
+      <c r="E95" s="6"/>
+      <c r="F95" s="8"/>
+      <c r="G95" s="6"/>
+      <c r="H95" s="6"/>
+      <c r="I95" s="6" t="str">
         <f t="array" ref="I95">_xlfn.SWITCH(H95,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J95" s="8"/>
-      <c r="K95" s="8"/>
-      <c r="L95" s="8"/>
+      <c r="J95" s="6"/>
+      <c r="K95" s="6"/>
+      <c r="L95" s="6"/>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A96" s="8"/>
-      <c r="B96" s="8"/>
-      <c r="C96" s="8"/>
-      <c r="D96" s="8"/>
-      <c r="E96" s="8"/>
-      <c r="F96" s="10"/>
-      <c r="G96" s="8"/>
-      <c r="H96" s="8"/>
-      <c r="I96" s="8" t="str">
+      <c r="A96" s="6"/>
+      <c r="B96" s="6"/>
+      <c r="C96" s="6"/>
+      <c r="D96" s="6"/>
+      <c r="E96" s="6"/>
+      <c r="F96" s="8"/>
+      <c r="G96" s="6"/>
+      <c r="H96" s="6"/>
+      <c r="I96" s="6" t="str">
         <f t="array" ref="I96">_xlfn.SWITCH(H96,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J96" s="8"/>
-      <c r="K96" s="8"/>
-      <c r="L96" s="8"/>
+      <c r="J96" s="6"/>
+      <c r="K96" s="6"/>
+      <c r="L96" s="6"/>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A97" s="8"/>
-      <c r="B97" s="8"/>
-      <c r="C97" s="8"/>
-      <c r="D97" s="8"/>
-      <c r="E97" s="8"/>
-      <c r="F97" s="10"/>
-      <c r="G97" s="8"/>
-      <c r="H97" s="8"/>
-      <c r="I97" s="8" t="str">
+      <c r="A97" s="6"/>
+      <c r="B97" s="6"/>
+      <c r="C97" s="6"/>
+      <c r="D97" s="6"/>
+      <c r="E97" s="6"/>
+      <c r="F97" s="8"/>
+      <c r="G97" s="6"/>
+      <c r="H97" s="6"/>
+      <c r="I97" s="6" t="str">
         <f t="array" ref="I97">_xlfn.SWITCH(H97,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J97" s="8"/>
-      <c r="K97" s="8"/>
-      <c r="L97" s="8"/>
+      <c r="J97" s="6"/>
+      <c r="K97" s="6"/>
+      <c r="L97" s="6"/>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A98" s="8"/>
-      <c r="B98" s="8"/>
-      <c r="C98" s="8"/>
-      <c r="D98" s="8"/>
-      <c r="E98" s="8"/>
-      <c r="F98" s="10"/>
-      <c r="G98" s="8"/>
-      <c r="H98" s="8"/>
-      <c r="I98" s="8" t="str">
+      <c r="A98" s="6"/>
+      <c r="B98" s="6"/>
+      <c r="C98" s="6"/>
+      <c r="D98" s="6"/>
+      <c r="E98" s="6"/>
+      <c r="F98" s="8"/>
+      <c r="G98" s="6"/>
+      <c r="H98" s="6"/>
+      <c r="I98" s="6" t="str">
         <f t="array" ref="I98">_xlfn.SWITCH(H98,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J98" s="8"/>
-      <c r="K98" s="8"/>
-      <c r="L98" s="8"/>
+      <c r="J98" s="6"/>
+      <c r="K98" s="6"/>
+      <c r="L98" s="6"/>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A99" s="8"/>
-      <c r="B99" s="8"/>
-      <c r="C99" s="8"/>
-      <c r="D99" s="8"/>
-      <c r="E99" s="8"/>
-      <c r="F99" s="10"/>
-      <c r="G99" s="8"/>
-      <c r="H99" s="8"/>
-      <c r="I99" s="8" t="str">
+      <c r="A99" s="6"/>
+      <c r="B99" s="6"/>
+      <c r="C99" s="6"/>
+      <c r="D99" s="6"/>
+      <c r="E99" s="6"/>
+      <c r="F99" s="8"/>
+      <c r="G99" s="6"/>
+      <c r="H99" s="6"/>
+      <c r="I99" s="6" t="str">
         <f t="array" ref="I99">_xlfn.SWITCH(H99,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J99" s="8"/>
-      <c r="K99" s="8"/>
-      <c r="L99" s="8"/>
+      <c r="J99" s="6"/>
+      <c r="K99" s="6"/>
+      <c r="L99" s="6"/>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A100" s="8"/>
-      <c r="B100" s="8"/>
-      <c r="C100" s="8"/>
-      <c r="D100" s="8"/>
-      <c r="E100" s="8"/>
-      <c r="F100" s="10"/>
-      <c r="G100" s="8"/>
-      <c r="H100" s="8"/>
-      <c r="I100" s="8" t="str">
+      <c r="A100" s="6"/>
+      <c r="B100" s="6"/>
+      <c r="C100" s="6"/>
+      <c r="D100" s="6"/>
+      <c r="E100" s="6"/>
+      <c r="F100" s="8"/>
+      <c r="G100" s="6"/>
+      <c r="H100" s="6"/>
+      <c r="I100" s="6" t="str">
         <f t="array" ref="I100">_xlfn.SWITCH(H100,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J100" s="8"/>
-      <c r="K100" s="8"/>
-      <c r="L100" s="8"/>
+      <c r="J100" s="6"/>
+      <c r="K100" s="6"/>
+      <c r="L100" s="6"/>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A101" s="8"/>
-      <c r="B101" s="8"/>
-      <c r="C101" s="8"/>
-      <c r="D101" s="8"/>
-      <c r="E101" s="8"/>
-      <c r="F101" s="10"/>
-      <c r="G101" s="8"/>
-      <c r="H101" s="8"/>
-      <c r="I101" s="8" t="str">
+      <c r="A101" s="6"/>
+      <c r="B101" s="6"/>
+      <c r="C101" s="6"/>
+      <c r="D101" s="6"/>
+      <c r="E101" s="6"/>
+      <c r="F101" s="8"/>
+      <c r="G101" s="6"/>
+      <c r="H101" s="6"/>
+      <c r="I101" s="6" t="str">
         <f t="array" ref="I101">_xlfn.SWITCH(H101,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J101" s="8"/>
-      <c r="K101" s="8"/>
-      <c r="L101" s="8"/>
+      <c r="J101" s="6"/>
+      <c r="K101" s="6"/>
+      <c r="L101" s="6"/>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A102" s="8"/>
-      <c r="B102" s="8"/>
-      <c r="C102" s="8"/>
-      <c r="D102" s="8"/>
-      <c r="E102" s="8"/>
-      <c r="F102" s="10"/>
-      <c r="G102" s="8"/>
-      <c r="H102" s="8"/>
-      <c r="I102" s="8" t="str">
+      <c r="A102" s="6"/>
+      <c r="B102" s="6"/>
+      <c r="C102" s="6"/>
+      <c r="D102" s="6"/>
+      <c r="E102" s="6"/>
+      <c r="F102" s="8"/>
+      <c r="G102" s="6"/>
+      <c r="H102" s="6"/>
+      <c r="I102" s="6" t="str">
         <f t="array" ref="I102">_xlfn.SWITCH(H102,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J102" s="8"/>
-      <c r="K102" s="8"/>
-      <c r="L102" s="8"/>
+      <c r="J102" s="6"/>
+      <c r="K102" s="6"/>
+      <c r="L102" s="6"/>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A103" s="8"/>
-      <c r="B103" s="8"/>
-      <c r="C103" s="8"/>
-      <c r="D103" s="8"/>
-      <c r="E103" s="8"/>
-      <c r="F103" s="10"/>
-      <c r="G103" s="8"/>
-      <c r="H103" s="8"/>
-      <c r="I103" s="8" t="str">
+      <c r="A103" s="6"/>
+      <c r="B103" s="6"/>
+      <c r="C103" s="6"/>
+      <c r="D103" s="6"/>
+      <c r="E103" s="6"/>
+      <c r="F103" s="8"/>
+      <c r="G103" s="6"/>
+      <c r="H103" s="6"/>
+      <c r="I103" s="6" t="str">
         <f t="array" ref="I103">_xlfn.SWITCH(H103,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J103" s="8"/>
-      <c r="K103" s="8"/>
-      <c r="L103" s="8"/>
+      <c r="J103" s="6"/>
+      <c r="K103" s="6"/>
+      <c r="L103" s="6"/>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A104" s="8"/>
-      <c r="B104" s="8"/>
-      <c r="C104" s="8"/>
-      <c r="D104" s="8"/>
-      <c r="E104" s="8"/>
-      <c r="F104" s="10"/>
-      <c r="G104" s="8"/>
-      <c r="H104" s="8"/>
-      <c r="I104" s="8" t="str">
+      <c r="A104" s="6"/>
+      <c r="B104" s="6"/>
+      <c r="C104" s="6"/>
+      <c r="D104" s="6"/>
+      <c r="E104" s="6"/>
+      <c r="F104" s="8"/>
+      <c r="G104" s="6"/>
+      <c r="H104" s="6"/>
+      <c r="I104" s="6" t="str">
         <f t="array" ref="I104">_xlfn.SWITCH(H104,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J104" s="8"/>
-      <c r="K104" s="8"/>
-      <c r="L104" s="8"/>
+      <c r="J104" s="6"/>
+      <c r="K104" s="6"/>
+      <c r="L104" s="6"/>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A105" s="8"/>
-      <c r="B105" s="8"/>
-      <c r="C105" s="8"/>
-      <c r="D105" s="8"/>
-      <c r="E105" s="8"/>
-      <c r="F105" s="10"/>
-      <c r="G105" s="8"/>
-      <c r="H105" s="8"/>
-      <c r="I105" s="8" t="str">
+      <c r="A105" s="6"/>
+      <c r="B105" s="6"/>
+      <c r="C105" s="6"/>
+      <c r="D105" s="6"/>
+      <c r="E105" s="6"/>
+      <c r="F105" s="8"/>
+      <c r="G105" s="6"/>
+      <c r="H105" s="6"/>
+      <c r="I105" s="6" t="str">
         <f t="array" ref="I105">_xlfn.SWITCH(H105,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J105" s="8"/>
-      <c r="K105" s="8"/>
-      <c r="L105" s="8"/>
+      <c r="J105" s="6"/>
+      <c r="K105" s="6"/>
+      <c r="L105" s="6"/>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A106" s="8"/>
-      <c r="B106" s="8"/>
-      <c r="C106" s="8"/>
-      <c r="D106" s="8"/>
-      <c r="E106" s="8"/>
-      <c r="F106" s="10"/>
-      <c r="G106" s="8"/>
-      <c r="H106" s="8"/>
-      <c r="I106" s="8" t="str">
+      <c r="A106" s="6"/>
+      <c r="B106" s="6"/>
+      <c r="C106" s="6"/>
+      <c r="D106" s="6"/>
+      <c r="E106" s="6"/>
+      <c r="F106" s="8"/>
+      <c r="G106" s="6"/>
+      <c r="H106" s="6"/>
+      <c r="I106" s="6" t="str">
         <f t="array" ref="I106">_xlfn.SWITCH(H106,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J106" s="8"/>
-      <c r="K106" s="8"/>
-      <c r="L106" s="8"/>
+      <c r="J106" s="6"/>
+      <c r="K106" s="6"/>
+      <c r="L106" s="6"/>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A107" s="8"/>
-      <c r="B107" s="8"/>
-      <c r="C107" s="8"/>
-      <c r="D107" s="8"/>
-      <c r="E107" s="8"/>
-      <c r="F107" s="10"/>
-      <c r="G107" s="8"/>
-      <c r="H107" s="8"/>
-      <c r="I107" s="8" t="str">
+      <c r="A107" s="6"/>
+      <c r="B107" s="6"/>
+      <c r="C107" s="6"/>
+      <c r="D107" s="6"/>
+      <c r="E107" s="6"/>
+      <c r="F107" s="8"/>
+      <c r="G107" s="6"/>
+      <c r="H107" s="6"/>
+      <c r="I107" s="6" t="str">
         <f t="array" ref="I107">_xlfn.SWITCH(H107,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J107" s="8"/>
-      <c r="K107" s="8"/>
-      <c r="L107" s="8"/>
+      <c r="J107" s="6"/>
+      <c r="K107" s="6"/>
+      <c r="L107" s="6"/>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A108" s="8"/>
-      <c r="B108" s="8"/>
-      <c r="C108" s="8"/>
-      <c r="D108" s="8"/>
-      <c r="E108" s="8"/>
-      <c r="F108" s="10"/>
-      <c r="G108" s="8"/>
-      <c r="H108" s="8"/>
-      <c r="I108" s="8" t="str">
+      <c r="A108" s="6"/>
+      <c r="B108" s="6"/>
+      <c r="C108" s="6"/>
+      <c r="D108" s="6"/>
+      <c r="E108" s="6"/>
+      <c r="F108" s="8"/>
+      <c r="G108" s="6"/>
+      <c r="H108" s="6"/>
+      <c r="I108" s="6" t="str">
         <f t="array" ref="I108">_xlfn.SWITCH(H108,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J108" s="8"/>
-      <c r="K108" s="8"/>
-      <c r="L108" s="8"/>
+      <c r="J108" s="6"/>
+      <c r="K108" s="6"/>
+      <c r="L108" s="6"/>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A109" s="8"/>
-      <c r="B109" s="8"/>
-      <c r="C109" s="8"/>
-      <c r="D109" s="8"/>
-      <c r="E109" s="8"/>
-      <c r="F109" s="10"/>
-      <c r="G109" s="8"/>
-      <c r="H109" s="8"/>
-      <c r="I109" s="8" t="str">
+      <c r="A109" s="6"/>
+      <c r="B109" s="6"/>
+      <c r="C109" s="6"/>
+      <c r="D109" s="6"/>
+      <c r="E109" s="6"/>
+      <c r="F109" s="8"/>
+      <c r="G109" s="6"/>
+      <c r="H109" s="6"/>
+      <c r="I109" s="6" t="str">
         <f t="array" ref="I109">_xlfn.SWITCH(H109,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J109" s="8"/>
-      <c r="K109" s="8"/>
-      <c r="L109" s="8"/>
+      <c r="J109" s="6"/>
+      <c r="K109" s="6"/>
+      <c r="L109" s="6"/>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A110" s="8"/>
-      <c r="B110" s="8"/>
-      <c r="C110" s="8"/>
-      <c r="D110" s="8"/>
-      <c r="E110" s="8"/>
-      <c r="F110" s="10"/>
-      <c r="G110" s="8"/>
-      <c r="H110" s="8"/>
-      <c r="I110" s="8" t="str">
+      <c r="A110" s="6"/>
+      <c r="B110" s="6"/>
+      <c r="C110" s="6"/>
+      <c r="D110" s="6"/>
+      <c r="E110" s="6"/>
+      <c r="F110" s="8"/>
+      <c r="G110" s="6"/>
+      <c r="H110" s="6"/>
+      <c r="I110" s="6" t="str">
         <f t="array" ref="I110">_xlfn.SWITCH(H110,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J110" s="8"/>
-      <c r="K110" s="8"/>
-      <c r="L110" s="8"/>
+      <c r="J110" s="6"/>
+      <c r="K110" s="6"/>
+      <c r="L110" s="6"/>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A111" s="8"/>
-      <c r="B111" s="8"/>
-      <c r="C111" s="8"/>
-      <c r="D111" s="8"/>
-      <c r="E111" s="8"/>
-      <c r="F111" s="10"/>
-      <c r="G111" s="8"/>
-      <c r="H111" s="8"/>
-      <c r="I111" s="8" t="str">
+      <c r="A111" s="6"/>
+      <c r="B111" s="6"/>
+      <c r="C111" s="6"/>
+      <c r="D111" s="6"/>
+      <c r="E111" s="6"/>
+      <c r="F111" s="8"/>
+      <c r="G111" s="6"/>
+      <c r="H111" s="6"/>
+      <c r="I111" s="6" t="str">
         <f t="array" ref="I111">_xlfn.SWITCH(H111,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v/>
       </c>
-      <c r="J111" s="8"/>
-      <c r="K111" s="8"/>
-      <c r="L111" s="8"/>
+      <c r="J111" s="6"/>
+      <c r="K111" s="6"/>
+      <c r="L111" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13296,199 +13315,199 @@
   <dimension ref="A1:L10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.77734375" style="5" customWidth="1"/>
-    <col min="4" max="4" width="10.77734375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" style="2"/>
+    <col min="1" max="1" width="4.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.77734375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="10.77734375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="24" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
+      <c r="A2" s="19">
         <v>0</v>
       </c>
-      <c r="B2" s="14">
+      <c r="B2" s="20">
         <v>46251</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="21">
         <f>75-SUM(E$2:E2)</f>
         <v>75</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="22">
         <f>75*(1-(A2/8))</f>
         <v>75</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
+      <c r="A3" s="19">
         <v>1</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="20">
         <v>46252</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="21">
         <f>75-SUM(E$2:E3)</f>
         <v>75</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="22">
         <f t="shared" ref="D3:D10" si="0">75*(1-(A3/8))</f>
         <v>65.625</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
+      <c r="A4" s="19">
         <v>2</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="20">
         <v>46253</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="21">
         <f>75-SUM(E$2:E4)</f>
         <v>75</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="22">
         <f t="shared" si="0"/>
         <v>56.25</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="22">
         <v>0</v>
       </c>
-      <c r="L4" s="3"/>
+      <c r="L4" s="2"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
+      <c r="A5" s="19">
         <v>3</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="20">
         <v>46254</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="21">
         <f>75-SUM(E$2:E5)</f>
         <v>75</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="22">
         <f t="shared" si="0"/>
         <v>46.875</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
+      <c r="A6" s="19">
         <v>4</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="20">
         <v>46255</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="21">
         <f>75-SUM(E$2:E6)</f>
         <v>75</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="22">
         <f t="shared" si="0"/>
         <v>37.5</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
+      <c r="A7" s="19">
         <v>5</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="20">
         <v>46258</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="21">
         <f>75-SUM(E$2:E7)</f>
         <v>75</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="22">
         <f t="shared" si="0"/>
         <v>28.125</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
+      <c r="A8" s="19">
         <v>6</v>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="20">
         <v>46259</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="21">
         <f>75-SUM(E$2:E8)</f>
         <v>75</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="22">
         <f t="shared" si="0"/>
         <v>18.75</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
+      <c r="A9" s="19">
         <v>7</v>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="20">
         <v>46260</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="21">
         <f>75-SUM(E$2:E9)</f>
         <v>75</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="22">
         <f t="shared" si="0"/>
         <v>9.375</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
+      <c r="A10" s="19">
         <v>8</v>
       </c>
-      <c r="B10" s="14">
+      <c r="B10" s="20">
         <v>46261</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="21">
         <f>75-SUM(E$2:E10)</f>
         <v>75</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" s="22">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" s="22">
         <v>0</v>
       </c>
     </row>

--- a/Business Analysis/checkupp_sprint_plan_2026.xlsx
+++ b/Business Analysis/checkupp_sprint_plan_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Business Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBAE6161-9D0C-475D-B5AB-1CB4A12B3B0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0F8B8C0-2E54-434B-8335-AFEC9F6EF476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint 01" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sprint 01'!$E$1:$E$112</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Sprint 02'!$E$1:$E$110</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -59,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="120">
   <si>
     <t>Epic</t>
   </si>
@@ -5370,116 +5371,19 @@
     <t>Contrast Pre-Processing, Regex Extraction &amp; Auto-Fill</t>
   </si>
   <si>
-    <t>Digital Weight Scale Camera Scanner with Image Pre-Processing
-* **Target Files**:
-* `checkupp-mobile-main/app/(tabs)/diabetes.tsx`
-* `checkupp-mobile-main/components/camera/ScaleScannerModal.tsx`
-* `checkupp-mobile-main/lib/utils/imageUtils.ts`
-* **Description**:
-1. Add a "Scan Scale" icon next to the Weight input field on the Diabetes form (and reusable shared modules).
-2. Implement `imageUtils.ts` threshold/contrast filter pre-processing on the captured camera frame to isolate glowing LCD digits from reflective or backlit scale surfaces before passing to ML Kit.
-3. Extract a 2-to-3 digit number (with or without a single decimal, e.g., 75.4 or 98) using Regex matching.
-4. Auto-fill the extracted value directly into the **Weight (kg)** field without triggering secondary contextual modals.
-5. Implement the 10-second timeout fallback alert ("Having trouble reading the screen...").
-* **Acceptance Criteria Covered**: US 20.3 - Weight Scale (AC 1, 2, 3, 4, 5)</t>
-  </si>
-  <si>
-    <t>Global Backend &amp; Validation Tasks</t>
-  </si>
-  <si>
-    <t>Controller, Validation &amp; Database Schema</t>
-  </si>
-  <si>
-    <t>Vitals &amp; Diabetes Measurement Ingestion Verification
-* **Target Files**:
-* `checkupp-api-main/src/modules/vitals/vitals.controller.ts`
-* `checkupp-api-main/src/modules/vitals/vitals.validation.ts`
-* `checkupp-api-main/tests/modules/vitals/vitals.test.ts`
-* **Description**:
-1. Ensure `vitals.validation.ts` accommodates auto-filled decimal and integer values strictly matching physiological sanity bounds (e.g., Systolic 50–250 mmHg, Weight 20–300 kg, Glucose 1–35 mmol/L or 20–600 mg/dL).
-2. Write unit and integration tests verifying that incoming payloads from both manual entry and camera-scanned flows validate identically and save correctly to user history.
-* **Acceptance Criteria Covered**: Cross-epic data integrity for US 19.3 &amp; US 20.3</t>
-  </si>
-  <si>
     <t>Live-scan digital blood pressure monitor</t>
-  </si>
-  <si>
-    <t>Implement Blood Pressure OCR Extraction and Y-Coordinate Mapping with Jest TDD
-Target Files:
-• checkupp-mobile-main/lib/scanner/bloodPressureScanner.js
-• checkupp-mobile-main/__tests__/cardiovascular/scan-monitor-image.test.js
-Description:
-1. Reuse the existing Google ML Kit Text Recognition integration.
-2. Extract three valid numeric values from the BP monitor OCR response.
-3. Sort OCR candidates using their vertical bounding-box position and map them to Systolic, Diastolic and Heart Rate according to the agreed screen-coordinate convention.
-4. Ignore unrelated values such as date, time, memory number and unit labels.
-5. Ensure shuffled ML Kit OCR results produce the same final BP values.
-6. Return null when one or more required readings cannot be reliably identified.
-7. Add Jest tests for normal, shuffled, incomplete, irrelevant and malformed OCR results.
-Acceptance Criteria Covered: US 19.3 – Extraction Logic (Y-Coordinate Sorting)</t>
   </si>
   <si>
     <t>Live-scan digital glucometer</t>
   </si>
   <si>
-    <t>Implement Glucometer Single-Value OCR Extraction and Regex Validation with Jest TDD
-Target Files:
-• checkupp-mobile-main/lib/scanner/glucoseScanner.js
-• checkupp-mobile-main/__tests__/diabetes/scan-glucometer-image.test.js
-Description:
-1. Reuse Google ML Kit Text Recognition to process the glucometer display.
-2. Extract one glucose value using regex validation.
-3. Support values such as 5, 5.6, 12 and 12.1.
-4. Ignore unrelated date, time, memory and unit values.
-5. Select the primary LCD value when multiple numeric OCR results are present.
-6. Reject malformed values, multiple decimal points, negative values, alphabetic text and empty OCR results.
-7. Add Jest tests covering normal, dark, glare, blur, multiple-number and invalid-value scenarios.
-Acceptance Criteria Covered: US 20.3 – Extraction Logic (Regex) and scan accuracy</t>
-  </si>
-  <si>
     <t>Live-scan digital weighing scale</t>
-  </si>
-  <si>
-    <t>Implement Digital Weighing Scale LCD OCR and Weight Validation with Jest TDD
-Target Files:
-• checkupp-mobile-main/lib/scanner/weightScanner.js
-• checkupp-mobile-main/__tests__/diabetes/scan-digital-scale-image.test.js
-Description:
-1. Implement OCR-based scanning specifically for the supplied digital LCD weighing scale; do not implement analog needle detection.
-2. Extract values such as 68, 68.7, 68.70, 98 and 98.40.
-3. Support OCR values containing the kg suffix, such as 68.70 kg and 68.70kg.
-4. Validate the extracted value before auto-fill using a regex such as ^\\d{2,3}(?:\\.\\d{1,2})?$.
-5. Reject negative, alphabetic, malformed, multiple-decimal, impossible and four-digit values.
-6. Use the supplied digital-scale image displaying 68.70 kg as the reference test scenario.
-7. Add Jest tests for normal, dark, glare, blur, rotation, obstruction and malformed OCR cases.
-Acceptance Criteria Covered: US 20.4 – Extraction Logic and Auto-Fill</t>
   </si>
   <si>
     <t>Shared Scanner</t>
   </si>
   <si>
     <t>Shared camera scanning</t>
-  </si>
-  <si>
-    <t>Implement Image Quality, Bounding-Box Filtering and Multi-Frame Stability with Jest TDD
-Target Files:
-• checkupp-mobile-main/lib/scanner/bloodPressureScanner.js
-• checkupp-mobile-main/lib/scanner/glucoseScanner.js
-• checkupp-mobile-main/lib/scanner/weightScanner.js
-• checkupp-mobile-main/__tests__/cardiovascular/scan-monitor-image.test.js
-• checkupp-mobile-main/__tests__/diabetes/scan-glucometer-image.test.js
-• checkupp-mobile-main/__tests__/diabetes/scan-digital-scale-image.test.js
-Description:
-1. Filter OCR results so only values inside the appropriate target bounding box are considered.
-2. Ignore numbers outside the target region and unrelated OCR text.
-3. Handle rotated OCR coordinates after normalization.
-4. Reject unreadable values caused by severe glare, blur or obstruction when confidence is insufficient.
-5. Implement multi-frame stability so a measurement must remain consistent before auto-fill.
-6. Treat equivalent weight formats such as 68.7 and 68.70 as the same numeric value.
-7. Reject fluctuating OCR results and insufficient frames.
-8. Ensure failed or uncertain scans never overwrite manually entered values.
-9. Add Jest tests for lighting, glare, blur, rotation, obstruction, target-box failures, unstable readings and false-positive protection.
-Acceptance Criteria Covered: US 19.3 – Extraction Reliability; US 20.3 – Scan Reliability; US 20.4 – Lighting/Contrast and Extraction Reliability</t>
   </si>
   <si>
     <t>Shared measurement reliability</t>
@@ -5580,38 +5484,6 @@
 Test Case 1 (US 6.1): Mock a file buffer upload to PUT /me/wallet/uploads/pending. Assert that the mocked Firebase bucket upload function is called and a 201 response is returned with the cloud URL.
 Test Case 2 (US 7.1): POST to /me/wallet/links with a valid e-script URL. Assert a 201 response and verify the database record contains fileType: LINK and the proper external URL 
 Test Case 3 (US 6.3, 7.4): DELETE /me/wallet/documents/:id. Assert that the database record is removed and an immutable AuditLog entry is written. For physical documents, assert that the mocked Firebase bucket delete method is invoked.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">TDD - </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Automated Jest test suite for 3-Dot Menu, Native Sharing &amp; Local Downloads</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Target Files:Create: checkupp-mobile/tests/wallet/walletCardInteractions.test.js
-Ambiguity-Free Technical Specification:
-Setup tests using @testing-library/react-native. Mock expo-file-system, expo-sharing, and React Native's Share and Alert modules.  
-Test Case 1 (US 6.6, 7.5): Render the FileCard component. Assert the explicit "View" and "Delete" buttons are absent, and the "Share" icon + "3-dot" icon are present.
-Test Case 2 (US 6.3, 7.4): Simulate press on the 3-dot menu. Assert Alert.alert (or ActionSheet) is called with "View/Open", "Download" (only for documents, not links/e-scipts), "Delete", and "Cancel".
-Test Case 3 (US 6.2, 7.3): Simulate press on the "Share" button for a document. Assert FileSystem.downloadAsync is called, followed by Sharing.shareAsync. For an e-script, assert Share.share is called with the URL.</t>
     </r>
   </si>
   <si>
@@ -5760,10 +5632,312 @@
     </r>
   </si>
   <si>
+    <t>19.3, 20.3, 20.5</t>
+  </si>
+  <si>
+    <t>19.3, 20.3, 20.6</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Implement Contextual Reading-Type Modal and Manual Fallback UI with Jest TDD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Target Files:
+checkupp-mobile/components/modals/ReadingTypeModal.tsx
+checkupp-mobile/components/camera/ScanMonitorModal.tsx
+checkupp-mobile/components/screening/CardiovascularHealth.tsx
+checkupp-mobile/components/screening/DiabetesCheck.tsx
+checkupp-mobile/test/DiabetesTest/scan-glucometer-modal.test.ts
+checkupp-mobile/test/Scanner/scan-fallback-ui.test.ts
+checkupp-mobile/test/DiabetesTest/save-reading-commit.test.ts
+Description:
+1. After a successful glucose scan, render a native bottom-sheet modal asking "What type of reading is this?" with three options: Fasting Glucose, Random Glucose, Post-Meal Glucose.
+2. Verify each modal option, when tapped, routes the scanned numeric value into the correct corresponding form field and closes the modal.
+3. Verify the modal does not appear for Blood Pressure or Weight scans (negative test — confirms no cross-contamination of the modal pattern into flows that shouldn't have it, per US 20.4 AC #3).
+4. Verify a persistent "Cancel / Enter Manually" button is present and tappable on the camera scan screen at all times — immediately on open, mid-scan, and independent of timeout state (not just after a timeout fires).
+5. Verify that upon successful multi-frame lock and auto-fill, a toast/banner renders with the exact text "Numbers scanned successfully. Please verify against your device." for the Cardiovascular (BP) flow.
+6. Add Jest tests for: modal-option-to-field routing (all 3 branches), modal absence on BP/Weight flows, fallback button visibility across scan lifecycle states (open/scanning/timeout/error), exact toast copy assertion, save-commit success path, and save-blocked-on-empty-fields path.
+Acceptance Criteria Covered: US 19.3 – Human-in-the-Loop Validation (toast), Fallback (manual entry); US 20.3 – Contextual UI Modal, Auto-Fill Execution, Validation (Save Reading commit); US 20.4 – Auto-Fill Execution (negative: no modal)"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Implement Scan Trigger Buttons in Cardiovascular and Diabetes Forms with Jest TDD
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Target Files:
+checkupp-mobile/components/screening/CardiovascularHealth.tsx
+checkupp-mobile/components/screening/DiabetesCheck.tsx
+checkupp-mobile/test/CardiovascularReading/scan-trigger-button.test.ts
+checkupp-mobile/test/DiabetesTest/scan-trigger-buttons.test.ts
+Description:
+Render a single "Scan Sphygmomanometer" (or "Scan Monitor") button in the Cardiovascular Health form, positioned next to/near the manual Blood Pressure input fields.
+Render two distinct buttons in the Diabetes Test form: "Scan Glucometer" (near the Blood Glucose section) and "Scan Weighing Scale" (near the Weight input field).
+Verify tapping "Scan Sphygmomanometer" opens the camera scan modal configured for the BP scanner flow (correct target bounding box copy, correct scanner module wired in).
+Verify tapping "Scan Glucometer" opens the camera scan modal configured for the glucose scanner flow.
+Verify tapping "Scan Weighing Scale" opens the camera scan modal configured for the weight scanner flow.
+Verify each button is disabled or hidden appropriately if camera permission has been permanently denied (graceful degradation — falls back to manual entry only, per shared permission handling).
+Verify each button has an accessible label/role matching its visible text (for screen-reader support).
+Verify only one scan modal can be open at a time — tapping a second scan button while one modal is already open does not stack or duplicate modals.
+Add Jest tests for: button presence/visibility per form, correct scanner-flow wiring per button tap, correct modal title/copy per flow, permission-denied disabled state, and accessibility label assertions.
+Acceptance Criteria Covered: US 19.3 – Trigger (Scan Monitor icon/button visible); US 20.3 – Trigger (Scan Glucometer button visible); US 20.4 – Trigger (Scan Scale icon visible)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Implement Shared Camera Performance, Permission, Timeout Handling &amp; Privacy with Jest TDD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Target Files:
+• checkupp-mobile/lib/scanner/deviceScanner.ts
+• checkupp-mobile/components/camera/ScanMonitorModal.tsx
+• checkupp-mobile-main/test/scanner/scanner-edge-cases.test.ts
+Description:
+1. Reuse the existing native camera permission implementation.
+2. Handle already-granted, requested, denied and revoked camera permissions gracefully.
+3. Limit ML Kit frame processing to 15–30 FPS instead of processing every camera frame.
+4. Start a 10-second timeout whenever a scanner opens.
+5. Cancel the timeout after successful detection, cancellation or scanner closure.
+6. Display the exact timeout message: "Having trouble reading the screen. Ensure there is no glare, or switch to manual entry."
+7. Provide an easy exit/manual-entry action after timeout.
+8. Add Jest fake-timer and mocked-permission tests.
+9. Add Jest tests verifying that toggling the Torch/Flashlight UI control updates the native camera torch state property correctly.
+10. Add a test assertion verifying that scanner execution operates 100% locally via on-device ML Kit with zero outbound HTTP/network requests initiated during the scan cycle.
+Acceptance Criteria Covered: US 19.3 – Permissions, Performance, Timeout; US 20.3 – Timeout; US 20.4 – Timeout</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Implement Image Quality, Bounding-Box Filtering and Multi-Frame Stability with Jest TDD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Target Files:
+• checkupp-mobile/lib/scanner/bloodPressureScanner.ts
+• checkupp-mobile/lib/scanner/glucoseScanner.ts
+• checkupp-mobile/lib/scanner/weightScanner.ts
+• checkupp-mobile/test/cardiovascular/scan-monitor-image.test.ts
+• checkupp-mobile/test/diabetes/scan-glucometer-image.test.ts
+• checkupp-mobile/test/diabetes/scan-digital-scale-image.test.ts
+Description:
+1. Filter OCR results so only values inside the appropriate target bounding box are considered.
+2. Ignore numbers outside the target region and unrelated OCR text.
+3. Handle rotated OCR coordinates after normalization.
+4. Reject unreadable values caused by severe glare, blur or obstruction when confidence is insufficient.
+5. Implement multi-frame stability so a measurement must remain consistent before auto-fill.
+6. Treat equivalent weight formats such as 68.7 and 68.70 as the same numeric value.
+7. Reject fluctuating OCR results and insufficient frames.
+8. Ensure failed or uncertain scans never overwrite manually entered values.
+9. Add Jest tests for lighting, glare, blur, rotation, obstruction, target-box failures, unstable readings and false-positive protection.
+Acceptance Criteria Covered: US 19.3 – Extraction Reliability; US 20.3 – Scan Reliability; US 20.4 – Lighting/Contrast and Extraction Reliability</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Implement Glucometer Single-Value OCR Extraction and Regex Validation with Jest TDD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Target Files:
+• checkupp-mobile/lib/scanner/glucoseScanner.ts
+• checkupp-mobile/test/DiabetesTest/scan-glucometer-image.test.ts
+Description:
+1. Reuse Google ML Kit Text Recognition to process the glucometer display.
+2. Extract one glucose value using regex validation.
+3. Support values such as 5, 5.6, 12 and 12.1.
+4. Ignore unrelated date, time, memory and unit values.
+5. Select the primary LCD value when multiple numeric OCR results are present.
+6. Reject malformed values, multiple decimal points, negative values, alphabetic text and empty OCR results.
+7. Add Jest tests covering normal, dark, glare, blur, multiple-number and invalid-value scenarios.
+Acceptance Criteria Covered: US 20.3 – Extraction Logic (Regex) and scan accuracy</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Implement Blood Pressure OCR Extraction and Y-Coordinate Mapping with Jest TDD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Target Files:
+• checkupp-mobile/lib/scanner/bloodPressureScanner.ts
+• checkupp-mobile/test/CardiovascularReading/scan-monitor-image.test.ts
+Description:
+1. Reuse the existing Google ML Kit Text Recognition integration.
+2. Extract three valid numeric values from the BP monitor OCR response.
+3. Sort OCR candidates using their vertical bounding-box position and map them to Systolic, Diastolic and Heart Rate according to the agreed screen-coordinate convention.
+4. Ignore unrelated values such as date, time, memory number and unit labels.
+5. Ensure shuffled ML Kit OCR results produce the same final BP values.
+6. Return null when one or more required readings cannot be reliably identified.
+7. Add Jest tests for normal, shuffled, incomplete, irrelevant and malformed OCR results.
+Acceptance Criteria Covered: US 19.3 – Extraction Logic (Y-Coordinate Sorting)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Implement Digital Weighing Scale LCD OCR and Weight Validation with Jest TDD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Target Files:
+• checkupp-mobile/lib/scanner/weightScanner.ts
+• checkupp-mobile/test/DiabetesTest/scan-digital-scale-image.test.ts
+Description:
+1. Implement OCR-based scanning specifically for the supplied digital LCD weighing scale; do not implement analog needle detection.
+2. Extract values such as 68, 68.7, 68.70, 98 and 98.40.
+3. Support OCR values containing the kg suffix, such as 68.70 kg and 68.70kg.
+4. Validate the extracted value before auto-fill using a regex such as ^\\d{2,3}(?:\\.\\d{1,2})?$.
+5. Reject negative, alphabetic, malformed, multiple-decimal, impossible and four-digit values.
+6. Use the supplied digital-scale image displaying 68.70 kg as the reference test scenario.
+7. Add Jest tests for normal, dark, glare, blur, rotation, obstruction and malformed OCR cases.
+Acceptance Criteria Covered: US 20.4 – Extraction Logic and Auto-Fill</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">TDD - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Automated Jest test suite for 3-Dot Menu, Native Sharing &amp; Local Downloads</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Target Files:Create: checkupp-mobile/tests/wallet/walletCardInteractions.test.ts
+Ambiguity-Free Technical Specification:
+Setup tests using @testing-library/react-native. Mock expo-file-system, expo-sharing, and React Native's Share and Alert modules.  
+Test Case 1 (US 6.6, 7.5): Render the FileCard component. Assert the explicit "View" and "Delete" buttons are absent, and the "Share" icon + "3-dot" icon are present.
+Test Case 2 (US 6.3, 7.4): Simulate press on the 3-dot menu. Assert Alert.alert (or ActionSheet) is called with "View/Open", "Download" (only for documents, not links/e-scipts), "Delete", and "Cancel".
+Test Case 3 (US 6.2, 7.3): Simulate press on the "Share" button for a document. Assert FileSystem.downloadAsync is called, followed by Sharing.shareAsync. For an e-script, assert Share.share is called with the URL.</t>
+    </r>
+  </si>
+  <si>
     <t>Cardiovascular Camera Scanner UI, Permission Handling &amp; Torch Toggle
 * **Target Files**:
-* `checkupp-mobile-main/app/(tabs)/cardiovascular.tsx`
-* `checkupp-mobile-main/components/camera/ScanMonitorModal.tsx`
+* `checkupp-mobile/components/screening/CardiovascularHealth.tsx`
+* `checkupp-mobile/components/camera/ScannerCameraModal.tsx`
 * **Description**:
 1. Add a "Scan Monitor" icon/button next to the manual input fields for Blood Pressure on the Cardiovascular screen.
 2. Implement `ScanMonitorModal.tsx` using `react-native-vision-camera` (or `expo-camera`).
@@ -5777,10 +5951,10 @@
   <si>
     <t>Blood Pressure ML Kit Extraction, Pre-Processing, Y-Coordinate Sorting &amp; Validation
 * **Target Files**:
-* `checkupp-mobile-main/lib/utils/ocrUtils.ts`
+* `checkupp-mobile/lib/utils/ocrUtils.ts`
 * `checkupp-mobile/lib/utils/imageUtils.ts
-* `checkupp-mobile-main/components/camera/ScanMonitorModal.tsx`
-* `checkupp-mobile-main/app/(tabs)/cardiovascular.tsx`
+* `checkupp-mobile/components/camera/ScannerCameraModal.tsx`
+* `checkupp-mobile/components/screening/CardiovascularHealth.tsx`
 * **Description**:
 0. Apply imageUtils.ts grayscale and adaptive threshold/contrast filtering to the camera frame buffer before ML Kit processing to strip screen reflections and isolate glowing LCD digits.
 1. Integrate Google ML Kit Text Recognition into the camera frame processor to extract numerical text strings dynamically.
@@ -5795,10 +5969,10 @@
   <si>
     <t>Glucometer ML Kit Scanning with Frame Pre-Processing &amp; Contextual Reading Modal
 * **Target Files**:
-* `checkupp-mobile-main/app/(tabs)/diabetes.tsx`
+* `checkupp-mobile/components/screening/DiabetesTest.tsx`
 * `checkupp-mobile/lib/utils/imageUtils.ts
-* `checkupp-mobile-main/components/camera/GlucometerScannerModal.tsx`
-* `checkupp-mobile-main/components/ReadingTypeBottomSheet.tsx`
+* `checkupp-mobile/components/camera/ScannerCameraModal.tsx`
+* `checkupp-mobile/components/ReadingTypeBottomSheet.tsx`
 * **Description**:
 1. Place a "Scan Glucometer" button prominently at the top of the Blood Glucose section in the Diabetes form.
 2. Apply imageUtils.ts threshold/contrast pre-processing to the camera frame to eliminate screen glare before passing to ML Kit.
@@ -5813,23 +5987,18 @@
 * **Acceptance Criteria Covered**: US 20.3 - Glucometer (AC 1, 2, 3, 4, 5, 6, 7)</t>
   </si>
   <si>
-    <t>Implement Shared Camera Performance, Permission, Timeout Handling &amp; Privacy with Jest TDD
-Target Files:
-• checkupp-mobile-main/lib/scanner/deviceScanner.js
-• checkupp-mobile/components/camera/ScanMonitorModal.tsx
-• checkupp-mobile-main/__tests__/scanner/scanner-edge-cases.test.js
-Description:
-1. Reuse the existing native camera permission implementation.
-2. Handle already-granted, requested, denied and revoked camera permissions gracefully.
-3. Limit ML Kit frame processing to 15–30 FPS instead of processing every camera frame.
-4. Start a 10-second timeout whenever a scanner opens.
-5. Cancel the timeout after successful detection, cancellation or scanner closure.
-6. Display the exact timeout message: "Having trouble reading the screen. Ensure there is no glare, or switch to manual entry."
-7. Provide an easy exit/manual-entry action after timeout.
-8. Add Jest fake-timer and mocked-permission tests.
-9. Add Jest tests verifying that toggling the Torch/Flashlight UI control updates the native camera torch state property correctly.
-10. Add a test assertion verifying that scanner execution operates 100% locally via on-device ML Kit with zero outbound HTTP/network requests initiated during the scan cycle.
-Acceptance Criteria Covered: US 19.3 – Permissions, Performance, Timeout; US 20.3 – Timeout; US 20.4 – Timeout</t>
+    <t>Digital Weight Scale Camera Scanner with Image Pre-Processing
+* **Target Files**:
+* `checkupp-mobile/components/screening/DiabetesTest.tsx`
+* `checkupp-mobile/components/camera/ScannerCameraModal.tsx`
+* `checkupp-mobile/lib/utils/imageUtils.ts`
+* **Description**:
+1. Add a "Scan Scale" icon next to the Weight input field on the Diabetes form (and reusable shared modules).
+2. Implement `imageUtils.ts` threshold/contrast filter pre-processing on the captured camera frame to isolate glowing LCD digits from reflective or backlit scale surfaces before passing to ML Kit.
+3. Extract a 2-to-3 digit number (with or without a single decimal, e.g., 75.4 or 98) using Regex matching.
+4. Auto-fill the extracted value directly into the **Weight (kg)** field without triggering secondary contextual modals.
+5. Implement the 10-second timeout fallback alert ("Having trouble reading the screen...").
+* **Acceptance Criteria Covered**: US 20.3 - Weight Scale (AC 1, 2, 3, 4, 5)</t>
   </si>
 </sst>
 </file>
@@ -5896,7 +6065,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5935,12 +6104,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -5973,7 +6136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6020,12 +6183,6 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -6041,10 +6198,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6714,22 +6871,22 @@
                   <c:v>75</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>75</c:v>
+                  <c:v>72</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>75</c:v>
+                  <c:v>65</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>75</c:v>
+                  <c:v>60</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>75</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>75</c:v>
+                  <c:v>35</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>75</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10891,191 +11048,191 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="22" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="19">
+      <c r="A2" s="17">
         <v>0</v>
       </c>
-      <c r="B2" s="20">
+      <c r="B2" s="18">
         <v>46237</v>
       </c>
-      <c r="C2" s="21">
+      <c r="C2" s="19">
         <f>82-SUM(E$2:E2)</f>
         <v>82</v>
       </c>
-      <c r="D2" s="22">
+      <c r="D2" s="20">
         <f xml:space="preserve"> 82*(1-1/8*A2)</f>
         <v>82</v>
       </c>
-      <c r="E2" s="22">
+      <c r="E2" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="19">
+      <c r="A3" s="17">
         <v>1</v>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="18">
         <v>46238</v>
       </c>
-      <c r="C3" s="21">
+      <c r="C3" s="19">
         <f>82-SUM(E$2:E3)</f>
         <v>74</v>
       </c>
-      <c r="D3" s="22">
+      <c r="D3" s="20">
         <f t="shared" ref="D3:D10" si="0" xml:space="preserve"> 82*(1-1/8*A3)</f>
         <v>71.75</v>
       </c>
-      <c r="E3" s="19">
+      <c r="E3" s="17">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="19">
+      <c r="A4" s="17">
         <v>2</v>
       </c>
-      <c r="B4" s="20">
+      <c r="B4" s="18">
         <v>46239</v>
       </c>
-      <c r="C4" s="21">
+      <c r="C4" s="19">
         <f>82-SUM(E$2:E4)</f>
         <v>66</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="20">
         <f t="shared" si="0"/>
         <v>61.5</v>
       </c>
-      <c r="E4" s="19">
+      <c r="E4" s="17">
         <v>8</v>
       </c>
       <c r="L4" s="2"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="19">
+      <c r="A5" s="17">
         <v>3</v>
       </c>
-      <c r="B5" s="20">
+      <c r="B5" s="18">
         <v>46240</v>
       </c>
-      <c r="C5" s="21">
+      <c r="C5" s="19">
         <f>82-SUM(E$2:E5)</f>
         <v>66</v>
       </c>
-      <c r="D5" s="22">
+      <c r="D5" s="20">
         <f t="shared" si="0"/>
         <v>51.25</v>
       </c>
-      <c r="E5" s="19">
+      <c r="E5" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="19">
+      <c r="A6" s="17">
         <v>4</v>
       </c>
-      <c r="B6" s="20">
+      <c r="B6" s="18">
         <v>46241</v>
       </c>
-      <c r="C6" s="21">
+      <c r="C6" s="19">
         <f>82-SUM(E$2:E6)</f>
         <v>66</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="20">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="17">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="19">
+      <c r="A7" s="17">
         <v>5</v>
       </c>
-      <c r="B7" s="20">
+      <c r="B7" s="18">
         <v>46244</v>
       </c>
-      <c r="C7" s="21">
+      <c r="C7" s="19">
         <f>82-SUM(E$2:E7)</f>
         <v>62</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="20">
         <f t="shared" si="0"/>
         <v>30.75</v>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="17">
         <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="19">
+      <c r="A8" s="17">
         <v>6</v>
       </c>
-      <c r="B8" s="20">
+      <c r="B8" s="18">
         <v>46245</v>
       </c>
-      <c r="C8" s="21">
+      <c r="C8" s="19">
         <f>82-SUM(E$2:E8)</f>
         <v>52</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="20">
         <f t="shared" si="0"/>
         <v>20.5</v>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="17">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="19">
+      <c r="A9" s="17">
         <v>7</v>
       </c>
-      <c r="B9" s="20">
+      <c r="B9" s="18">
         <v>46246</v>
       </c>
-      <c r="C9" s="21">
+      <c r="C9" s="19">
         <f>82-SUM(E$2:E9)</f>
         <v>37</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="20">
         <f t="shared" si="0"/>
         <v>10.25</v>
       </c>
-      <c r="E9" s="19">
+      <c r="E9" s="17">
         <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="19">
+      <c r="A10" s="17">
         <v>8</v>
       </c>
-      <c r="B10" s="20">
+      <c r="B10" s="18">
         <v>46247</v>
       </c>
-      <c r="C10" s="21">
+      <c r="C10" s="19">
         <f>82-SUM(E$2:E10)</f>
         <v>0</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="20">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E10" s="19">
+      <c r="E10" s="17">
         <v>37</v>
       </c>
     </row>
@@ -11087,7 +11244,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA30D3B6-4BBC-427B-918A-C301767B692F}">
-  <dimension ref="A1:L111"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:L110"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.88671875" bestFit="1" customWidth="1"/>
@@ -11142,22 +11300,22 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="172.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="172.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12">
         <v>1</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D2" s="12"/>
       <c r="E2" s="12" t="s">
         <v>31</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="G2" s="12" t="s">
         <v>29</v>
@@ -11175,22 +11333,22 @@
       <c r="K2" s="12"/>
       <c r="L2" s="12"/>
     </row>
-    <row r="3" spans="1:12" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="158.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="12">
         <v>2</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D3" s="12"/>
       <c r="E3" s="12" t="s">
         <v>31</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G3" s="12" t="s">
         <v>29</v>
@@ -11208,22 +11366,22 @@
       <c r="K3" s="12"/>
       <c r="L3" s="12"/>
     </row>
-    <row r="4" spans="1:12" ht="403.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="403.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="12">
         <v>3</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="D4" s="12"/>
       <c r="E4" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="18" t="s">
-        <v>114</v>
+      <c r="F4" s="16" t="s">
+        <v>105</v>
       </c>
       <c r="G4" s="12" t="s">
         <v>29</v>
@@ -11239,22 +11397,22 @@
       <c r="K4" s="12"/>
       <c r="L4" s="12"/>
     </row>
-    <row r="5" spans="1:12" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="12">
         <v>4</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D5" s="12"/>
       <c r="E5" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="18" t="s">
-        <v>113</v>
+      <c r="F5" s="16" t="s">
+        <v>104</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>29</v>
@@ -11275,17 +11433,17 @@
         <v>5</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="18" t="s">
-        <v>110</v>
+      <c r="F6" s="16" t="s">
+        <v>101</v>
       </c>
       <c r="G6" s="12" t="s">
         <v>29</v>
@@ -11308,17 +11466,17 @@
         <v>6</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D7" s="12"/>
       <c r="E7" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="18" t="s">
-        <v>101</v>
+      <c r="F7" s="16" t="s">
+        <v>93</v>
       </c>
       <c r="G7" s="12" t="s">
         <v>29</v>
@@ -11341,17 +11499,17 @@
         <v>7</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D8" s="12"/>
       <c r="E8" s="12" t="s">
         <v>20</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="G8" s="12" t="s">
         <v>29</v>
@@ -11374,7 +11532,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C9" s="12">
         <v>6.5</v>
@@ -11383,8 +11541,8 @@
       <c r="E9" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="18" t="s">
-        <v>104</v>
+      <c r="F9" s="16" t="s">
+        <v>96</v>
       </c>
       <c r="G9" s="12" t="s">
         <v>29</v>
@@ -11407,17 +11565,17 @@
         <v>9</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="12" t="s">
         <v>20</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="G10" s="12" t="s">
         <v>29</v>
@@ -11452,7 +11610,7 @@
         <v>20</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G11" s="14" t="s">
         <v>24</v>
@@ -11487,7 +11645,7 @@
         <v>20</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G12" s="14" t="s">
         <v>24</v>
@@ -11522,7 +11680,7 @@
         <v>20</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G13" s="14" t="s">
         <v>24</v>
@@ -11557,7 +11715,7 @@
         <v>20</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="G14" s="14" t="s">
         <v>24</v>
@@ -11575,57 +11733,57 @@
       <c r="K14" s="14"/>
       <c r="L14" s="14"/>
     </row>
-    <row r="15" spans="1:12" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="16">
+    <row r="15" spans="1:12" ht="244.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="6">
         <v>14</v>
       </c>
-      <c r="B15" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="E15" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="F15" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="G15" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="H15" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="I15" s="16">
+      <c r="B15" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C15" s="6">
+        <v>19.3</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I15" s="6">
         <f t="array" ref="I15">_xlfn.SWITCH(H15,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v>3</v>
-      </c>
-      <c r="J15" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-    </row>
-    <row r="16" spans="1:12" ht="244.8" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+    </row>
+    <row r="16" spans="1:12" ht="230.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C16" s="6">
-        <v>19.3</v>
+        <v>20.3</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>31</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>29</v>
@@ -11641,7 +11799,7 @@
       <c r="K16" s="6"/>
       <c r="L16" s="6"/>
     </row>
-    <row r="17" spans="1:12" ht="230.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" ht="244.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>16</v>
       </c>
@@ -11649,16 +11807,16 @@
         <v>80</v>
       </c>
       <c r="C17" s="6">
-        <v>20.3</v>
+        <v>20.399999999999999</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E17" s="6" t="s">
         <v>31</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>29</v>
@@ -11674,24 +11832,24 @@
       <c r="K17" s="6"/>
       <c r="L17" s="6"/>
     </row>
-    <row r="18" spans="1:12" ht="244.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" ht="316.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C18" s="6">
-        <v>20.399999999999999</v>
+        <v>86</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>98</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>31</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>29</v>
@@ -11700,30 +11858,31 @@
         <v>30</v>
       </c>
       <c r="I18" s="6">
+        <f t="array" ref="I18">_xlfn.SWITCH(H18,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
       <c r="J18" s="6"/>
       <c r="K18" s="6"/>
       <c r="L18" s="6"/>
     </row>
-    <row r="19" spans="1:12" ht="316.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" ht="345.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>31</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>29</v>
@@ -11732,59 +11891,76 @@
         <v>30</v>
       </c>
       <c r="I19" s="6">
+        <f t="array" ref="I19">_xlfn.SWITCH(H19,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
         <v>5</v>
       </c>
       <c r="J19" s="6"/>
       <c r="K19" s="6"/>
       <c r="L19" s="6"/>
     </row>
-    <row r="20" spans="1:12" ht="345.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>96</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="D20" s="6"/>
       <c r="E20" s="6" t="s">
         <v>31</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="I20" s="6">
-        <v>5</v>
+        <f t="array" ref="I20">_xlfn.SWITCH(H20,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>2</v>
       </c>
       <c r="J20" s="6"/>
       <c r="K20" s="6"/>
       <c r="L20" s="6"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
+    <row r="21" spans="1:12" ht="409.6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="6">
+        <v>20</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>107</v>
+      </c>
       <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
+      <c r="E21" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I21" s="6">
+        <f t="array" ref="I21">_xlfn.SWITCH(H21,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v>1</v>
+      </c>
       <c r="J21" s="6"/>
       <c r="K21" s="6"/>
       <c r="L21" s="6"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6"/>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
@@ -11798,7 +11974,7 @@
       <c r="K22" s="6"/>
       <c r="L22" s="6"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="6"/>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
@@ -11812,7 +11988,7 @@
       <c r="K23" s="6"/>
       <c r="L23" s="6"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -11821,12 +11997,15 @@
       <c r="F24" s="8"/>
       <c r="G24" s="6"/>
       <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
+      <c r="I24" s="6" t="str">
+        <f t="array" ref="I24">_xlfn.SWITCH(H24,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
+        <v/>
+      </c>
       <c r="J24" s="6"/>
       <c r="K24" s="6"/>
       <c r="L24" s="6"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6"/>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
@@ -11843,7 +12022,7 @@
       <c r="K25" s="6"/>
       <c r="L25" s="6"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -11860,7 +12039,7 @@
       <c r="K26" s="6"/>
       <c r="L26" s="6"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="6"/>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
@@ -11877,7 +12056,7 @@
       <c r="K27" s="6"/>
       <c r="L27" s="6"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6"/>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -11894,7 +12073,7 @@
       <c r="K28" s="6"/>
       <c r="L28" s="6"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
@@ -11911,7 +12090,7 @@
       <c r="K29" s="6"/>
       <c r="L29" s="6"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -11928,13 +12107,13 @@
       <c r="K30" s="6"/>
       <c r="L30" s="6"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
       <c r="D31" s="6"/>
       <c r="E31" s="6"/>
-      <c r="F31" s="8"/>
+      <c r="F31" s="5"/>
       <c r="G31" s="6"/>
       <c r="H31" s="6"/>
       <c r="I31" s="6" t="str">
@@ -11945,13 +12124,13 @@
       <c r="K31" s="6"/>
       <c r="L31" s="6"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6"/>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
       <c r="D32" s="6"/>
       <c r="E32" s="6"/>
-      <c r="F32" s="5"/>
+      <c r="F32" s="7"/>
       <c r="G32" s="6"/>
       <c r="H32" s="6"/>
       <c r="I32" s="6" t="str">
@@ -11962,7 +12141,7 @@
       <c r="K32" s="6"/>
       <c r="L32" s="6"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="6"/>
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
@@ -11979,7 +12158,7 @@
       <c r="K33" s="6"/>
       <c r="L33" s="6"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="6"/>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
@@ -11996,7 +12175,7 @@
       <c r="K34" s="6"/>
       <c r="L34" s="6"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="6"/>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
@@ -12013,7 +12192,7 @@
       <c r="K35" s="6"/>
       <c r="L35" s="6"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6"/>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -12030,7 +12209,7 @@
       <c r="K36" s="6"/>
       <c r="L36" s="6"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="6"/>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -12047,7 +12226,7 @@
       <c r="K37" s="6"/>
       <c r="L37" s="6"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="6"/>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
@@ -12064,7 +12243,7 @@
       <c r="K38" s="6"/>
       <c r="L38" s="6"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="6"/>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
@@ -12081,7 +12260,7 @@
       <c r="K39" s="6"/>
       <c r="L39" s="6"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="6"/>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
@@ -12098,7 +12277,7 @@
       <c r="K40" s="6"/>
       <c r="L40" s="6"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="6"/>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -12115,7 +12294,7 @@
       <c r="K41" s="6"/>
       <c r="L41" s="6"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="6"/>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -12132,7 +12311,7 @@
       <c r="K42" s="6"/>
       <c r="L42" s="6"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="6"/>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -12149,7 +12328,7 @@
       <c r="K43" s="6"/>
       <c r="L43" s="6"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="6"/>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -12166,7 +12345,7 @@
       <c r="K44" s="6"/>
       <c r="L44" s="6"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="6"/>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
@@ -12183,7 +12362,7 @@
       <c r="K45" s="6"/>
       <c r="L45" s="6"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="6"/>
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
@@ -12200,7 +12379,7 @@
       <c r="K46" s="6"/>
       <c r="L46" s="6"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="6"/>
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
@@ -12217,7 +12396,7 @@
       <c r="K47" s="6"/>
       <c r="L47" s="6"/>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="6"/>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -12234,13 +12413,13 @@
       <c r="K48" s="6"/>
       <c r="L48" s="6"/>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="6"/>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
       <c r="D49" s="6"/>
       <c r="E49" s="6"/>
-      <c r="F49" s="7"/>
+      <c r="F49" s="8"/>
       <c r="G49" s="6"/>
       <c r="H49" s="6"/>
       <c r="I49" s="6" t="str">
@@ -12251,7 +12430,7 @@
       <c r="K49" s="6"/>
       <c r="L49" s="6"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="6"/>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
@@ -12268,7 +12447,7 @@
       <c r="K50" s="6"/>
       <c r="L50" s="6"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="6"/>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -12285,7 +12464,7 @@
       <c r="K51" s="6"/>
       <c r="L51" s="6"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="6"/>
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
@@ -12302,7 +12481,7 @@
       <c r="K52" s="6"/>
       <c r="L52" s="6"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="6"/>
       <c r="B53" s="6"/>
       <c r="C53" s="6"/>
@@ -12319,7 +12498,7 @@
       <c r="K53" s="6"/>
       <c r="L53" s="6"/>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="6"/>
       <c r="B54" s="6"/>
       <c r="C54" s="6"/>
@@ -12336,13 +12515,13 @@
       <c r="K54" s="6"/>
       <c r="L54" s="6"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6"/>
       <c r="B55" s="6"/>
       <c r="C55" s="6"/>
       <c r="D55" s="6"/>
       <c r="E55" s="6"/>
-      <c r="F55" s="8"/>
+      <c r="F55" s="7"/>
       <c r="G55" s="6"/>
       <c r="H55" s="6"/>
       <c r="I55" s="6" t="str">
@@ -12353,7 +12532,7 @@
       <c r="K55" s="6"/>
       <c r="L55" s="6"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="6"/>
       <c r="B56" s="6"/>
       <c r="C56" s="6"/>
@@ -12370,7 +12549,7 @@
       <c r="K56" s="6"/>
       <c r="L56" s="6"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="6"/>
       <c r="B57" s="6"/>
       <c r="C57" s="6"/>
@@ -12387,7 +12566,7 @@
       <c r="K57" s="6"/>
       <c r="L57" s="6"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="6"/>
       <c r="B58" s="6"/>
       <c r="C58" s="6"/>
@@ -12404,7 +12583,7 @@
       <c r="K58" s="6"/>
       <c r="L58" s="6"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="6"/>
       <c r="B59" s="6"/>
       <c r="C59" s="6"/>
@@ -12421,7 +12600,7 @@
       <c r="K59" s="6"/>
       <c r="L59" s="6"/>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="6"/>
       <c r="B60" s="6"/>
       <c r="C60" s="6"/>
@@ -12438,7 +12617,7 @@
       <c r="K60" s="6"/>
       <c r="L60" s="6"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="6"/>
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
@@ -12455,7 +12634,7 @@
       <c r="K61" s="6"/>
       <c r="L61" s="6"/>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="6"/>
       <c r="B62" s="6"/>
       <c r="C62" s="6"/>
@@ -12472,7 +12651,7 @@
       <c r="K62" s="6"/>
       <c r="L62" s="6"/>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="6"/>
       <c r="B63" s="6"/>
       <c r="C63" s="6"/>
@@ -12489,7 +12668,7 @@
       <c r="K63" s="6"/>
       <c r="L63" s="6"/>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="6"/>
       <c r="B64" s="6"/>
       <c r="C64" s="6"/>
@@ -12506,7 +12685,7 @@
       <c r="K64" s="6"/>
       <c r="L64" s="6"/>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="6"/>
       <c r="B65" s="6"/>
       <c r="C65" s="6"/>
@@ -12523,13 +12702,13 @@
       <c r="K65" s="6"/>
       <c r="L65" s="6"/>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="6"/>
       <c r="B66" s="6"/>
       <c r="C66" s="6"/>
       <c r="D66" s="6"/>
       <c r="E66" s="6"/>
-      <c r="F66" s="7"/>
+      <c r="F66" s="5"/>
       <c r="G66" s="6"/>
       <c r="H66" s="6"/>
       <c r="I66" s="6" t="str">
@@ -12540,13 +12719,13 @@
       <c r="K66" s="6"/>
       <c r="L66" s="6"/>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="6"/>
       <c r="B67" s="6"/>
       <c r="C67" s="6"/>
       <c r="D67" s="6"/>
       <c r="E67" s="6"/>
-      <c r="F67" s="5"/>
+      <c r="F67" s="7"/>
       <c r="G67" s="6"/>
       <c r="H67" s="6"/>
       <c r="I67" s="6" t="str">
@@ -12557,13 +12736,13 @@
       <c r="K67" s="6"/>
       <c r="L67" s="6"/>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="6"/>
       <c r="B68" s="6"/>
       <c r="C68" s="6"/>
       <c r="D68" s="6"/>
       <c r="E68" s="6"/>
-      <c r="F68" s="7"/>
+      <c r="F68" s="5"/>
       <c r="G68" s="6"/>
       <c r="H68" s="6"/>
       <c r="I68" s="6" t="str">
@@ -12574,7 +12753,7 @@
       <c r="K68" s="6"/>
       <c r="L68" s="6"/>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="6"/>
       <c r="B69" s="6"/>
       <c r="C69" s="6"/>
@@ -12591,13 +12770,13 @@
       <c r="K69" s="6"/>
       <c r="L69" s="6"/>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="6"/>
       <c r="B70" s="6"/>
       <c r="C70" s="6"/>
       <c r="D70" s="6"/>
       <c r="E70" s="6"/>
-      <c r="F70" s="5"/>
+      <c r="F70" s="7"/>
       <c r="G70" s="6"/>
       <c r="H70" s="6"/>
       <c r="I70" s="6" t="str">
@@ -12608,7 +12787,7 @@
       <c r="K70" s="6"/>
       <c r="L70" s="6"/>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="6"/>
       <c r="B71" s="6"/>
       <c r="C71" s="6"/>
@@ -12625,7 +12804,7 @@
       <c r="K71" s="6"/>
       <c r="L71" s="6"/>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="6"/>
       <c r="B72" s="6"/>
       <c r="C72" s="6"/>
@@ -12642,7 +12821,7 @@
       <c r="K72" s="6"/>
       <c r="L72" s="6"/>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="6"/>
       <c r="B73" s="6"/>
       <c r="C73" s="6"/>
@@ -12659,7 +12838,7 @@
       <c r="K73" s="6"/>
       <c r="L73" s="6"/>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="6"/>
       <c r="B74" s="6"/>
       <c r="C74" s="6"/>
@@ -12676,13 +12855,13 @@
       <c r="K74" s="6"/>
       <c r="L74" s="6"/>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="6"/>
       <c r="B75" s="6"/>
       <c r="C75" s="6"/>
       <c r="D75" s="6"/>
       <c r="E75" s="6"/>
-      <c r="F75" s="7"/>
+      <c r="F75" s="8"/>
       <c r="G75" s="6"/>
       <c r="H75" s="6"/>
       <c r="I75" s="6" t="str">
@@ -12693,7 +12872,7 @@
       <c r="K75" s="6"/>
       <c r="L75" s="6"/>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="6"/>
       <c r="B76" s="6"/>
       <c r="C76" s="6"/>
@@ -12710,7 +12889,7 @@
       <c r="K76" s="6"/>
       <c r="L76" s="6"/>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="6"/>
       <c r="B77" s="6"/>
       <c r="C77" s="6"/>
@@ -12727,7 +12906,7 @@
       <c r="K77" s="6"/>
       <c r="L77" s="6"/>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="6"/>
       <c r="B78" s="6"/>
       <c r="C78" s="6"/>
@@ -12744,7 +12923,7 @@
       <c r="K78" s="6"/>
       <c r="L78" s="6"/>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="6"/>
       <c r="B79" s="6"/>
       <c r="C79" s="6"/>
@@ -12761,7 +12940,7 @@
       <c r="K79" s="6"/>
       <c r="L79" s="6"/>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="6"/>
       <c r="B80" s="6"/>
       <c r="C80" s="6"/>
@@ -12778,7 +12957,7 @@
       <c r="K80" s="6"/>
       <c r="L80" s="6"/>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="6"/>
       <c r="B81" s="6"/>
       <c r="C81" s="6"/>
@@ -12795,7 +12974,7 @@
       <c r="K81" s="6"/>
       <c r="L81" s="6"/>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="6"/>
       <c r="B82" s="6"/>
       <c r="C82" s="6"/>
@@ -12812,7 +12991,7 @@
       <c r="K82" s="6"/>
       <c r="L82" s="6"/>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="6"/>
       <c r="B83" s="6"/>
       <c r="C83" s="6"/>
@@ -12829,7 +13008,7 @@
       <c r="K83" s="6"/>
       <c r="L83" s="6"/>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="6"/>
       <c r="B84" s="6"/>
       <c r="C84" s="6"/>
@@ -12846,7 +13025,7 @@
       <c r="K84" s="6"/>
       <c r="L84" s="6"/>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="6"/>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
@@ -12863,7 +13042,7 @@
       <c r="K85" s="6"/>
       <c r="L85" s="6"/>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="6"/>
       <c r="B86" s="6"/>
       <c r="C86" s="6"/>
@@ -12880,7 +13059,7 @@
       <c r="K86" s="6"/>
       <c r="L86" s="6"/>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="6"/>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
@@ -12897,7 +13076,7 @@
       <c r="K87" s="6"/>
       <c r="L87" s="6"/>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="6"/>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -12914,7 +13093,7 @@
       <c r="K88" s="6"/>
       <c r="L88" s="6"/>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="6"/>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -12931,7 +13110,7 @@
       <c r="K89" s="6"/>
       <c r="L89" s="6"/>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="6"/>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
@@ -12948,7 +13127,7 @@
       <c r="K90" s="6"/>
       <c r="L90" s="6"/>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="6"/>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
@@ -12965,7 +13144,7 @@
       <c r="K91" s="6"/>
       <c r="L91" s="6"/>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="6"/>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -12982,7 +13161,7 @@
       <c r="K92" s="6"/>
       <c r="L92" s="6"/>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="6"/>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -12999,7 +13178,7 @@
       <c r="K93" s="6"/>
       <c r="L93" s="6"/>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="6"/>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -13016,7 +13195,7 @@
       <c r="K94" s="6"/>
       <c r="L94" s="6"/>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="6"/>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -13033,7 +13212,7 @@
       <c r="K95" s="6"/>
       <c r="L95" s="6"/>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="6"/>
       <c r="B96" s="6"/>
       <c r="C96" s="6"/>
@@ -13050,7 +13229,7 @@
       <c r="K96" s="6"/>
       <c r="L96" s="6"/>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="6"/>
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
@@ -13067,7 +13246,7 @@
       <c r="K97" s="6"/>
       <c r="L97" s="6"/>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="6"/>
       <c r="B98" s="6"/>
       <c r="C98" s="6"/>
@@ -13084,7 +13263,7 @@
       <c r="K98" s="6"/>
       <c r="L98" s="6"/>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="6"/>
       <c r="B99" s="6"/>
       <c r="C99" s="6"/>
@@ -13101,7 +13280,7 @@
       <c r="K99" s="6"/>
       <c r="L99" s="6"/>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="6"/>
       <c r="B100" s="6"/>
       <c r="C100" s="6"/>
@@ -13118,7 +13297,7 @@
       <c r="K100" s="6"/>
       <c r="L100" s="6"/>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="6"/>
       <c r="B101" s="6"/>
       <c r="C101" s="6"/>
@@ -13135,7 +13314,7 @@
       <c r="K101" s="6"/>
       <c r="L101" s="6"/>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="6"/>
       <c r="B102" s="6"/>
       <c r="C102" s="6"/>
@@ -13152,7 +13331,7 @@
       <c r="K102" s="6"/>
       <c r="L102" s="6"/>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="6"/>
       <c r="B103" s="6"/>
       <c r="C103" s="6"/>
@@ -13169,7 +13348,7 @@
       <c r="K103" s="6"/>
       <c r="L103" s="6"/>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="6"/>
       <c r="B104" s="6"/>
       <c r="C104" s="6"/>
@@ -13186,7 +13365,7 @@
       <c r="K104" s="6"/>
       <c r="L104" s="6"/>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="6"/>
       <c r="B105" s="6"/>
       <c r="C105" s="6"/>
@@ -13203,7 +13382,7 @@
       <c r="K105" s="6"/>
       <c r="L105" s="6"/>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="6"/>
       <c r="B106" s="6"/>
       <c r="C106" s="6"/>
@@ -13220,7 +13399,7 @@
       <c r="K106" s="6"/>
       <c r="L106" s="6"/>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="6"/>
       <c r="B107" s="6"/>
       <c r="C107" s="6"/>
@@ -13237,7 +13416,7 @@
       <c r="K107" s="6"/>
       <c r="L107" s="6"/>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="6"/>
       <c r="B108" s="6"/>
       <c r="C108" s="6"/>
@@ -13254,7 +13433,7 @@
       <c r="K108" s="6"/>
       <c r="L108" s="6"/>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="6"/>
       <c r="B109" s="6"/>
       <c r="C109" s="6"/>
@@ -13271,7 +13450,7 @@
       <c r="K109" s="6"/>
       <c r="L109" s="6"/>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="6"/>
       <c r="B110" s="6"/>
       <c r="C110" s="6"/>
@@ -13288,24 +13467,16 @@
       <c r="K110" s="6"/>
       <c r="L110" s="6"/>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A111" s="6"/>
-      <c r="B111" s="6"/>
-      <c r="C111" s="6"/>
-      <c r="D111" s="6"/>
-      <c r="E111" s="6"/>
-      <c r="F111" s="8"/>
-      <c r="G111" s="6"/>
-      <c r="H111" s="6"/>
-      <c r="I111" s="6" t="str">
-        <f t="array" ref="I111">_xlfn.SWITCH(H111,"XS",1,"S",2,"M",3,"L",5,"XL",8,"XXL",13,"XXXL",21,"")</f>
-        <v/>
-      </c>
-      <c r="J111" s="6"/>
-      <c r="K111" s="6"/>
-      <c r="L111" s="6"/>
-    </row>
   </sheetData>
+  <autoFilter ref="E1:E110" xr:uid="{AA30D3B6-4BBC-427B-918A-C301767B692F}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Backend"/>
+        <filter val="Frontend"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -13323,192 +13494,192 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="22" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="19">
+      <c r="A2" s="17">
         <v>0</v>
       </c>
-      <c r="B2" s="20">
+      <c r="B2" s="18">
         <v>46251</v>
       </c>
-      <c r="C2" s="21">
+      <c r="C2" s="19">
         <f>75-SUM(E$2:E2)</f>
         <v>75</v>
       </c>
-      <c r="D2" s="22">
+      <c r="D2" s="20">
         <f>75*(1-(A2/8))</f>
         <v>75</v>
       </c>
-      <c r="E2" s="22">
+      <c r="E2" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="19">
+      <c r="A3" s="17">
         <v>1</v>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="18">
         <v>46252</v>
       </c>
-      <c r="C3" s="21">
+      <c r="C3" s="19">
         <f>75-SUM(E$2:E3)</f>
         <v>75</v>
       </c>
-      <c r="D3" s="22">
+      <c r="D3" s="20">
         <f t="shared" ref="D3:D10" si="0">75*(1-(A3/8))</f>
         <v>65.625</v>
       </c>
-      <c r="E3" s="22">
+      <c r="E3" s="20">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="19">
+      <c r="A4" s="17">
         <v>2</v>
       </c>
-      <c r="B4" s="20">
+      <c r="B4" s="18">
         <v>46253</v>
       </c>
-      <c r="C4" s="21">
+      <c r="C4" s="19">
         <f>75-SUM(E$2:E4)</f>
         <v>75</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="20">
         <f t="shared" si="0"/>
         <v>56.25</v>
       </c>
-      <c r="E4" s="22">
+      <c r="E4" s="20">
         <v>0</v>
       </c>
       <c r="L4" s="2"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="19">
+      <c r="A5" s="17">
         <v>3</v>
       </c>
-      <c r="B5" s="20">
+      <c r="B5" s="18">
         <v>46254</v>
       </c>
-      <c r="C5" s="21">
+      <c r="C5" s="19">
         <f>75-SUM(E$2:E5)</f>
-        <v>75</v>
-      </c>
-      <c r="D5" s="22">
+        <v>72</v>
+      </c>
+      <c r="D5" s="20">
         <f t="shared" si="0"/>
         <v>46.875</v>
       </c>
-      <c r="E5" s="22">
-        <v>0</v>
+      <c r="E5" s="20">
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="19">
+      <c r="A6" s="17">
         <v>4</v>
       </c>
-      <c r="B6" s="20">
+      <c r="B6" s="18">
         <v>46255</v>
       </c>
-      <c r="C6" s="21">
+      <c r="C6" s="19">
         <f>75-SUM(E$2:E6)</f>
-        <v>75</v>
-      </c>
-      <c r="D6" s="22">
+        <v>65</v>
+      </c>
+      <c r="D6" s="20">
         <f t="shared" si="0"/>
         <v>37.5</v>
       </c>
-      <c r="E6" s="22">
-        <v>0</v>
+      <c r="E6" s="20">
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="19">
+      <c r="A7" s="17">
         <v>5</v>
       </c>
-      <c r="B7" s="20">
+      <c r="B7" s="18">
         <v>46258</v>
       </c>
-      <c r="C7" s="21">
+      <c r="C7" s="19">
         <f>75-SUM(E$2:E7)</f>
-        <v>75</v>
-      </c>
-      <c r="D7" s="22">
+        <v>60</v>
+      </c>
+      <c r="D7" s="20">
         <f t="shared" si="0"/>
         <v>28.125</v>
       </c>
-      <c r="E7" s="22">
-        <v>0</v>
+      <c r="E7" s="20">
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="19">
+      <c r="A8" s="17">
         <v>6</v>
       </c>
-      <c r="B8" s="20">
+      <c r="B8" s="18">
         <v>46259</v>
       </c>
-      <c r="C8" s="21">
+      <c r="C8" s="19">
         <f>75-SUM(E$2:E8)</f>
-        <v>75</v>
-      </c>
-      <c r="D8" s="22">
+        <v>48</v>
+      </c>
+      <c r="D8" s="20">
         <f t="shared" si="0"/>
         <v>18.75</v>
       </c>
-      <c r="E8" s="22">
-        <v>0</v>
+      <c r="E8" s="20">
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="19">
+      <c r="A9" s="17">
         <v>7</v>
       </c>
-      <c r="B9" s="20">
+      <c r="B9" s="18">
         <v>46260</v>
       </c>
-      <c r="C9" s="21">
+      <c r="C9" s="19">
         <f>75-SUM(E$2:E9)</f>
-        <v>75</v>
-      </c>
-      <c r="D9" s="22">
+        <v>35</v>
+      </c>
+      <c r="D9" s="20">
         <f t="shared" si="0"/>
         <v>9.375</v>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="20">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="17">
+        <v>8</v>
+      </c>
+      <c r="B10" s="18">
+        <v>46261</v>
+      </c>
+      <c r="C10" s="19">
+        <f>75-SUM(E$2:E10)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="19">
-        <v>8</v>
-      </c>
-      <c r="B10" s="20">
-        <v>46261</v>
-      </c>
-      <c r="C10" s="21">
-        <f>75-SUM(E$2:E10)</f>
-        <v>75</v>
-      </c>
-      <c r="D10" s="22">
+      <c r="D10" s="20">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E10" s="22">
-        <v>0</v>
+      <c r="E10" s="20">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
